--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -258,14 +258,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -298,13 +298,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -897,10 +897,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>11677</v>
+        <v>11717</v>
       </c>
       <c r="D2">
-        <v>0.13</v>
+        <v>0.34</v>
       </c>
       <c r="E2">
         <v>11856</v>
@@ -909,25 +909,25 @@
         <v>8065</v>
       </c>
       <c r="G2">
-        <v>-1.51</v>
+        <v>-1.17</v>
       </c>
       <c r="H2">
-        <v>44.79</v>
+        <v>45.28</v>
       </c>
       <c r="I2">
-        <v>-1.51</v>
+        <v>1.01</v>
       </c>
       <c r="J2">
-        <v>14.98</v>
+        <v>12.87</v>
       </c>
       <c r="K2">
-        <v>13.89</v>
+        <v>15.79</v>
       </c>
       <c r="L2">
-        <v>44.63</v>
+        <v>44.36</v>
       </c>
       <c r="M2">
-        <v>28.08</v>
+        <v>28.65</v>
       </c>
       <c r="N2">
         <v>85</v>
@@ -936,19 +936,19 @@
         <v>85</v>
       </c>
       <c r="P2">
-        <v>11671.8</v>
+        <v>11695.2</v>
       </c>
       <c r="Q2">
-        <v>11133.22</v>
+        <v>11210.78</v>
       </c>
       <c r="R2">
-        <v>10494.58</v>
+        <v>10521.4</v>
       </c>
       <c r="S2">
-        <v>9631.389999999999</v>
+        <v>9645.02</v>
       </c>
       <c r="T2">
-        <v>21.24</v>
+        <v>21.48</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -963,43 +963,43 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>67.20999999999999</v>
+        <v>67.91</v>
       </c>
       <c r="Z2">
-        <v>392.45</v>
+        <v>383.99</v>
       </c>
       <c r="AA2">
-        <v>365.82</v>
+        <v>369.45</v>
       </c>
       <c r="AB2">
-        <v>26.63</v>
+        <v>14.54</v>
       </c>
       <c r="AC2">
-        <v>29.36</v>
+        <v>20.85</v>
       </c>
       <c r="AD2">
-        <v>44.04</v>
+        <v>33.2</v>
       </c>
       <c r="AE2">
-        <v>241.92</v>
+        <v>242.36</v>
       </c>
       <c r="AF2">
-        <v>-60.41</v>
+        <v>-45.87</v>
       </c>
       <c r="AG2">
-        <v>12256.77</v>
+        <v>12265.21</v>
       </c>
       <c r="AH2">
-        <v>10009.68</v>
+        <v>10156.34</v>
       </c>
       <c r="AI2">
-        <v>10974.73</v>
+        <v>11011.93</v>
       </c>
       <c r="AJ2" t="s">
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>80.16</v>
+        <v>81.03</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1010,10 +1010,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>547.05</v>
+        <v>540.95</v>
       </c>
       <c r="D3">
-        <v>1.79</v>
+        <v>-1.12</v>
       </c>
       <c r="E3">
         <v>670.25</v>
@@ -1022,25 +1022,25 @@
         <v>222.01</v>
       </c>
       <c r="G3">
-        <v>-18.38</v>
+        <v>-19.29</v>
       </c>
       <c r="H3">
-        <v>146.41</v>
+        <v>143.66</v>
       </c>
       <c r="I3">
-        <v>4.44</v>
+        <v>-0.6</v>
       </c>
       <c r="J3">
-        <v>-18.38</v>
+        <v>-18.09</v>
       </c>
       <c r="K3">
-        <v>-0.16</v>
+        <v>2.99</v>
       </c>
       <c r="L3">
-        <v>146.46</v>
+        <v>140.99</v>
       </c>
       <c r="M3">
-        <v>18.7</v>
+        <v>17.97</v>
       </c>
       <c r="N3">
         <v>99</v>
@@ -1049,19 +1049,19 @@
         <v>94</v>
       </c>
       <c r="P3">
-        <v>538.34</v>
+        <v>537.6900000000001</v>
       </c>
       <c r="Q3">
-        <v>541.1900000000001</v>
+        <v>538.71</v>
       </c>
       <c r="R3">
-        <v>575.54</v>
+        <v>575.1799999999999</v>
       </c>
       <c r="S3">
-        <v>410.35</v>
+        <v>411.69</v>
       </c>
       <c r="T3">
-        <v>33.31</v>
+        <v>31.4</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1076,34 +1076,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>47.9</v>
+        <v>46.03</v>
       </c>
       <c r="Z3">
-        <v>-12.19</v>
+        <v>-11.26</v>
       </c>
       <c r="AA3">
-        <v>-13.3</v>
+        <v>-12.89</v>
       </c>
       <c r="AB3">
-        <v>1.11</v>
+        <v>1.63</v>
       </c>
       <c r="AC3">
-        <v>86.37</v>
+        <v>89.44</v>
       </c>
       <c r="AD3">
-        <v>80.31999999999999</v>
+        <v>83.75</v>
       </c>
       <c r="AE3">
-        <v>22.74</v>
+        <v>22.19</v>
       </c>
       <c r="AF3">
-        <v>-77.56999999999999</v>
+        <v>-72.08</v>
       </c>
       <c r="AG3">
-        <v>574.39</v>
+        <v>562.47</v>
       </c>
       <c r="AH3">
-        <v>507.99</v>
+        <v>514.96</v>
       </c>
       <c r="AI3">
         <v>600.11</v>
@@ -1112,7 +1112,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>18.32</v>
+        <v>18.84</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1123,10 +1123,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>363.1</v>
+        <v>360.35</v>
       </c>
       <c r="D4">
-        <v>-2.17</v>
+        <v>-0.76</v>
       </c>
       <c r="E4">
         <v>614.95</v>
@@ -1135,25 +1135,25 @@
         <v>303.75</v>
       </c>
       <c r="G4">
-        <v>-40.95</v>
+        <v>-41.4</v>
       </c>
       <c r="H4">
-        <v>19.54</v>
+        <v>18.63</v>
       </c>
       <c r="I4">
-        <v>7.54</v>
+        <v>3.05</v>
       </c>
       <c r="J4">
-        <v>9.66</v>
+        <v>7.07</v>
       </c>
       <c r="K4">
-        <v>-5.82</v>
+        <v>-5.31</v>
       </c>
       <c r="L4">
-        <v>-41.03</v>
+        <v>-40.57</v>
       </c>
       <c r="M4">
-        <v>-18.67</v>
+        <v>-18.2</v>
       </c>
       <c r="N4">
         <v>15</v>
@@ -1162,19 +1162,19 @@
         <v>14</v>
       </c>
       <c r="P4">
-        <v>362.91</v>
+        <v>365.04</v>
       </c>
       <c r="Q4">
-        <v>339.02</v>
+        <v>340.59</v>
       </c>
       <c r="R4">
-        <v>327.81</v>
+        <v>328.71</v>
       </c>
       <c r="S4">
-        <v>398.39</v>
+        <v>397.48</v>
       </c>
       <c r="T4">
-        <v>-8.859999999999999</v>
+        <v>-9.34</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1189,34 +1189,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>62.86</v>
+        <v>60.95</v>
       </c>
       <c r="Z4">
-        <v>9.1</v>
+        <v>9.25</v>
       </c>
       <c r="AA4">
-        <v>4.69</v>
+        <v>5.6</v>
       </c>
       <c r="AB4">
-        <v>4.41</v>
+        <v>3.65</v>
       </c>
       <c r="AC4">
-        <v>73.39</v>
+        <v>54.93</v>
       </c>
       <c r="AD4">
-        <v>85.61</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="AE4">
-        <v>14.64</v>
+        <v>14.34</v>
       </c>
       <c r="AF4">
-        <v>-45.53</v>
+        <v>-63.66</v>
       </c>
       <c r="AG4">
-        <v>370.78</v>
+        <v>373.35</v>
       </c>
       <c r="AH4">
-        <v>307.25</v>
+        <v>307.83</v>
       </c>
       <c r="AI4">
         <v>335.86</v>
@@ -1225,7 +1225,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>59.6</v>
+        <v>59.86</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1236,10 +1236,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>2021.3</v>
+        <v>2032</v>
       </c>
       <c r="D5">
-        <v>0.62</v>
+        <v>0.53</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1248,46 +1248,46 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-7.13</v>
+        <v>-6.64</v>
       </c>
       <c r="H5">
-        <v>23.87</v>
+        <v>24.53</v>
       </c>
       <c r="I5">
-        <v>-3.56</v>
+        <v>-3.47</v>
       </c>
       <c r="J5">
-        <v>5.5</v>
+        <v>6.49</v>
       </c>
       <c r="K5">
-        <v>15.85</v>
+        <v>17.53</v>
       </c>
       <c r="L5">
-        <v>4.54</v>
+        <v>4.77</v>
       </c>
       <c r="M5">
-        <v>7.61</v>
+        <v>7.47</v>
       </c>
       <c r="N5">
         <v>57</v>
       </c>
       <c r="O5">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P5">
-        <v>2061.44</v>
+        <v>2046.84</v>
       </c>
       <c r="Q5">
-        <v>1946.15</v>
+        <v>1954.29</v>
       </c>
       <c r="R5">
-        <v>1845.81</v>
+        <v>1851.28</v>
       </c>
       <c r="S5">
-        <v>1914.11</v>
+        <v>1913.42</v>
       </c>
       <c r="T5">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1302,34 +1302,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>60.77</v>
+        <v>61.87</v>
       </c>
       <c r="Z5">
-        <v>59.92</v>
+        <v>57.62</v>
       </c>
       <c r="AA5">
-        <v>53.39</v>
+        <v>54.24</v>
       </c>
       <c r="AB5">
-        <v>6.53</v>
+        <v>3.38</v>
       </c>
       <c r="AC5">
-        <v>40.28</v>
+        <v>22.18</v>
       </c>
       <c r="AD5">
-        <v>63.03</v>
+        <v>40.97</v>
       </c>
       <c r="AE5">
-        <v>48.83</v>
+        <v>47.62</v>
       </c>
       <c r="AF5">
-        <v>-38.88</v>
+        <v>-31.77</v>
       </c>
       <c r="AG5">
-        <v>2131.95</v>
+        <v>2140.16</v>
       </c>
       <c r="AH5">
-        <v>1760.35</v>
+        <v>1768.42</v>
       </c>
       <c r="AI5">
         <v>1958.53</v>
@@ -1338,7 +1338,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>41.73</v>
+        <v>38.05</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1349,10 +1349,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>11471</v>
+        <v>11550</v>
       </c>
       <c r="D6">
-        <v>1.85</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E6">
         <v>14451.52</v>
@@ -1361,46 +1361,46 @@
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-20.62</v>
+        <v>-20.08</v>
       </c>
       <c r="H6">
-        <v>31.16</v>
+        <v>32.06</v>
       </c>
       <c r="I6">
-        <v>-1.1</v>
+        <v>0.65</v>
       </c>
       <c r="J6">
-        <v>7.67</v>
+        <v>7.42</v>
       </c>
       <c r="K6">
-        <v>13.61</v>
+        <v>15.21</v>
       </c>
       <c r="L6">
-        <v>-17.06</v>
+        <v>-16.26</v>
       </c>
       <c r="M6">
-        <v>25.25</v>
+        <v>25.42</v>
       </c>
       <c r="N6">
         <v>29</v>
       </c>
       <c r="O6">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="P6">
-        <v>11418.4</v>
+        <v>11433.4</v>
       </c>
       <c r="Q6">
-        <v>10895.55</v>
+        <v>10948.75</v>
       </c>
       <c r="R6">
-        <v>10643.28</v>
+        <v>10668.88</v>
       </c>
       <c r="S6">
-        <v>10809.7</v>
+        <v>10803.8</v>
       </c>
       <c r="T6">
-        <v>6.12</v>
+        <v>6.91</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1415,43 +1415,43 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>64.92</v>
+        <v>66.44</v>
       </c>
       <c r="Z6">
-        <v>241.62</v>
+        <v>251.28</v>
       </c>
       <c r="AA6">
-        <v>186.23</v>
+        <v>199.24</v>
       </c>
       <c r="AB6">
-        <v>55.38</v>
+        <v>52.03</v>
       </c>
       <c r="AC6">
-        <v>62.99</v>
+        <v>60.73</v>
       </c>
       <c r="AD6">
-        <v>70.89</v>
+        <v>64.3</v>
       </c>
       <c r="AE6">
-        <v>251.62</v>
+        <v>247.01</v>
       </c>
       <c r="AF6">
-        <v>-34.55</v>
+        <v>-35.76</v>
       </c>
       <c r="AG6">
-        <v>11788.77</v>
+        <v>11865.69</v>
       </c>
       <c r="AH6">
-        <v>10002.33</v>
+        <v>10031.81</v>
       </c>
       <c r="AI6">
-        <v>10739.59</v>
+        <v>10764.47</v>
       </c>
       <c r="AJ6" t="s">
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>47.58</v>
+        <v>48.18</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1462,10 +1462,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>1102.2</v>
+        <v>1093.3</v>
       </c>
       <c r="D7">
-        <v>2.24</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1474,46 +1474,46 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-4.88</v>
+        <v>-5.65</v>
       </c>
       <c r="H7">
-        <v>37.51</v>
+        <v>36.4</v>
       </c>
       <c r="I7">
-        <v>-4.41</v>
+        <v>-4.85</v>
       </c>
       <c r="J7">
-        <v>8.01</v>
+        <v>6.91</v>
       </c>
       <c r="K7">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="L7">
-        <v>24.5</v>
+        <v>22.58</v>
       </c>
       <c r="M7">
-        <v>12.73</v>
+        <v>12.56</v>
       </c>
       <c r="N7">
         <v>71</v>
       </c>
       <c r="O7">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P7">
-        <v>1126.56</v>
+        <v>1115.42</v>
       </c>
       <c r="Q7">
-        <v>1074.98</v>
+        <v>1079.31</v>
       </c>
       <c r="R7">
-        <v>1004.11</v>
+        <v>1008.2</v>
       </c>
       <c r="S7">
-        <v>974.1</v>
+        <v>974.13</v>
       </c>
       <c r="T7">
-        <v>13.15</v>
+        <v>12.23</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1528,34 +1528,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>57.22</v>
+        <v>55.32</v>
       </c>
       <c r="Z7">
-        <v>32.89</v>
+        <v>29.93</v>
       </c>
       <c r="AA7">
-        <v>32.64</v>
+        <v>32.1</v>
       </c>
       <c r="AB7">
-        <v>0.25</v>
+        <v>-2.16</v>
       </c>
       <c r="AC7">
-        <v>38.99</v>
+        <v>18.61</v>
       </c>
       <c r="AD7">
-        <v>64.53</v>
+        <v>40.26</v>
       </c>
       <c r="AE7">
-        <v>31.59</v>
+        <v>30.47</v>
       </c>
       <c r="AF7">
-        <v>-28.78</v>
+        <v>-36.44</v>
       </c>
       <c r="AG7">
-        <v>1173.04</v>
+        <v>1172.18</v>
       </c>
       <c r="AH7">
-        <v>976.91</v>
+        <v>986.4400000000001</v>
       </c>
       <c r="AI7">
         <v>1067.72</v>
@@ -1564,7 +1564,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>32.51</v>
+        <v>29.69</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1575,10 +1575,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>141.14</v>
+        <v>140.61</v>
       </c>
       <c r="D8">
-        <v>-1.45</v>
+        <v>-0.38</v>
       </c>
       <c r="E8">
         <v>148.95</v>
@@ -1587,46 +1587,46 @@
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>-5.24</v>
+        <v>-5.6</v>
       </c>
       <c r="H8">
-        <v>21.71</v>
+        <v>21.26</v>
       </c>
       <c r="I8">
-        <v>-1.71</v>
+        <v>-1.15</v>
       </c>
       <c r="J8">
-        <v>6.22</v>
+        <v>3.5</v>
       </c>
       <c r="K8">
-        <v>4.3</v>
+        <v>2.46</v>
       </c>
       <c r="L8">
-        <v>1.93</v>
+        <v>4.93</v>
       </c>
       <c r="M8">
-        <v>0.84</v>
+        <v>1.6</v>
       </c>
       <c r="N8">
         <v>43</v>
       </c>
       <c r="O8">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P8">
-        <v>142.41</v>
+        <v>142.09</v>
       </c>
       <c r="Q8">
-        <v>141.78</v>
+        <v>141.97</v>
       </c>
       <c r="R8">
-        <v>137.68</v>
+        <v>137.72</v>
       </c>
       <c r="S8">
-        <v>133.64</v>
+        <v>133.7</v>
       </c>
       <c r="T8">
-        <v>5.61</v>
+        <v>5.17</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1641,34 +1641,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>52.76</v>
+        <v>51.35</v>
       </c>
       <c r="Z8">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="AA8">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="AB8">
-        <v>-0.03</v>
+        <v>-0.17</v>
       </c>
       <c r="AC8">
-        <v>38.37</v>
+        <v>24.76</v>
       </c>
       <c r="AD8">
-        <v>38.37</v>
+        <v>34.79</v>
       </c>
       <c r="AE8">
-        <v>4.03</v>
+        <v>3.99</v>
       </c>
       <c r="AF8">
-        <v>-39.16</v>
+        <v>-69.11</v>
       </c>
       <c r="AG8">
-        <v>147.01</v>
+        <v>146.68</v>
       </c>
       <c r="AH8">
-        <v>136.54</v>
+        <v>137.26</v>
       </c>
       <c r="AI8">
         <v>131.91</v>
@@ -1677,7 +1677,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>24.55</v>
+        <v>24.22</v>
       </c>
     </row>
   </sheetData>
@@ -1875,13 +1875,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>14.84</v>
+        <v>14.98</v>
       </c>
       <c r="D7" s="5">
-        <v>14.98</v>
+        <v>12.87</v>
       </c>
       <c r="E7" s="6">
-        <v>0.14</v>
+        <v>-2.11</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1892,13 +1892,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-16.49</v>
+        <v>-18.38</v>
       </c>
       <c r="D8" s="5">
-        <v>-18.38</v>
+        <v>-18.09</v>
       </c>
       <c r="E8" s="7">
-        <v>-1.89</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1909,13 +1909,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>13.59</v>
+        <v>9.66</v>
       </c>
       <c r="D9" s="5">
-        <v>9.66</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-3.93</v>
+        <v>7.07</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-2.59</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1926,13 +1926,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>6.01</v>
+        <v>5.5</v>
       </c>
       <c r="D10" s="5">
-        <v>5.5</v>
+        <v>6.49</v>
       </c>
       <c r="E10" s="7">
-        <v>-0.51</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1943,13 +1943,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>6.45</v>
+        <v>7.67</v>
       </c>
       <c r="D11" s="5">
-        <v>7.67</v>
+        <v>7.42</v>
       </c>
       <c r="E11" s="6">
-        <v>1.22</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1960,13 +1960,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="5">
-        <v>7.39</v>
+        <v>8.01</v>
       </c>
       <c r="D12" s="5">
-        <v>8.01</v>
+        <v>6.91</v>
       </c>
       <c r="E12" s="6">
-        <v>0.62</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1977,13 +1977,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="5">
-        <v>9.51</v>
+        <v>6.22</v>
       </c>
       <c r="D13" s="5">
-        <v>6.22</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-3.29</v>
+        <v>3.5</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-2.72</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1994,13 +1994,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="5">
-        <v>1.23</v>
+        <v>-1.51</v>
       </c>
       <c r="D14" s="5">
-        <v>-1.51</v>
+        <v>1.01</v>
       </c>
       <c r="E14" s="7">
-        <v>-2.74</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2011,13 +2011,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="5">
-        <v>2.55</v>
+        <v>4.44</v>
       </c>
       <c r="D15" s="5">
-        <v>4.44</v>
+        <v>-0.6</v>
       </c>
       <c r="E15" s="6">
-        <v>1.89</v>
+        <v>-5.04</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2028,13 +2028,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>11.49</v>
+        <v>7.54</v>
       </c>
       <c r="D16" s="5">
-        <v>7.54</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-3.95</v>
+        <v>3.05</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-4.49</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2045,13 +2045,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="5">
-        <v>-1</v>
+        <v>-3.56</v>
       </c>
       <c r="D17" s="5">
-        <v>-3.56</v>
+        <v>-3.47</v>
       </c>
       <c r="E17" s="7">
-        <v>-2.56</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2062,13 +2062,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="5">
-        <v>-0.71</v>
+        <v>-1.1</v>
       </c>
       <c r="D18" s="5">
-        <v>-1.1</v>
+        <v>0.65</v>
       </c>
       <c r="E18" s="7">
-        <v>-0.39</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2079,13 +2079,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="5">
-        <v>-5.54</v>
+        <v>-4.41</v>
       </c>
       <c r="D19" s="5">
-        <v>-4.41</v>
+        <v>-4.85</v>
       </c>
       <c r="E19" s="6">
-        <v>1.13</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2096,13 +2096,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="5">
-        <v>1.27</v>
+        <v>-1.71</v>
       </c>
       <c r="D20" s="5">
-        <v>-1.71</v>
+        <v>-1.15</v>
       </c>
       <c r="E20" s="7">
-        <v>-2.98</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2113,13 +2113,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="5">
-        <v>47.01</v>
+        <v>44.63</v>
       </c>
       <c r="D21" s="5">
-        <v>44.63</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-2.38</v>
+        <v>44.36</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-0.27</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2130,13 +2130,13 @@
         <v>11</v>
       </c>
       <c r="C22" s="5">
-        <v>139.21</v>
+        <v>146.46</v>
       </c>
       <c r="D22" s="5">
-        <v>146.46</v>
+        <v>140.99</v>
       </c>
       <c r="E22" s="6">
-        <v>7.25</v>
+        <v>-5.47</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2147,13 +2147,13 @@
         <v>11</v>
       </c>
       <c r="C23" s="5">
-        <v>-39.3</v>
+        <v>-41.03</v>
       </c>
       <c r="D23" s="5">
-        <v>-41.03</v>
+        <v>-40.57</v>
       </c>
       <c r="E23" s="7">
-        <v>-1.73</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2164,13 +2164,13 @@
         <v>11</v>
       </c>
       <c r="C24" s="5">
-        <v>4.83</v>
+        <v>4.54</v>
       </c>
       <c r="D24" s="5">
-        <v>4.54</v>
+        <v>4.77</v>
       </c>
       <c r="E24" s="7">
-        <v>-0.29</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2181,13 +2181,13 @@
         <v>11</v>
       </c>
       <c r="C25" s="5">
-        <v>-18.26</v>
+        <v>-17.06</v>
       </c>
       <c r="D25" s="5">
-        <v>-17.06</v>
-      </c>
-      <c r="E25" s="6">
-        <v>1.2</v>
+        <v>-16.26</v>
+      </c>
+      <c r="E25" s="7">
+        <v>0.8</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2198,13 +2198,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="5">
-        <v>23.12</v>
+        <v>24.5</v>
       </c>
       <c r="D26" s="5">
-        <v>24.5</v>
+        <v>22.58</v>
       </c>
       <c r="E26" s="6">
-        <v>1.38</v>
+        <v>-1.92</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2215,13 +2215,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="5">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="D27" s="5">
-        <v>1.93</v>
-      </c>
-      <c r="E27" s="6">
-        <v>0.07000000000000001</v>
+        <v>4.93</v>
+      </c>
+      <c r="E27" s="7">
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2232,13 +2232,13 @@
         <v>10</v>
       </c>
       <c r="C28" s="5">
-        <v>11.61</v>
+        <v>13.89</v>
       </c>
       <c r="D28" s="5">
-        <v>13.89</v>
-      </c>
-      <c r="E28" s="6">
-        <v>2.28</v>
+        <v>15.79</v>
+      </c>
+      <c r="E28" s="7">
+        <v>1.9</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2249,13 +2249,13 @@
         <v>10</v>
       </c>
       <c r="C29" s="5">
-        <v>-0.33</v>
+        <v>-0.16</v>
       </c>
       <c r="D29" s="5">
-        <v>-0.16</v>
-      </c>
-      <c r="E29" s="6">
-        <v>0.17</v>
+        <v>2.99</v>
+      </c>
+      <c r="E29" s="7">
+        <v>3.15</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2266,13 +2266,13 @@
         <v>10</v>
       </c>
       <c r="C30" s="5">
-        <v>-6.69</v>
+        <v>-5.82</v>
       </c>
       <c r="D30" s="5">
-        <v>-5.82</v>
-      </c>
-      <c r="E30" s="6">
-        <v>0.87</v>
+        <v>-5.31</v>
+      </c>
+      <c r="E30" s="7">
+        <v>0.51</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2283,13 +2283,13 @@
         <v>10</v>
       </c>
       <c r="C31" s="5">
-        <v>11.97</v>
+        <v>15.85</v>
       </c>
       <c r="D31" s="5">
-        <v>15.85</v>
-      </c>
-      <c r="E31" s="6">
-        <v>3.88</v>
+        <v>17.53</v>
+      </c>
+      <c r="E31" s="7">
+        <v>1.68</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2300,13 +2300,13 @@
         <v>10</v>
       </c>
       <c r="C32" s="5">
-        <v>8.039999999999999</v>
+        <v>13.61</v>
       </c>
       <c r="D32" s="5">
-        <v>13.61</v>
-      </c>
-      <c r="E32" s="6">
-        <v>5.57</v>
+        <v>15.21</v>
+      </c>
+      <c r="E32" s="7">
+        <v>1.6</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2317,13 +2317,13 @@
         <v>10</v>
       </c>
       <c r="C33" s="5">
-        <v>15.16</v>
+        <v>21.9</v>
       </c>
       <c r="D33" s="5">
-        <v>21.9</v>
-      </c>
-      <c r="E33" s="6">
-        <v>6.74</v>
+        <v>22</v>
+      </c>
+      <c r="E33" s="7">
+        <v>0.1</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2334,13 +2334,13 @@
         <v>10</v>
       </c>
       <c r="C34" s="5">
-        <v>4.51</v>
+        <v>4.3</v>
       </c>
       <c r="D34" s="5">
-        <v>4.3</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-0.21</v>
+        <v>2.46</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-1.84</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2351,13 +2351,13 @@
         <v>6</v>
       </c>
       <c r="C35" s="5">
-        <v>-1.64</v>
+        <v>-1.51</v>
       </c>
       <c r="D35" s="5">
-        <v>-1.51</v>
-      </c>
-      <c r="E35" s="6">
-        <v>0.13</v>
+        <v>-1.17</v>
+      </c>
+      <c r="E35" s="7">
+        <v>0.34</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2368,13 +2368,13 @@
         <v>6</v>
       </c>
       <c r="C36" s="5">
-        <v>-19.81</v>
+        <v>-18.38</v>
       </c>
       <c r="D36" s="5">
-        <v>-18.38</v>
+        <v>-19.29</v>
       </c>
       <c r="E36" s="6">
-        <v>1.43</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2385,13 +2385,13 @@
         <v>6</v>
       </c>
       <c r="C37" s="5">
-        <v>-39.72</v>
+        <v>-40.95</v>
       </c>
       <c r="D37" s="5">
-        <v>-40.95</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-1.23</v>
+        <v>-41.4</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-0.45</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2402,13 +2402,13 @@
         <v>6</v>
       </c>
       <c r="C38" s="5">
-        <v>-7.7</v>
+        <v>-7.13</v>
       </c>
       <c r="D38" s="5">
-        <v>-7.13</v>
-      </c>
-      <c r="E38" s="6">
-        <v>0.57</v>
+        <v>-6.64</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0.49</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="C39" s="5">
-        <v>-22.06</v>
+        <v>-20.62</v>
       </c>
       <c r="D39" s="5">
-        <v>-20.62</v>
-      </c>
-      <c r="E39" s="6">
-        <v>1.44</v>
+        <v>-20.08</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0.54</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2436,13 +2436,13 @@
         <v>6</v>
       </c>
       <c r="C40" s="5">
-        <v>-6.97</v>
+        <v>-4.88</v>
       </c>
       <c r="D40" s="5">
-        <v>-4.88</v>
+        <v>-5.65</v>
       </c>
       <c r="E40" s="6">
-        <v>2.09</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2453,13 +2453,13 @@
         <v>6</v>
       </c>
       <c r="C41" s="5">
-        <v>-3.85</v>
+        <v>-5.24</v>
       </c>
       <c r="D41" s="5">
-        <v>-5.24</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-1.39</v>
+        <v>-5.6</v>
+      </c>
+      <c r="E41" s="6">
+        <v>-0.36</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2470,13 +2470,13 @@
         <v>2</v>
       </c>
       <c r="C42" s="5">
-        <v>11662</v>
+        <v>11677</v>
       </c>
       <c r="D42" s="5">
-        <v>11677</v>
-      </c>
-      <c r="E42" s="6">
-        <v>15</v>
+        <v>11717</v>
+      </c>
+      <c r="E42" s="7">
+        <v>40</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2487,13 +2487,13 @@
         <v>2</v>
       </c>
       <c r="C43" s="5">
-        <v>537.45</v>
+        <v>547.05</v>
       </c>
       <c r="D43" s="5">
-        <v>547.05</v>
+        <v>540.95</v>
       </c>
       <c r="E43" s="6">
-        <v>9.6</v>
+        <v>-6.1</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2504,13 +2504,13 @@
         <v>2</v>
       </c>
       <c r="C44" s="5">
-        <v>371.15</v>
+        <v>363.1</v>
       </c>
       <c r="D44" s="5">
-        <v>363.1</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-8.050000000000001</v>
+        <v>360.35</v>
+      </c>
+      <c r="E44" s="6">
+        <v>-2.75</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2521,13 +2521,13 @@
         <v>2</v>
       </c>
       <c r="C45" s="5">
-        <v>2008.9</v>
+        <v>2021.3</v>
       </c>
       <c r="D45" s="5">
-        <v>2021.3</v>
-      </c>
-      <c r="E45" s="6">
-        <v>12.4</v>
+        <v>2032</v>
+      </c>
+      <c r="E45" s="7">
+        <v>10.7</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2538,13 +2538,13 @@
         <v>2</v>
       </c>
       <c r="C46" s="5">
-        <v>11263</v>
+        <v>11471</v>
       </c>
       <c r="D46" s="5">
-        <v>11471</v>
-      </c>
-      <c r="E46" s="6">
-        <v>208</v>
+        <v>11550</v>
+      </c>
+      <c r="E46" s="7">
+        <v>79</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2555,13 +2555,13 @@
         <v>2</v>
       </c>
       <c r="C47" s="5">
-        <v>1078</v>
+        <v>1102.2</v>
       </c>
       <c r="D47" s="5">
-        <v>1102.2</v>
+        <v>1093.3</v>
       </c>
       <c r="E47" s="6">
-        <v>24.2</v>
+        <v>-8.9</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2572,13 +2572,13 @@
         <v>2</v>
       </c>
       <c r="C48" s="5">
-        <v>143.22</v>
+        <v>141.14</v>
       </c>
       <c r="D48" s="5">
-        <v>141.14</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-2.08</v>
+        <v>140.61</v>
+      </c>
+      <c r="E48" s="6">
+        <v>-0.53</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2589,13 +2589,13 @@
         <v>24</v>
       </c>
       <c r="C49" s="5">
-        <v>66.95999999999999</v>
+        <v>67.20999999999999</v>
       </c>
       <c r="D49" s="5">
-        <v>67.20999999999999</v>
-      </c>
-      <c r="E49" s="6">
-        <v>0.25</v>
+        <v>67.91</v>
+      </c>
+      <c r="E49" s="7">
+        <v>0.7</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2606,13 +2606,13 @@
         <v>24</v>
       </c>
       <c r="C50" s="5">
-        <v>44.62</v>
+        <v>47.9</v>
       </c>
       <c r="D50" s="5">
-        <v>47.9</v>
+        <v>46.03</v>
       </c>
       <c r="E50" s="6">
-        <v>3.28</v>
+        <v>-1.87</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2623,13 +2623,13 @@
         <v>24</v>
       </c>
       <c r="C51" s="5">
-        <v>68.73</v>
+        <v>62.86</v>
       </c>
       <c r="D51" s="5">
-        <v>62.86</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-5.87</v>
+        <v>60.95</v>
+      </c>
+      <c r="E51" s="6">
+        <v>-1.91</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2640,13 +2640,13 @@
         <v>24</v>
       </c>
       <c r="C52" s="5">
-        <v>59.5</v>
+        <v>60.77</v>
       </c>
       <c r="D52" s="5">
-        <v>60.77</v>
-      </c>
-      <c r="E52" s="6">
-        <v>1.27</v>
+        <v>61.87</v>
+      </c>
+      <c r="E52" s="7">
+        <v>1.1</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2657,13 +2657,13 @@
         <v>24</v>
       </c>
       <c r="C53" s="5">
-        <v>60.55</v>
+        <v>64.92</v>
       </c>
       <c r="D53" s="5">
-        <v>64.92</v>
-      </c>
-      <c r="E53" s="6">
-        <v>4.37</v>
+        <v>66.44</v>
+      </c>
+      <c r="E53" s="7">
+        <v>1.52</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2674,13 +2674,13 @@
         <v>24</v>
       </c>
       <c r="C54" s="5">
-        <v>53.15</v>
+        <v>57.22</v>
       </c>
       <c r="D54" s="5">
-        <v>57.22</v>
+        <v>55.32</v>
       </c>
       <c r="E54" s="6">
-        <v>4.07</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2691,13 +2691,13 @@
         <v>24</v>
       </c>
       <c r="C55" s="5">
-        <v>58.66</v>
+        <v>52.76</v>
       </c>
       <c r="D55" s="5">
-        <v>52.76</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-5.9</v>
+        <v>51.35</v>
+      </c>
+      <c r="E55" s="6">
+        <v>-1.41</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2708,13 +2708,13 @@
         <v>31</v>
       </c>
       <c r="C56" s="5">
-        <v>-58.43</v>
+        <v>-60.41</v>
       </c>
       <c r="D56" s="5">
-        <v>-60.41</v>
+        <v>-45.87</v>
       </c>
       <c r="E56" s="7">
-        <v>-1.98</v>
+        <v>14.54</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2725,13 +2725,13 @@
         <v>31</v>
       </c>
       <c r="C57" s="5">
-        <v>-68.67</v>
+        <v>-77.56999999999999</v>
       </c>
       <c r="D57" s="5">
-        <v>-77.56999999999999</v>
+        <v>-72.08</v>
       </c>
       <c r="E57" s="7">
-        <v>-8.9</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -2742,13 +2742,13 @@
         <v>31</v>
       </c>
       <c r="C58" s="5">
-        <v>197.08</v>
+        <v>-45.53</v>
       </c>
       <c r="D58" s="5">
-        <v>-45.53</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-242.61</v>
+        <v>-63.66</v>
+      </c>
+      <c r="E58" s="6">
+        <v>-18.13</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -2759,13 +2759,13 @@
         <v>31</v>
       </c>
       <c r="C59" s="5">
-        <v>58.1</v>
+        <v>-38.88</v>
       </c>
       <c r="D59" s="5">
-        <v>-38.88</v>
+        <v>-31.77</v>
       </c>
       <c r="E59" s="7">
-        <v>-96.98</v>
+        <v>7.11</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -2776,13 +2776,13 @@
         <v>31</v>
       </c>
       <c r="C60" s="5">
-        <v>-54.08</v>
+        <v>-34.55</v>
       </c>
       <c r="D60" s="5">
-        <v>-34.55</v>
+        <v>-35.76</v>
       </c>
       <c r="E60" s="6">
-        <v>19.53</v>
+        <v>-1.21</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -2793,13 +2793,13 @@
         <v>31</v>
       </c>
       <c r="C61" s="5">
-        <v>55.09</v>
+        <v>-28.78</v>
       </c>
       <c r="D61" s="5">
-        <v>-28.78</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-83.87</v>
+        <v>-36.44</v>
+      </c>
+      <c r="E61" s="6">
+        <v>-7.66</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -2810,13 +2810,13 @@
         <v>31</v>
       </c>
       <c r="C62" s="5">
-        <v>61.19</v>
+        <v>-39.16</v>
       </c>
       <c r="D62" s="5">
-        <v>-39.16</v>
-      </c>
-      <c r="E62" s="7">
-        <v>-100.35</v>
+        <v>-69.11</v>
+      </c>
+      <c r="E62" s="6">
+        <v>-29.95</v>
       </c>
     </row>
   </sheetData>
@@ -2881,16 +2881,16 @@
         <v>7</v>
       </c>
       <c r="D2" s="10">
-        <v>59.1</v>
+        <v>58.6</v>
       </c>
       <c r="E2" s="10">
         <v>90</v>
       </c>
       <c r="F2" s="10">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="G2" s="10">
-        <v>9.1</v>
+        <v>10.1</v>
       </c>
       <c r="H2" s="10">
         <v>57</v>
@@ -3021,25 +3021,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="13">
-        <v>0.2808</v>
+        <v>0.2865</v>
       </c>
       <c r="B2" s="13">
-        <v>0.2525</v>
+        <v>0.2542</v>
       </c>
       <c r="C2" s="13">
-        <v>0.187</v>
+        <v>0.1797</v>
       </c>
       <c r="D2" s="13">
-        <v>0.1273</v>
+        <v>0.1256</v>
       </c>
       <c r="E2" s="13">
-        <v>0.0761</v>
+        <v>0.0747</v>
       </c>
       <c r="F2" s="13">
-        <v>0.008399999999999999</v>
+        <v>0.016</v>
       </c>
       <c r="G2" s="13">
-        <v>-0.1867</v>
+        <v>-0.182</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="73">
   <si>
     <t>Symbol</t>
   </si>
@@ -172,7 +172,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>51.4 → 40.2</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>51.4</t>
+  </si>
+  <si>
+    <t>40.2</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -374,17 +401,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -756,8 +784,7 @@
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
     <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="18" width="10.7109375" customWidth="1"/>
-    <col min="19" max="19" width="9.7109375" customWidth="1"/>
+    <col min="17" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -897,37 +924,37 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>11717</v>
+        <v>11700</v>
       </c>
       <c r="D2">
-        <v>0.34</v>
+        <v>-0.15</v>
       </c>
       <c r="E2">
         <v>11856</v>
       </c>
       <c r="F2">
-        <v>8065</v>
+        <v>8082.75</v>
       </c>
       <c r="G2">
-        <v>-1.17</v>
+        <v>-1.32</v>
       </c>
       <c r="H2">
-        <v>45.28</v>
+        <v>44.75</v>
       </c>
       <c r="I2">
-        <v>1.01</v>
+        <v>-0.85</v>
       </c>
       <c r="J2">
-        <v>12.87</v>
+        <v>15.09</v>
       </c>
       <c r="K2">
-        <v>15.79</v>
+        <v>13.53</v>
       </c>
       <c r="L2">
-        <v>44.36</v>
+        <v>45.07</v>
       </c>
       <c r="M2">
-        <v>28.65</v>
+        <v>28.32</v>
       </c>
       <c r="N2">
         <v>85</v>
@@ -936,19 +963,19 @@
         <v>85</v>
       </c>
       <c r="P2">
-        <v>11695.2</v>
+        <v>11675.2</v>
       </c>
       <c r="Q2">
-        <v>11210.78</v>
+        <v>11279.62</v>
       </c>
       <c r="R2">
-        <v>10521.4</v>
+        <v>10549.78</v>
       </c>
       <c r="S2">
-        <v>9645.02</v>
+        <v>9658.91</v>
       </c>
       <c r="T2">
-        <v>21.48</v>
+        <v>21.13</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -963,43 +990,43 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>67.91</v>
+        <v>67.25</v>
       </c>
       <c r="Z2">
-        <v>383.99</v>
+        <v>371.63</v>
       </c>
       <c r="AA2">
-        <v>369.45</v>
+        <v>369.89</v>
       </c>
       <c r="AB2">
-        <v>14.54</v>
+        <v>1.74</v>
       </c>
       <c r="AC2">
-        <v>20.85</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="AD2">
-        <v>33.2</v>
+        <v>19.89</v>
       </c>
       <c r="AE2">
-        <v>242.36</v>
+        <v>235.12</v>
       </c>
       <c r="AF2">
-        <v>-45.87</v>
+        <v>-48.7</v>
       </c>
       <c r="AG2">
-        <v>12265.21</v>
+        <v>12267.72</v>
       </c>
       <c r="AH2">
-        <v>10156.34</v>
+        <v>10291.53</v>
       </c>
       <c r="AI2">
-        <v>11011.93</v>
+        <v>11043.15</v>
       </c>
       <c r="AJ2" t="s">
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>81.03</v>
+        <v>81.78</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1010,10 +1037,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>540.95</v>
+        <v>538.25</v>
       </c>
       <c r="D3">
-        <v>-1.12</v>
+        <v>-0.5</v>
       </c>
       <c r="E3">
         <v>670.25</v>
@@ -1022,25 +1049,25 @@
         <v>222.01</v>
       </c>
       <c r="G3">
-        <v>-19.29</v>
+        <v>-19.69</v>
       </c>
       <c r="H3">
-        <v>143.66</v>
+        <v>142.44</v>
       </c>
       <c r="I3">
-        <v>-0.6</v>
+        <v>1.48</v>
       </c>
       <c r="J3">
-        <v>-18.09</v>
+        <v>-8.85</v>
       </c>
       <c r="K3">
-        <v>2.99</v>
+        <v>3.82</v>
       </c>
       <c r="L3">
-        <v>140.99</v>
+        <v>138.97</v>
       </c>
       <c r="M3">
-        <v>17.97</v>
+        <v>17.62</v>
       </c>
       <c r="N3">
         <v>99</v>
@@ -1049,19 +1076,19 @@
         <v>94</v>
       </c>
       <c r="P3">
-        <v>537.6900000000001</v>
+        <v>539.26</v>
       </c>
       <c r="Q3">
-        <v>538.71</v>
+        <v>537.2</v>
       </c>
       <c r="R3">
-        <v>575.1799999999999</v>
+        <v>574.51</v>
       </c>
       <c r="S3">
-        <v>411.69</v>
+        <v>413.01</v>
       </c>
       <c r="T3">
-        <v>31.4</v>
+        <v>30.32</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1076,34 +1103,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>46.03</v>
+        <v>45.2</v>
       </c>
       <c r="Z3">
-        <v>-11.26</v>
+        <v>-10.63</v>
       </c>
       <c r="AA3">
-        <v>-12.89</v>
+        <v>-12.44</v>
       </c>
       <c r="AB3">
-        <v>1.63</v>
+        <v>1.81</v>
       </c>
       <c r="AC3">
-        <v>89.44</v>
+        <v>83.31</v>
       </c>
       <c r="AD3">
-        <v>83.75</v>
+        <v>86.37</v>
       </c>
       <c r="AE3">
-        <v>22.19</v>
+        <v>21.46</v>
       </c>
       <c r="AF3">
-        <v>-72.08</v>
+        <v>-72.64</v>
       </c>
       <c r="AG3">
-        <v>562.47</v>
+        <v>556.4</v>
       </c>
       <c r="AH3">
-        <v>514.96</v>
+        <v>518</v>
       </c>
       <c r="AI3">
         <v>600.11</v>
@@ -1112,7 +1139,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>18.84</v>
+        <v>18.66</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1123,10 +1150,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>360.35</v>
+        <v>363.95</v>
       </c>
       <c r="D4">
-        <v>-0.76</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>614.95</v>
@@ -1135,46 +1162,46 @@
         <v>303.75</v>
       </c>
       <c r="G4">
-        <v>-41.4</v>
+        <v>-40.82</v>
       </c>
       <c r="H4">
-        <v>18.63</v>
+        <v>19.82</v>
       </c>
       <c r="I4">
-        <v>3.05</v>
+        <v>4.55</v>
       </c>
       <c r="J4">
-        <v>7.07</v>
+        <v>10.64</v>
       </c>
       <c r="K4">
-        <v>-5.31</v>
+        <v>-6.6</v>
       </c>
       <c r="L4">
-        <v>-40.57</v>
+        <v>-38.92</v>
       </c>
       <c r="M4">
-        <v>-18.2</v>
+        <v>-17.89</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
       <c r="O4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P4">
-        <v>365.04</v>
+        <v>368.21</v>
       </c>
       <c r="Q4">
-        <v>340.59</v>
+        <v>342.28</v>
       </c>
       <c r="R4">
-        <v>328.71</v>
+        <v>329.73</v>
       </c>
       <c r="S4">
-        <v>397.48</v>
+        <v>396.64</v>
       </c>
       <c r="T4">
-        <v>-9.34</v>
+        <v>-8.24</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1189,34 +1216,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>60.95</v>
+        <v>62.56</v>
       </c>
       <c r="Z4">
-        <v>9.25</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AA4">
-        <v>5.6</v>
+        <v>6.39</v>
       </c>
       <c r="AB4">
-        <v>3.65</v>
+        <v>3.16</v>
       </c>
       <c r="AC4">
-        <v>54.93</v>
+        <v>47.98</v>
       </c>
       <c r="AD4">
-        <v>71.65000000000001</v>
+        <v>58.77</v>
       </c>
       <c r="AE4">
-        <v>14.34</v>
+        <v>14.1</v>
       </c>
       <c r="AF4">
-        <v>-63.66</v>
+        <v>-61.09</v>
       </c>
       <c r="AG4">
-        <v>373.35</v>
+        <v>376.23</v>
       </c>
       <c r="AH4">
-        <v>307.83</v>
+        <v>308.33</v>
       </c>
       <c r="AI4">
         <v>335.86</v>
@@ -1225,7 +1252,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>59.86</v>
+        <v>60.33</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1236,10 +1263,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>2032</v>
+        <v>2020.5</v>
       </c>
       <c r="D5">
-        <v>0.53</v>
+        <v>-0.57</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1248,46 +1275,46 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-6.64</v>
+        <v>-7.17</v>
       </c>
       <c r="H5">
-        <v>24.53</v>
+        <v>23.82</v>
       </c>
       <c r="I5">
-        <v>-3.47</v>
+        <v>-3.14</v>
       </c>
       <c r="J5">
-        <v>6.49</v>
+        <v>8.09</v>
       </c>
       <c r="K5">
-        <v>17.53</v>
+        <v>16.11</v>
       </c>
       <c r="L5">
-        <v>4.77</v>
+        <v>5.02</v>
       </c>
       <c r="M5">
-        <v>7.47</v>
+        <v>7.14</v>
       </c>
       <c r="N5">
         <v>57</v>
       </c>
       <c r="O5">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P5">
-        <v>2046.84</v>
+        <v>2033.74</v>
       </c>
       <c r="Q5">
-        <v>1954.29</v>
+        <v>1962.84</v>
       </c>
       <c r="R5">
-        <v>1851.28</v>
+        <v>1856.86</v>
       </c>
       <c r="S5">
-        <v>1913.42</v>
+        <v>1912.64</v>
       </c>
       <c r="T5">
-        <v>6.2</v>
+        <v>5.64</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1302,34 +1329,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>61.87</v>
+        <v>59.92</v>
       </c>
       <c r="Z5">
-        <v>57.62</v>
+        <v>54.25</v>
       </c>
       <c r="AA5">
         <v>54.24</v>
       </c>
       <c r="AB5">
-        <v>3.38</v>
+        <v>0.01</v>
       </c>
       <c r="AC5">
-        <v>22.18</v>
+        <v>22.85</v>
       </c>
       <c r="AD5">
-        <v>40.97</v>
+        <v>28.44</v>
       </c>
       <c r="AE5">
-        <v>47.62</v>
+        <v>46.07</v>
       </c>
       <c r="AF5">
-        <v>-31.77</v>
+        <v>-63.26</v>
       </c>
       <c r="AG5">
-        <v>2140.16</v>
+        <v>2144.1</v>
       </c>
       <c r="AH5">
-        <v>1768.42</v>
+        <v>1781.57</v>
       </c>
       <c r="AI5">
         <v>1958.53</v>
@@ -1338,7 +1365,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>38.05</v>
+        <v>34.31</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1349,10 +1376,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>11550</v>
+        <v>11579</v>
       </c>
       <c r="D6">
-        <v>0.6899999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="E6">
         <v>14451.52</v>
@@ -1361,46 +1388,46 @@
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-20.08</v>
+        <v>-19.88</v>
       </c>
       <c r="H6">
-        <v>32.06</v>
+        <v>32.39</v>
       </c>
       <c r="I6">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="J6">
-        <v>7.42</v>
+        <v>10.42</v>
       </c>
       <c r="K6">
-        <v>15.21</v>
+        <v>11.8</v>
       </c>
       <c r="L6">
-        <v>-16.26</v>
+        <v>-14.48</v>
       </c>
       <c r="M6">
-        <v>25.42</v>
+        <v>25.26</v>
       </c>
       <c r="N6">
         <v>29</v>
       </c>
       <c r="O6">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="P6">
-        <v>11433.4</v>
+        <v>11450</v>
       </c>
       <c r="Q6">
-        <v>10948.75</v>
+        <v>11001.15</v>
       </c>
       <c r="R6">
-        <v>10668.88</v>
+        <v>10695.66</v>
       </c>
       <c r="S6">
-        <v>10803.8</v>
+        <v>10795.97</v>
       </c>
       <c r="T6">
-        <v>6.91</v>
+        <v>7.25</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1415,43 +1442,43 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>66.44</v>
+        <v>67</v>
       </c>
       <c r="Z6">
-        <v>251.28</v>
+        <v>258.29</v>
       </c>
       <c r="AA6">
-        <v>199.24</v>
+        <v>211.05</v>
       </c>
       <c r="AB6">
-        <v>52.03</v>
+        <v>47.24</v>
       </c>
       <c r="AC6">
-        <v>60.73</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="AD6">
-        <v>64.3</v>
+        <v>63.19</v>
       </c>
       <c r="AE6">
-        <v>247.01</v>
+        <v>242.01</v>
       </c>
       <c r="AF6">
-        <v>-35.76</v>
+        <v>-59.25</v>
       </c>
       <c r="AG6">
-        <v>11865.69</v>
+        <v>11937.16</v>
       </c>
       <c r="AH6">
-        <v>10031.81</v>
+        <v>10065.14</v>
       </c>
       <c r="AI6">
-        <v>10764.47</v>
+        <v>10772.48</v>
       </c>
       <c r="AJ6" t="s">
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>48.18</v>
+        <v>48.63</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1462,10 +1489,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>1093.3</v>
+        <v>1094.2</v>
       </c>
       <c r="D7">
-        <v>-0.8100000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1474,46 +1501,46 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-5.65</v>
+        <v>-5.57</v>
       </c>
       <c r="H7">
-        <v>36.4</v>
+        <v>36.51</v>
       </c>
       <c r="I7">
-        <v>-4.85</v>
+        <v>-5.57</v>
       </c>
       <c r="J7">
-        <v>6.91</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="K7">
-        <v>22</v>
+        <v>19.96</v>
       </c>
       <c r="L7">
-        <v>22.58</v>
+        <v>24.82</v>
       </c>
       <c r="M7">
-        <v>12.56</v>
+        <v>12.46</v>
       </c>
       <c r="N7">
         <v>71</v>
       </c>
       <c r="O7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P7">
-        <v>1115.42</v>
+        <v>1102.5</v>
       </c>
       <c r="Q7">
-        <v>1079.31</v>
+        <v>1082.96</v>
       </c>
       <c r="R7">
-        <v>1008.2</v>
+        <v>1012.44</v>
       </c>
       <c r="S7">
         <v>974.13</v>
       </c>
       <c r="T7">
-        <v>12.23</v>
+        <v>12.33</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1528,34 +1555,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>55.32</v>
+        <v>55.48</v>
       </c>
       <c r="Z7">
-        <v>29.93</v>
+        <v>27.35</v>
       </c>
       <c r="AA7">
-        <v>32.1</v>
+        <v>31.15</v>
       </c>
       <c r="AB7">
-        <v>-2.16</v>
+        <v>-3.8</v>
       </c>
       <c r="AC7">
-        <v>18.61</v>
+        <v>21.77</v>
       </c>
       <c r="AD7">
-        <v>40.26</v>
+        <v>26.46</v>
       </c>
       <c r="AE7">
-        <v>30.47</v>
+        <v>29.34</v>
       </c>
       <c r="AF7">
-        <v>-36.44</v>
+        <v>-31.83</v>
       </c>
       <c r="AG7">
-        <v>1172.18</v>
+        <v>1171.88</v>
       </c>
       <c r="AH7">
-        <v>986.4400000000001</v>
+        <v>994.03</v>
       </c>
       <c r="AI7">
         <v>1067.72</v>
@@ -1564,7 +1591,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>29.69</v>
+        <v>27.88</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1575,10 +1602,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>140.61</v>
+        <v>135.56</v>
       </c>
       <c r="D8">
-        <v>-0.38</v>
+        <v>-3.59</v>
       </c>
       <c r="E8">
         <v>148.95</v>
@@ -1587,46 +1614,46 @@
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>-5.6</v>
+        <v>-8.99</v>
       </c>
       <c r="H8">
-        <v>21.26</v>
+        <v>16.9</v>
       </c>
       <c r="I8">
-        <v>-1.15</v>
+        <v>-4.65</v>
       </c>
       <c r="J8">
-        <v>3.5</v>
+        <v>-0.85</v>
       </c>
       <c r="K8">
-        <v>2.46</v>
+        <v>-1.59</v>
       </c>
       <c r="L8">
-        <v>4.93</v>
+        <v>5.13</v>
       </c>
       <c r="M8">
-        <v>1.6</v>
+        <v>-0.12</v>
       </c>
       <c r="N8">
         <v>43</v>
       </c>
       <c r="O8">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="P8">
-        <v>142.09</v>
+        <v>140.76</v>
       </c>
       <c r="Q8">
-        <v>141.97</v>
+        <v>141.67</v>
       </c>
       <c r="R8">
-        <v>137.72</v>
+        <v>137.61</v>
       </c>
       <c r="S8">
-        <v>133.7</v>
+        <v>133.73</v>
       </c>
       <c r="T8">
-        <v>5.17</v>
+        <v>1.37</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1641,34 +1668,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>51.35</v>
+        <v>40.25</v>
       </c>
       <c r="Z8">
-        <v>1.24</v>
+        <v>0.68</v>
       </c>
       <c r="AA8">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="AB8">
-        <v>-0.17</v>
+        <v>-0.59</v>
       </c>
       <c r="AC8">
-        <v>24.76</v>
+        <v>9.34</v>
       </c>
       <c r="AD8">
-        <v>34.79</v>
+        <v>24.16</v>
       </c>
       <c r="AE8">
-        <v>3.99</v>
+        <v>4.38</v>
       </c>
       <c r="AF8">
-        <v>-69.11</v>
+        <v>873.22</v>
       </c>
       <c r="AG8">
-        <v>146.68</v>
+        <v>147.18</v>
       </c>
       <c r="AH8">
-        <v>137.26</v>
+        <v>136.15</v>
       </c>
       <c r="AI8">
         <v>131.91</v>
@@ -1677,7 +1704,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>24.22</v>
+        <v>27.78</v>
       </c>
     </row>
   </sheetData>
@@ -1838,12 +1865,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>50</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1851,972 +1913,972 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>55</v>
+      <c r="B6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>14.98</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>12.87</v>
       </c>
-      <c r="E7" s="6">
-        <v>-2.11</v>
+      <c r="D7" s="6">
+        <v>15.09</v>
+      </c>
+      <c r="E7" s="7">
+        <v>2.22</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-18.38</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>-18.09</v>
       </c>
+      <c r="D8" s="6">
+        <v>-8.85</v>
+      </c>
       <c r="E8" s="7">
-        <v>0.29</v>
+        <v>9.24</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>9.66</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>7.07</v>
       </c>
-      <c r="E9" s="6">
-        <v>-2.59</v>
+      <c r="D9" s="6">
+        <v>10.64</v>
+      </c>
+      <c r="E9" s="7">
+        <v>3.57</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>5.5</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>6.49</v>
       </c>
+      <c r="D10" s="6">
+        <v>8.09</v>
+      </c>
       <c r="E10" s="7">
-        <v>0.99</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>7.67</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>7.42</v>
       </c>
-      <c r="E11" s="6">
-        <v>-0.25</v>
+      <c r="D11" s="6">
+        <v>10.42</v>
+      </c>
+      <c r="E11" s="7">
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="5">
-        <v>8.01</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6">
         <v>6.91</v>
       </c>
-      <c r="E12" s="6">
-        <v>-1.1</v>
+      <c r="D12" s="6">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="E12" s="7">
+        <v>1.79</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="5">
-        <v>6.22</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C13" s="6">
         <v>3.5</v>
       </c>
-      <c r="E13" s="6">
-        <v>-2.72</v>
+      <c r="D13" s="6">
+        <v>-0.85</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-4.35</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="5">
-        <v>-1.51</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C14" s="6">
         <v>1.01</v>
       </c>
-      <c r="E14" s="7">
-        <v>2.52</v>
+      <c r="D14" s="6">
+        <v>-0.85</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-1.86</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="5">
-        <v>4.44</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C15" s="6">
         <v>-0.6</v>
       </c>
-      <c r="E15" s="6">
-        <v>-5.04</v>
+      <c r="D15" s="6">
+        <v>1.48</v>
+      </c>
+      <c r="E15" s="7">
+        <v>2.08</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="5">
-        <v>7.54</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C16" s="6">
         <v>3.05</v>
       </c>
-      <c r="E16" s="6">
-        <v>-4.49</v>
+      <c r="D16" s="6">
+        <v>4.55</v>
+      </c>
+      <c r="E16" s="7">
+        <v>1.5</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="5">
-        <v>-3.56</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C17" s="6">
         <v>-3.47</v>
       </c>
+      <c r="D17" s="6">
+        <v>-3.14</v>
+      </c>
       <c r="E17" s="7">
-        <v>0.09</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="5">
-        <v>-1.1</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C18" s="6">
         <v>0.65</v>
       </c>
+      <c r="D18" s="6">
+        <v>0.72</v>
+      </c>
       <c r="E18" s="7">
-        <v>1.75</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="5">
-        <v>-4.41</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C19" s="6">
         <v>-4.85</v>
       </c>
-      <c r="E19" s="6">
-        <v>-0.44</v>
+      <c r="D19" s="6">
+        <v>-5.57</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-0.72</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="5">
-        <v>-1.71</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C20" s="6">
         <v>-1.15</v>
       </c>
-      <c r="E20" s="7">
+      <c r="D20" s="6">
+        <v>-4.65</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-3.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>44.36</v>
+      </c>
+      <c r="D21" s="6">
+        <v>45.07</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="6">
+        <v>140.99</v>
+      </c>
+      <c r="D22" s="6">
+        <v>138.97</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-2.02</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-40.57</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-38.92</v>
+      </c>
+      <c r="E23" s="7">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>4.77</v>
+      </c>
+      <c r="D24" s="6">
+        <v>5.02</v>
+      </c>
+      <c r="E24" s="7">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-16.26</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-14.48</v>
+      </c>
+      <c r="E25" s="7">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>22.58</v>
+      </c>
+      <c r="D26" s="6">
+        <v>24.82</v>
+      </c>
+      <c r="E26" s="7">
+        <v>2.24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>4.93</v>
+      </c>
+      <c r="D27" s="6">
+        <v>5.13</v>
+      </c>
+      <c r="E27" s="7">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="6">
+        <v>15.79</v>
+      </c>
+      <c r="D28" s="6">
+        <v>13.53</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-2.26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="6">
+        <v>2.99</v>
+      </c>
+      <c r="D29" s="6">
+        <v>3.82</v>
+      </c>
+      <c r="E29" s="7">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-5.31</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-6.6</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-1.29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="6">
+        <v>17.53</v>
+      </c>
+      <c r="D31" s="6">
+        <v>16.11</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-1.42</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="6">
+        <v>15.21</v>
+      </c>
+      <c r="D32" s="6">
+        <v>11.8</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-3.41</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6">
+        <v>22</v>
+      </c>
+      <c r="D33" s="6">
+        <v>19.96</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-2.04</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>2.46</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-1.59</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-4.05</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-1.17</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-1.32</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-19.29</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-19.69</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-41.4</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-40.82</v>
+      </c>
+      <c r="E37" s="7">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-6.64</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-7.17</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-20.08</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-19.88</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-5.65</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-5.57</v>
+      </c>
+      <c r="E40" s="7">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-5.6</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-8.99</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-3.39</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="6">
+        <v>11717</v>
+      </c>
+      <c r="D42" s="6">
+        <v>11700</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="6">
+        <v>540.95</v>
+      </c>
+      <c r="D43" s="6">
+        <v>538.25</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-2.7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="6">
+        <v>360.35</v>
+      </c>
+      <c r="D44" s="6">
+        <v>363.95</v>
+      </c>
+      <c r="E44" s="7">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="6">
+        <v>2032</v>
+      </c>
+      <c r="D45" s="6">
+        <v>2020.5</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-11.5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="6">
+        <v>11550</v>
+      </c>
+      <c r="D46" s="6">
+        <v>11579</v>
+      </c>
+      <c r="E46" s="7">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="6">
+        <v>1093.3</v>
+      </c>
+      <c r="D47" s="6">
+        <v>1094.2</v>
+      </c>
+      <c r="E47" s="7">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="6">
+        <v>140.61</v>
+      </c>
+      <c r="D48" s="6">
+        <v>135.56</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-5.05</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="6">
+        <v>67.91</v>
+      </c>
+      <c r="D49" s="6">
+        <v>67.25</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-0.66</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="6">
+        <v>46.03</v>
+      </c>
+      <c r="D50" s="6">
+        <v>45.2</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-0.83</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="6">
+        <v>60.95</v>
+      </c>
+      <c r="D51" s="6">
+        <v>62.56</v>
+      </c>
+      <c r="E51" s="7">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="6">
+        <v>61.87</v>
+      </c>
+      <c r="D52" s="6">
+        <v>59.92</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-1.95</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="6">
+        <v>66.44</v>
+      </c>
+      <c r="D53" s="6">
+        <v>67</v>
+      </c>
+      <c r="E53" s="7">
         <v>0.5600000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="6">
+        <v>55.32</v>
+      </c>
+      <c r="D54" s="6">
+        <v>55.48</v>
+      </c>
+      <c r="E54" s="7">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="6">
+        <v>51.35</v>
+      </c>
+      <c r="D55" s="6">
+        <v>40.25</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-11.1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="5">
-        <v>44.63</v>
-      </c>
-      <c r="D21" s="5">
-        <v>44.36</v>
-      </c>
-      <c r="E21" s="6">
-        <v>-0.27</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B56" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" s="6">
+        <v>-45.87</v>
+      </c>
+      <c r="D56" s="6">
+        <v>-48.7</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-2.83</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="5">
-        <v>146.46</v>
-      </c>
-      <c r="D22" s="5">
-        <v>140.99</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-5.47</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B57" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C57" s="6">
+        <v>-72.08</v>
+      </c>
+      <c r="D57" s="6">
+        <v>-72.64</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="5">
-        <v>-41.03</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-40.57</v>
-      </c>
-      <c r="E23" s="7">
-        <v>0.46</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B58" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="6">
+        <v>-63.66</v>
+      </c>
+      <c r="D58" s="6">
+        <v>-61.09</v>
+      </c>
+      <c r="E58" s="7">
+        <v>2.57</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="5">
-        <v>4.54</v>
-      </c>
-      <c r="D24" s="5">
-        <v>4.77</v>
-      </c>
-      <c r="E24" s="7">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="B59" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="6">
+        <v>-31.77</v>
+      </c>
+      <c r="D59" s="6">
+        <v>-63.26</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-31.49</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>-17.06</v>
-      </c>
-      <c r="D25" s="5">
-        <v>-16.26</v>
-      </c>
-      <c r="E25" s="7">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="B60" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="6">
+        <v>-35.76</v>
+      </c>
+      <c r="D60" s="6">
+        <v>-59.25</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-23.49</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>24.5</v>
-      </c>
-      <c r="D26" s="5">
-        <v>22.58</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-1.92</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="B61" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="6">
+        <v>-36.44</v>
+      </c>
+      <c r="D61" s="6">
+        <v>-31.83</v>
+      </c>
+      <c r="E61" s="7">
+        <v>4.61</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>1.93</v>
-      </c>
-      <c r="D27" s="5">
-        <v>4.93</v>
-      </c>
-      <c r="E27" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="5">
-        <v>13.89</v>
-      </c>
-      <c r="D28" s="5">
-        <v>15.79</v>
-      </c>
-      <c r="E28" s="7">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-0.16</v>
-      </c>
-      <c r="D29" s="5">
-        <v>2.99</v>
-      </c>
-      <c r="E29" s="7">
-        <v>3.15</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-5.82</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-5.31</v>
-      </c>
-      <c r="E30" s="7">
-        <v>0.51</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="5">
-        <v>15.85</v>
-      </c>
-      <c r="D31" s="5">
-        <v>17.53</v>
-      </c>
-      <c r="E31" s="7">
-        <v>1.68</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="5">
-        <v>13.61</v>
-      </c>
-      <c r="D32" s="5">
-        <v>15.21</v>
-      </c>
-      <c r="E32" s="7">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="5">
-        <v>21.9</v>
-      </c>
-      <c r="D33" s="5">
-        <v>22</v>
-      </c>
-      <c r="E33" s="7">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>4.3</v>
-      </c>
-      <c r="D34" s="5">
-        <v>2.46</v>
-      </c>
-      <c r="E34" s="6">
-        <v>-1.84</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-1.51</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-1.17</v>
-      </c>
-      <c r="E35" s="7">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-18.38</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-19.29</v>
-      </c>
-      <c r="E36" s="6">
-        <v>-0.91</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="5">
-        <v>-40.95</v>
-      </c>
-      <c r="D37" s="5">
-        <v>-41.4</v>
-      </c>
-      <c r="E37" s="6">
-        <v>-0.45</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="5">
-        <v>-7.13</v>
-      </c>
-      <c r="D38" s="5">
-        <v>-6.64</v>
-      </c>
-      <c r="E38" s="7">
-        <v>0.49</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-20.62</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-20.08</v>
-      </c>
-      <c r="E39" s="7">
-        <v>0.54</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="5">
-        <v>-4.88</v>
-      </c>
-      <c r="D40" s="5">
-        <v>-5.65</v>
-      </c>
-      <c r="E40" s="6">
-        <v>-0.77</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="5">
-        <v>-5.24</v>
-      </c>
-      <c r="D41" s="5">
-        <v>-5.6</v>
-      </c>
-      <c r="E41" s="6">
-        <v>-0.36</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="5">
-        <v>11677</v>
-      </c>
-      <c r="D42" s="5">
-        <v>11717</v>
-      </c>
-      <c r="E42" s="7">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="5">
-        <v>547.05</v>
-      </c>
-      <c r="D43" s="5">
-        <v>540.95</v>
-      </c>
-      <c r="E43" s="6">
-        <v>-6.1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="5">
-        <v>363.1</v>
-      </c>
-      <c r="D44" s="5">
-        <v>360.35</v>
-      </c>
-      <c r="E44" s="6">
-        <v>-2.75</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="5">
-        <v>2021.3</v>
-      </c>
-      <c r="D45" s="5">
-        <v>2032</v>
-      </c>
-      <c r="E45" s="7">
-        <v>10.7</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="5">
-        <v>11471</v>
-      </c>
-      <c r="D46" s="5">
-        <v>11550</v>
-      </c>
-      <c r="E46" s="7">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="5">
-        <v>1102.2</v>
-      </c>
-      <c r="D47" s="5">
-        <v>1093.3</v>
-      </c>
-      <c r="E47" s="6">
-        <v>-8.9</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="5">
-        <v>141.14</v>
-      </c>
-      <c r="D48" s="5">
-        <v>140.61</v>
-      </c>
-      <c r="E48" s="6">
-        <v>-0.53</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" s="5">
-        <v>67.20999999999999</v>
-      </c>
-      <c r="D49" s="5">
-        <v>67.91</v>
-      </c>
-      <c r="E49" s="7">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="5">
-        <v>47.9</v>
-      </c>
-      <c r="D50" s="5">
-        <v>46.03</v>
-      </c>
-      <c r="E50" s="6">
-        <v>-1.87</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="5">
-        <v>62.86</v>
-      </c>
-      <c r="D51" s="5">
-        <v>60.95</v>
-      </c>
-      <c r="E51" s="6">
-        <v>-1.91</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="5">
-        <v>60.77</v>
-      </c>
-      <c r="D52" s="5">
-        <v>61.87</v>
-      </c>
-      <c r="E52" s="7">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="5">
-        <v>64.92</v>
-      </c>
-      <c r="D53" s="5">
-        <v>66.44</v>
-      </c>
-      <c r="E53" s="7">
-        <v>1.52</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="5">
-        <v>57.22</v>
-      </c>
-      <c r="D54" s="5">
-        <v>55.32</v>
-      </c>
-      <c r="E54" s="6">
-        <v>-1.9</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="5">
-        <v>52.76</v>
-      </c>
-      <c r="D55" s="5">
-        <v>51.35</v>
-      </c>
-      <c r="E55" s="6">
-        <v>-1.41</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B56" s="3" t="s">
+      <c r="B62" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C56" s="5">
-        <v>-60.41</v>
-      </c>
-      <c r="D56" s="5">
-        <v>-45.87</v>
-      </c>
-      <c r="E56" s="7">
-        <v>14.54</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C57" s="5">
-        <v>-77.56999999999999</v>
-      </c>
-      <c r="D57" s="5">
-        <v>-72.08</v>
-      </c>
-      <c r="E57" s="7">
-        <v>5.49</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C58" s="5">
-        <v>-45.53</v>
-      </c>
-      <c r="D58" s="5">
-        <v>-63.66</v>
-      </c>
-      <c r="E58" s="6">
-        <v>-18.13</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C59" s="5">
-        <v>-38.88</v>
-      </c>
-      <c r="D59" s="5">
-        <v>-31.77</v>
-      </c>
-      <c r="E59" s="7">
-        <v>7.11</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="5">
-        <v>-34.55</v>
-      </c>
-      <c r="D60" s="5">
-        <v>-35.76</v>
-      </c>
-      <c r="E60" s="6">
-        <v>-1.21</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="5">
-        <v>-28.78</v>
-      </c>
-      <c r="D61" s="5">
-        <v>-36.44</v>
-      </c>
-      <c r="E61" s="6">
-        <v>-7.66</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="5">
-        <v>-39.16</v>
-      </c>
-      <c r="D62" s="5">
+      <c r="C62" s="6">
         <v>-69.11</v>
       </c>
-      <c r="E62" s="6">
-        <v>-29.95</v>
+      <c r="D62" s="6">
+        <v>873.22</v>
+      </c>
+      <c r="E62" s="7">
+        <v>942.33</v>
       </c>
     </row>
   </sheetData>
@@ -2842,60 +2904,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C1" s="8" t="s">
+      <c r="B1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="11">
+        <v>68.8</v>
+      </c>
+      <c r="C2" s="12">
+        <v>7</v>
+      </c>
+      <c r="D2" s="11">
+        <v>56.8</v>
+      </c>
+      <c r="E2" s="11">
+        <v>90</v>
+      </c>
+      <c r="F2" s="11">
+        <v>6.2</v>
+      </c>
+      <c r="G2" s="11">
+        <v>8.1</v>
+      </c>
+      <c r="H2" s="11">
         <v>57</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="10">
-        <v>68.8</v>
-      </c>
-      <c r="C2" s="11">
-        <v>7</v>
-      </c>
-      <c r="D2" s="10">
-        <v>58.6</v>
-      </c>
-      <c r="E2" s="10">
-        <v>90</v>
-      </c>
-      <c r="F2" s="10">
-        <v>3.7</v>
-      </c>
-      <c r="G2" s="10">
-        <v>10.1</v>
-      </c>
-      <c r="H2" s="10">
-        <v>57</v>
-      </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>40</v>
       </c>
     </row>
@@ -2997,49 +3059,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="13">
-        <v>0.2865</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.2542</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.1797</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.1256</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.0747</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0.016</v>
-      </c>
-      <c r="G2" s="13">
-        <v>-0.182</v>
+      <c r="A2" s="14">
+        <v>0.2832</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.2526</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.1762</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.1246</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.07139999999999999</v>
+      </c>
+      <c r="F2" s="14">
+        <v>-0.0012</v>
+      </c>
+      <c r="G2" s="14">
+        <v>-0.1789</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="64">
   <si>
     <t>Symbol</t>
   </si>
@@ -172,34 +172,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>51.4 → 40.2</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>51.4</t>
-  </si>
-  <si>
-    <t>40.2</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -401,18 +374,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -783,8 +755,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -924,10 +896,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>11700</v>
+        <v>11661</v>
       </c>
       <c r="D2">
-        <v>-0.15</v>
+        <v>-0.33</v>
       </c>
       <c r="E2">
         <v>11856</v>
@@ -936,46 +908,46 @@
         <v>8082.75</v>
       </c>
       <c r="G2">
-        <v>-1.32</v>
+        <v>-1.64</v>
       </c>
       <c r="H2">
-        <v>44.75</v>
+        <v>44.27</v>
       </c>
       <c r="I2">
-        <v>-0.85</v>
+        <v>0.35</v>
       </c>
       <c r="J2">
-        <v>15.09</v>
+        <v>12.96</v>
       </c>
       <c r="K2">
-        <v>13.53</v>
+        <v>13.95</v>
       </c>
       <c r="L2">
-        <v>45.07</v>
+        <v>43.7</v>
       </c>
       <c r="M2">
-        <v>28.32</v>
+        <v>27.86</v>
       </c>
       <c r="N2">
         <v>85</v>
       </c>
       <c r="O2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P2">
-        <v>11675.2</v>
+        <v>11683.4</v>
       </c>
       <c r="Q2">
-        <v>11279.62</v>
+        <v>11346.1</v>
       </c>
       <c r="R2">
-        <v>10549.78</v>
+        <v>10577.82</v>
       </c>
       <c r="S2">
-        <v>9658.91</v>
+        <v>9672.469999999999</v>
       </c>
       <c r="T2">
-        <v>21.13</v>
+        <v>20.56</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -990,34 +962,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>67.25</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="Z2">
-        <v>371.63</v>
+        <v>354.6</v>
       </c>
       <c r="AA2">
-        <v>369.89</v>
+        <v>366.83</v>
       </c>
       <c r="AB2">
-        <v>1.74</v>
+        <v>-12.23</v>
       </c>
       <c r="AC2">
-        <v>9.460000000000001</v>
+        <v>6.98</v>
       </c>
       <c r="AD2">
-        <v>19.89</v>
+        <v>12.43</v>
       </c>
       <c r="AE2">
-        <v>235.12</v>
+        <v>228.54</v>
       </c>
       <c r="AF2">
-        <v>-48.7</v>
+        <v>-67.95999999999999</v>
       </c>
       <c r="AG2">
-        <v>12267.72</v>
+        <v>12240.02</v>
       </c>
       <c r="AH2">
-        <v>10291.53</v>
+        <v>10452.18</v>
       </c>
       <c r="AI2">
         <v>11043.15</v>
@@ -1026,7 +998,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>81.78</v>
+        <v>78.76000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1037,10 +1009,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>538.25</v>
+        <v>527.65</v>
       </c>
       <c r="D3">
-        <v>-0.5</v>
+        <v>-1.97</v>
       </c>
       <c r="E3">
         <v>670.25</v>
@@ -1049,25 +1021,25 @@
         <v>222.01</v>
       </c>
       <c r="G3">
-        <v>-19.69</v>
+        <v>-21.28</v>
       </c>
       <c r="H3">
-        <v>142.44</v>
+        <v>137.67</v>
       </c>
       <c r="I3">
-        <v>1.48</v>
+        <v>-0.93</v>
       </c>
       <c r="J3">
-        <v>-8.85</v>
+        <v>-7.18</v>
       </c>
       <c r="K3">
-        <v>3.82</v>
+        <v>-1.82</v>
       </c>
       <c r="L3">
-        <v>138.97</v>
+        <v>134.57</v>
       </c>
       <c r="M3">
-        <v>17.62</v>
+        <v>17.01</v>
       </c>
       <c r="N3">
         <v>99</v>
@@ -1076,19 +1048,19 @@
         <v>94</v>
       </c>
       <c r="P3">
-        <v>539.26</v>
+        <v>538.27</v>
       </c>
       <c r="Q3">
-        <v>537.2</v>
+        <v>535.9</v>
       </c>
       <c r="R3">
-        <v>574.51</v>
+        <v>573.96</v>
       </c>
       <c r="S3">
-        <v>413.01</v>
+        <v>414.3</v>
       </c>
       <c r="T3">
-        <v>30.32</v>
+        <v>27.36</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1103,43 +1075,43 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>45.2</v>
+        <v>41.97</v>
       </c>
       <c r="Z3">
-        <v>-10.63</v>
+        <v>-10.85</v>
       </c>
       <c r="AA3">
-        <v>-12.44</v>
+        <v>-12.12</v>
       </c>
       <c r="AB3">
-        <v>1.81</v>
+        <v>1.27</v>
       </c>
       <c r="AC3">
-        <v>83.31</v>
+        <v>61.62</v>
       </c>
       <c r="AD3">
-        <v>86.37</v>
+        <v>78.13</v>
       </c>
       <c r="AE3">
-        <v>21.46</v>
+        <v>20.87</v>
       </c>
       <c r="AF3">
-        <v>-72.64</v>
+        <v>-67.18000000000001</v>
       </c>
       <c r="AG3">
-        <v>556.4</v>
+        <v>553.88</v>
       </c>
       <c r="AH3">
-        <v>518</v>
+        <v>517.92</v>
       </c>
       <c r="AI3">
-        <v>600.11</v>
+        <v>594.16</v>
       </c>
       <c r="AJ3" t="s">
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>18.66</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1150,58 +1122,58 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>363.95</v>
+        <v>356.6</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>-2.02</v>
       </c>
       <c r="E4">
-        <v>614.95</v>
+        <v>604.85</v>
       </c>
       <c r="F4">
         <v>303.75</v>
       </c>
       <c r="G4">
-        <v>-40.82</v>
+        <v>-41.04</v>
       </c>
       <c r="H4">
-        <v>19.82</v>
+        <v>17.4</v>
       </c>
       <c r="I4">
-        <v>4.55</v>
+        <v>-6.77</v>
       </c>
       <c r="J4">
-        <v>10.64</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="K4">
-        <v>-6.6</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="L4">
-        <v>-38.92</v>
+        <v>-42.01</v>
       </c>
       <c r="M4">
-        <v>-17.89</v>
+        <v>-18.27</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
       <c r="O4">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="P4">
-        <v>368.21</v>
+        <v>363.03</v>
       </c>
       <c r="Q4">
-        <v>342.28</v>
+        <v>343.32</v>
       </c>
       <c r="R4">
-        <v>329.73</v>
+        <v>330.68</v>
       </c>
       <c r="S4">
-        <v>396.64</v>
+        <v>395.79</v>
       </c>
       <c r="T4">
-        <v>-8.24</v>
+        <v>-9.9</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1216,34 +1188,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>62.56</v>
+        <v>57.36</v>
       </c>
       <c r="Z4">
-        <v>9.550000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="AA4">
-        <v>6.39</v>
+        <v>6.93</v>
       </c>
       <c r="AB4">
-        <v>3.16</v>
+        <v>2.16</v>
       </c>
       <c r="AC4">
-        <v>47.98</v>
+        <v>41.61</v>
       </c>
       <c r="AD4">
-        <v>58.77</v>
+        <v>48.17</v>
       </c>
       <c r="AE4">
-        <v>14.1</v>
+        <v>14.04</v>
       </c>
       <c r="AF4">
-        <v>-61.09</v>
+        <v>-69.39</v>
       </c>
       <c r="AG4">
-        <v>376.23</v>
+        <v>377.71</v>
       </c>
       <c r="AH4">
-        <v>308.33</v>
+        <v>308.93</v>
       </c>
       <c r="AI4">
         <v>335.86</v>
@@ -1252,7 +1224,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>60.33</v>
+        <v>59.15</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1263,10 +1235,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>2020.5</v>
+        <v>2025</v>
       </c>
       <c r="D5">
-        <v>-0.57</v>
+        <v>0.22</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1275,46 +1247,46 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-7.17</v>
+        <v>-6.96</v>
       </c>
       <c r="H5">
-        <v>23.82</v>
+        <v>24.1</v>
       </c>
       <c r="I5">
-        <v>-3.14</v>
+        <v>-2.92</v>
       </c>
       <c r="J5">
-        <v>8.09</v>
+        <v>9.48</v>
       </c>
       <c r="K5">
-        <v>16.11</v>
+        <v>17.18</v>
       </c>
       <c r="L5">
-        <v>5.02</v>
+        <v>5.8</v>
       </c>
       <c r="M5">
-        <v>7.14</v>
+        <v>7.22</v>
       </c>
       <c r="N5">
         <v>57</v>
       </c>
       <c r="O5">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P5">
-        <v>2033.74</v>
+        <v>2021.54</v>
       </c>
       <c r="Q5">
-        <v>1962.84</v>
+        <v>1972.16</v>
       </c>
       <c r="R5">
-        <v>1856.86</v>
+        <v>1862.67</v>
       </c>
       <c r="S5">
-        <v>1912.64</v>
+        <v>1911.97</v>
       </c>
       <c r="T5">
-        <v>5.64</v>
+        <v>5.91</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1329,34 +1301,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>59.92</v>
+        <v>60.44</v>
       </c>
       <c r="Z5">
-        <v>54.25</v>
+        <v>51.34</v>
       </c>
       <c r="AA5">
-        <v>54.24</v>
+        <v>53.66</v>
       </c>
       <c r="AB5">
-        <v>0.01</v>
+        <v>-2.32</v>
       </c>
       <c r="AC5">
-        <v>22.85</v>
+        <v>18.07</v>
       </c>
       <c r="AD5">
-        <v>28.44</v>
+        <v>21.03</v>
       </c>
       <c r="AE5">
-        <v>46.07</v>
+        <v>45.02</v>
       </c>
       <c r="AF5">
-        <v>-63.26</v>
+        <v>-40.52</v>
       </c>
       <c r="AG5">
-        <v>2144.1</v>
+        <v>2145.52</v>
       </c>
       <c r="AH5">
-        <v>1781.57</v>
+        <v>1798.79</v>
       </c>
       <c r="AI5">
         <v>1958.53</v>
@@ -1365,7 +1337,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>34.31</v>
+        <v>31.83</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1376,10 +1348,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>11579</v>
+        <v>11500</v>
       </c>
       <c r="D6">
-        <v>0.25</v>
+        <v>-0.68</v>
       </c>
       <c r="E6">
         <v>14451.52</v>
@@ -1388,46 +1360,46 @@
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-19.88</v>
+        <v>-20.42</v>
       </c>
       <c r="H6">
-        <v>32.39</v>
+        <v>31.49</v>
       </c>
       <c r="I6">
-        <v>0.72</v>
+        <v>0.99</v>
       </c>
       <c r="J6">
-        <v>10.42</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K6">
-        <v>11.8</v>
+        <v>11.56</v>
       </c>
       <c r="L6">
-        <v>-14.48</v>
+        <v>-16.13</v>
       </c>
       <c r="M6">
-        <v>25.26</v>
+        <v>24.12</v>
       </c>
       <c r="N6">
         <v>29</v>
       </c>
       <c r="O6">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="P6">
-        <v>11450</v>
+        <v>11472.6</v>
       </c>
       <c r="Q6">
-        <v>11001.15</v>
+        <v>11055.3</v>
       </c>
       <c r="R6">
-        <v>10695.66</v>
+        <v>10721.86</v>
       </c>
       <c r="S6">
-        <v>10795.97</v>
+        <v>10787.75</v>
       </c>
       <c r="T6">
-        <v>7.25</v>
+        <v>6.6</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1442,43 +1414,43 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>67</v>
+        <v>63.85</v>
       </c>
       <c r="Z6">
-        <v>258.29</v>
+        <v>254.54</v>
       </c>
       <c r="AA6">
-        <v>211.05</v>
+        <v>219.75</v>
       </c>
       <c r="AB6">
-        <v>47.24</v>
+        <v>34.79</v>
       </c>
       <c r="AC6">
-        <v>65.84999999999999</v>
+        <v>56.29</v>
       </c>
       <c r="AD6">
-        <v>63.19</v>
+        <v>60.96</v>
       </c>
       <c r="AE6">
-        <v>242.01</v>
+        <v>236.79</v>
       </c>
       <c r="AF6">
-        <v>-59.25</v>
+        <v>-67.3</v>
       </c>
       <c r="AG6">
-        <v>11937.16</v>
+        <v>11974.17</v>
       </c>
       <c r="AH6">
-        <v>10065.14</v>
+        <v>10136.43</v>
       </c>
       <c r="AI6">
-        <v>10772.48</v>
+        <v>10779.62</v>
       </c>
       <c r="AJ6" t="s">
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>48.63</v>
+        <v>49.03</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1489,10 +1461,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>1094.2</v>
+        <v>1090.8</v>
       </c>
       <c r="D7">
-        <v>0.08</v>
+        <v>-0.31</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1501,46 +1473,46 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-5.57</v>
+        <v>-5.87</v>
       </c>
       <c r="H7">
-        <v>36.51</v>
+        <v>36.09</v>
       </c>
       <c r="I7">
-        <v>-5.57</v>
+        <v>-4.72</v>
       </c>
       <c r="J7">
-        <v>8.699999999999999</v>
+        <v>6.81</v>
       </c>
       <c r="K7">
-        <v>19.96</v>
+        <v>19.81</v>
       </c>
       <c r="L7">
-        <v>24.82</v>
+        <v>24.08</v>
       </c>
       <c r="M7">
-        <v>12.46</v>
+        <v>12.55</v>
       </c>
       <c r="N7">
         <v>71</v>
       </c>
       <c r="O7">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P7">
-        <v>1102.5</v>
+        <v>1091.7</v>
       </c>
       <c r="Q7">
-        <v>1082.96</v>
+        <v>1085.62</v>
       </c>
       <c r="R7">
-        <v>1012.44</v>
+        <v>1016.72</v>
       </c>
       <c r="S7">
-        <v>974.13</v>
+        <v>974.14</v>
       </c>
       <c r="T7">
-        <v>12.33</v>
+        <v>11.98</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1555,34 +1527,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>55.48</v>
+        <v>54.68</v>
       </c>
       <c r="Z7">
-        <v>27.35</v>
+        <v>24.74</v>
       </c>
       <c r="AA7">
-        <v>31.15</v>
+        <v>29.86</v>
       </c>
       <c r="AB7">
-        <v>-3.8</v>
+        <v>-5.13</v>
       </c>
       <c r="AC7">
-        <v>21.77</v>
+        <v>15.17</v>
       </c>
       <c r="AD7">
-        <v>26.46</v>
+        <v>18.52</v>
       </c>
       <c r="AE7">
-        <v>29.34</v>
+        <v>28.12</v>
       </c>
       <c r="AF7">
-        <v>-31.83</v>
+        <v>-76.84999999999999</v>
       </c>
       <c r="AG7">
-        <v>1171.88</v>
+        <v>1171.97</v>
       </c>
       <c r="AH7">
-        <v>994.03</v>
+        <v>999.26</v>
       </c>
       <c r="AI7">
         <v>1067.72</v>
@@ -1591,7 +1563,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>27.88</v>
+        <v>26.22</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1602,10 +1574,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>135.56</v>
+        <v>135.6</v>
       </c>
       <c r="D8">
-        <v>-3.59</v>
+        <v>0.03</v>
       </c>
       <c r="E8">
         <v>148.95</v>
@@ -1614,46 +1586,46 @@
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>-8.99</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="H8">
-        <v>16.9</v>
+        <v>16.94</v>
       </c>
       <c r="I8">
-        <v>-4.65</v>
+        <v>-5.37</v>
       </c>
       <c r="J8">
-        <v>-0.85</v>
+        <v>-4.27</v>
       </c>
       <c r="K8">
-        <v>-1.59</v>
+        <v>-3.84</v>
       </c>
       <c r="L8">
-        <v>5.13</v>
+        <v>9.34</v>
       </c>
       <c r="M8">
-        <v>-0.12</v>
+        <v>-1.08</v>
       </c>
       <c r="N8">
         <v>43</v>
       </c>
       <c r="O8">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="P8">
-        <v>140.76</v>
+        <v>139.23</v>
       </c>
       <c r="Q8">
-        <v>141.67</v>
+        <v>141.14</v>
       </c>
       <c r="R8">
-        <v>137.61</v>
+        <v>137.53</v>
       </c>
       <c r="S8">
-        <v>133.73</v>
+        <v>133.76</v>
       </c>
       <c r="T8">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1668,34 +1640,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>40.25</v>
+        <v>40.36</v>
       </c>
       <c r="Z8">
-        <v>0.68</v>
+        <v>0.24</v>
       </c>
       <c r="AA8">
-        <v>1.27</v>
+        <v>1.06</v>
       </c>
       <c r="AB8">
-        <v>-0.59</v>
+        <v>-0.82</v>
       </c>
       <c r="AC8">
-        <v>9.34</v>
+        <v>2.38</v>
       </c>
       <c r="AD8">
-        <v>24.16</v>
+        <v>12.16</v>
       </c>
       <c r="AE8">
-        <v>4.38</v>
+        <v>4.34</v>
       </c>
       <c r="AF8">
-        <v>873.22</v>
+        <v>-46.09</v>
       </c>
       <c r="AG8">
-        <v>147.18</v>
+        <v>146.85</v>
       </c>
       <c r="AH8">
-        <v>136.15</v>
+        <v>135.42</v>
       </c>
       <c r="AI8">
         <v>131.91</v>
@@ -1704,7 +1676,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>27.78</v>
+        <v>30.87</v>
       </c>
     </row>
   </sheetData>
@@ -1865,47 +1837,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1913,972 +1850,972 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>64</v>
+      <c r="B6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>12.87</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>15.09</v>
       </c>
-      <c r="E7" s="7">
-        <v>2.22</v>
+      <c r="D7" s="5">
+        <v>12.96</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-2.13</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-18.09</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>-8.85</v>
       </c>
+      <c r="D8" s="5">
+        <v>-7.18</v>
+      </c>
       <c r="E8" s="7">
-        <v>9.24</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>7.07</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>10.64</v>
       </c>
-      <c r="E9" s="7">
-        <v>3.57</v>
+      <c r="D9" s="5">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-2.6</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>6.49</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>8.09</v>
       </c>
+      <c r="D10" s="5">
+        <v>9.48</v>
+      </c>
       <c r="E10" s="7">
-        <v>1.6</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>7.42</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>10.42</v>
       </c>
-      <c r="E11" s="7">
-        <v>3</v>
+      <c r="D11" s="5">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-1.22</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="6">
-        <v>6.91</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>8.699999999999999</v>
       </c>
-      <c r="E12" s="7">
-        <v>1.79</v>
+      <c r="D12" s="5">
+        <v>6.81</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-1.89</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="6">
-        <v>3.5</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>-0.85</v>
       </c>
-      <c r="E13" s="8">
-        <v>-4.35</v>
+      <c r="D13" s="5">
+        <v>-4.27</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-3.42</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="6">
-        <v>1.01</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" s="5">
         <v>-0.85</v>
       </c>
-      <c r="E14" s="8">
-        <v>-1.86</v>
+      <c r="D14" s="5">
+        <v>0.35</v>
+      </c>
+      <c r="E14" s="7">
+        <v>1.2</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="6">
-        <v>-0.6</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C15" s="5">
         <v>1.48</v>
       </c>
-      <c r="E15" s="7">
-        <v>2.08</v>
+      <c r="D15" s="5">
+        <v>-0.93</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-2.41</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="6">
-        <v>3.05</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C16" s="5">
         <v>4.55</v>
       </c>
-      <c r="E16" s="7">
-        <v>1.5</v>
+      <c r="D16" s="5">
+        <v>-6.77</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-11.32</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="6">
-        <v>-3.47</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C17" s="5">
         <v>-3.14</v>
       </c>
+      <c r="D17" s="5">
+        <v>-2.92</v>
+      </c>
       <c r="E17" s="7">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="6">
-        <v>0.65</v>
-      </c>
-      <c r="D18" s="6">
+      <c r="C18" s="5">
         <v>0.72</v>
       </c>
+      <c r="D18" s="5">
+        <v>0.99</v>
+      </c>
       <c r="E18" s="7">
-        <v>0.07000000000000001</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="6">
-        <v>-4.85</v>
-      </c>
-      <c r="D19" s="6">
+      <c r="C19" s="5">
         <v>-5.57</v>
       </c>
-      <c r="E19" s="8">
+      <c r="D19" s="5">
+        <v>-4.72</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-4.65</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-5.37</v>
+      </c>
+      <c r="E20" s="6">
         <v>-0.72</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>45.07</v>
+      </c>
+      <c r="D21" s="5">
+        <v>43.7</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-1.37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="5">
+        <v>138.97</v>
+      </c>
+      <c r="D22" s="5">
+        <v>134.57</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-4.4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5">
+        <v>-38.92</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-42.01</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-3.09</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5">
+        <v>5.02</v>
+      </c>
+      <c r="D24" s="5">
+        <v>5.8</v>
+      </c>
+      <c r="E24" s="7">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-14.48</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-16.13</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-1.65</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>24.82</v>
+      </c>
+      <c r="D26" s="5">
+        <v>24.08</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-0.74</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-1.15</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-4.65</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-3.5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>5.13</v>
+      </c>
+      <c r="D27" s="5">
+        <v>9.34</v>
+      </c>
+      <c r="E27" s="7">
+        <v>4.21</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>44.36</v>
-      </c>
-      <c r="D21" s="6">
-        <v>45.07</v>
-      </c>
-      <c r="E21" s="7">
-        <v>0.71</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="5">
+        <v>13.53</v>
+      </c>
+      <c r="D28" s="5">
+        <v>13.95</v>
+      </c>
+      <c r="E28" s="7">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="6">
-        <v>140.99</v>
-      </c>
-      <c r="D22" s="6">
-        <v>138.97</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-2.02</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="5">
+        <v>3.82</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-1.82</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-5.64</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-40.57</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-38.92</v>
-      </c>
-      <c r="E23" s="7">
-        <v>1.65</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-6.6</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-9.289999999999999</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-2.69</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6">
-        <v>4.77</v>
-      </c>
-      <c r="D24" s="6">
-        <v>5.02</v>
-      </c>
-      <c r="E24" s="7">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="5">
+        <v>16.11</v>
+      </c>
+      <c r="D31" s="5">
+        <v>17.18</v>
+      </c>
+      <c r="E31" s="7">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-16.26</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-14.48</v>
-      </c>
-      <c r="E25" s="7">
-        <v>1.78</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="5">
+        <v>11.8</v>
+      </c>
+      <c r="D32" s="5">
+        <v>11.56</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>22.58</v>
-      </c>
-      <c r="D26" s="6">
-        <v>24.82</v>
-      </c>
-      <c r="E26" s="7">
-        <v>2.24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="5">
+        <v>19.96</v>
+      </c>
+      <c r="D33" s="5">
+        <v>19.81</v>
+      </c>
+      <c r="E33" s="6">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>4.93</v>
-      </c>
-      <c r="D27" s="6">
-        <v>5.13</v>
-      </c>
-      <c r="E27" s="7">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>-1.59</v>
+      </c>
+      <c r="D34" s="5">
+        <v>-3.84</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-2.25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="6">
-        <v>15.79</v>
-      </c>
-      <c r="D28" s="6">
-        <v>13.53</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-2.26</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B35" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-1.32</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-1.64</v>
+      </c>
+      <c r="E35" s="6">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="6">
-        <v>2.99</v>
-      </c>
-      <c r="D29" s="6">
-        <v>3.82</v>
-      </c>
-      <c r="E29" s="7">
-        <v>0.83</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B36" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-19.69</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-21.28</v>
+      </c>
+      <c r="E36" s="6">
+        <v>-1.59</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-5.31</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-6.6</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-1.29</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="B37" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="5">
+        <v>-40.82</v>
+      </c>
+      <c r="D37" s="5">
+        <v>-41.04</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="6">
-        <v>17.53</v>
-      </c>
-      <c r="D31" s="6">
-        <v>16.11</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-1.42</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="B38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="5">
+        <v>-7.17</v>
+      </c>
+      <c r="D38" s="5">
+        <v>-6.96</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="6">
-        <v>15.21</v>
-      </c>
-      <c r="D32" s="6">
-        <v>11.8</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-3.41</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="B39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="5">
+        <v>-19.88</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-20.42</v>
+      </c>
+      <c r="E39" s="6">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="6">
-        <v>22</v>
-      </c>
-      <c r="D33" s="6">
-        <v>19.96</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-2.04</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="B40" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="5">
+        <v>-5.57</v>
+      </c>
+      <c r="D40" s="5">
+        <v>-5.87</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>2.46</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-1.59</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-4.05</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="B41" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="5">
+        <v>-8.99</v>
+      </c>
+      <c r="D41" s="5">
+        <v>-8.960000000000001</v>
+      </c>
+      <c r="E41" s="7">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-1.17</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-1.32</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-0.15</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
+      <c r="B42" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="5">
+        <v>11700</v>
+      </c>
+      <c r="D42" s="5">
+        <v>11661</v>
+      </c>
+      <c r="E42" s="6">
+        <v>-39</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-19.29</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-19.69</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
+      <c r="B43" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="5">
+        <v>538.25</v>
+      </c>
+      <c r="D43" s="5">
+        <v>527.65</v>
+      </c>
+      <c r="E43" s="6">
+        <v>-10.6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-41.4</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-40.82</v>
-      </c>
-      <c r="E37" s="7">
-        <v>0.58</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
+      <c r="B44" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="5">
+        <v>363.95</v>
+      </c>
+      <c r="D44" s="5">
+        <v>356.6</v>
+      </c>
+      <c r="E44" s="6">
+        <v>-7.35</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-6.64</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-7.17</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-0.53</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
+      <c r="B45" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="5">
+        <v>2020.5</v>
+      </c>
+      <c r="D45" s="5">
+        <v>2025</v>
+      </c>
+      <c r="E45" s="7">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-20.08</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-19.88</v>
-      </c>
-      <c r="E39" s="7">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
+      <c r="B46" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="5">
+        <v>11579</v>
+      </c>
+      <c r="D46" s="5">
+        <v>11500</v>
+      </c>
+      <c r="E46" s="6">
+        <v>-79</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-5.65</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-5.57</v>
-      </c>
-      <c r="E40" s="7">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
+      <c r="B47" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="5">
+        <v>1094.2</v>
+      </c>
+      <c r="D47" s="5">
+        <v>1090.8</v>
+      </c>
+      <c r="E47" s="6">
+        <v>-3.4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-5.6</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-8.99</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-3.39</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
+      <c r="B48" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="5">
+        <v>135.56</v>
+      </c>
+      <c r="D48" s="5">
+        <v>135.6</v>
+      </c>
+      <c r="E48" s="7">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="6">
-        <v>11717</v>
-      </c>
-      <c r="D42" s="6">
-        <v>11700</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-17</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
+      <c r="B49" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="5">
+        <v>67.25</v>
+      </c>
+      <c r="D49" s="5">
+        <v>65.68000000000001</v>
+      </c>
+      <c r="E49" s="6">
+        <v>-1.57</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="6">
-        <v>540.95</v>
-      </c>
-      <c r="D43" s="6">
-        <v>538.25</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-2.7</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
+      <c r="B50" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="5">
+        <v>45.2</v>
+      </c>
+      <c r="D50" s="5">
+        <v>41.97</v>
+      </c>
+      <c r="E50" s="6">
+        <v>-3.23</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B44" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="6">
-        <v>360.35</v>
-      </c>
-      <c r="D44" s="6">
-        <v>363.95</v>
-      </c>
-      <c r="E44" s="7">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
+      <c r="B51" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="5">
+        <v>62.56</v>
+      </c>
+      <c r="D51" s="5">
+        <v>57.36</v>
+      </c>
+      <c r="E51" s="6">
+        <v>-5.2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B45" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="6">
-        <v>2032</v>
-      </c>
-      <c r="D45" s="6">
-        <v>2020.5</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-11.5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
+      <c r="B52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="5">
+        <v>59.92</v>
+      </c>
+      <c r="D52" s="5">
+        <v>60.44</v>
+      </c>
+      <c r="E52" s="7">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B46" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="6">
-        <v>11550</v>
-      </c>
-      <c r="D46" s="6">
-        <v>11579</v>
-      </c>
-      <c r="E46" s="7">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
+      <c r="B53" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="5">
+        <v>67</v>
+      </c>
+      <c r="D53" s="5">
+        <v>63.85</v>
+      </c>
+      <c r="E53" s="6">
+        <v>-3.15</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B47" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="6">
-        <v>1093.3</v>
-      </c>
-      <c r="D47" s="6">
-        <v>1094.2</v>
-      </c>
-      <c r="E47" s="7">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
+      <c r="B54" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="5">
+        <v>55.48</v>
+      </c>
+      <c r="D54" s="5">
+        <v>54.68</v>
+      </c>
+      <c r="E54" s="6">
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B48" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="6">
-        <v>140.61</v>
-      </c>
-      <c r="D48" s="6">
-        <v>135.56</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-5.05</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
+      <c r="B55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="5">
+        <v>40.25</v>
+      </c>
+      <c r="D55" s="5">
+        <v>40.36</v>
+      </c>
+      <c r="E55" s="7">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B49" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" s="6">
-        <v>67.91</v>
-      </c>
-      <c r="D49" s="6">
-        <v>67.25</v>
-      </c>
-      <c r="E49" s="8">
-        <v>-0.66</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
+      <c r="B56" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" s="5">
+        <v>-48.7</v>
+      </c>
+      <c r="D56" s="5">
+        <v>-67.95999999999999</v>
+      </c>
+      <c r="E56" s="6">
+        <v>-19.26</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B50" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="6">
-        <v>46.03</v>
-      </c>
-      <c r="D50" s="6">
-        <v>45.2</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-0.83</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
+      <c r="B57" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C57" s="5">
+        <v>-72.64</v>
+      </c>
+      <c r="D57" s="5">
+        <v>-67.18000000000001</v>
+      </c>
+      <c r="E57" s="7">
+        <v>5.46</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B51" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="6">
-        <v>60.95</v>
-      </c>
-      <c r="D51" s="6">
-        <v>62.56</v>
-      </c>
-      <c r="E51" s="7">
-        <v>1.61</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
+      <c r="B58" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="5">
+        <v>-61.09</v>
+      </c>
+      <c r="D58" s="5">
+        <v>-69.39</v>
+      </c>
+      <c r="E58" s="6">
+        <v>-8.300000000000001</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B52" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="6">
-        <v>61.87</v>
-      </c>
-      <c r="D52" s="6">
-        <v>59.92</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-1.95</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
+      <c r="B59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="5">
+        <v>-63.26</v>
+      </c>
+      <c r="D59" s="5">
+        <v>-40.52</v>
+      </c>
+      <c r="E59" s="7">
+        <v>22.74</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B53" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="6">
-        <v>66.44</v>
-      </c>
-      <c r="D53" s="6">
-        <v>67</v>
-      </c>
-      <c r="E53" s="7">
-        <v>0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
+      <c r="B60" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="5">
+        <v>-59.25</v>
+      </c>
+      <c r="D60" s="5">
+        <v>-67.3</v>
+      </c>
+      <c r="E60" s="6">
+        <v>-8.050000000000001</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B54" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="6">
-        <v>55.32</v>
-      </c>
-      <c r="D54" s="6">
-        <v>55.48</v>
-      </c>
-      <c r="E54" s="7">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
+      <c r="B61" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="5">
+        <v>-31.83</v>
+      </c>
+      <c r="D61" s="5">
+        <v>-76.84999999999999</v>
+      </c>
+      <c r="E61" s="6">
+        <v>-45.02</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B55" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="6">
-        <v>51.35</v>
-      </c>
-      <c r="D55" s="6">
-        <v>40.25</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-11.1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B56" s="5" t="s">
+      <c r="B62" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C56" s="6">
-        <v>-45.87</v>
-      </c>
-      <c r="D56" s="6">
-        <v>-48.7</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-2.83</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C57" s="6">
-        <v>-72.08</v>
-      </c>
-      <c r="D57" s="6">
-        <v>-72.64</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C58" s="6">
-        <v>-63.66</v>
-      </c>
-      <c r="D58" s="6">
-        <v>-61.09</v>
-      </c>
-      <c r="E58" s="7">
-        <v>2.57</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C59" s="6">
-        <v>-31.77</v>
-      </c>
-      <c r="D59" s="6">
-        <v>-63.26</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-31.49</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="6">
-        <v>-35.76</v>
-      </c>
-      <c r="D60" s="6">
-        <v>-59.25</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-23.49</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="6">
-        <v>-36.44</v>
-      </c>
-      <c r="D61" s="6">
-        <v>-31.83</v>
-      </c>
-      <c r="E61" s="7">
-        <v>4.61</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="6">
-        <v>-69.11</v>
-      </c>
-      <c r="D62" s="6">
+      <c r="C62" s="5">
         <v>873.22</v>
       </c>
-      <c r="E62" s="7">
-        <v>942.33</v>
+      <c r="D62" s="5">
+        <v>-46.09</v>
+      </c>
+      <c r="E62" s="6">
+        <v>-919.3099999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2904,60 +2841,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>72</v>
+      <c r="B1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>68.8</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>7</v>
       </c>
-      <c r="D2" s="11">
-        <v>56.8</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>54.9</v>
+      </c>
+      <c r="E2" s="10">
         <v>90</v>
       </c>
-      <c r="F2" s="11">
-        <v>6.2</v>
-      </c>
-      <c r="G2" s="11">
-        <v>8.1</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>5</v>
+      </c>
+      <c r="G2" s="10">
+        <v>6.8</v>
+      </c>
+      <c r="H2" s="10">
         <v>57</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>40</v>
       </c>
     </row>
@@ -3059,49 +2996,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="14">
-        <v>0.2832</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.2526</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.1762</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.1246</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.07139999999999999</v>
-      </c>
-      <c r="F2" s="14">
-        <v>-0.0012</v>
-      </c>
-      <c r="G2" s="14">
-        <v>-0.1789</v>
+      <c r="A2" s="13">
+        <v>0.2786</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.2412</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.1701</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.1255</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.0722</v>
+      </c>
+      <c r="F2" s="13">
+        <v>-0.0108</v>
+      </c>
+      <c r="G2" s="13">
+        <v>-0.1827</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="64">
   <si>
     <t>Symbol</t>
   </si>
@@ -258,14 +258,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -298,13 +298,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -755,8 +755,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -896,10 +896,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>11661</v>
+        <v>11700</v>
       </c>
       <c r="D2">
-        <v>-0.33</v>
+        <v>0.33</v>
       </c>
       <c r="E2">
         <v>11856</v>
@@ -908,46 +908,46 @@
         <v>8082.75</v>
       </c>
       <c r="G2">
-        <v>-1.64</v>
+        <v>-1.32</v>
       </c>
       <c r="H2">
+        <v>44.75</v>
+      </c>
+      <c r="I2">
+        <v>0.33</v>
+      </c>
+      <c r="J2">
+        <v>13.25</v>
+      </c>
+      <c r="K2">
+        <v>16.34</v>
+      </c>
+      <c r="L2">
         <v>44.27</v>
       </c>
-      <c r="I2">
-        <v>0.35</v>
-      </c>
-      <c r="J2">
-        <v>12.96</v>
-      </c>
-      <c r="K2">
-        <v>13.95</v>
-      </c>
-      <c r="L2">
-        <v>43.7</v>
-      </c>
       <c r="M2">
-        <v>27.86</v>
+        <v>28.5</v>
       </c>
       <c r="N2">
         <v>85</v>
       </c>
       <c r="O2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P2">
-        <v>11683.4</v>
+        <v>11691</v>
       </c>
       <c r="Q2">
-        <v>11346.1</v>
+        <v>11408.95</v>
       </c>
       <c r="R2">
-        <v>10577.82</v>
+        <v>10604.58</v>
       </c>
       <c r="S2">
-        <v>9672.469999999999</v>
+        <v>9686.120000000001</v>
       </c>
       <c r="T2">
-        <v>20.56</v>
+        <v>20.79</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -962,43 +962,43 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>65.68000000000001</v>
+        <v>66.52</v>
       </c>
       <c r="Z2">
-        <v>354.6</v>
+        <v>340.33</v>
       </c>
       <c r="AA2">
-        <v>366.83</v>
+        <v>361.53</v>
       </c>
       <c r="AB2">
-        <v>-12.23</v>
+        <v>-21.2</v>
       </c>
       <c r="AC2">
-        <v>6.98</v>
+        <v>4.77</v>
       </c>
       <c r="AD2">
-        <v>12.43</v>
+        <v>7.07</v>
       </c>
       <c r="AE2">
-        <v>228.54</v>
+        <v>221.07</v>
       </c>
       <c r="AF2">
-        <v>-67.95999999999999</v>
+        <v>-42.3</v>
       </c>
       <c r="AG2">
-        <v>12240.02</v>
+        <v>12207.15</v>
       </c>
       <c r="AH2">
-        <v>10452.18</v>
+        <v>10610.75</v>
       </c>
       <c r="AI2">
-        <v>11043.15</v>
+        <v>11061.79</v>
       </c>
       <c r="AJ2" t="s">
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>78.76000000000001</v>
+        <v>76.56999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1009,10 +1009,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>527.65</v>
+        <v>500.6</v>
       </c>
       <c r="D3">
-        <v>-1.97</v>
+        <v>-5.13</v>
       </c>
       <c r="E3">
         <v>670.25</v>
@@ -1021,46 +1021,46 @@
         <v>222.01</v>
       </c>
       <c r="G3">
-        <v>-21.28</v>
+        <v>-25.31</v>
       </c>
       <c r="H3">
-        <v>137.67</v>
+        <v>125.49</v>
       </c>
       <c r="I3">
-        <v>-0.93</v>
+        <v>-6.86</v>
       </c>
       <c r="J3">
-        <v>-7.18</v>
+        <v>-9.59</v>
       </c>
       <c r="K3">
-        <v>-1.82</v>
+        <v>-3.97</v>
       </c>
       <c r="L3">
-        <v>134.57</v>
+        <v>119.39</v>
       </c>
       <c r="M3">
-        <v>17.01</v>
+        <v>16.62</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="P3">
-        <v>538.27</v>
+        <v>530.9</v>
       </c>
       <c r="Q3">
-        <v>535.9</v>
+        <v>534.65</v>
       </c>
       <c r="R3">
-        <v>573.96</v>
+        <v>572.79</v>
       </c>
       <c r="S3">
-        <v>414.3</v>
+        <v>415.46</v>
       </c>
       <c r="T3">
-        <v>27.36</v>
+        <v>20.49</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1075,43 +1075,43 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>41.97</v>
+        <v>35.07</v>
       </c>
       <c r="Z3">
-        <v>-10.85</v>
+        <v>-13.06</v>
       </c>
       <c r="AA3">
-        <v>-12.12</v>
+        <v>-12.31</v>
       </c>
       <c r="AB3">
-        <v>1.27</v>
+        <v>-0.75</v>
       </c>
       <c r="AC3">
-        <v>61.62</v>
+        <v>35.1</v>
       </c>
       <c r="AD3">
-        <v>78.13</v>
+        <v>60.01</v>
       </c>
       <c r="AE3">
-        <v>20.87</v>
+        <v>21.85</v>
       </c>
       <c r="AF3">
-        <v>-67.18000000000001</v>
+        <v>41.39</v>
       </c>
       <c r="AG3">
-        <v>553.88</v>
+        <v>558.25</v>
       </c>
       <c r="AH3">
-        <v>517.92</v>
+        <v>511.05</v>
       </c>
       <c r="AI3">
-        <v>594.16</v>
+        <v>580.8099999999999</v>
       </c>
       <c r="AJ3" t="s">
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>16.6</v>
+        <v>19.73</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1122,10 +1122,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>356.6</v>
+        <v>362.4</v>
       </c>
       <c r="D4">
-        <v>-2.02</v>
+        <v>1.63</v>
       </c>
       <c r="E4">
         <v>604.85</v>
@@ -1134,46 +1134,46 @@
         <v>303.75</v>
       </c>
       <c r="G4">
-        <v>-41.04</v>
+        <v>-40.08</v>
       </c>
       <c r="H4">
-        <v>17.4</v>
+        <v>19.31</v>
       </c>
       <c r="I4">
-        <v>-6.77</v>
+        <v>-2.36</v>
       </c>
       <c r="J4">
-        <v>8.039999999999999</v>
+        <v>7.89</v>
       </c>
       <c r="K4">
-        <v>-9.289999999999999</v>
+        <v>1.57</v>
       </c>
       <c r="L4">
-        <v>-42.01</v>
+        <v>-37.99</v>
       </c>
       <c r="M4">
-        <v>-18.27</v>
+        <v>-17.92</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
       <c r="O4">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="P4">
-        <v>363.03</v>
+        <v>361.28</v>
       </c>
       <c r="Q4">
-        <v>343.32</v>
+        <v>344.86</v>
       </c>
       <c r="R4">
-        <v>330.68</v>
+        <v>331.86</v>
       </c>
       <c r="S4">
-        <v>395.79</v>
+        <v>394.96</v>
       </c>
       <c r="T4">
-        <v>-9.9</v>
+        <v>-8.24</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1188,34 +1188,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>57.36</v>
+        <v>60.17</v>
       </c>
       <c r="Z4">
-        <v>9.1</v>
+        <v>9.09</v>
       </c>
       <c r="AA4">
-        <v>6.93</v>
+        <v>7.37</v>
       </c>
       <c r="AB4">
-        <v>2.16</v>
+        <v>1.73</v>
       </c>
       <c r="AC4">
-        <v>41.61</v>
+        <v>40.35</v>
       </c>
       <c r="AD4">
-        <v>48.17</v>
+        <v>43.31</v>
       </c>
       <c r="AE4">
-        <v>14.04</v>
+        <v>13.98</v>
       </c>
       <c r="AF4">
-        <v>-69.39</v>
+        <v>-62.4</v>
       </c>
       <c r="AG4">
-        <v>377.71</v>
+        <v>379.79</v>
       </c>
       <c r="AH4">
-        <v>308.93</v>
+        <v>309.94</v>
       </c>
       <c r="AI4">
         <v>335.86</v>
@@ -1224,7 +1224,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>59.15</v>
+        <v>57.87</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1235,10 +1235,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>2025</v>
+        <v>2008.3</v>
       </c>
       <c r="D5">
-        <v>0.22</v>
+        <v>-0.82</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1247,46 +1247,46 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-6.96</v>
+        <v>-7.73</v>
       </c>
       <c r="H5">
-        <v>24.1</v>
+        <v>23.07</v>
       </c>
       <c r="I5">
-        <v>-2.92</v>
+        <v>-0.03</v>
       </c>
       <c r="J5">
-        <v>9.48</v>
+        <v>9.23</v>
       </c>
       <c r="K5">
-        <v>17.18</v>
+        <v>14.56</v>
       </c>
       <c r="L5">
-        <v>5.8</v>
+        <v>4.64</v>
       </c>
       <c r="M5">
-        <v>7.22</v>
+        <v>6.71</v>
       </c>
       <c r="N5">
         <v>57</v>
       </c>
       <c r="O5">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="P5">
-        <v>2021.54</v>
+        <v>2021.42</v>
       </c>
       <c r="Q5">
-        <v>1972.16</v>
+        <v>1979.87</v>
       </c>
       <c r="R5">
-        <v>1862.67</v>
+        <v>1868.64</v>
       </c>
       <c r="S5">
-        <v>1911.97</v>
+        <v>1911.16</v>
       </c>
       <c r="T5">
-        <v>5.91</v>
+        <v>5.08</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1301,34 +1301,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>60.44</v>
+        <v>57.43</v>
       </c>
       <c r="Z5">
-        <v>51.34</v>
+        <v>47.15</v>
       </c>
       <c r="AA5">
-        <v>53.66</v>
+        <v>52.36</v>
       </c>
       <c r="AB5">
-        <v>-2.32</v>
+        <v>-5.21</v>
       </c>
       <c r="AC5">
-        <v>18.07</v>
+        <v>8.81</v>
       </c>
       <c r="AD5">
-        <v>21.03</v>
+        <v>16.57</v>
       </c>
       <c r="AE5">
-        <v>45.02</v>
+        <v>43.73</v>
       </c>
       <c r="AF5">
-        <v>-40.52</v>
+        <v>-36.61</v>
       </c>
       <c r="AG5">
-        <v>2145.52</v>
+        <v>2144.61</v>
       </c>
       <c r="AH5">
-        <v>1798.79</v>
+        <v>1815.13</v>
       </c>
       <c r="AI5">
         <v>1958.53</v>
@@ -1337,7 +1337,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>31.83</v>
+        <v>29.67</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1348,10 +1348,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>11500</v>
+        <v>11475</v>
       </c>
       <c r="D6">
-        <v>-0.68</v>
+        <v>-0.22</v>
       </c>
       <c r="E6">
         <v>14451.52</v>
@@ -1360,46 +1360,46 @@
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-20.42</v>
+        <v>-20.6</v>
       </c>
       <c r="H6">
-        <v>31.49</v>
+        <v>31.2</v>
       </c>
       <c r="I6">
-        <v>0.99</v>
+        <v>1.88</v>
       </c>
       <c r="J6">
-        <v>9.199999999999999</v>
+        <v>10.16</v>
       </c>
       <c r="K6">
-        <v>11.56</v>
+        <v>10.69</v>
       </c>
       <c r="L6">
-        <v>-16.13</v>
+        <v>-15.94</v>
       </c>
       <c r="M6">
-        <v>24.12</v>
+        <v>24.65</v>
       </c>
       <c r="N6">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="O6">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="P6">
-        <v>11472.6</v>
+        <v>11515</v>
       </c>
       <c r="Q6">
-        <v>11055.3</v>
+        <v>11109.15</v>
       </c>
       <c r="R6">
-        <v>10721.86</v>
+        <v>10748.82</v>
       </c>
       <c r="S6">
-        <v>10787.75</v>
+        <v>10780.36</v>
       </c>
       <c r="T6">
-        <v>6.6</v>
+        <v>6.44</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1414,34 +1414,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>63.85</v>
+        <v>62.84</v>
       </c>
       <c r="Z6">
-        <v>254.54</v>
+        <v>246.71</v>
       </c>
       <c r="AA6">
-        <v>219.75</v>
+        <v>225.14</v>
       </c>
       <c r="AB6">
-        <v>34.79</v>
+        <v>21.57</v>
       </c>
       <c r="AC6">
-        <v>56.29</v>
+        <v>44.54</v>
       </c>
       <c r="AD6">
-        <v>60.96</v>
+        <v>55.56</v>
       </c>
       <c r="AE6">
-        <v>236.79</v>
+        <v>230.88</v>
       </c>
       <c r="AF6">
-        <v>-67.3</v>
+        <v>-39.92</v>
       </c>
       <c r="AG6">
-        <v>11974.17</v>
+        <v>11991.32</v>
       </c>
       <c r="AH6">
-        <v>10136.43</v>
+        <v>10226.98</v>
       </c>
       <c r="AI6">
         <v>10779.62</v>
@@ -1450,7 +1450,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>49.03</v>
+        <v>48.42</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1461,10 +1461,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>1090.8</v>
+        <v>1087</v>
       </c>
       <c r="D7">
-        <v>-0.31</v>
+        <v>-0.35</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1473,46 +1473,46 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-5.87</v>
+        <v>-6.2</v>
       </c>
       <c r="H7">
-        <v>36.09</v>
+        <v>35.61</v>
       </c>
       <c r="I7">
-        <v>-4.72</v>
+        <v>0.83</v>
       </c>
       <c r="J7">
-        <v>6.81</v>
+        <v>4.76</v>
       </c>
       <c r="K7">
-        <v>19.81</v>
+        <v>18.01</v>
       </c>
       <c r="L7">
-        <v>24.08</v>
+        <v>23.92</v>
       </c>
       <c r="M7">
-        <v>12.55</v>
+        <v>11.69</v>
       </c>
       <c r="N7">
         <v>71</v>
       </c>
       <c r="O7">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="P7">
-        <v>1091.7</v>
+        <v>1093.5</v>
       </c>
       <c r="Q7">
-        <v>1085.62</v>
+        <v>1087.15</v>
       </c>
       <c r="R7">
-        <v>1016.72</v>
+        <v>1020.97</v>
       </c>
       <c r="S7">
-        <v>974.14</v>
+        <v>974.15</v>
       </c>
       <c r="T7">
-        <v>11.98</v>
+        <v>11.58</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1527,34 +1527,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>54.68</v>
+        <v>53.74</v>
       </c>
       <c r="Z7">
-        <v>24.74</v>
+        <v>22.11</v>
       </c>
       <c r="AA7">
-        <v>29.86</v>
+        <v>28.31</v>
       </c>
       <c r="AB7">
-        <v>-5.13</v>
+        <v>-6.2</v>
       </c>
       <c r="AC7">
-        <v>15.17</v>
+        <v>9.74</v>
       </c>
       <c r="AD7">
-        <v>18.52</v>
+        <v>15.56</v>
       </c>
       <c r="AE7">
-        <v>28.12</v>
+        <v>27.06</v>
       </c>
       <c r="AF7">
-        <v>-76.84999999999999</v>
+        <v>-58.65</v>
       </c>
       <c r="AG7">
-        <v>1171.97</v>
+        <v>1172.39</v>
       </c>
       <c r="AH7">
-        <v>999.26</v>
+        <v>1001.91</v>
       </c>
       <c r="AI7">
         <v>1067.72</v>
@@ -1563,7 +1563,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>26.22</v>
+        <v>24.26</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1574,10 +1574,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>135.6</v>
+        <v>134.14</v>
       </c>
       <c r="D8">
-        <v>0.03</v>
+        <v>-1.08</v>
       </c>
       <c r="E8">
         <v>148.95</v>
@@ -1586,46 +1586,46 @@
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>-8.960000000000001</v>
+        <v>-9.94</v>
       </c>
       <c r="H8">
-        <v>16.94</v>
+        <v>15.68</v>
       </c>
       <c r="I8">
-        <v>-5.37</v>
+        <v>-6.34</v>
       </c>
       <c r="J8">
-        <v>-4.27</v>
+        <v>-8.25</v>
       </c>
       <c r="K8">
-        <v>-3.84</v>
+        <v>-9.94</v>
       </c>
       <c r="L8">
-        <v>9.34</v>
+        <v>-1.51</v>
       </c>
       <c r="M8">
-        <v>-1.08</v>
+        <v>-2.26</v>
       </c>
       <c r="N8">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="O8">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="P8">
-        <v>139.23</v>
+        <v>137.41</v>
       </c>
       <c r="Q8">
-        <v>141.14</v>
+        <v>140.56</v>
       </c>
       <c r="R8">
-        <v>137.53</v>
+        <v>137.42</v>
       </c>
       <c r="S8">
-        <v>133.76</v>
+        <v>133.77</v>
       </c>
       <c r="T8">
-        <v>1.38</v>
+        <v>0.28</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1640,34 +1640,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>40.36</v>
+        <v>37.64</v>
       </c>
       <c r="Z8">
-        <v>0.24</v>
+        <v>-0.23</v>
       </c>
       <c r="AA8">
-        <v>1.06</v>
+        <v>0.8</v>
       </c>
       <c r="AB8">
-        <v>-0.82</v>
+        <v>-1.03</v>
       </c>
       <c r="AC8">
-        <v>2.38</v>
+        <v>0.18</v>
       </c>
       <c r="AD8">
-        <v>12.16</v>
+        <v>3.97</v>
       </c>
       <c r="AE8">
-        <v>4.34</v>
+        <v>4.28</v>
       </c>
       <c r="AF8">
-        <v>-46.09</v>
+        <v>-62.13</v>
       </c>
       <c r="AG8">
-        <v>146.85</v>
+        <v>146.66</v>
       </c>
       <c r="AH8">
-        <v>135.42</v>
+        <v>134.46</v>
       </c>
       <c r="AI8">
         <v>131.91</v>
@@ -1676,7 +1676,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>30.87</v>
+        <v>34.67</v>
       </c>
     </row>
   </sheetData>
@@ -1817,7 +1817,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1874,13 +1874,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>15.09</v>
+        <v>12.96</v>
       </c>
       <c r="D7" s="5">
-        <v>12.96</v>
+        <v>13.25</v>
       </c>
       <c r="E7" s="6">
-        <v>-2.13</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1891,13 +1891,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-8.85</v>
+        <v>-7.18</v>
       </c>
       <c r="D8" s="5">
-        <v>-7.18</v>
+        <v>-9.59</v>
       </c>
       <c r="E8" s="7">
-        <v>1.67</v>
+        <v>-2.41</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1908,13 +1908,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>10.64</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="D9" s="5">
-        <v>8.039999999999999</v>
-      </c>
-      <c r="E9" s="6">
-        <v>-2.6</v>
+        <v>7.89</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-0.15</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1925,13 +1925,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>8.09</v>
+        <v>9.48</v>
       </c>
       <c r="D10" s="5">
-        <v>9.48</v>
+        <v>9.23</v>
       </c>
       <c r="E10" s="7">
-        <v>1.39</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1942,13 +1942,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>10.42</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D11" s="5">
-        <v>9.199999999999999</v>
+        <v>10.16</v>
       </c>
       <c r="E11" s="6">
-        <v>-1.22</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1959,13 +1959,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="5">
-        <v>8.699999999999999</v>
+        <v>6.81</v>
       </c>
       <c r="D12" s="5">
-        <v>6.81</v>
-      </c>
-      <c r="E12" s="6">
-        <v>-1.89</v>
+        <v>4.76</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-2.05</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1976,13 +1976,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="5">
-        <v>-0.85</v>
+        <v>-4.27</v>
       </c>
       <c r="D13" s="5">
-        <v>-4.27</v>
-      </c>
-      <c r="E13" s="6">
-        <v>-3.42</v>
+        <v>-8.25</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-3.98</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1993,13 +1993,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="5">
-        <v>-0.85</v>
+        <v>0.35</v>
       </c>
       <c r="D14" s="5">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="E14" s="7">
-        <v>1.2</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2010,13 +2010,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="5">
-        <v>1.48</v>
+        <v>-0.93</v>
       </c>
       <c r="D15" s="5">
-        <v>-0.93</v>
-      </c>
-      <c r="E15" s="6">
-        <v>-2.41</v>
+        <v>-6.86</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-5.93</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2027,13 +2027,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>4.55</v>
+        <v>-6.77</v>
       </c>
       <c r="D16" s="5">
-        <v>-6.77</v>
+        <v>-2.36</v>
       </c>
       <c r="E16" s="6">
-        <v>-11.32</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2044,13 +2044,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="5">
-        <v>-3.14</v>
+        <v>-2.92</v>
       </c>
       <c r="D17" s="5">
-        <v>-2.92</v>
-      </c>
-      <c r="E17" s="7">
-        <v>0.22</v>
+        <v>-0.03</v>
+      </c>
+      <c r="E17" s="6">
+        <v>2.89</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2061,13 +2061,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="5">
-        <v>0.72</v>
+        <v>0.99</v>
       </c>
       <c r="D18" s="5">
-        <v>0.99</v>
-      </c>
-      <c r="E18" s="7">
-        <v>0.27</v>
+        <v>1.88</v>
+      </c>
+      <c r="E18" s="6">
+        <v>0.89</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2078,13 +2078,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="5">
-        <v>-5.57</v>
+        <v>-4.72</v>
       </c>
       <c r="D19" s="5">
-        <v>-4.72</v>
-      </c>
-      <c r="E19" s="7">
-        <v>0.85</v>
+        <v>0.83</v>
+      </c>
+      <c r="E19" s="6">
+        <v>5.55</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2095,13 +2095,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="5">
-        <v>-4.65</v>
+        <v>-5.37</v>
       </c>
       <c r="D20" s="5">
-        <v>-5.37</v>
-      </c>
-      <c r="E20" s="6">
-        <v>-0.72</v>
+        <v>-6.34</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.97</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2112,13 +2112,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="5">
-        <v>45.07</v>
+        <v>43.7</v>
       </c>
       <c r="D21" s="5">
-        <v>43.7</v>
+        <v>44.27</v>
       </c>
       <c r="E21" s="6">
-        <v>-1.37</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2129,13 +2129,13 @@
         <v>11</v>
       </c>
       <c r="C22" s="5">
-        <v>138.97</v>
+        <v>134.57</v>
       </c>
       <c r="D22" s="5">
-        <v>134.57</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-4.4</v>
+        <v>119.39</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-15.18</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2146,13 +2146,13 @@
         <v>11</v>
       </c>
       <c r="C23" s="5">
-        <v>-38.92</v>
+        <v>-42.01</v>
       </c>
       <c r="D23" s="5">
-        <v>-42.01</v>
+        <v>-37.99</v>
       </c>
       <c r="E23" s="6">
-        <v>-3.09</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2163,13 +2163,13 @@
         <v>11</v>
       </c>
       <c r="C24" s="5">
-        <v>5.02</v>
+        <v>5.8</v>
       </c>
       <c r="D24" s="5">
-        <v>5.8</v>
+        <v>4.64</v>
       </c>
       <c r="E24" s="7">
-        <v>0.78</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2180,13 +2180,13 @@
         <v>11</v>
       </c>
       <c r="C25" s="5">
-        <v>-14.48</v>
+        <v>-16.13</v>
       </c>
       <c r="D25" s="5">
-        <v>-16.13</v>
+        <v>-15.94</v>
       </c>
       <c r="E25" s="6">
-        <v>-1.65</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2197,13 +2197,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="5">
-        <v>24.82</v>
+        <v>24.08</v>
       </c>
       <c r="D26" s="5">
-        <v>24.08</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-0.74</v>
+        <v>23.92</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2214,13 +2214,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="5">
-        <v>5.13</v>
+        <v>9.34</v>
       </c>
       <c r="D27" s="5">
-        <v>9.34</v>
+        <v>-1.51</v>
       </c>
       <c r="E27" s="7">
-        <v>4.21</v>
+        <v>-10.85</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2231,13 +2231,13 @@
         <v>10</v>
       </c>
       <c r="C28" s="5">
-        <v>13.53</v>
+        <v>13.95</v>
       </c>
       <c r="D28" s="5">
-        <v>13.95</v>
-      </c>
-      <c r="E28" s="7">
-        <v>0.42</v>
+        <v>16.34</v>
+      </c>
+      <c r="E28" s="6">
+        <v>2.39</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2248,13 +2248,13 @@
         <v>10</v>
       </c>
       <c r="C29" s="5">
-        <v>3.82</v>
+        <v>-1.82</v>
       </c>
       <c r="D29" s="5">
-        <v>-1.82</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-5.64</v>
+        <v>-3.97</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-2.15</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2265,13 +2265,13 @@
         <v>10</v>
       </c>
       <c r="C30" s="5">
-        <v>-6.6</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="D30" s="5">
-        <v>-9.289999999999999</v>
+        <v>1.57</v>
       </c>
       <c r="E30" s="6">
-        <v>-2.69</v>
+        <v>10.86</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2282,13 +2282,13 @@
         <v>10</v>
       </c>
       <c r="C31" s="5">
-        <v>16.11</v>
+        <v>17.18</v>
       </c>
       <c r="D31" s="5">
-        <v>17.18</v>
+        <v>14.56</v>
       </c>
       <c r="E31" s="7">
-        <v>1.07</v>
+        <v>-2.62</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2299,13 +2299,13 @@
         <v>10</v>
       </c>
       <c r="C32" s="5">
-        <v>11.8</v>
+        <v>11.56</v>
       </c>
       <c r="D32" s="5">
-        <v>11.56</v>
-      </c>
-      <c r="E32" s="6">
-        <v>-0.24</v>
+        <v>10.69</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-0.87</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2316,13 +2316,13 @@
         <v>10</v>
       </c>
       <c r="C33" s="5">
-        <v>19.96</v>
+        <v>19.81</v>
       </c>
       <c r="D33" s="5">
-        <v>19.81</v>
-      </c>
-      <c r="E33" s="6">
-        <v>-0.15</v>
+        <v>18.01</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-1.8</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2333,13 +2333,13 @@
         <v>10</v>
       </c>
       <c r="C34" s="5">
-        <v>-1.59</v>
+        <v>-3.84</v>
       </c>
       <c r="D34" s="5">
-        <v>-3.84</v>
-      </c>
-      <c r="E34" s="6">
-        <v>-2.25</v>
+        <v>-9.94</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-6.1</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2350,13 +2350,13 @@
         <v>6</v>
       </c>
       <c r="C35" s="5">
+        <v>-1.64</v>
+      </c>
+      <c r="D35" s="5">
         <v>-1.32</v>
       </c>
-      <c r="D35" s="5">
-        <v>-1.64</v>
-      </c>
       <c r="E35" s="6">
-        <v>-0.32</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2367,13 +2367,13 @@
         <v>6</v>
       </c>
       <c r="C36" s="5">
-        <v>-19.69</v>
+        <v>-21.28</v>
       </c>
       <c r="D36" s="5">
-        <v>-21.28</v>
-      </c>
-      <c r="E36" s="6">
-        <v>-1.59</v>
+        <v>-25.31</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-4.03</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2384,13 +2384,13 @@
         <v>6</v>
       </c>
       <c r="C37" s="5">
-        <v>-40.82</v>
+        <v>-41.04</v>
       </c>
       <c r="D37" s="5">
-        <v>-41.04</v>
+        <v>-40.08</v>
       </c>
       <c r="E37" s="6">
-        <v>-0.22</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2401,13 +2401,13 @@
         <v>6</v>
       </c>
       <c r="C38" s="5">
-        <v>-7.17</v>
+        <v>-6.96</v>
       </c>
       <c r="D38" s="5">
-        <v>-6.96</v>
+        <v>-7.73</v>
       </c>
       <c r="E38" s="7">
-        <v>0.21</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2418,13 +2418,13 @@
         <v>6</v>
       </c>
       <c r="C39" s="5">
-        <v>-19.88</v>
+        <v>-20.42</v>
       </c>
       <c r="D39" s="5">
-        <v>-20.42</v>
-      </c>
-      <c r="E39" s="6">
-        <v>-0.54</v>
+        <v>-20.6</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-0.18</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2435,13 +2435,13 @@
         <v>6</v>
       </c>
       <c r="C40" s="5">
-        <v>-5.57</v>
+        <v>-5.87</v>
       </c>
       <c r="D40" s="5">
-        <v>-5.87</v>
-      </c>
-      <c r="E40" s="6">
-        <v>-0.3</v>
+        <v>-6.2</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-0.33</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2452,13 +2452,13 @@
         <v>6</v>
       </c>
       <c r="C41" s="5">
-        <v>-8.99</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="D41" s="5">
-        <v>-8.960000000000001</v>
+        <v>-9.94</v>
       </c>
       <c r="E41" s="7">
-        <v>0.03</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2469,13 +2469,13 @@
         <v>2</v>
       </c>
       <c r="C42" s="5">
+        <v>11661</v>
+      </c>
+      <c r="D42" s="5">
         <v>11700</v>
       </c>
-      <c r="D42" s="5">
-        <v>11661</v>
-      </c>
       <c r="E42" s="6">
-        <v>-39</v>
+        <v>39</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2486,13 +2486,13 @@
         <v>2</v>
       </c>
       <c r="C43" s="5">
-        <v>538.25</v>
+        <v>527.65</v>
       </c>
       <c r="D43" s="5">
-        <v>527.65</v>
-      </c>
-      <c r="E43" s="6">
-        <v>-10.6</v>
+        <v>500.6</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-27.05</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2503,13 +2503,13 @@
         <v>2</v>
       </c>
       <c r="C44" s="5">
-        <v>363.95</v>
+        <v>356.6</v>
       </c>
       <c r="D44" s="5">
-        <v>356.6</v>
+        <v>362.4</v>
       </c>
       <c r="E44" s="6">
-        <v>-7.35</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2520,13 +2520,13 @@
         <v>2</v>
       </c>
       <c r="C45" s="5">
-        <v>2020.5</v>
+        <v>2025</v>
       </c>
       <c r="D45" s="5">
-        <v>2025</v>
+        <v>2008.3</v>
       </c>
       <c r="E45" s="7">
-        <v>4.5</v>
+        <v>-16.7</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2537,13 +2537,13 @@
         <v>2</v>
       </c>
       <c r="C46" s="5">
-        <v>11579</v>
+        <v>11500</v>
       </c>
       <c r="D46" s="5">
-        <v>11500</v>
-      </c>
-      <c r="E46" s="6">
-        <v>-79</v>
+        <v>11475</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-25</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2554,13 +2554,13 @@
         <v>2</v>
       </c>
       <c r="C47" s="5">
-        <v>1094.2</v>
+        <v>1090.8</v>
       </c>
       <c r="D47" s="5">
-        <v>1090.8</v>
-      </c>
-      <c r="E47" s="6">
-        <v>-3.4</v>
+        <v>1087</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-3.8</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2571,251 +2571,285 @@
         <v>2</v>
       </c>
       <c r="C48" s="5">
-        <v>135.56</v>
+        <v>135.6</v>
       </c>
       <c r="D48" s="5">
-        <v>135.6</v>
+        <v>134.14</v>
       </c>
       <c r="E48" s="7">
-        <v>0.04</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C49" s="5">
-        <v>67.25</v>
+        <v>29</v>
       </c>
       <c r="D49" s="5">
-        <v>65.68000000000001</v>
+        <v>43</v>
       </c>
       <c r="E49" s="6">
-        <v>-1.57</v>
+        <v>14</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C50" s="5">
-        <v>45.2</v>
+        <v>43</v>
       </c>
       <c r="D50" s="5">
-        <v>41.97</v>
-      </c>
-      <c r="E50" s="6">
-        <v>-3.23</v>
+        <v>29</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-14</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C51" s="5">
-        <v>62.56</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="D51" s="5">
-        <v>57.36</v>
+        <v>66.52</v>
       </c>
       <c r="E51" s="6">
-        <v>-5.2</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C52" s="5">
-        <v>59.92</v>
+        <v>41.97</v>
       </c>
       <c r="D52" s="5">
-        <v>60.44</v>
+        <v>35.07</v>
       </c>
       <c r="E52" s="7">
-        <v>0.52</v>
+        <v>-6.9</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C53" s="5">
-        <v>67</v>
+        <v>57.36</v>
       </c>
       <c r="D53" s="5">
-        <v>63.85</v>
+        <v>60.17</v>
       </c>
       <c r="E53" s="6">
-        <v>-3.15</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C54" s="5">
-        <v>55.48</v>
+        <v>60.44</v>
       </c>
       <c r="D54" s="5">
-        <v>54.68</v>
-      </c>
-      <c r="E54" s="6">
-        <v>-0.8</v>
+        <v>57.43</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-3.01</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C55" s="5">
-        <v>40.25</v>
+        <v>63.85</v>
       </c>
       <c r="D55" s="5">
-        <v>40.36</v>
+        <v>62.84</v>
       </c>
       <c r="E55" s="7">
-        <v>0.11</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C56" s="5">
-        <v>-48.7</v>
+        <v>54.68</v>
       </c>
       <c r="D56" s="5">
-        <v>-67.95999999999999</v>
-      </c>
-      <c r="E56" s="6">
-        <v>-19.26</v>
+        <v>53.74</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C57" s="5">
-        <v>-72.64</v>
+        <v>40.36</v>
       </c>
       <c r="D57" s="5">
-        <v>-67.18000000000001</v>
+        <v>37.64</v>
       </c>
       <c r="E57" s="7">
-        <v>5.46</v>
+        <v>-2.72</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C58" s="5">
-        <v>-61.09</v>
+        <v>-67.95999999999999</v>
       </c>
       <c r="D58" s="5">
-        <v>-69.39</v>
+        <v>-42.3</v>
       </c>
       <c r="E58" s="6">
-        <v>-8.300000000000001</v>
+        <v>25.66</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C59" s="5">
-        <v>-63.26</v>
+        <v>-67.18000000000001</v>
       </c>
       <c r="D59" s="5">
-        <v>-40.52</v>
-      </c>
-      <c r="E59" s="7">
-        <v>22.74</v>
+        <v>41.39</v>
+      </c>
+      <c r="E59" s="6">
+        <v>108.57</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C60" s="5">
-        <v>-59.25</v>
+        <v>-69.39</v>
       </c>
       <c r="D60" s="5">
-        <v>-67.3</v>
+        <v>-62.4</v>
       </c>
       <c r="E60" s="6">
-        <v>-8.050000000000001</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C61" s="5">
-        <v>-31.83</v>
+        <v>-40.52</v>
       </c>
       <c r="D61" s="5">
-        <v>-76.84999999999999</v>
+        <v>-36.61</v>
       </c>
       <c r="E61" s="6">
-        <v>-45.02</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C62" s="5">
-        <v>873.22</v>
+        <v>-67.3</v>
       </c>
       <c r="D62" s="5">
+        <v>-39.92</v>
+      </c>
+      <c r="E62" s="6">
+        <v>27.38</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="5">
+        <v>-76.84999999999999</v>
+      </c>
+      <c r="D63" s="5">
+        <v>-58.65</v>
+      </c>
+      <c r="E63" s="6">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="5">
         <v>-46.09</v>
       </c>
-      <c r="E62" s="6">
-        <v>-919.3099999999999</v>
+      <c r="D64" s="5">
+        <v>-62.13</v>
+      </c>
+      <c r="E64" s="7">
+        <v>-16.04</v>
       </c>
     </row>
   </sheetData>
@@ -2880,13 +2914,13 @@
         <v>7</v>
       </c>
       <c r="D2" s="10">
-        <v>54.9</v>
+        <v>53.3</v>
       </c>
       <c r="E2" s="10">
         <v>90</v>
       </c>
       <c r="F2" s="10">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="G2" s="10">
         <v>6.8</v>
@@ -3020,25 +3054,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="13">
-        <v>0.2786</v>
+        <v>0.285</v>
       </c>
       <c r="B2" s="13">
-        <v>0.2412</v>
+        <v>0.2465</v>
       </c>
       <c r="C2" s="13">
-        <v>0.1701</v>
+        <v>0.1662</v>
       </c>
       <c r="D2" s="13">
-        <v>0.1255</v>
+        <v>0.1169</v>
       </c>
       <c r="E2" s="13">
-        <v>0.0722</v>
+        <v>0.06709999999999999</v>
       </c>
       <c r="F2" s="13">
-        <v>-0.0108</v>
+        <v>-0.0226</v>
       </c>
       <c r="G2" s="13">
-        <v>-0.1827</v>
+        <v>-0.1792</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="72">
   <si>
     <t>Symbol</t>
   </si>
@@ -172,7 +172,31 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>50 DMA &gt; 200 DMA</t>
+  </si>
+  <si>
+    <t>No → Yes</t>
+  </si>
+  <si>
+    <t>🟢 GOLDEN CROSS</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -374,17 +398,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -756,7 +781,8 @@
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
     <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="19" width="10.7109375" customWidth="1"/>
+    <col min="17" max="18" width="10.7109375" customWidth="1"/>
+    <col min="19" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -899,7 +925,7 @@
         <v>11700</v>
       </c>
       <c r="D2">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>11856</v>
@@ -914,40 +940,40 @@
         <v>44.75</v>
       </c>
       <c r="I2">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="J2">
-        <v>13.25</v>
+        <v>12.04</v>
       </c>
       <c r="K2">
-        <v>16.34</v>
+        <v>16.26</v>
       </c>
       <c r="L2">
-        <v>44.27</v>
+        <v>43.38</v>
       </c>
       <c r="M2">
-        <v>28.5</v>
+        <v>28.07</v>
       </c>
       <c r="N2">
         <v>85</v>
       </c>
       <c r="O2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P2">
-        <v>11691</v>
+        <v>11695.6</v>
       </c>
       <c r="Q2">
-        <v>11408.95</v>
+        <v>11467.82</v>
       </c>
       <c r="R2">
-        <v>10604.58</v>
+        <v>10631.74</v>
       </c>
       <c r="S2">
-        <v>9686.120000000001</v>
+        <v>9699.959999999999</v>
       </c>
       <c r="T2">
-        <v>20.79</v>
+        <v>20.62</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -965,40 +991,40 @@
         <v>66.52</v>
       </c>
       <c r="Z2">
-        <v>340.33</v>
+        <v>325.27</v>
       </c>
       <c r="AA2">
-        <v>361.53</v>
+        <v>354.28</v>
       </c>
       <c r="AB2">
-        <v>-21.2</v>
+        <v>-29.01</v>
       </c>
       <c r="AC2">
-        <v>4.77</v>
+        <v>4.33</v>
       </c>
       <c r="AD2">
-        <v>7.07</v>
+        <v>5.36</v>
       </c>
       <c r="AE2">
-        <v>221.07</v>
+        <v>213.85</v>
       </c>
       <c r="AF2">
-        <v>-42.3</v>
+        <v>-55.74</v>
       </c>
       <c r="AG2">
-        <v>12207.15</v>
+        <v>12156.98</v>
       </c>
       <c r="AH2">
-        <v>10610.75</v>
+        <v>10778.67</v>
       </c>
       <c r="AI2">
-        <v>11061.79</v>
+        <v>11083.45</v>
       </c>
       <c r="AJ2" t="s">
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>76.56999999999999</v>
+        <v>74.67</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1009,10 +1035,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>500.6</v>
+        <v>481.4</v>
       </c>
       <c r="D3">
-        <v>-5.13</v>
+        <v>-3.84</v>
       </c>
       <c r="E3">
         <v>670.25</v>
@@ -1021,46 +1047,46 @@
         <v>222.01</v>
       </c>
       <c r="G3">
-        <v>-25.31</v>
+        <v>-28.18</v>
       </c>
       <c r="H3">
-        <v>125.49</v>
+        <v>116.84</v>
       </c>
       <c r="I3">
-        <v>-6.86</v>
+        <v>-12</v>
       </c>
       <c r="J3">
-        <v>-9.59</v>
+        <v>-8.42</v>
       </c>
       <c r="K3">
-        <v>-3.97</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="L3">
-        <v>119.39</v>
+        <v>107.56</v>
       </c>
       <c r="M3">
-        <v>16.62</v>
+        <v>15.51</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="P3">
-        <v>530.9</v>
+        <v>517.77</v>
       </c>
       <c r="Q3">
-        <v>534.65</v>
+        <v>531.77</v>
       </c>
       <c r="R3">
-        <v>572.79</v>
+        <v>571.38</v>
       </c>
       <c r="S3">
-        <v>415.46</v>
+        <v>416.52</v>
       </c>
       <c r="T3">
-        <v>20.49</v>
+        <v>15.58</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1075,43 +1101,43 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>35.07</v>
+        <v>31.16</v>
       </c>
       <c r="Z3">
-        <v>-13.06</v>
+        <v>-16.17</v>
       </c>
       <c r="AA3">
-        <v>-12.31</v>
+        <v>-13.08</v>
       </c>
       <c r="AB3">
-        <v>-0.75</v>
+        <v>-3.09</v>
       </c>
       <c r="AC3">
-        <v>35.1</v>
+        <v>11.65</v>
       </c>
       <c r="AD3">
-        <v>60.01</v>
+        <v>36.12</v>
       </c>
       <c r="AE3">
-        <v>21.85</v>
+        <v>22.77</v>
       </c>
       <c r="AF3">
-        <v>41.39</v>
+        <v>164.94</v>
       </c>
       <c r="AG3">
-        <v>558.25</v>
+        <v>565.16</v>
       </c>
       <c r="AH3">
-        <v>511.05</v>
+        <v>498.38</v>
       </c>
       <c r="AI3">
-        <v>580.8099999999999</v>
+        <v>562.11</v>
       </c>
       <c r="AJ3" t="s">
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>19.73</v>
+        <v>24.68</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1125,7 +1151,7 @@
         <v>362.4</v>
       </c>
       <c r="D4">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>604.85</v>
@@ -1140,40 +1166,40 @@
         <v>19.31</v>
       </c>
       <c r="I4">
-        <v>-2.36</v>
+        <v>-0.19</v>
       </c>
       <c r="J4">
-        <v>7.89</v>
+        <v>9.34</v>
       </c>
       <c r="K4">
-        <v>1.57</v>
+        <v>4.47</v>
       </c>
       <c r="L4">
-        <v>-37.99</v>
+        <v>-36.22</v>
       </c>
       <c r="M4">
-        <v>-17.92</v>
+        <v>-17.79</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
       <c r="O4">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="P4">
-        <v>361.28</v>
+        <v>361.14</v>
       </c>
       <c r="Q4">
-        <v>344.86</v>
+        <v>346.27</v>
       </c>
       <c r="R4">
-        <v>331.86</v>
+        <v>332.88</v>
       </c>
       <c r="S4">
-        <v>394.96</v>
+        <v>394.12</v>
       </c>
       <c r="T4">
-        <v>-8.24</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1191,31 +1217,31 @@
         <v>60.17</v>
       </c>
       <c r="Z4">
-        <v>9.09</v>
+        <v>8.99</v>
       </c>
       <c r="AA4">
-        <v>7.37</v>
+        <v>7.69</v>
       </c>
       <c r="AB4">
-        <v>1.73</v>
+        <v>1.3</v>
       </c>
       <c r="AC4">
-        <v>40.35</v>
+        <v>36.28</v>
       </c>
       <c r="AD4">
-        <v>43.31</v>
+        <v>39.41</v>
       </c>
       <c r="AE4">
-        <v>13.98</v>
+        <v>13.93</v>
       </c>
       <c r="AF4">
-        <v>-62.4</v>
+        <v>-77.38</v>
       </c>
       <c r="AG4">
-        <v>379.79</v>
+        <v>381.66</v>
       </c>
       <c r="AH4">
-        <v>309.94</v>
+        <v>310.89</v>
       </c>
       <c r="AI4">
         <v>335.86</v>
@@ -1224,7 +1250,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>57.87</v>
+        <v>56.76</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1235,10 +1261,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>2008.3</v>
+        <v>2005</v>
       </c>
       <c r="D5">
-        <v>-0.82</v>
+        <v>-0.16</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1247,46 +1273,46 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-7.73</v>
+        <v>-7.88</v>
       </c>
       <c r="H5">
-        <v>23.07</v>
+        <v>22.87</v>
       </c>
       <c r="I5">
-        <v>-0.03</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="J5">
-        <v>9.23</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="K5">
-        <v>14.56</v>
+        <v>14.58</v>
       </c>
       <c r="L5">
-        <v>4.64</v>
+        <v>4.28</v>
       </c>
       <c r="M5">
-        <v>6.71</v>
+        <v>6.39</v>
       </c>
       <c r="N5">
         <v>57</v>
       </c>
       <c r="O5">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P5">
-        <v>2021.42</v>
+        <v>2018.16</v>
       </c>
       <c r="Q5">
-        <v>1979.87</v>
+        <v>1987.05</v>
       </c>
       <c r="R5">
-        <v>1868.64</v>
+        <v>1874.68</v>
       </c>
       <c r="S5">
-        <v>1911.16</v>
+        <v>1910.49</v>
       </c>
       <c r="T5">
-        <v>5.08</v>
+        <v>4.95</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1301,34 +1327,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>57.43</v>
+        <v>56.82</v>
       </c>
       <c r="Z5">
-        <v>47.15</v>
+        <v>43.07</v>
       </c>
       <c r="AA5">
-        <v>52.36</v>
+        <v>50.5</v>
       </c>
       <c r="AB5">
-        <v>-5.21</v>
+        <v>-7.43</v>
       </c>
       <c r="AC5">
-        <v>8.81</v>
+        <v>2.7</v>
       </c>
       <c r="AD5">
-        <v>16.57</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="AE5">
-        <v>43.73</v>
+        <v>42.82</v>
       </c>
       <c r="AF5">
-        <v>-36.61</v>
+        <v>-30.41</v>
       </c>
       <c r="AG5">
-        <v>2144.61</v>
+        <v>2142.31</v>
       </c>
       <c r="AH5">
-        <v>1815.13</v>
+        <v>1831.78</v>
       </c>
       <c r="AI5">
         <v>1958.53</v>
@@ -1337,7 +1363,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>29.67</v>
+        <v>26.61</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1351,7 +1377,7 @@
         <v>11475</v>
       </c>
       <c r="D6">
-        <v>-0.22</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>14451.52</v>
@@ -1366,19 +1392,19 @@
         <v>31.2</v>
       </c>
       <c r="I6">
-        <v>1.88</v>
+        <v>0.03</v>
       </c>
       <c r="J6">
-        <v>10.16</v>
+        <v>10.36</v>
       </c>
       <c r="K6">
-        <v>10.69</v>
+        <v>11.27</v>
       </c>
       <c r="L6">
-        <v>-15.94</v>
+        <v>-17.91</v>
       </c>
       <c r="M6">
-        <v>24.65</v>
+        <v>24.33</v>
       </c>
       <c r="N6">
         <v>43</v>
@@ -1387,70 +1413,70 @@
         <v>49</v>
       </c>
       <c r="P6">
-        <v>11515</v>
+        <v>11515.8</v>
       </c>
       <c r="Q6">
-        <v>11109.15</v>
+        <v>11167.95</v>
       </c>
       <c r="R6">
-        <v>10748.82</v>
+        <v>10774.34</v>
       </c>
       <c r="S6">
-        <v>10780.36</v>
+        <v>10773.8</v>
       </c>
       <c r="T6">
-        <v>6.44</v>
+        <v>6.51</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
       </c>
       <c r="V6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="W6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="X6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y6">
         <v>62.84</v>
       </c>
       <c r="Z6">
-        <v>246.71</v>
+        <v>237.77</v>
       </c>
       <c r="AA6">
-        <v>225.14</v>
+        <v>227.67</v>
       </c>
       <c r="AB6">
-        <v>21.57</v>
+        <v>10.1</v>
       </c>
       <c r="AC6">
-        <v>44.54</v>
+        <v>28.51</v>
       </c>
       <c r="AD6">
-        <v>55.56</v>
+        <v>43.11</v>
       </c>
       <c r="AE6">
-        <v>230.88</v>
+        <v>225.39</v>
       </c>
       <c r="AF6">
-        <v>-39.92</v>
+        <v>190.16</v>
       </c>
       <c r="AG6">
-        <v>11991.32</v>
+        <v>11976.45</v>
       </c>
       <c r="AH6">
-        <v>10226.98</v>
+        <v>10359.45</v>
       </c>
       <c r="AI6">
-        <v>10779.62</v>
+        <v>10787.84</v>
       </c>
       <c r="AJ6" t="s">
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>48.42</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1461,10 +1487,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>1087</v>
+        <v>1089.3</v>
       </c>
       <c r="D7">
-        <v>-0.35</v>
+        <v>0.21</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1473,25 +1499,25 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-6.2</v>
+        <v>-6</v>
       </c>
       <c r="H7">
-        <v>35.61</v>
+        <v>35.9</v>
       </c>
       <c r="I7">
-        <v>0.83</v>
+        <v>-1.17</v>
       </c>
       <c r="J7">
-        <v>4.76</v>
+        <v>3.12</v>
       </c>
       <c r="K7">
-        <v>18.01</v>
+        <v>17.95</v>
       </c>
       <c r="L7">
-        <v>23.92</v>
+        <v>24.09</v>
       </c>
       <c r="M7">
-        <v>11.69</v>
+        <v>11.61</v>
       </c>
       <c r="N7">
         <v>71</v>
@@ -1500,19 +1526,19 @@
         <v>77</v>
       </c>
       <c r="P7">
-        <v>1093.5</v>
+        <v>1090.92</v>
       </c>
       <c r="Q7">
-        <v>1087.15</v>
+        <v>1088.42</v>
       </c>
       <c r="R7">
-        <v>1020.97</v>
+        <v>1024.97</v>
       </c>
       <c r="S7">
-        <v>974.15</v>
+        <v>974.23</v>
       </c>
       <c r="T7">
-        <v>11.58</v>
+        <v>11.81</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1527,34 +1553,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>53.74</v>
+        <v>54.25</v>
       </c>
       <c r="Z7">
-        <v>22.11</v>
+        <v>19.98</v>
       </c>
       <c r="AA7">
-        <v>28.31</v>
+        <v>26.65</v>
       </c>
       <c r="AB7">
-        <v>-6.2</v>
+        <v>-6.67</v>
       </c>
       <c r="AC7">
-        <v>9.74</v>
+        <v>4.87</v>
       </c>
       <c r="AD7">
-        <v>15.56</v>
+        <v>9.93</v>
       </c>
       <c r="AE7">
-        <v>27.06</v>
+        <v>26.67</v>
       </c>
       <c r="AF7">
-        <v>-58.65</v>
+        <v>-77.02</v>
       </c>
       <c r="AG7">
-        <v>1172.39</v>
+        <v>1172.96</v>
       </c>
       <c r="AH7">
-        <v>1001.91</v>
+        <v>1003.87</v>
       </c>
       <c r="AI7">
         <v>1067.72</v>
@@ -1563,7 +1589,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>24.26</v>
+        <v>23.42</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1577,7 +1603,7 @@
         <v>134.14</v>
       </c>
       <c r="D8">
-        <v>-1.08</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>148.95</v>
@@ -1592,40 +1618,40 @@
         <v>15.68</v>
       </c>
       <c r="I8">
-        <v>-6.34</v>
+        <v>-4.96</v>
       </c>
       <c r="J8">
-        <v>-8.25</v>
+        <v>-7.93</v>
       </c>
       <c r="K8">
-        <v>-9.94</v>
+        <v>-7.57</v>
       </c>
       <c r="L8">
-        <v>-1.51</v>
+        <v>-2.5</v>
       </c>
       <c r="M8">
-        <v>-2.26</v>
+        <v>-2.13</v>
       </c>
       <c r="N8">
         <v>29</v>
       </c>
       <c r="O8">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="P8">
-        <v>137.41</v>
+        <v>136.01</v>
       </c>
       <c r="Q8">
-        <v>140.56</v>
+        <v>140.07</v>
       </c>
       <c r="R8">
-        <v>137.42</v>
+        <v>137.32</v>
       </c>
       <c r="S8">
-        <v>133.77</v>
+        <v>133.74</v>
       </c>
       <c r="T8">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1643,31 +1669,31 @@
         <v>37.64</v>
       </c>
       <c r="Z8">
-        <v>-0.23</v>
+        <v>-0.59</v>
       </c>
       <c r="AA8">
-        <v>0.8</v>
+        <v>0.52</v>
       </c>
       <c r="AB8">
-        <v>-1.03</v>
+        <v>-1.12</v>
       </c>
       <c r="AC8">
         <v>0.18</v>
       </c>
       <c r="AD8">
-        <v>3.97</v>
+        <v>0.92</v>
       </c>
       <c r="AE8">
-        <v>4.28</v>
+        <v>4.22</v>
       </c>
       <c r="AF8">
-        <v>-62.13</v>
+        <v>-69.67</v>
       </c>
       <c r="AG8">
-        <v>146.66</v>
+        <v>146.6</v>
       </c>
       <c r="AH8">
-        <v>134.46</v>
+        <v>133.55</v>
       </c>
       <c r="AI8">
         <v>131.91</v>
@@ -1676,7 +1702,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>34.67</v>
+        <v>37.96</v>
       </c>
     </row>
   </sheetData>
@@ -1817,7 +1843,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1837,1025 +1863,842 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>55</v>
-      </c>
+      <c r="A6" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>12.96</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C8" s="6">
         <v>13.25</v>
       </c>
-      <c r="E7" s="6">
-        <v>0.29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="D8" s="6">
+        <v>12.04</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-1.21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-7.18</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C9" s="6">
         <v>-9.59</v>
       </c>
-      <c r="E8" s="7">
-        <v>-2.41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="D9" s="6">
+        <v>-8.42</v>
+      </c>
+      <c r="E9" s="8">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>8.039999999999999</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C10" s="6">
         <v>7.89</v>
       </c>
-      <c r="E9" s="7">
+      <c r="D10" s="6">
+        <v>9.34</v>
+      </c>
+      <c r="E10" s="8">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>9.23</v>
+      </c>
+      <c r="D11" s="6">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-1.09</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>10.16</v>
+      </c>
+      <c r="D12" s="6">
+        <v>10.36</v>
+      </c>
+      <c r="E12" s="8">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>4.76</v>
+      </c>
+      <c r="D13" s="6">
+        <v>3.12</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-1.64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-8.25</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-7.93</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6">
+        <v>0.33</v>
+      </c>
+      <c r="D15" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-6.86</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-12</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-5.14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-2.36</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-0.19</v>
+      </c>
+      <c r="E17" s="8">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-0.03</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-0.78</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>1.88</v>
+      </c>
+      <c r="D19" s="6">
+        <v>0.03</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-1.85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>0.83</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-1.17</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-6.34</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-4.96</v>
+      </c>
+      <c r="E21" s="8">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="6">
+        <v>44.27</v>
+      </c>
+      <c r="D22" s="6">
+        <v>43.38</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-0.89</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="6">
+        <v>119.39</v>
+      </c>
+      <c r="D23" s="6">
+        <v>107.56</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-11.83</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-37.99</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-36.22</v>
+      </c>
+      <c r="E24" s="8">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>4.64</v>
+      </c>
+      <c r="D25" s="6">
+        <v>4.28</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-0.36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-15.94</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-17.91</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-1.97</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>23.92</v>
+      </c>
+      <c r="D27" s="6">
+        <v>24.09</v>
+      </c>
+      <c r="E27" s="8">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-1.51</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-2.5</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-0.99</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="6">
+        <v>16.34</v>
+      </c>
+      <c r="D29" s="6">
+        <v>16.26</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-0.08</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-3.97</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-8.609999999999999</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-4.64</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="6">
+        <v>1.57</v>
+      </c>
+      <c r="D31" s="6">
+        <v>4.47</v>
+      </c>
+      <c r="E31" s="8">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="6">
+        <v>14.56</v>
+      </c>
+      <c r="D32" s="6">
+        <v>14.58</v>
+      </c>
+      <c r="E32" s="8">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6">
+        <v>10.69</v>
+      </c>
+      <c r="D33" s="6">
+        <v>11.27</v>
+      </c>
+      <c r="E33" s="8">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>18.01</v>
+      </c>
+      <c r="D34" s="6">
+        <v>17.95</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-9.94</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-7.57</v>
+      </c>
+      <c r="E35" s="8">
+        <v>2.37</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-25.31</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-28.18</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-2.87</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-7.73</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-7.88</v>
+      </c>
+      <c r="E37" s="7">
         <v>-0.15</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-6.2</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-6</v>
+      </c>
+      <c r="E38" s="8">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="6">
+        <v>500.6</v>
+      </c>
+      <c r="D39" s="6">
+        <v>481.4</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-19.2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="5">
-        <v>9.48</v>
-      </c>
-      <c r="D10" s="5">
-        <v>9.23</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-0.25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="B40" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="6">
+        <v>2008.3</v>
+      </c>
+      <c r="D40" s="6">
+        <v>2005</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-3.3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="6">
+        <v>1087</v>
+      </c>
+      <c r="D41" s="6">
+        <v>1089.3</v>
+      </c>
+      <c r="E41" s="8">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="6">
+        <v>35.07</v>
+      </c>
+      <c r="D42" s="6">
+        <v>31.16</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-3.91</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="6">
+        <v>57.43</v>
+      </c>
+      <c r="D43" s="6">
+        <v>56.82</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-0.61</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="6">
+        <v>53.74</v>
+      </c>
+      <c r="D44" s="6">
+        <v>54.25</v>
+      </c>
+      <c r="E44" s="8">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-42.3</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-55.74</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-13.44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C46" s="6">
+        <v>41.39</v>
+      </c>
+      <c r="D46" s="6">
+        <v>164.94</v>
+      </c>
+      <c r="E46" s="8">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-62.4</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-77.38</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-14.98</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-36.61</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-30.41</v>
+      </c>
+      <c r="E48" s="8">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="5">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="D11" s="5">
-        <v>10.16</v>
-      </c>
-      <c r="E11" s="6">
-        <v>0.96</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="B49" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-39.92</v>
+      </c>
+      <c r="D49" s="6">
+        <v>190.16</v>
+      </c>
+      <c r="E49" s="8">
+        <v>230.08</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="5">
-        <v>6.81</v>
-      </c>
-      <c r="D12" s="5">
-        <v>4.76</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-2.05</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="B50" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50" s="6">
+        <v>-58.65</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-77.02</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-18.37</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="5">
-        <v>-4.27</v>
-      </c>
-      <c r="D13" s="5">
-        <v>-8.25</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-3.98</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="5">
-        <v>0.35</v>
-      </c>
-      <c r="D14" s="5">
-        <v>0.33</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-0.02</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-0.93</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-6.86</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-5.93</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>-6.77</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-2.36</v>
-      </c>
-      <c r="E16" s="6">
-        <v>4.41</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-2.92</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.03</v>
-      </c>
-      <c r="E17" s="6">
-        <v>2.89</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>0.99</v>
-      </c>
-      <c r="D18" s="5">
-        <v>1.88</v>
-      </c>
-      <c r="E18" s="6">
-        <v>0.89</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-4.72</v>
-      </c>
-      <c r="D19" s="5">
-        <v>0.83</v>
-      </c>
-      <c r="E19" s="6">
-        <v>5.55</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-5.37</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-6.34</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.97</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="5">
-        <v>43.7</v>
-      </c>
-      <c r="D21" s="5">
-        <v>44.27</v>
-      </c>
-      <c r="E21" s="6">
-        <v>0.57</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="5">
-        <v>134.57</v>
-      </c>
-      <c r="D22" s="5">
-        <v>119.39</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-15.18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="5">
-        <v>-42.01</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-37.99</v>
-      </c>
-      <c r="E23" s="6">
-        <v>4.02</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="5">
-        <v>5.8</v>
-      </c>
-      <c r="D24" s="5">
-        <v>4.64</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-1.16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>-16.13</v>
-      </c>
-      <c r="D25" s="5">
-        <v>-15.94</v>
-      </c>
-      <c r="E25" s="6">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>24.08</v>
-      </c>
-      <c r="D26" s="5">
-        <v>23.92</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-0.16</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>9.34</v>
-      </c>
-      <c r="D27" s="5">
-        <v>-1.51</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-10.85</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="5">
-        <v>13.95</v>
-      </c>
-      <c r="D28" s="5">
-        <v>16.34</v>
-      </c>
-      <c r="E28" s="6">
-        <v>2.39</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-1.82</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-3.97</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-2.15</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-9.289999999999999</v>
-      </c>
-      <c r="D30" s="5">
-        <v>1.57</v>
-      </c>
-      <c r="E30" s="6">
-        <v>10.86</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="5">
-        <v>17.18</v>
-      </c>
-      <c r="D31" s="5">
-        <v>14.56</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-2.62</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="5">
-        <v>11.56</v>
-      </c>
-      <c r="D32" s="5">
-        <v>10.69</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-0.87</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="5">
-        <v>19.81</v>
-      </c>
-      <c r="D33" s="5">
-        <v>18.01</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-1.8</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>-3.84</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-9.94</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-6.1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-1.64</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-1.32</v>
-      </c>
-      <c r="E35" s="6">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-21.28</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-25.31</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-4.03</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="5">
-        <v>-41.04</v>
-      </c>
-      <c r="D37" s="5">
-        <v>-40.08</v>
-      </c>
-      <c r="E37" s="6">
-        <v>0.96</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="5">
-        <v>-6.96</v>
-      </c>
-      <c r="D38" s="5">
-        <v>-7.73</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-0.77</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-20.42</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-20.6</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-0.18</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="5">
-        <v>-5.87</v>
-      </c>
-      <c r="D40" s="5">
-        <v>-6.2</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-0.33</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="5">
-        <v>-8.960000000000001</v>
-      </c>
-      <c r="D41" s="5">
-        <v>-9.94</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-0.98</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="5">
-        <v>11661</v>
-      </c>
-      <c r="D42" s="5">
-        <v>11700</v>
-      </c>
-      <c r="E42" s="6">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="5">
-        <v>527.65</v>
-      </c>
-      <c r="D43" s="5">
-        <v>500.6</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-27.05</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="5">
-        <v>356.6</v>
-      </c>
-      <c r="D44" s="5">
-        <v>362.4</v>
-      </c>
-      <c r="E44" s="6">
-        <v>5.8</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="5">
-        <v>2025</v>
-      </c>
-      <c r="D45" s="5">
-        <v>2008.3</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-16.7</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="5">
-        <v>11500</v>
-      </c>
-      <c r="D46" s="5">
-        <v>11475</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-25</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="5">
-        <v>1090.8</v>
-      </c>
-      <c r="D47" s="5">
-        <v>1087</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-3.8</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="5">
-        <v>135.6</v>
-      </c>
-      <c r="D48" s="5">
-        <v>134.14</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-1.46</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C49" s="5">
-        <v>29</v>
-      </c>
-      <c r="D49" s="5">
-        <v>43</v>
-      </c>
-      <c r="E49" s="6">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C50" s="5">
-        <v>43</v>
-      </c>
-      <c r="D50" s="5">
-        <v>29</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="5">
-        <v>65.68000000000001</v>
-      </c>
-      <c r="D51" s="5">
-        <v>66.52</v>
-      </c>
-      <c r="E51" s="6">
-        <v>0.84</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="5">
-        <v>41.97</v>
-      </c>
-      <c r="D52" s="5">
-        <v>35.07</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-6.9</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="5">
-        <v>57.36</v>
-      </c>
-      <c r="D53" s="5">
-        <v>60.17</v>
-      </c>
-      <c r="E53" s="6">
-        <v>2.81</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="5">
-        <v>60.44</v>
-      </c>
-      <c r="D54" s="5">
-        <v>57.43</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-3.01</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="5">
-        <v>63.85</v>
-      </c>
-      <c r="D55" s="5">
-        <v>62.84</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-1.01</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="5">
-        <v>54.68</v>
-      </c>
-      <c r="D56" s="5">
-        <v>53.74</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-0.9399999999999999</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="5">
-        <v>40.36</v>
-      </c>
-      <c r="D57" s="5">
-        <v>37.64</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-2.72</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B58" s="3" t="s">
+      <c r="B51" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C58" s="5">
-        <v>-67.95999999999999</v>
-      </c>
-      <c r="D58" s="5">
-        <v>-42.3</v>
-      </c>
-      <c r="E58" s="6">
-        <v>25.66</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C59" s="5">
-        <v>-67.18000000000001</v>
-      </c>
-      <c r="D59" s="5">
-        <v>41.39</v>
-      </c>
-      <c r="E59" s="6">
-        <v>108.57</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="5">
-        <v>-69.39</v>
-      </c>
-      <c r="D60" s="5">
-        <v>-62.4</v>
-      </c>
-      <c r="E60" s="6">
-        <v>6.99</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="5">
-        <v>-40.52</v>
-      </c>
-      <c r="D61" s="5">
-        <v>-36.61</v>
-      </c>
-      <c r="E61" s="6">
-        <v>3.91</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="5">
-        <v>-67.3</v>
-      </c>
-      <c r="D62" s="5">
-        <v>-39.92</v>
-      </c>
-      <c r="E62" s="6">
-        <v>27.38</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="5">
-        <v>-76.84999999999999</v>
-      </c>
-      <c r="D63" s="5">
-        <v>-58.65</v>
-      </c>
-      <c r="E63" s="6">
-        <v>18.2</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="5">
-        <v>-46.09</v>
-      </c>
-      <c r="D64" s="5">
+      <c r="C51" s="6">
         <v>-62.13</v>
       </c>
-      <c r="E64" s="7">
-        <v>-16.04</v>
+      <c r="D51" s="6">
+        <v>-69.67</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-7.54</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2875,61 +2718,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C1" s="8" t="s">
+      <c r="B1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="11">
+        <v>68.8</v>
+      </c>
+      <c r="C2" s="12">
+        <v>7</v>
+      </c>
+      <c r="D2" s="11">
+        <v>52.8</v>
+      </c>
+      <c r="E2" s="11">
+        <v>90</v>
+      </c>
+      <c r="F2" s="11">
+        <v>3.8</v>
+      </c>
+      <c r="G2" s="11">
+        <v>6.9</v>
+      </c>
+      <c r="H2" s="11">
         <v>57</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="F1" s="8" t="s">
+      <c r="I2" s="11">
         <v>60</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="10">
-        <v>68.8</v>
-      </c>
-      <c r="C2" s="11">
-        <v>7</v>
-      </c>
-      <c r="D2" s="10">
-        <v>53.3</v>
-      </c>
-      <c r="E2" s="10">
-        <v>90</v>
-      </c>
-      <c r="F2" s="10">
-        <v>3.9</v>
-      </c>
-      <c r="G2" s="10">
-        <v>6.8</v>
-      </c>
-      <c r="H2" s="10">
-        <v>57</v>
-      </c>
-      <c r="I2" s="10">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -3030,49 +2873,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="13">
-        <v>0.285</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.2465</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.1662</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.1169</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.06709999999999999</v>
-      </c>
-      <c r="F2" s="13">
-        <v>-0.0226</v>
-      </c>
-      <c r="G2" s="13">
-        <v>-0.1792</v>
+      <c r="A2" s="14">
+        <v>0.2807</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.2433</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.1551</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.1161</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.0639</v>
+      </c>
+      <c r="F2" s="14">
+        <v>-0.0213</v>
+      </c>
+      <c r="G2" s="14">
+        <v>-0.1779</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="77">
   <si>
     <t>Symbol</t>
   </si>
@@ -197,6 +197,21 @@
   </si>
   <si>
     <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>Left 52W High Zone</t>
+  </si>
+  <si>
+    <t>-1.3% → -2.1%</t>
+  </si>
+  <si>
+    <t>⚪ NEUTRAL</t>
+  </si>
+  <si>
+    <t>-1.3%</t>
+  </si>
+  <si>
+    <t>-2.1%</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -248,7 +263,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -289,13 +304,20 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -323,6 +345,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,7 +426,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -406,14 +434,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -422,7 +451,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -781,8 +810,7 @@
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
     <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="18" width="10.7109375" customWidth="1"/>
-    <col min="19" max="19" width="9.7109375" customWidth="1"/>
+    <col min="17" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -922,58 +950,58 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>11700</v>
+        <v>11607</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>-0.79</v>
       </c>
       <c r="E2">
         <v>11856</v>
       </c>
       <c r="F2">
-        <v>8082.75</v>
+        <v>8099.51</v>
       </c>
       <c r="G2">
-        <v>-1.32</v>
+        <v>-2.1</v>
       </c>
       <c r="H2">
-        <v>44.75</v>
+        <v>43.3</v>
       </c>
       <c r="I2">
-        <v>0.2</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="J2">
-        <v>12.04</v>
+        <v>10.31</v>
       </c>
       <c r="K2">
-        <v>16.26</v>
+        <v>12.5</v>
       </c>
       <c r="L2">
-        <v>43.38</v>
+        <v>43.6</v>
       </c>
       <c r="M2">
-        <v>28.07</v>
+        <v>27.69</v>
       </c>
       <c r="N2">
         <v>85</v>
       </c>
       <c r="O2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P2">
-        <v>11695.6</v>
+        <v>11673.6</v>
       </c>
       <c r="Q2">
-        <v>11467.82</v>
+        <v>11528</v>
       </c>
       <c r="R2">
-        <v>10631.74</v>
+        <v>10659.26</v>
       </c>
       <c r="S2">
-        <v>9699.959999999999</v>
+        <v>9713.450000000001</v>
       </c>
       <c r="T2">
-        <v>20.62</v>
+        <v>19.49</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -988,34 +1016,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>66.52</v>
+        <v>62.31</v>
       </c>
       <c r="Z2">
-        <v>325.27</v>
+        <v>302.35</v>
       </c>
       <c r="AA2">
-        <v>354.28</v>
+        <v>343.89</v>
       </c>
       <c r="AB2">
-        <v>-29.01</v>
+        <v>-41.55</v>
       </c>
       <c r="AC2">
         <v>4.33</v>
       </c>
       <c r="AD2">
-        <v>5.36</v>
+        <v>4.47</v>
       </c>
       <c r="AE2">
-        <v>213.85</v>
+        <v>211.93</v>
       </c>
       <c r="AF2">
-        <v>-55.74</v>
+        <v>-40.39</v>
       </c>
       <c r="AG2">
-        <v>12156.98</v>
+        <v>12002.64</v>
       </c>
       <c r="AH2">
-        <v>10778.67</v>
+        <v>11053.36</v>
       </c>
       <c r="AI2">
         <v>11083.45</v>
@@ -1024,7 +1052,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>74.67</v>
+        <v>68.73999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1035,10 +1063,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>481.4</v>
+        <v>484.05</v>
       </c>
       <c r="D3">
-        <v>-3.84</v>
+        <v>0.55</v>
       </c>
       <c r="E3">
         <v>670.25</v>
@@ -1047,25 +1075,25 @@
         <v>222.01</v>
       </c>
       <c r="G3">
-        <v>-28.18</v>
+        <v>-27.78</v>
       </c>
       <c r="H3">
-        <v>116.84</v>
+        <v>118.03</v>
       </c>
       <c r="I3">
-        <v>-12</v>
+        <v>-10.52</v>
       </c>
       <c r="J3">
-        <v>-8.42</v>
+        <v>-10.19</v>
       </c>
       <c r="K3">
-        <v>-8.609999999999999</v>
+        <v>-11.97</v>
       </c>
       <c r="L3">
-        <v>107.56</v>
+        <v>115.1</v>
       </c>
       <c r="M3">
-        <v>15.51</v>
+        <v>16.34</v>
       </c>
       <c r="N3">
         <v>99</v>
@@ -1074,19 +1102,19 @@
         <v>90</v>
       </c>
       <c r="P3">
-        <v>517.77</v>
+        <v>506.39</v>
       </c>
       <c r="Q3">
-        <v>531.77</v>
+        <v>529.71</v>
       </c>
       <c r="R3">
-        <v>571.38</v>
+        <v>569.5599999999999</v>
       </c>
       <c r="S3">
-        <v>416.52</v>
+        <v>417.59</v>
       </c>
       <c r="T3">
-        <v>15.58</v>
+        <v>15.91</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1101,43 +1129,43 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>31.16</v>
+        <v>32.29</v>
       </c>
       <c r="Z3">
-        <v>-16.17</v>
+        <v>-18.22</v>
       </c>
       <c r="AA3">
-        <v>-13.08</v>
+        <v>-14.11</v>
       </c>
       <c r="AB3">
-        <v>-3.09</v>
+        <v>-4.11</v>
       </c>
       <c r="AC3">
-        <v>11.65</v>
+        <v>2.24</v>
       </c>
       <c r="AD3">
-        <v>36.12</v>
+        <v>16.33</v>
       </c>
       <c r="AE3">
-        <v>22.77</v>
+        <v>22.49</v>
       </c>
       <c r="AF3">
-        <v>164.94</v>
+        <v>10.87</v>
       </c>
       <c r="AG3">
-        <v>565.16</v>
+        <v>569.3099999999999</v>
       </c>
       <c r="AH3">
-        <v>498.38</v>
+        <v>490.11</v>
       </c>
       <c r="AI3">
-        <v>562.11</v>
+        <v>553.0599999999999</v>
       </c>
       <c r="AJ3" t="s">
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>24.68</v>
+        <v>28.97</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1148,10 +1176,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>362.4</v>
+        <v>355.55</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>-1.89</v>
       </c>
       <c r="E4">
         <v>604.85</v>
@@ -1160,46 +1188,46 @@
         <v>303.75</v>
       </c>
       <c r="G4">
-        <v>-40.08</v>
+        <v>-41.22</v>
       </c>
       <c r="H4">
-        <v>19.31</v>
+        <v>17.05</v>
       </c>
       <c r="I4">
-        <v>-0.19</v>
+        <v>-1.33</v>
       </c>
       <c r="J4">
-        <v>9.34</v>
+        <v>6.37</v>
       </c>
       <c r="K4">
-        <v>4.47</v>
+        <v>3.78</v>
       </c>
       <c r="L4">
-        <v>-36.22</v>
+        <v>-38.12</v>
       </c>
       <c r="M4">
-        <v>-17.79</v>
+        <v>-18.09</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
       <c r="O4">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="P4">
-        <v>361.14</v>
+        <v>360.18</v>
       </c>
       <c r="Q4">
-        <v>346.27</v>
+        <v>347.39</v>
       </c>
       <c r="R4">
-        <v>332.88</v>
+        <v>333.86</v>
       </c>
       <c r="S4">
-        <v>394.12</v>
+        <v>393.25</v>
       </c>
       <c r="T4">
-        <v>-8.050000000000001</v>
+        <v>-9.59</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1214,34 +1242,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>60.17</v>
+        <v>55.19</v>
       </c>
       <c r="Z4">
-        <v>8.99</v>
+        <v>8.26</v>
       </c>
       <c r="AA4">
-        <v>7.69</v>
+        <v>7.8</v>
       </c>
       <c r="AB4">
-        <v>1.3</v>
+        <v>0.46</v>
       </c>
       <c r="AC4">
-        <v>36.28</v>
+        <v>32.03</v>
       </c>
       <c r="AD4">
-        <v>39.41</v>
+        <v>36.22</v>
       </c>
       <c r="AE4">
-        <v>13.93</v>
+        <v>14.01</v>
       </c>
       <c r="AF4">
-        <v>-77.38</v>
+        <v>-62.63</v>
       </c>
       <c r="AG4">
-        <v>381.66</v>
+        <v>382.45</v>
       </c>
       <c r="AH4">
-        <v>310.89</v>
+        <v>312.34</v>
       </c>
       <c r="AI4">
         <v>335.86</v>
@@ -1250,7 +1278,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>56.76</v>
+        <v>56.31</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1261,10 +1289,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>2005</v>
+        <v>2011.2</v>
       </c>
       <c r="D5">
-        <v>-0.16</v>
+        <v>0.31</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1273,46 +1301,46 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-7.88</v>
+        <v>-7.6</v>
       </c>
       <c r="H5">
-        <v>22.87</v>
+        <v>23.25</v>
       </c>
       <c r="I5">
-        <v>-0.8100000000000001</v>
+        <v>-1.02</v>
       </c>
       <c r="J5">
-        <v>8.140000000000001</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="K5">
-        <v>14.58</v>
+        <v>13.5</v>
       </c>
       <c r="L5">
-        <v>4.28</v>
+        <v>5.41</v>
       </c>
       <c r="M5">
-        <v>6.39</v>
+        <v>6.08</v>
       </c>
       <c r="N5">
         <v>57</v>
       </c>
       <c r="O5">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="P5">
-        <v>2018.16</v>
+        <v>2014</v>
       </c>
       <c r="Q5">
-        <v>1987.05</v>
+        <v>1992.58</v>
       </c>
       <c r="R5">
-        <v>1874.68</v>
+        <v>1881.41</v>
       </c>
       <c r="S5">
-        <v>1910.49</v>
+        <v>1909.86</v>
       </c>
       <c r="T5">
-        <v>4.95</v>
+        <v>5.31</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1327,34 +1355,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>56.82</v>
+        <v>57.72</v>
       </c>
       <c r="Z5">
-        <v>43.07</v>
+        <v>39.87</v>
       </c>
       <c r="AA5">
-        <v>50.5</v>
+        <v>48.37</v>
       </c>
       <c r="AB5">
-        <v>-7.43</v>
+        <v>-8.5</v>
       </c>
       <c r="AC5">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="AD5">
-        <v>9.859999999999999</v>
+        <v>4.33</v>
       </c>
       <c r="AE5">
-        <v>42.82</v>
+        <v>41.25</v>
       </c>
       <c r="AF5">
-        <v>-30.41</v>
+        <v>-72.28</v>
       </c>
       <c r="AG5">
-        <v>2142.31</v>
+        <v>2142.66</v>
       </c>
       <c r="AH5">
-        <v>1831.78</v>
+        <v>1842.49</v>
       </c>
       <c r="AI5">
         <v>1958.53</v>
@@ -1363,7 +1391,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>26.61</v>
+        <v>23.97</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1374,10 +1402,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>11475</v>
+        <v>11254</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>-1.93</v>
       </c>
       <c r="E6">
         <v>14451.52</v>
@@ -1386,46 +1414,46 @@
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-20.6</v>
+        <v>-22.13</v>
       </c>
       <c r="H6">
-        <v>31.2</v>
+        <v>28.68</v>
       </c>
       <c r="I6">
-        <v>0.03</v>
+        <v>-2.56</v>
       </c>
       <c r="J6">
-        <v>10.36</v>
+        <v>9.27</v>
       </c>
       <c r="K6">
-        <v>11.27</v>
+        <v>7.51</v>
       </c>
       <c r="L6">
-        <v>-17.91</v>
+        <v>-18.08</v>
       </c>
       <c r="M6">
-        <v>24.33</v>
+        <v>23.72</v>
       </c>
       <c r="N6">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="O6">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="P6">
-        <v>11515.8</v>
+        <v>11456.6</v>
       </c>
       <c r="Q6">
-        <v>11167.95</v>
+        <v>11208.35</v>
       </c>
       <c r="R6">
-        <v>10774.34</v>
+        <v>10802.06</v>
       </c>
       <c r="S6">
-        <v>10773.8</v>
+        <v>10766.98</v>
       </c>
       <c r="T6">
-        <v>6.51</v>
+        <v>4.52</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1440,34 +1468,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>62.84</v>
+        <v>54.08</v>
       </c>
       <c r="Z6">
-        <v>237.77</v>
+        <v>210.42</v>
       </c>
       <c r="AA6">
-        <v>227.67</v>
+        <v>224.22</v>
       </c>
       <c r="AB6">
-        <v>10.1</v>
+        <v>-13.8</v>
       </c>
       <c r="AC6">
-        <v>28.51</v>
+        <v>15.73</v>
       </c>
       <c r="AD6">
-        <v>43.11</v>
+        <v>29.59</v>
       </c>
       <c r="AE6">
-        <v>225.39</v>
+        <v>228.15</v>
       </c>
       <c r="AF6">
-        <v>190.16</v>
+        <v>-60.63</v>
       </c>
       <c r="AG6">
-        <v>11976.45</v>
+        <v>11942.27</v>
       </c>
       <c r="AH6">
-        <v>10359.45</v>
+        <v>10474.43</v>
       </c>
       <c r="AI6">
         <v>10787.84</v>
@@ -1476,7 +1504,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>47.9</v>
+        <v>41.81</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1487,10 +1515,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>1089.3</v>
+        <v>1094.3</v>
       </c>
       <c r="D7">
-        <v>0.21</v>
+        <v>0.46</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1499,46 +1527,46 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-6</v>
+        <v>-5.57</v>
       </c>
       <c r="H7">
-        <v>35.9</v>
+        <v>36.52</v>
       </c>
       <c r="I7">
-        <v>-1.17</v>
+        <v>0.09</v>
       </c>
       <c r="J7">
-        <v>3.12</v>
+        <v>2.85</v>
       </c>
       <c r="K7">
-        <v>17.95</v>
+        <v>18.55</v>
       </c>
       <c r="L7">
-        <v>24.09</v>
+        <v>28.29</v>
       </c>
       <c r="M7">
-        <v>11.61</v>
+        <v>11.25</v>
       </c>
       <c r="N7">
         <v>71</v>
       </c>
       <c r="O7">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P7">
-        <v>1090.92</v>
+        <v>1091.12</v>
       </c>
       <c r="Q7">
-        <v>1088.42</v>
+        <v>1089.67</v>
       </c>
       <c r="R7">
-        <v>1024.97</v>
+        <v>1029.43</v>
       </c>
       <c r="S7">
-        <v>974.23</v>
+        <v>974.39</v>
       </c>
       <c r="T7">
-        <v>11.81</v>
+        <v>12.31</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1553,34 +1581,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>54.25</v>
+        <v>55.4</v>
       </c>
       <c r="Z7">
-        <v>19.98</v>
+        <v>18.48</v>
       </c>
       <c r="AA7">
-        <v>26.65</v>
+        <v>25.01</v>
       </c>
       <c r="AB7">
-        <v>-6.67</v>
+        <v>-6.53</v>
       </c>
       <c r="AC7">
-        <v>4.87</v>
+        <v>5.97</v>
       </c>
       <c r="AD7">
-        <v>9.93</v>
+        <v>6.86</v>
       </c>
       <c r="AE7">
-        <v>26.67</v>
+        <v>25.65</v>
       </c>
       <c r="AF7">
-        <v>-77.02</v>
+        <v>-64.43000000000001</v>
       </c>
       <c r="AG7">
-        <v>1172.96</v>
+        <v>1173.76</v>
       </c>
       <c r="AH7">
-        <v>1003.87</v>
+        <v>1005.58</v>
       </c>
       <c r="AI7">
         <v>1067.72</v>
@@ -1589,7 +1617,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>23.42</v>
+        <v>22.69</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1600,10 +1628,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>134.14</v>
+        <v>135.69</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="E8">
         <v>148.95</v>
@@ -1612,46 +1640,46 @@
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>-9.94</v>
+        <v>-8.9</v>
       </c>
       <c r="H8">
-        <v>15.68</v>
+        <v>17.01</v>
       </c>
       <c r="I8">
-        <v>-4.96</v>
+        <v>-3.5</v>
       </c>
       <c r="J8">
-        <v>-7.93</v>
+        <v>-5.68</v>
       </c>
       <c r="K8">
-        <v>-7.57</v>
+        <v>-3.79</v>
       </c>
       <c r="L8">
-        <v>-2.5</v>
+        <v>1.3</v>
       </c>
       <c r="M8">
-        <v>-2.13</v>
+        <v>-1.49</v>
       </c>
       <c r="N8">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="O8">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="P8">
-        <v>136.01</v>
+        <v>135.03</v>
       </c>
       <c r="Q8">
-        <v>140.07</v>
+        <v>139.56</v>
       </c>
       <c r="R8">
-        <v>137.32</v>
+        <v>137.3</v>
       </c>
       <c r="S8">
-        <v>133.74</v>
+        <v>133.69</v>
       </c>
       <c r="T8">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1666,34 +1694,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>37.64</v>
+        <v>42.42</v>
       </c>
       <c r="Z8">
-        <v>-0.59</v>
+        <v>-0.75</v>
       </c>
       <c r="AA8">
-        <v>0.52</v>
+        <v>0.27</v>
       </c>
       <c r="AB8">
-        <v>-1.12</v>
+        <v>-1.02</v>
       </c>
       <c r="AC8">
-        <v>0.18</v>
+        <v>7.04</v>
       </c>
       <c r="AD8">
-        <v>0.92</v>
+        <v>2.47</v>
       </c>
       <c r="AE8">
-        <v>4.22</v>
+        <v>4.12</v>
       </c>
       <c r="AF8">
-        <v>-69.67</v>
+        <v>-63.9</v>
       </c>
       <c r="AG8">
-        <v>146.6</v>
+        <v>145.76</v>
       </c>
       <c r="AH8">
-        <v>133.55</v>
+        <v>133.37</v>
       </c>
       <c r="AI8">
         <v>131.91</v>
@@ -1702,7 +1730,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>37.96</v>
+        <v>39.96</v>
       </c>
     </row>
   </sheetData>
@@ -1843,7 +1871,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1921,784 +1949,1042 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+      <c r="C5" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="B8" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C9" s="7">
         <v>13.25</v>
       </c>
-      <c r="D8" s="6">
-        <v>12.04</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-1.21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="D9" s="7">
+        <v>10.31</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-2.94</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C10" s="7">
         <v>-9.59</v>
       </c>
-      <c r="D9" s="6">
-        <v>-8.42</v>
-      </c>
-      <c r="E9" s="8">
-        <v>1.17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="D10" s="7">
+        <v>-10.19</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C11" s="7">
         <v>7.89</v>
       </c>
-      <c r="D10" s="6">
-        <v>9.34</v>
-      </c>
-      <c r="E10" s="8">
-        <v>1.45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="D11" s="7">
+        <v>6.37</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-1.52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C12" s="7">
         <v>9.23</v>
       </c>
-      <c r="D11" s="6">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-1.09</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="D12" s="7">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-1.19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C13" s="7">
         <v>10.16</v>
       </c>
-      <c r="D12" s="6">
-        <v>10.36</v>
-      </c>
-      <c r="E12" s="8">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="D13" s="7">
+        <v>9.27</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-0.89</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C14" s="7">
         <v>4.76</v>
       </c>
-      <c r="D13" s="6">
-        <v>3.12</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-1.64</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="D14" s="7">
+        <v>2.85</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-1.91</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C15" s="7">
         <v>-8.25</v>
       </c>
-      <c r="D14" s="6">
-        <v>-7.93</v>
-      </c>
-      <c r="E14" s="8">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="D15" s="7">
+        <v>-5.68</v>
+      </c>
+      <c r="E15" s="9">
+        <v>2.57</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B16" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C16" s="7">
         <v>0.33</v>
       </c>
-      <c r="D15" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="E15" s="7">
+      <c r="D16" s="7">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-1.27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-6.86</v>
+      </c>
+      <c r="D17" s="7">
+        <v>-10.52</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-3.66</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-2.36</v>
+      </c>
+      <c r="D18" s="7">
+        <v>-1.33</v>
+      </c>
+      <c r="E18" s="9">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>-0.03</v>
+      </c>
+      <c r="D19" s="7">
+        <v>-1.02</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-0.99</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7">
+        <v>1.88</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-2.56</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-4.44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7">
+        <v>0.83</v>
+      </c>
+      <c r="D21" s="7">
+        <v>0.09</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-0.74</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="7">
+        <v>-6.34</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-3.5</v>
+      </c>
+      <c r="E22" s="9">
+        <v>2.84</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="7">
+        <v>44.27</v>
+      </c>
+      <c r="D23" s="7">
+        <v>43.6</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="7">
+        <v>119.39</v>
+      </c>
+      <c r="D24" s="7">
+        <v>115.1</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-4.29</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="7">
+        <v>-37.99</v>
+      </c>
+      <c r="D25" s="7">
+        <v>-38.12</v>
+      </c>
+      <c r="E25" s="8">
         <v>-0.13</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="7">
+        <v>4.64</v>
+      </c>
+      <c r="D26" s="7">
+        <v>5.41</v>
+      </c>
+      <c r="E26" s="9">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="7">
+        <v>-15.94</v>
+      </c>
+      <c r="D27" s="7">
+        <v>-18.08</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-2.14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="7">
+        <v>23.92</v>
+      </c>
+      <c r="D28" s="7">
+        <v>28.29</v>
+      </c>
+      <c r="E28" s="9">
+        <v>4.37</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="7">
+        <v>-1.51</v>
+      </c>
+      <c r="D29" s="7">
+        <v>1.3</v>
+      </c>
+      <c r="E29" s="9">
+        <v>2.81</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="7">
+        <v>16.34</v>
+      </c>
+      <c r="D30" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-3.84</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-6.86</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-12</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-5.14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B31" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="7">
+        <v>-3.97</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-11.97</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-2.36</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-0.19</v>
-      </c>
-      <c r="E17" s="8">
-        <v>2.17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B32" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="7">
+        <v>1.57</v>
+      </c>
+      <c r="D32" s="7">
+        <v>3.78</v>
+      </c>
+      <c r="E32" s="9">
+        <v>2.21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-0.03</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-0.8100000000000001</v>
-      </c>
-      <c r="E18" s="7">
+      <c r="B33" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="7">
+        <v>14.56</v>
+      </c>
+      <c r="D33" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="7">
+        <v>10.69</v>
+      </c>
+      <c r="D34" s="7">
+        <v>7.51</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-3.18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="7">
+        <v>18.01</v>
+      </c>
+      <c r="D35" s="7">
+        <v>18.55</v>
+      </c>
+      <c r="E35" s="9">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="7">
+        <v>-9.94</v>
+      </c>
+      <c r="D36" s="7">
+        <v>-3.79</v>
+      </c>
+      <c r="E36" s="9">
+        <v>6.15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="7">
+        <v>-1.32</v>
+      </c>
+      <c r="D37" s="7">
+        <v>-2.1</v>
+      </c>
+      <c r="E37" s="8">
         <v>-0.78</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="7">
+        <v>-25.31</v>
+      </c>
+      <c r="D38" s="7">
+        <v>-27.78</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-2.47</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="7">
+        <v>-40.08</v>
+      </c>
+      <c r="D39" s="7">
+        <v>-41.22</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-1.14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="7">
+        <v>-7.73</v>
+      </c>
+      <c r="D40" s="7">
+        <v>-7.6</v>
+      </c>
+      <c r="E40" s="9">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>1.88</v>
-      </c>
-      <c r="D19" s="6">
-        <v>0.03</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-1.85</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B41" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="7">
+        <v>-20.6</v>
+      </c>
+      <c r="D41" s="7">
+        <v>-22.13</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-1.53</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>0.83</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-1.17</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B42" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="7">
+        <v>-6.2</v>
+      </c>
+      <c r="D42" s="7">
+        <v>-5.57</v>
+      </c>
+      <c r="E42" s="9">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-6.34</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-4.96</v>
-      </c>
-      <c r="E21" s="8">
-        <v>1.38</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B43" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="7">
+        <v>-9.94</v>
+      </c>
+      <c r="D43" s="7">
+        <v>-8.9</v>
+      </c>
+      <c r="E43" s="9">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="6">
-        <v>44.27</v>
-      </c>
-      <c r="D22" s="6">
-        <v>43.38</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-0.89</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B44" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="7">
+        <v>11700</v>
+      </c>
+      <c r="D44" s="7">
+        <v>11607</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-93</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="6">
-        <v>119.39</v>
-      </c>
-      <c r="D23" s="6">
-        <v>107.56</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-11.83</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B45" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="7">
+        <v>500.6</v>
+      </c>
+      <c r="D45" s="7">
+        <v>484.05</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-16.55</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-37.99</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-36.22</v>
-      </c>
-      <c r="E24" s="8">
-        <v>1.77</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B46" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="7">
+        <v>362.4</v>
+      </c>
+      <c r="D46" s="7">
+        <v>355.55</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-6.85</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>4.64</v>
-      </c>
-      <c r="D25" s="6">
-        <v>4.28</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-0.36</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B47" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="7">
+        <v>2008.3</v>
+      </c>
+      <c r="D47" s="7">
+        <v>2011.2</v>
+      </c>
+      <c r="E47" s="9">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-15.94</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-17.91</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-1.97</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B48" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="7">
+        <v>11475</v>
+      </c>
+      <c r="D48" s="7">
+        <v>11254</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-221</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>23.92</v>
-      </c>
-      <c r="D27" s="6">
-        <v>24.09</v>
-      </c>
-      <c r="E27" s="8">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B49" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="7">
+        <v>1087</v>
+      </c>
+      <c r="D49" s="7">
+        <v>1094.3</v>
+      </c>
+      <c r="E49" s="9">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-1.51</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-2.5</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-0.99</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B50" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="7">
+        <v>134.14</v>
+      </c>
+      <c r="D50" s="7">
+        <v>135.69</v>
+      </c>
+      <c r="E50" s="9">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51" s="7">
+        <v>43</v>
+      </c>
+      <c r="D51" s="7">
+        <v>29</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52" s="7">
+        <v>29</v>
+      </c>
+      <c r="D52" s="7">
+        <v>43</v>
+      </c>
+      <c r="E52" s="9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="6">
-        <v>16.34</v>
-      </c>
-      <c r="D29" s="6">
-        <v>16.26</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-0.08</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B53" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="7">
+        <v>66.52</v>
+      </c>
+      <c r="D53" s="7">
+        <v>62.31</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-4.21</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-3.97</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-8.609999999999999</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-4.64</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="B54" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="7">
+        <v>35.07</v>
+      </c>
+      <c r="D54" s="7">
+        <v>32.29</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-2.78</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="6">
-        <v>1.57</v>
-      </c>
-      <c r="D31" s="6">
-        <v>4.47</v>
-      </c>
-      <c r="E31" s="8">
-        <v>2.9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="B55" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="7">
+        <v>60.17</v>
+      </c>
+      <c r="D55" s="7">
+        <v>55.19</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-4.98</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="6">
-        <v>14.56</v>
-      </c>
-      <c r="D32" s="6">
-        <v>14.58</v>
-      </c>
-      <c r="E32" s="8">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="B56" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="7">
+        <v>57.43</v>
+      </c>
+      <c r="D56" s="7">
+        <v>57.72</v>
+      </c>
+      <c r="E56" s="9">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="6">
-        <v>10.69</v>
-      </c>
-      <c r="D33" s="6">
-        <v>11.27</v>
-      </c>
-      <c r="E33" s="8">
-        <v>0.58</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="B57" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="7">
+        <v>62.84</v>
+      </c>
+      <c r="D57" s="7">
+        <v>54.08</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-8.76</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>18.01</v>
-      </c>
-      <c r="D34" s="6">
-        <v>17.95</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="B58" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="7">
+        <v>53.74</v>
+      </c>
+      <c r="D58" s="7">
+        <v>55.4</v>
+      </c>
+      <c r="E58" s="9">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-9.94</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-7.57</v>
-      </c>
-      <c r="E35" s="8">
-        <v>2.37</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
+      <c r="B59" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="7">
+        <v>37.64</v>
+      </c>
+      <c r="D59" s="7">
+        <v>42.42</v>
+      </c>
+      <c r="E59" s="9">
+        <v>4.78</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="7">
+        <v>-42.3</v>
+      </c>
+      <c r="D60" s="7">
+        <v>-40.39</v>
+      </c>
+      <c r="E60" s="9">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-25.31</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-28.18</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-2.87</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
+      <c r="B61" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="7">
+        <v>41.39</v>
+      </c>
+      <c r="D61" s="7">
+        <v>10.87</v>
+      </c>
+      <c r="E61" s="8">
+        <v>-30.52</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="7">
+        <v>-62.4</v>
+      </c>
+      <c r="D62" s="7">
+        <v>-62.63</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-7.73</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-7.88</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-0.15</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
+      <c r="B63" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="7">
+        <v>-36.61</v>
+      </c>
+      <c r="D63" s="7">
+        <v>-72.28</v>
+      </c>
+      <c r="E63" s="8">
+        <v>-35.67</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="7">
+        <v>-39.92</v>
+      </c>
+      <c r="D64" s="7">
+        <v>-60.63</v>
+      </c>
+      <c r="E64" s="8">
+        <v>-20.71</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-6.2</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-6</v>
-      </c>
-      <c r="E38" s="8">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C39" s="6">
-        <v>500.6</v>
-      </c>
-      <c r="D39" s="6">
-        <v>481.4</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-19.2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C40" s="6">
-        <v>2008.3</v>
-      </c>
-      <c r="D40" s="6">
-        <v>2005</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-3.3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="6">
-        <v>1087</v>
-      </c>
-      <c r="D41" s="6">
-        <v>1089.3</v>
-      </c>
-      <c r="E41" s="8">
-        <v>2.3</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" s="6">
-        <v>35.07</v>
-      </c>
-      <c r="D42" s="6">
-        <v>31.16</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-3.91</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="6">
-        <v>57.43</v>
-      </c>
-      <c r="D43" s="6">
-        <v>56.82</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-0.61</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C44" s="6">
-        <v>53.74</v>
-      </c>
-      <c r="D44" s="6">
-        <v>54.25</v>
-      </c>
-      <c r="E44" s="8">
-        <v>0.51</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B45" s="5" t="s">
+      <c r="B65" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C45" s="6">
-        <v>-42.3</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-55.74</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-13.44</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B46" s="5" t="s">
+      <c r="C65" s="7">
+        <v>-58.65</v>
+      </c>
+      <c r="D65" s="7">
+        <v>-64.43000000000001</v>
+      </c>
+      <c r="E65" s="8">
+        <v>-5.78</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B66" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C46" s="6">
-        <v>41.39</v>
-      </c>
-      <c r="D46" s="6">
-        <v>164.94</v>
-      </c>
-      <c r="E46" s="8">
-        <v>123.55</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-62.4</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-77.38</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-14.98</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-36.61</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-30.41</v>
-      </c>
-      <c r="E48" s="8">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-39.92</v>
-      </c>
-      <c r="D49" s="6">
-        <v>190.16</v>
-      </c>
-      <c r="E49" s="8">
-        <v>230.08</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C50" s="6">
-        <v>-58.65</v>
-      </c>
-      <c r="D50" s="6">
-        <v>-77.02</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-18.37</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C51" s="6">
+      <c r="C66" s="7">
         <v>-62.13</v>
       </c>
-      <c r="D51" s="6">
-        <v>-69.67</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-7.54</v>
+      <c r="D66" s="7">
+        <v>-63.9</v>
+      </c>
+      <c r="E66" s="8">
+        <v>-1.77</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2718,60 +3004,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="G1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="C1" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>71</v>
       </c>
+      <c r="E1" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="12">
         <v>68.8</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="13">
         <v>7</v>
       </c>
-      <c r="D2" s="11">
-        <v>52.8</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="12">
+        <v>51.3</v>
+      </c>
+      <c r="E2" s="12">
         <v>90</v>
       </c>
-      <c r="F2" s="11">
-        <v>3.8</v>
-      </c>
-      <c r="G2" s="11">
-        <v>6.9</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="12">
+        <v>3</v>
+      </c>
+      <c r="G2" s="12">
+        <v>5.7</v>
+      </c>
+      <c r="H2" s="12">
         <v>57</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="12">
         <v>60</v>
       </c>
     </row>
@@ -2873,49 +3159,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="14" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="14">
-        <v>0.2807</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.2433</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.1551</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.1161</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.0639</v>
-      </c>
-      <c r="F2" s="14">
-        <v>-0.0213</v>
-      </c>
-      <c r="G2" s="14">
-        <v>-0.1779</v>
+      <c r="A2" s="15">
+        <v>0.2769</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.2372</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.1634</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.1125</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.0608</v>
+      </c>
+      <c r="F2" s="15">
+        <v>-0.0149</v>
+      </c>
+      <c r="G2" s="15">
+        <v>-0.1809</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="73">
   <si>
     <t>Symbol</t>
   </si>
@@ -187,31 +187,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>50 DMA &gt; 200 DMA</t>
-  </si>
-  <si>
-    <t>No → Yes</t>
-  </si>
-  <si>
-    <t>🟢 GOLDEN CROSS</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>Left 52W High Zone</t>
-  </si>
-  <si>
-    <t>-1.3% → -2.1%</t>
-  </si>
-  <si>
-    <t>⚪ NEUTRAL</t>
-  </si>
-  <si>
-    <t>-1.3%</t>
+    <t>Near 52W High</t>
+  </si>
+  <si>
+    <t>-2.1% → -1.8%</t>
+  </si>
+  <si>
+    <t>🟢 BREAKOUT WATCH</t>
   </si>
   <si>
     <t>-2.1%</t>
+  </si>
+  <si>
+    <t>-1.8%</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -263,7 +251,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -304,20 +292,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -345,12 +326,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -426,7 +401,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -434,15 +409,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -451,7 +425,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -950,10 +924,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>11607</v>
+        <v>11645</v>
       </c>
       <c r="D2">
-        <v>-0.79</v>
+        <v>0.33</v>
       </c>
       <c r="E2">
         <v>11856</v>
@@ -962,25 +936,25 @@
         <v>8099.51</v>
       </c>
       <c r="G2">
-        <v>-2.1</v>
+        <v>-1.78</v>
       </c>
       <c r="H2">
-        <v>43.3</v>
+        <v>43.77</v>
       </c>
       <c r="I2">
-        <v>-0.9399999999999999</v>
+        <v>-0.47</v>
       </c>
       <c r="J2">
-        <v>10.31</v>
+        <v>11.93</v>
       </c>
       <c r="K2">
-        <v>12.5</v>
+        <v>10.7</v>
       </c>
       <c r="L2">
-        <v>43.6</v>
+        <v>43.16</v>
       </c>
       <c r="M2">
-        <v>27.69</v>
+        <v>28.34</v>
       </c>
       <c r="N2">
         <v>85</v>
@@ -989,19 +963,19 @@
         <v>83</v>
       </c>
       <c r="P2">
-        <v>11673.6</v>
+        <v>11662.6</v>
       </c>
       <c r="Q2">
-        <v>11528</v>
+        <v>11560.32</v>
       </c>
       <c r="R2">
-        <v>10659.26</v>
+        <v>10688.48</v>
       </c>
       <c r="S2">
-        <v>9713.450000000001</v>
+        <v>9727.68</v>
       </c>
       <c r="T2">
-        <v>19.49</v>
+        <v>19.71</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -1016,34 +990,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>62.31</v>
+        <v>63.33</v>
       </c>
       <c r="Z2">
-        <v>302.35</v>
+        <v>283.97</v>
       </c>
       <c r="AA2">
-        <v>343.89</v>
+        <v>331.91</v>
       </c>
       <c r="AB2">
-        <v>-41.55</v>
+        <v>-47.94</v>
       </c>
       <c r="AC2">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="AD2">
-        <v>4.47</v>
+        <v>4.3</v>
       </c>
       <c r="AE2">
-        <v>211.93</v>
+        <v>210.22</v>
       </c>
       <c r="AF2">
-        <v>-40.39</v>
+        <v>-43.47</v>
       </c>
       <c r="AG2">
-        <v>12002.64</v>
+        <v>11966.21</v>
       </c>
       <c r="AH2">
-        <v>11053.36</v>
+        <v>11154.44</v>
       </c>
       <c r="AI2">
         <v>11083.45</v>
@@ -1052,7 +1026,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>68.73999999999999</v>
+        <v>61.63</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1063,10 +1037,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>484.05</v>
+        <v>500.7</v>
       </c>
       <c r="D3">
-        <v>0.55</v>
+        <v>3.44</v>
       </c>
       <c r="E3">
         <v>670.25</v>
@@ -1075,46 +1049,46 @@
         <v>222.01</v>
       </c>
       <c r="G3">
-        <v>-27.78</v>
+        <v>-25.3</v>
       </c>
       <c r="H3">
-        <v>118.03</v>
+        <v>125.53</v>
       </c>
       <c r="I3">
-        <v>-10.52</v>
+        <v>-6.98</v>
       </c>
       <c r="J3">
-        <v>-10.19</v>
+        <v>-4.67</v>
       </c>
       <c r="K3">
-        <v>-11.97</v>
+        <v>-8.41</v>
       </c>
       <c r="L3">
-        <v>115.1</v>
+        <v>124.8</v>
       </c>
       <c r="M3">
-        <v>16.34</v>
+        <v>17.4</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="P3">
-        <v>506.39</v>
+        <v>498.88</v>
       </c>
       <c r="Q3">
-        <v>529.71</v>
+        <v>528.26</v>
       </c>
       <c r="R3">
-        <v>569.5599999999999</v>
+        <v>567.9299999999999</v>
       </c>
       <c r="S3">
-        <v>417.59</v>
+        <v>418.76</v>
       </c>
       <c r="T3">
-        <v>15.91</v>
+        <v>19.57</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1129,34 +1103,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>32.29</v>
+        <v>39.01</v>
       </c>
       <c r="Z3">
-        <v>-18.22</v>
+        <v>-18.28</v>
       </c>
       <c r="AA3">
-        <v>-14.11</v>
+        <v>-14.94</v>
       </c>
       <c r="AB3">
-        <v>-4.11</v>
+        <v>-3.34</v>
       </c>
       <c r="AC3">
-        <v>2.24</v>
+        <v>17.87</v>
       </c>
       <c r="AD3">
-        <v>16.33</v>
+        <v>10.58</v>
       </c>
       <c r="AE3">
-        <v>22.49</v>
+        <v>23</v>
       </c>
       <c r="AF3">
-        <v>10.87</v>
+        <v>59.65</v>
       </c>
       <c r="AG3">
-        <v>569.3099999999999</v>
+        <v>569.9299999999999</v>
       </c>
       <c r="AH3">
-        <v>490.11</v>
+        <v>486.6</v>
       </c>
       <c r="AI3">
         <v>553.0599999999999</v>
@@ -1165,7 +1139,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>28.97</v>
+        <v>29.21</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1176,10 +1150,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>355.55</v>
+        <v>353.55</v>
       </c>
       <c r="D4">
-        <v>-1.89</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E4">
         <v>604.85</v>
@@ -1188,46 +1162,46 @@
         <v>303.75</v>
       </c>
       <c r="G4">
-        <v>-41.22</v>
+        <v>-41.55</v>
       </c>
       <c r="H4">
-        <v>17.05</v>
+        <v>16.4</v>
       </c>
       <c r="I4">
-        <v>-1.33</v>
+        <v>-2.86</v>
       </c>
       <c r="J4">
-        <v>6.37</v>
+        <v>6.12</v>
       </c>
       <c r="K4">
-        <v>3.78</v>
+        <v>3.95</v>
       </c>
       <c r="L4">
-        <v>-38.12</v>
+        <v>-38.11</v>
       </c>
       <c r="M4">
-        <v>-18.09</v>
+        <v>-18.16</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
       <c r="O4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P4">
-        <v>360.18</v>
+        <v>358.1</v>
       </c>
       <c r="Q4">
-        <v>347.39</v>
+        <v>348.56</v>
       </c>
       <c r="R4">
-        <v>333.86</v>
+        <v>334.68</v>
       </c>
       <c r="S4">
-        <v>393.25</v>
+        <v>392.38</v>
       </c>
       <c r="T4">
-        <v>-9.59</v>
+        <v>-9.9</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1242,34 +1216,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>55.19</v>
+        <v>53.79</v>
       </c>
       <c r="Z4">
-        <v>8.26</v>
+        <v>7.43</v>
       </c>
       <c r="AA4">
-        <v>7.8</v>
+        <v>7.73</v>
       </c>
       <c r="AB4">
-        <v>0.46</v>
+        <v>-0.3</v>
       </c>
       <c r="AC4">
-        <v>32.03</v>
+        <v>18.92</v>
       </c>
       <c r="AD4">
-        <v>36.22</v>
+        <v>29.08</v>
       </c>
       <c r="AE4">
-        <v>14.01</v>
+        <v>13.6</v>
       </c>
       <c r="AF4">
-        <v>-62.63</v>
+        <v>-85.95</v>
       </c>
       <c r="AG4">
-        <v>382.45</v>
+        <v>382.75</v>
       </c>
       <c r="AH4">
-        <v>312.34</v>
+        <v>314.38</v>
       </c>
       <c r="AI4">
         <v>335.86</v>
@@ -1278,7 +1252,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>56.31</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1289,10 +1263,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>2011.2</v>
+        <v>2012</v>
       </c>
       <c r="D5">
-        <v>0.31</v>
+        <v>0.04</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1301,46 +1275,46 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-7.6</v>
+        <v>-7.56</v>
       </c>
       <c r="H5">
-        <v>23.25</v>
+        <v>23.3</v>
       </c>
       <c r="I5">
-        <v>-1.02</v>
+        <v>-0.42</v>
       </c>
       <c r="J5">
-        <v>8.039999999999999</v>
+        <v>5.86</v>
       </c>
       <c r="K5">
-        <v>13.5</v>
+        <v>14.83</v>
       </c>
       <c r="L5">
-        <v>5.41</v>
+        <v>5.1</v>
       </c>
       <c r="M5">
-        <v>6.08</v>
+        <v>6.13</v>
       </c>
       <c r="N5">
         <v>57</v>
       </c>
       <c r="O5">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P5">
-        <v>2014</v>
+        <v>2012.3</v>
       </c>
       <c r="Q5">
-        <v>1992.58</v>
+        <v>1999.36</v>
       </c>
       <c r="R5">
-        <v>1881.41</v>
+        <v>1887.79</v>
       </c>
       <c r="S5">
-        <v>1909.86</v>
+        <v>1909.34</v>
       </c>
       <c r="T5">
-        <v>5.31</v>
+        <v>5.38</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1355,34 +1329,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>57.72</v>
+        <v>57.84</v>
       </c>
       <c r="Z5">
-        <v>39.87</v>
+        <v>36.97</v>
       </c>
       <c r="AA5">
-        <v>48.37</v>
+        <v>46.09</v>
       </c>
       <c r="AB5">
-        <v>-8.5</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="AC5">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="AD5">
-        <v>4.33</v>
+        <v>2.46</v>
       </c>
       <c r="AE5">
-        <v>41.25</v>
+        <v>40.3</v>
       </c>
       <c r="AF5">
-        <v>-72.28</v>
+        <v>-36.26</v>
       </c>
       <c r="AG5">
-        <v>2142.66</v>
+        <v>2139.25</v>
       </c>
       <c r="AH5">
-        <v>1842.49</v>
+        <v>1859.46</v>
       </c>
       <c r="AI5">
         <v>1958.53</v>
@@ -1391,7 +1365,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>23.97</v>
+        <v>21.63</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1402,10 +1376,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>11254</v>
+        <v>11380</v>
       </c>
       <c r="D6">
-        <v>-1.93</v>
+        <v>1.12</v>
       </c>
       <c r="E6">
         <v>14451.52</v>
@@ -1414,46 +1388,46 @@
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-22.13</v>
+        <v>-21.25</v>
       </c>
       <c r="H6">
-        <v>28.68</v>
+        <v>30.12</v>
       </c>
       <c r="I6">
-        <v>-2.56</v>
+        <v>-1.72</v>
       </c>
       <c r="J6">
-        <v>9.27</v>
+        <v>8.94</v>
       </c>
       <c r="K6">
-        <v>7.51</v>
+        <v>9.4</v>
       </c>
       <c r="L6">
-        <v>-18.08</v>
+        <v>-17.83</v>
       </c>
       <c r="M6">
-        <v>23.72</v>
+        <v>24.15</v>
       </c>
       <c r="N6">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="O6">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P6">
-        <v>11456.6</v>
+        <v>11416.8</v>
       </c>
       <c r="Q6">
-        <v>11208.35</v>
+        <v>11256.1</v>
       </c>
       <c r="R6">
-        <v>10802.06</v>
+        <v>10824.6</v>
       </c>
       <c r="S6">
-        <v>10766.98</v>
+        <v>10761.64</v>
       </c>
       <c r="T6">
-        <v>4.52</v>
+        <v>5.75</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1468,34 +1442,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>54.08</v>
+        <v>57.7</v>
       </c>
       <c r="Z6">
-        <v>210.42</v>
+        <v>196.64</v>
       </c>
       <c r="AA6">
-        <v>224.22</v>
+        <v>218.7</v>
       </c>
       <c r="AB6">
-        <v>-13.8</v>
+        <v>-22.06</v>
       </c>
       <c r="AC6">
-        <v>15.73</v>
+        <v>12.07</v>
       </c>
       <c r="AD6">
-        <v>29.59</v>
+        <v>18.77</v>
       </c>
       <c r="AE6">
-        <v>228.15</v>
+        <v>222.49</v>
       </c>
       <c r="AF6">
-        <v>-60.63</v>
+        <v>-52.16</v>
       </c>
       <c r="AG6">
-        <v>11942.27</v>
+        <v>11893.32</v>
       </c>
       <c r="AH6">
-        <v>10474.43</v>
+        <v>10618.88</v>
       </c>
       <c r="AI6">
         <v>10787.84</v>
@@ -1504,7 +1478,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>41.81</v>
+        <v>36.53</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1515,10 +1489,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>1094.3</v>
+        <v>1080.2</v>
       </c>
       <c r="D7">
-        <v>0.46</v>
+        <v>-1.29</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1527,46 +1501,46 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-5.57</v>
+        <v>-6.78</v>
       </c>
       <c r="H7">
-        <v>36.52</v>
+        <v>34.76</v>
       </c>
       <c r="I7">
-        <v>0.09</v>
+        <v>-1.28</v>
       </c>
       <c r="J7">
-        <v>2.85</v>
+        <v>1.03</v>
       </c>
       <c r="K7">
-        <v>18.55</v>
+        <v>19.01</v>
       </c>
       <c r="L7">
-        <v>28.29</v>
+        <v>25.6</v>
       </c>
       <c r="M7">
-        <v>11.25</v>
+        <v>10.58</v>
       </c>
       <c r="N7">
         <v>71</v>
       </c>
       <c r="O7">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P7">
-        <v>1091.12</v>
+        <v>1088.32</v>
       </c>
       <c r="Q7">
-        <v>1089.67</v>
+        <v>1090.67</v>
       </c>
       <c r="R7">
-        <v>1029.43</v>
+        <v>1033.3</v>
       </c>
       <c r="S7">
-        <v>974.39</v>
+        <v>974.53</v>
       </c>
       <c r="T7">
-        <v>12.31</v>
+        <v>10.84</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1581,34 +1555,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>55.4</v>
+        <v>51.47</v>
       </c>
       <c r="Z7">
-        <v>18.48</v>
+        <v>15.98</v>
       </c>
       <c r="AA7">
-        <v>25.01</v>
+        <v>23.21</v>
       </c>
       <c r="AB7">
-        <v>-6.53</v>
+        <v>-7.23</v>
       </c>
       <c r="AC7">
-        <v>5.97</v>
+        <v>5.07</v>
       </c>
       <c r="AD7">
-        <v>6.86</v>
+        <v>5.3</v>
       </c>
       <c r="AE7">
-        <v>25.65</v>
+        <v>25.1</v>
       </c>
       <c r="AF7">
-        <v>-64.43000000000001</v>
+        <v>-68.72</v>
       </c>
       <c r="AG7">
         <v>1173.76</v>
       </c>
       <c r="AH7">
-        <v>1005.58</v>
+        <v>1007.57</v>
       </c>
       <c r="AI7">
         <v>1067.72</v>
@@ -1617,7 +1591,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>22.69</v>
+        <v>23.66</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1628,10 +1602,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>135.69</v>
+        <v>134.57</v>
       </c>
       <c r="D8">
-        <v>1.16</v>
+        <v>-0.83</v>
       </c>
       <c r="E8">
         <v>148.95</v>
@@ -1640,46 +1614,46 @@
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>-8.9</v>
+        <v>-9.65</v>
       </c>
       <c r="H8">
-        <v>17.01</v>
+        <v>16.05</v>
       </c>
       <c r="I8">
-        <v>-3.5</v>
+        <v>-0.73</v>
       </c>
       <c r="J8">
-        <v>-5.68</v>
+        <v>-7.75</v>
       </c>
       <c r="K8">
-        <v>-3.79</v>
+        <v>-4.49</v>
       </c>
       <c r="L8">
-        <v>1.3</v>
+        <v>-0.28</v>
       </c>
       <c r="M8">
-        <v>-1.49</v>
+        <v>-0.67</v>
       </c>
       <c r="N8">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="O8">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P8">
-        <v>135.03</v>
+        <v>134.83</v>
       </c>
       <c r="Q8">
-        <v>139.56</v>
+        <v>139.17</v>
       </c>
       <c r="R8">
-        <v>137.3</v>
+        <v>137.23</v>
       </c>
       <c r="S8">
-        <v>133.69</v>
+        <v>133.65</v>
       </c>
       <c r="T8">
-        <v>1.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1694,34 +1668,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>42.42</v>
+        <v>40.03</v>
       </c>
       <c r="Z8">
-        <v>-0.75</v>
+        <v>-0.95</v>
       </c>
       <c r="AA8">
-        <v>0.27</v>
+        <v>0.03</v>
       </c>
       <c r="AB8">
-        <v>-1.02</v>
+        <v>-0.97</v>
       </c>
       <c r="AC8">
-        <v>7.04</v>
+        <v>10.57</v>
       </c>
       <c r="AD8">
-        <v>2.47</v>
+        <v>5.93</v>
       </c>
       <c r="AE8">
-        <v>4.12</v>
+        <v>4.01</v>
       </c>
       <c r="AF8">
-        <v>-63.9</v>
+        <v>-67.7</v>
       </c>
       <c r="AG8">
-        <v>145.76</v>
+        <v>145.59</v>
       </c>
       <c r="AH8">
-        <v>133.37</v>
+        <v>132.75</v>
       </c>
       <c r="AI8">
         <v>131.91</v>
@@ -1730,7 +1704,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>39.96</v>
+        <v>42.45</v>
       </c>
     </row>
   </sheetData>
@@ -1871,7 +1845,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1911,7 +1885,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>55</v>
@@ -1923,1068 +1897,1028 @@
         <v>57</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>10.31</v>
+      </c>
+      <c r="D7" s="6">
+        <v>11.93</v>
+      </c>
+      <c r="E7" s="7">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-10.19</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-4.67</v>
+      </c>
+      <c r="E8" s="7">
+        <v>5.52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>6.37</v>
+      </c>
+      <c r="D9" s="6">
+        <v>6.12</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="D10" s="6">
+        <v>5.86</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-2.18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>9.27</v>
+      </c>
+      <c r="D11" s="6">
+        <v>8.94</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>2.85</v>
+      </c>
+      <c r="D12" s="6">
+        <v>1.03</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-1.82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-5.68</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-7.75</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-2.07</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="B14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-0.47</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-10.52</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-6.98</v>
+      </c>
+      <c r="E15" s="7">
+        <v>3.54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-1.33</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-2.86</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-1.53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-1.02</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-0.42</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-2.56</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-1.72</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0.09</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-1.28</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-1.37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-3.5</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-0.73</v>
+      </c>
+      <c r="E20" s="7">
+        <v>2.77</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>13.25</v>
-      </c>
-      <c r="D9" s="7">
-        <v>10.31</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-2.94</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>43.6</v>
+      </c>
+      <c r="D21" s="6">
+        <v>43.16</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>-9.59</v>
-      </c>
-      <c r="D10" s="7">
-        <v>-10.19</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="6">
+        <v>115.1</v>
+      </c>
+      <c r="D22" s="6">
+        <v>124.8</v>
+      </c>
+      <c r="E22" s="7">
+        <v>9.699999999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>7.89</v>
-      </c>
-      <c r="D11" s="7">
-        <v>6.37</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-1.52</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-38.12</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-38.11</v>
+      </c>
+      <c r="E23" s="7">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>9.23</v>
-      </c>
-      <c r="D12" s="7">
-        <v>8.039999999999999</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-1.19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>5.41</v>
+      </c>
+      <c r="D24" s="6">
+        <v>5.1</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>10.16</v>
-      </c>
-      <c r="D13" s="7">
-        <v>9.27</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-0.89</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-18.08</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-17.83</v>
+      </c>
+      <c r="E25" s="7">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>4.76</v>
-      </c>
-      <c r="D14" s="7">
-        <v>2.85</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-1.91</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>28.29</v>
+      </c>
+      <c r="D26" s="6">
+        <v>25.6</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-2.69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="7">
-        <v>-8.25</v>
-      </c>
-      <c r="D15" s="7">
-        <v>-5.68</v>
-      </c>
-      <c r="E15" s="9">
-        <v>2.57</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>1.3</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-0.28</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-1.58</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="7">
-        <v>0.33</v>
-      </c>
-      <c r="D16" s="7">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-1.27</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="6">
+        <v>12.5</v>
+      </c>
+      <c r="D28" s="6">
+        <v>10.7</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-1.8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-6.86</v>
-      </c>
-      <c r="D17" s="7">
-        <v>-10.52</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-3.66</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-11.97</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-8.41</v>
+      </c>
+      <c r="E29" s="7">
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-2.36</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-1.33</v>
-      </c>
-      <c r="E18" s="9">
-        <v>1.03</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="6">
+        <v>3.78</v>
+      </c>
+      <c r="D30" s="6">
+        <v>3.95</v>
+      </c>
+      <c r="E30" s="7">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>-0.03</v>
-      </c>
-      <c r="D19" s="7">
-        <v>-1.02</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-0.99</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="6">
+        <v>13.5</v>
+      </c>
+      <c r="D31" s="6">
+        <v>14.83</v>
+      </c>
+      <c r="E31" s="7">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>1.88</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-2.56</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-4.44</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="6">
+        <v>7.51</v>
+      </c>
+      <c r="D32" s="6">
+        <v>9.4</v>
+      </c>
+      <c r="E32" s="7">
+        <v>1.89</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>0.83</v>
-      </c>
-      <c r="D21" s="7">
-        <v>0.09</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-0.74</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6">
+        <v>18.55</v>
+      </c>
+      <c r="D33" s="6">
+        <v>19.01</v>
+      </c>
+      <c r="E33" s="7">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="7">
-        <v>-6.34</v>
-      </c>
-      <c r="D22" s="7">
-        <v>-3.5</v>
-      </c>
-      <c r="E22" s="9">
-        <v>2.84</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-3.79</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-4.49</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="7">
-        <v>44.27</v>
-      </c>
-      <c r="D23" s="7">
-        <v>43.6</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-0.67</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B35" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-2.1</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-1.78</v>
+      </c>
+      <c r="E35" s="7">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="7">
-        <v>119.39</v>
-      </c>
-      <c r="D24" s="7">
-        <v>115.1</v>
-      </c>
-      <c r="E24" s="8">
+      <c r="B36" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-27.78</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-25.3</v>
+      </c>
+      <c r="E36" s="7">
+        <v>2.48</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-41.22</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-41.55</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-7.6</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-7.56</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-22.13</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-21.25</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-5.57</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-6.78</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-1.21</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-8.9</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-9.65</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="6">
+        <v>11607</v>
+      </c>
+      <c r="D42" s="6">
+        <v>11645</v>
+      </c>
+      <c r="E42" s="7">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="6">
+        <v>484.05</v>
+      </c>
+      <c r="D43" s="6">
+        <v>500.7</v>
+      </c>
+      <c r="E43" s="7">
+        <v>16.65</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="6">
+        <v>355.55</v>
+      </c>
+      <c r="D44" s="6">
+        <v>353.55</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="6">
+        <v>2011.2</v>
+      </c>
+      <c r="D45" s="6">
+        <v>2012</v>
+      </c>
+      <c r="E45" s="7">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="6">
+        <v>11254</v>
+      </c>
+      <c r="D46" s="6">
+        <v>11380</v>
+      </c>
+      <c r="E46" s="7">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="6">
+        <v>1094.3</v>
+      </c>
+      <c r="D47" s="6">
+        <v>1080.2</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-14.1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="6">
+        <v>135.69</v>
+      </c>
+      <c r="D48" s="6">
+        <v>134.57</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-1.12</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49" s="6">
+        <v>29</v>
+      </c>
+      <c r="D49" s="6">
+        <v>43</v>
+      </c>
+      <c r="E49" s="7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" s="6">
+        <v>43</v>
+      </c>
+      <c r="D50" s="6">
+        <v>29</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="6">
+        <v>62.31</v>
+      </c>
+      <c r="D51" s="6">
+        <v>63.33</v>
+      </c>
+      <c r="E51" s="7">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="6">
+        <v>32.29</v>
+      </c>
+      <c r="D52" s="6">
+        <v>39.01</v>
+      </c>
+      <c r="E52" s="7">
+        <v>6.72</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="6">
+        <v>55.19</v>
+      </c>
+      <c r="D53" s="6">
+        <v>53.79</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-1.4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="6">
+        <v>57.72</v>
+      </c>
+      <c r="D54" s="6">
+        <v>57.84</v>
+      </c>
+      <c r="E54" s="7">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="6">
+        <v>54.08</v>
+      </c>
+      <c r="D55" s="6">
+        <v>57.7</v>
+      </c>
+      <c r="E55" s="7">
+        <v>3.62</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="6">
+        <v>55.4</v>
+      </c>
+      <c r="D56" s="6">
+        <v>51.47</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-3.93</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="6">
+        <v>42.42</v>
+      </c>
+      <c r="D57" s="6">
+        <v>40.03</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-2.39</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="6">
+        <v>-40.39</v>
+      </c>
+      <c r="D58" s="6">
+        <v>-43.47</v>
+      </c>
+      <c r="E58" s="8">
+        <v>-3.08</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="6">
+        <v>10.87</v>
+      </c>
+      <c r="D59" s="6">
+        <v>59.65</v>
+      </c>
+      <c r="E59" s="7">
+        <v>48.78</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="6">
+        <v>-62.63</v>
+      </c>
+      <c r="D60" s="6">
+        <v>-85.95</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-23.32</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="6">
+        <v>-72.28</v>
+      </c>
+      <c r="D61" s="6">
+        <v>-36.26</v>
+      </c>
+      <c r="E61" s="7">
+        <v>36.02</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="6">
+        <v>-60.63</v>
+      </c>
+      <c r="D62" s="6">
+        <v>-52.16</v>
+      </c>
+      <c r="E62" s="7">
+        <v>8.470000000000001</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="6">
+        <v>-64.43000000000001</v>
+      </c>
+      <c r="D63" s="6">
+        <v>-68.72</v>
+      </c>
+      <c r="E63" s="8">
         <v>-4.29</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="7">
-        <v>-37.99</v>
-      </c>
-      <c r="D25" s="7">
-        <v>-38.12</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-0.13</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="7">
-        <v>4.64</v>
-      </c>
-      <c r="D26" s="7">
-        <v>5.41</v>
-      </c>
-      <c r="E26" s="9">
-        <v>0.77</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="7">
-        <v>-15.94</v>
-      </c>
-      <c r="D27" s="7">
-        <v>-18.08</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-2.14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7">
-        <v>23.92</v>
-      </c>
-      <c r="D28" s="7">
-        <v>28.29</v>
-      </c>
-      <c r="E28" s="9">
-        <v>4.37</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="7">
-        <v>-1.51</v>
-      </c>
-      <c r="D29" s="7">
-        <v>1.3</v>
-      </c>
-      <c r="E29" s="9">
-        <v>2.81</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="7">
-        <v>16.34</v>
-      </c>
-      <c r="D30" s="7">
-        <v>12.5</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-3.84</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-3.97</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-11.97</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-8</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="7">
-        <v>1.57</v>
-      </c>
-      <c r="D32" s="7">
-        <v>3.78</v>
-      </c>
-      <c r="E32" s="9">
-        <v>2.21</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="7">
-        <v>14.56</v>
-      </c>
-      <c r="D33" s="7">
-        <v>13.5</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-1.06</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="7">
-        <v>10.69</v>
-      </c>
-      <c r="D34" s="7">
-        <v>7.51</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-3.18</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="7">
-        <v>18.01</v>
-      </c>
-      <c r="D35" s="7">
-        <v>18.55</v>
-      </c>
-      <c r="E35" s="9">
-        <v>0.54</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="7">
-        <v>-9.94</v>
-      </c>
-      <c r="D36" s="7">
-        <v>-3.79</v>
-      </c>
-      <c r="E36" s="9">
-        <v>6.15</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="7">
-        <v>-1.32</v>
-      </c>
-      <c r="D37" s="7">
-        <v>-2.1</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-0.78</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="7">
-        <v>-25.31</v>
-      </c>
-      <c r="D38" s="7">
-        <v>-27.78</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-2.47</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="7">
-        <v>-40.08</v>
-      </c>
-      <c r="D39" s="7">
-        <v>-41.22</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-1.14</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="7">
-        <v>-7.73</v>
-      </c>
-      <c r="D40" s="7">
-        <v>-7.6</v>
-      </c>
-      <c r="E40" s="9">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="7">
-        <v>-20.6</v>
-      </c>
-      <c r="D41" s="7">
-        <v>-22.13</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-1.53</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="7">
-        <v>-6.2</v>
-      </c>
-      <c r="D42" s="7">
-        <v>-5.57</v>
-      </c>
-      <c r="E42" s="9">
-        <v>0.63</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="7">
-        <v>-9.94</v>
-      </c>
-      <c r="D43" s="7">
-        <v>-8.9</v>
-      </c>
-      <c r="E43" s="9">
-        <v>1.04</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="7">
-        <v>11700</v>
-      </c>
-      <c r="D44" s="7">
-        <v>11607</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-93</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="7">
-        <v>500.6</v>
-      </c>
-      <c r="D45" s="7">
-        <v>484.05</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-16.55</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="7">
-        <v>362.4</v>
-      </c>
-      <c r="D46" s="7">
-        <v>355.55</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-6.85</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="7">
-        <v>2008.3</v>
-      </c>
-      <c r="D47" s="7">
-        <v>2011.2</v>
-      </c>
-      <c r="E47" s="9">
-        <v>2.9</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="7">
-        <v>11475</v>
-      </c>
-      <c r="D48" s="7">
-        <v>11254</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-221</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="7">
-        <v>1087</v>
-      </c>
-      <c r="D49" s="7">
-        <v>1094.3</v>
-      </c>
-      <c r="E49" s="9">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="7">
-        <v>134.14</v>
-      </c>
-      <c r="D50" s="7">
-        <v>135.69</v>
-      </c>
-      <c r="E50" s="9">
-        <v>1.55</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C51" s="7">
-        <v>43</v>
-      </c>
-      <c r="D51" s="7">
-        <v>29</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C52" s="7">
-        <v>29</v>
-      </c>
-      <c r="D52" s="7">
-        <v>43</v>
-      </c>
-      <c r="E52" s="9">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="7">
-        <v>66.52</v>
-      </c>
-      <c r="D53" s="7">
-        <v>62.31</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-4.21</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="7">
-        <v>35.07</v>
-      </c>
-      <c r="D54" s="7">
-        <v>32.29</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-2.78</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="7">
-        <v>60.17</v>
-      </c>
-      <c r="D55" s="7">
-        <v>55.19</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-4.98</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="7">
-        <v>57.43</v>
-      </c>
-      <c r="D56" s="7">
-        <v>57.72</v>
-      </c>
-      <c r="E56" s="9">
-        <v>0.29</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="7">
-        <v>62.84</v>
-      </c>
-      <c r="D57" s="7">
-        <v>54.08</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-8.76</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="7">
-        <v>53.74</v>
-      </c>
-      <c r="D58" s="7">
-        <v>55.4</v>
-      </c>
-      <c r="E58" s="9">
-        <v>1.66</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="7">
-        <v>37.64</v>
-      </c>
-      <c r="D59" s="7">
-        <v>42.42</v>
-      </c>
-      <c r="E59" s="9">
-        <v>4.78</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B60" s="6" t="s">
+      <c r="B64" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C60" s="7">
-        <v>-42.3</v>
-      </c>
-      <c r="D60" s="7">
-        <v>-40.39</v>
-      </c>
-      <c r="E60" s="9">
-        <v>1.91</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="7">
-        <v>41.39</v>
-      </c>
-      <c r="D61" s="7">
-        <v>10.87</v>
-      </c>
-      <c r="E61" s="8">
-        <v>-30.52</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="7">
-        <v>-62.4</v>
-      </c>
-      <c r="D62" s="7">
-        <v>-62.63</v>
-      </c>
-      <c r="E62" s="8">
-        <v>-0.23</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="7">
-        <v>-36.61</v>
-      </c>
-      <c r="D63" s="7">
-        <v>-72.28</v>
-      </c>
-      <c r="E63" s="8">
-        <v>-35.67</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="7">
-        <v>-39.92</v>
-      </c>
-      <c r="D64" s="7">
-        <v>-60.63</v>
+      <c r="C64" s="6">
+        <v>-63.9</v>
+      </c>
+      <c r="D64" s="6">
+        <v>-67.7</v>
       </c>
       <c r="E64" s="8">
-        <v>-20.71</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="7">
-        <v>-58.65</v>
-      </c>
-      <c r="D65" s="7">
-        <v>-64.43000000000001</v>
-      </c>
-      <c r="E65" s="8">
-        <v>-5.78</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="7">
-        <v>-62.13</v>
-      </c>
-      <c r="D66" s="7">
-        <v>-63.9</v>
-      </c>
-      <c r="E66" s="8">
-        <v>-1.77</v>
+        <v>-3.8</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3004,60 +2938,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="G1" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="F1" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>76</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="11">
         <v>68.8</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="12">
         <v>7</v>
       </c>
-      <c r="D2" s="12">
-        <v>51.3</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="11">
+        <v>51.9</v>
+      </c>
+      <c r="E2" s="11">
         <v>90</v>
       </c>
-      <c r="F2" s="12">
-        <v>3</v>
-      </c>
-      <c r="G2" s="12">
-        <v>5.7</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="F2" s="11">
+        <v>3.1</v>
+      </c>
+      <c r="G2" s="11">
+        <v>6.4</v>
+      </c>
+      <c r="H2" s="11">
         <v>57</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>60</v>
       </c>
     </row>
@@ -3159,49 +3093,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="15">
-        <v>0.2769</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.2372</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.1634</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.1125</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0.0608</v>
-      </c>
-      <c r="F2" s="15">
-        <v>-0.0149</v>
-      </c>
-      <c r="G2" s="15">
-        <v>-0.1809</v>
+      <c r="A2" s="14">
+        <v>0.2834</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.2415</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.174</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.1058</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.0613</v>
+      </c>
+      <c r="F2" s="14">
+        <v>-0.0067</v>
+      </c>
+      <c r="G2" s="14">
+        <v>-0.1816</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="64">
   <si>
     <t>Symbol</t>
   </si>
@@ -172,34 +172,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>Near 52W High</t>
-  </si>
-  <si>
-    <t>-2.1% → -1.8%</t>
-  </si>
-  <si>
-    <t>🟢 BREAKOUT WATCH</t>
-  </si>
-  <si>
-    <t>-2.1%</t>
-  </si>
-  <si>
-    <t>-1.8%</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -285,14 +258,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -325,13 +298,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -401,15 +374,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -783,8 +755,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -924,37 +896,37 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>11645</v>
+        <v>11793</v>
       </c>
       <c r="D2">
-        <v>0.33</v>
+        <v>1.27</v>
       </c>
       <c r="E2">
         <v>11856</v>
       </c>
       <c r="F2">
-        <v>8099.51</v>
+        <v>8469.309999999999</v>
       </c>
       <c r="G2">
-        <v>-1.78</v>
+        <v>-0.53</v>
       </c>
       <c r="H2">
-        <v>43.77</v>
+        <v>39.24</v>
       </c>
       <c r="I2">
-        <v>-0.47</v>
+        <v>1.13</v>
       </c>
       <c r="J2">
-        <v>11.93</v>
+        <v>7.22</v>
       </c>
       <c r="K2">
-        <v>10.7</v>
+        <v>13.36</v>
       </c>
       <c r="L2">
-        <v>43.16</v>
+        <v>45.6</v>
       </c>
       <c r="M2">
-        <v>28.34</v>
+        <v>28.65</v>
       </c>
       <c r="N2">
         <v>85</v>
@@ -963,19 +935,19 @@
         <v>83</v>
       </c>
       <c r="P2">
-        <v>11662.6</v>
+        <v>11689</v>
       </c>
       <c r="Q2">
-        <v>11560.32</v>
+        <v>11585.8</v>
       </c>
       <c r="R2">
-        <v>10688.48</v>
+        <v>10721.46</v>
       </c>
       <c r="S2">
-        <v>9727.68</v>
+        <v>9742.799999999999</v>
       </c>
       <c r="T2">
-        <v>19.71</v>
+        <v>21.04</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -990,43 +962,43 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>63.33</v>
+        <v>67.08</v>
       </c>
       <c r="Z2">
-        <v>283.97</v>
+        <v>278.14</v>
       </c>
       <c r="AA2">
-        <v>331.91</v>
+        <v>321.15</v>
       </c>
       <c r="AB2">
-        <v>-47.94</v>
+        <v>-43.01</v>
       </c>
       <c r="AC2">
-        <v>4.25</v>
+        <v>11.84</v>
       </c>
       <c r="AD2">
-        <v>4.3</v>
+        <v>6.81</v>
       </c>
       <c r="AE2">
-        <v>210.22</v>
+        <v>207.56</v>
       </c>
       <c r="AF2">
-        <v>-43.47</v>
+        <v>-58.53</v>
       </c>
       <c r="AG2">
-        <v>11966.21</v>
+        <v>11982.38</v>
       </c>
       <c r="AH2">
-        <v>11154.44</v>
+        <v>11189.22</v>
       </c>
       <c r="AI2">
-        <v>11083.45</v>
+        <v>11083.81</v>
       </c>
       <c r="AJ2" t="s">
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>61.63</v>
+        <v>57.32</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1037,10 +1009,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>500.7</v>
+        <v>486.95</v>
       </c>
       <c r="D3">
-        <v>3.44</v>
+        <v>-2.75</v>
       </c>
       <c r="E3">
         <v>670.25</v>
@@ -1049,46 +1021,46 @@
         <v>222.01</v>
       </c>
       <c r="G3">
-        <v>-25.3</v>
+        <v>-27.35</v>
       </c>
       <c r="H3">
-        <v>125.53</v>
+        <v>119.34</v>
       </c>
       <c r="I3">
-        <v>-6.98</v>
+        <v>-7.71</v>
       </c>
       <c r="J3">
-        <v>-4.67</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="K3">
-        <v>-8.41</v>
+        <v>-14.83</v>
       </c>
       <c r="L3">
-        <v>124.8</v>
+        <v>117.65</v>
       </c>
       <c r="M3">
-        <v>17.4</v>
+        <v>16.73</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="P3">
-        <v>498.88</v>
+        <v>490.74</v>
       </c>
       <c r="Q3">
-        <v>528.26</v>
+        <v>524.8200000000001</v>
       </c>
       <c r="R3">
-        <v>567.9299999999999</v>
+        <v>566.41</v>
       </c>
       <c r="S3">
-        <v>418.76</v>
+        <v>419.81</v>
       </c>
       <c r="T3">
-        <v>19.57</v>
+        <v>15.99</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1103,34 +1075,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>39.01</v>
+        <v>35.85</v>
       </c>
       <c r="Z3">
-        <v>-18.28</v>
+        <v>-19.22</v>
       </c>
       <c r="AA3">
-        <v>-14.94</v>
+        <v>-15.8</v>
       </c>
       <c r="AB3">
-        <v>-3.34</v>
+        <v>-3.42</v>
       </c>
       <c r="AC3">
-        <v>17.87</v>
+        <v>27.2</v>
       </c>
       <c r="AD3">
-        <v>10.58</v>
+        <v>15.77</v>
       </c>
       <c r="AE3">
-        <v>23</v>
+        <v>22.57</v>
       </c>
       <c r="AF3">
-        <v>59.65</v>
+        <v>-37.85</v>
       </c>
       <c r="AG3">
-        <v>569.9299999999999</v>
+        <v>568.23</v>
       </c>
       <c r="AH3">
-        <v>486.6</v>
+        <v>481.4</v>
       </c>
       <c r="AI3">
         <v>553.0599999999999</v>
@@ -1139,7 +1111,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>29.21</v>
+        <v>29.41</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1150,10 +1122,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>353.55</v>
+        <v>354.35</v>
       </c>
       <c r="D4">
-        <v>-0.5600000000000001</v>
+        <v>0.23</v>
       </c>
       <c r="E4">
         <v>604.85</v>
@@ -1162,46 +1134,46 @@
         <v>303.75</v>
       </c>
       <c r="G4">
-        <v>-41.55</v>
+        <v>-41.42</v>
       </c>
       <c r="H4">
-        <v>16.4</v>
+        <v>16.66</v>
       </c>
       <c r="I4">
-        <v>-2.86</v>
+        <v>-0.63</v>
       </c>
       <c r="J4">
-        <v>6.12</v>
+        <v>7.33</v>
       </c>
       <c r="K4">
-        <v>3.95</v>
+        <v>5.45</v>
       </c>
       <c r="L4">
-        <v>-38.11</v>
+        <v>-37.28</v>
       </c>
       <c r="M4">
-        <v>-18.16</v>
+        <v>-18.12</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
       <c r="O4">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="P4">
-        <v>358.1</v>
+        <v>357.65</v>
       </c>
       <c r="Q4">
-        <v>348.56</v>
+        <v>349.97</v>
       </c>
       <c r="R4">
-        <v>334.68</v>
+        <v>335.59</v>
       </c>
       <c r="S4">
-        <v>392.38</v>
+        <v>391.58</v>
       </c>
       <c r="T4">
-        <v>-9.9</v>
+        <v>-9.51</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1216,34 +1188,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>53.79</v>
+        <v>54.29</v>
       </c>
       <c r="Z4">
-        <v>7.43</v>
+        <v>6.77</v>
       </c>
       <c r="AA4">
-        <v>7.73</v>
+        <v>7.54</v>
       </c>
       <c r="AB4">
-        <v>-0.3</v>
+        <v>-0.77</v>
       </c>
       <c r="AC4">
-        <v>18.92</v>
+        <v>7.48</v>
       </c>
       <c r="AD4">
-        <v>29.08</v>
+        <v>19.48</v>
       </c>
       <c r="AE4">
-        <v>13.6</v>
+        <v>13.01</v>
       </c>
       <c r="AF4">
-        <v>-85.95</v>
+        <v>-87.95</v>
       </c>
       <c r="AG4">
-        <v>382.75</v>
+        <v>382.56</v>
       </c>
       <c r="AH4">
-        <v>314.38</v>
+        <v>317.38</v>
       </c>
       <c r="AI4">
         <v>335.86</v>
@@ -1252,7 +1224,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>53.5</v>
+        <v>51.07</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1263,10 +1235,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="D5">
-        <v>0.04</v>
+        <v>0.2</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1275,46 +1247,46 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-7.56</v>
+        <v>-7.38</v>
       </c>
       <c r="H5">
-        <v>23.3</v>
+        <v>23.54</v>
       </c>
       <c r="I5">
-        <v>-0.42</v>
+        <v>-0.44</v>
       </c>
       <c r="J5">
-        <v>5.86</v>
+        <v>7.44</v>
       </c>
       <c r="K5">
-        <v>14.83</v>
+        <v>14.16</v>
       </c>
       <c r="L5">
-        <v>5.1</v>
+        <v>4.72</v>
       </c>
       <c r="M5">
-        <v>6.13</v>
+        <v>6.17</v>
       </c>
       <c r="N5">
         <v>57</v>
       </c>
       <c r="O5">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P5">
-        <v>2012.3</v>
+        <v>2010.5</v>
       </c>
       <c r="Q5">
-        <v>1999.36</v>
+        <v>2005.69</v>
       </c>
       <c r="R5">
-        <v>1887.79</v>
+        <v>1894.82</v>
       </c>
       <c r="S5">
-        <v>1909.34</v>
+        <v>1908.98</v>
       </c>
       <c r="T5">
-        <v>5.38</v>
+        <v>5.61</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1329,34 +1301,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>57.84</v>
+        <v>58.49</v>
       </c>
       <c r="Z5">
-        <v>36.97</v>
+        <v>34.6</v>
       </c>
       <c r="AA5">
-        <v>46.09</v>
+        <v>43.8</v>
       </c>
       <c r="AB5">
-        <v>-9.119999999999999</v>
+        <v>-9.19</v>
       </c>
       <c r="AC5">
-        <v>3.2</v>
+        <v>5.97</v>
       </c>
       <c r="AD5">
-        <v>2.46</v>
+        <v>3.55</v>
       </c>
       <c r="AE5">
-        <v>40.3</v>
+        <v>38.72</v>
       </c>
       <c r="AF5">
-        <v>-36.26</v>
+        <v>-70.34</v>
       </c>
       <c r="AG5">
-        <v>2139.25</v>
+        <v>2135.74</v>
       </c>
       <c r="AH5">
-        <v>1859.46</v>
+        <v>1875.63</v>
       </c>
       <c r="AI5">
         <v>1958.53</v>
@@ -1365,7 +1337,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>21.63</v>
+        <v>20.13</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1376,10 +1348,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>11380</v>
+        <v>11368</v>
       </c>
       <c r="D6">
-        <v>1.12</v>
+        <v>-0.11</v>
       </c>
       <c r="E6">
         <v>14451.52</v>
@@ -1388,46 +1360,46 @@
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-21.25</v>
+        <v>-21.34</v>
       </c>
       <c r="H6">
-        <v>30.12</v>
+        <v>29.98</v>
       </c>
       <c r="I6">
-        <v>-1.72</v>
+        <v>-1.15</v>
       </c>
       <c r="J6">
-        <v>8.94</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="K6">
-        <v>9.4</v>
+        <v>8.44</v>
       </c>
       <c r="L6">
-        <v>-17.83</v>
+        <v>-19.18</v>
       </c>
       <c r="M6">
-        <v>24.15</v>
+        <v>24.11</v>
       </c>
       <c r="N6">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="O6">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="P6">
-        <v>11416.8</v>
+        <v>11390.4</v>
       </c>
       <c r="Q6">
-        <v>11256.1</v>
+        <v>11292.7</v>
       </c>
       <c r="R6">
-        <v>10824.6</v>
+        <v>10851.26</v>
       </c>
       <c r="S6">
-        <v>10761.64</v>
+        <v>10756.97</v>
       </c>
       <c r="T6">
-        <v>5.75</v>
+        <v>5.68</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1442,34 +1414,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>57.7</v>
+        <v>57.24</v>
       </c>
       <c r="Z6">
-        <v>196.64</v>
+        <v>182.65</v>
       </c>
       <c r="AA6">
-        <v>218.7</v>
+        <v>211.49</v>
       </c>
       <c r="AB6">
-        <v>-22.06</v>
+        <v>-28.84</v>
       </c>
       <c r="AC6">
-        <v>12.07</v>
+        <v>11.6</v>
       </c>
       <c r="AD6">
-        <v>18.77</v>
+        <v>13.13</v>
       </c>
       <c r="AE6">
-        <v>222.49</v>
+        <v>215.17</v>
       </c>
       <c r="AF6">
-        <v>-52.16</v>
+        <v>-45.29</v>
       </c>
       <c r="AG6">
-        <v>11893.32</v>
+        <v>11860.23</v>
       </c>
       <c r="AH6">
-        <v>10618.88</v>
+        <v>10725.17</v>
       </c>
       <c r="AI6">
         <v>10787.84</v>
@@ -1478,7 +1450,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>36.53</v>
+        <v>32.58</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1489,10 +1461,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>1080.2</v>
+        <v>1095</v>
       </c>
       <c r="D7">
-        <v>-1.29</v>
+        <v>1.37</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1501,25 +1473,25 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-6.78</v>
+        <v>-5.51</v>
       </c>
       <c r="H7">
-        <v>34.76</v>
+        <v>36.61</v>
       </c>
       <c r="I7">
-        <v>-1.28</v>
+        <v>0.39</v>
       </c>
       <c r="J7">
-        <v>1.03</v>
+        <v>3.27</v>
       </c>
       <c r="K7">
-        <v>19.01</v>
+        <v>19.47</v>
       </c>
       <c r="L7">
-        <v>25.6</v>
+        <v>27.11</v>
       </c>
       <c r="M7">
-        <v>10.58</v>
+        <v>10.87</v>
       </c>
       <c r="N7">
         <v>71</v>
@@ -1528,19 +1500,19 @@
         <v>78</v>
       </c>
       <c r="P7">
-        <v>1088.32</v>
+        <v>1089.16</v>
       </c>
       <c r="Q7">
-        <v>1090.67</v>
+        <v>1093.43</v>
       </c>
       <c r="R7">
-        <v>1033.3</v>
+        <v>1037.52</v>
       </c>
       <c r="S7">
-        <v>974.53</v>
+        <v>974.79</v>
       </c>
       <c r="T7">
-        <v>10.84</v>
+        <v>12.33</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1555,34 +1527,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>51.47</v>
+        <v>55.08</v>
       </c>
       <c r="Z7">
-        <v>15.98</v>
+        <v>15.01</v>
       </c>
       <c r="AA7">
-        <v>23.21</v>
+        <v>21.57</v>
       </c>
       <c r="AB7">
-        <v>-7.23</v>
+        <v>-6.56</v>
       </c>
       <c r="AC7">
-        <v>5.07</v>
+        <v>8.48</v>
       </c>
       <c r="AD7">
-        <v>5.3</v>
+        <v>6.51</v>
       </c>
       <c r="AE7">
-        <v>25.1</v>
+        <v>24.89</v>
       </c>
       <c r="AF7">
-        <v>-68.72</v>
+        <v>-25.15</v>
       </c>
       <c r="AG7">
-        <v>1173.76</v>
+        <v>1172.99</v>
       </c>
       <c r="AH7">
-        <v>1007.57</v>
+        <v>1013.86</v>
       </c>
       <c r="AI7">
         <v>1067.72</v>
@@ -1591,7 +1563,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>23.66</v>
+        <v>22.55</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1602,10 +1574,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>134.57</v>
+        <v>136.96</v>
       </c>
       <c r="D8">
-        <v>-0.83</v>
+        <v>1.78</v>
       </c>
       <c r="E8">
         <v>148.95</v>
@@ -1614,46 +1586,46 @@
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>-9.65</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="H8">
-        <v>16.05</v>
+        <v>18.11</v>
       </c>
       <c r="I8">
-        <v>-0.73</v>
+        <v>1</v>
       </c>
       <c r="J8">
-        <v>-7.75</v>
+        <v>-3.89</v>
       </c>
       <c r="K8">
-        <v>-4.49</v>
+        <v>-1.75</v>
       </c>
       <c r="L8">
-        <v>-0.28</v>
+        <v>1.26</v>
       </c>
       <c r="M8">
-        <v>-0.67</v>
+        <v>-0.32</v>
       </c>
       <c r="N8">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="O8">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="P8">
-        <v>134.83</v>
+        <v>135.1</v>
       </c>
       <c r="Q8">
-        <v>139.17</v>
+        <v>139.09</v>
       </c>
       <c r="R8">
-        <v>137.23</v>
+        <v>137.27</v>
       </c>
       <c r="S8">
-        <v>133.65</v>
+        <v>133.62</v>
       </c>
       <c r="T8">
-        <v>0.6899999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1668,34 +1640,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>40.03</v>
+        <v>46.9</v>
       </c>
       <c r="Z8">
-        <v>-0.95</v>
+        <v>-0.91</v>
       </c>
       <c r="AA8">
-        <v>0.03</v>
+        <v>-0.16</v>
       </c>
       <c r="AB8">
-        <v>-0.97</v>
+        <v>-0.75</v>
       </c>
       <c r="AC8">
-        <v>10.57</v>
+        <v>24.21</v>
       </c>
       <c r="AD8">
-        <v>5.93</v>
+        <v>13.94</v>
       </c>
       <c r="AE8">
-        <v>4.01</v>
+        <v>4.11</v>
       </c>
       <c r="AF8">
-        <v>-67.7</v>
+        <v>-49.95</v>
       </c>
       <c r="AG8">
-        <v>145.59</v>
+        <v>145.58</v>
       </c>
       <c r="AH8">
-        <v>132.75</v>
+        <v>132.6</v>
       </c>
       <c r="AI8">
         <v>131.91</v>
@@ -1704,7 +1676,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>42.45</v>
+        <v>38.83</v>
       </c>
     </row>
   </sheetData>
@@ -1865,47 +1837,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1913,1006 +1850,1006 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>64</v>
+      <c r="B6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>10.31</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>11.93</v>
       </c>
-      <c r="E7" s="7">
-        <v>1.62</v>
+      <c r="D7" s="5">
+        <v>7.22</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-4.71</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-10.19</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>-4.67</v>
       </c>
-      <c r="E8" s="7">
-        <v>5.52</v>
+      <c r="D8" s="5">
+        <v>-8.050000000000001</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-3.38</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>6.37</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>6.12</v>
       </c>
-      <c r="E9" s="8">
-        <v>-0.25</v>
+      <c r="D9" s="5">
+        <v>7.33</v>
+      </c>
+      <c r="E9" s="7">
+        <v>1.21</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>8.039999999999999</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>5.86</v>
       </c>
-      <c r="E10" s="8">
-        <v>-2.18</v>
+      <c r="D10" s="5">
+        <v>7.44</v>
+      </c>
+      <c r="E10" s="7">
+        <v>1.58</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>9.27</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>8.94</v>
       </c>
-      <c r="E11" s="8">
-        <v>-0.33</v>
+      <c r="D11" s="5">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0.11</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="6">
-        <v>2.85</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>1.03</v>
       </c>
-      <c r="E12" s="8">
-        <v>-1.82</v>
+      <c r="D12" s="5">
+        <v>3.27</v>
+      </c>
+      <c r="E12" s="7">
+        <v>2.24</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="6">
-        <v>-5.68</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>-7.75</v>
       </c>
-      <c r="E13" s="8">
-        <v>-2.07</v>
+      <c r="D13" s="5">
+        <v>-3.89</v>
+      </c>
+      <c r="E13" s="7">
+        <v>3.86</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="6">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" s="5">
         <v>-0.47</v>
       </c>
+      <c r="D14" s="5">
+        <v>1.13</v>
+      </c>
       <c r="E14" s="7">
-        <v>0.47</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="6">
-        <v>-10.52</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C15" s="5">
         <v>-6.98</v>
       </c>
-      <c r="E15" s="7">
-        <v>3.54</v>
+      <c r="D15" s="5">
+        <v>-7.71</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-0.73</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="6">
-        <v>-1.33</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C16" s="5">
         <v>-2.86</v>
       </c>
-      <c r="E16" s="8">
-        <v>-1.53</v>
+      <c r="D16" s="5">
+        <v>-0.63</v>
+      </c>
+      <c r="E16" s="7">
+        <v>2.23</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="6">
-        <v>-1.02</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C17" s="5">
         <v>-0.42</v>
       </c>
-      <c r="E17" s="7">
-        <v>0.6</v>
+      <c r="D17" s="5">
+        <v>-0.44</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-0.02</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="6">
-        <v>-2.56</v>
-      </c>
-      <c r="D18" s="6">
+      <c r="C18" s="5">
         <v>-1.72</v>
       </c>
+      <c r="D18" s="5">
+        <v>-1.15</v>
+      </c>
       <c r="E18" s="7">
-        <v>0.84</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="6">
-        <v>0.09</v>
-      </c>
-      <c r="D19" s="6">
+      <c r="C19" s="5">
         <v>-1.28</v>
       </c>
-      <c r="E19" s="8">
-        <v>-1.37</v>
+      <c r="D19" s="5">
+        <v>0.39</v>
+      </c>
+      <c r="E19" s="7">
+        <v>1.67</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="6">
-        <v>-3.5</v>
-      </c>
-      <c r="D20" s="6">
+      <c r="C20" s="5">
         <v>-0.73</v>
       </c>
+      <c r="D20" s="5">
+        <v>1</v>
+      </c>
       <c r="E20" s="7">
-        <v>2.77</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="6">
-        <v>43.6</v>
-      </c>
-      <c r="D21" s="6">
+      <c r="C21" s="5">
         <v>43.16</v>
       </c>
-      <c r="E21" s="8">
-        <v>-0.44</v>
+      <c r="D21" s="5">
+        <v>45.6</v>
+      </c>
+      <c r="E21" s="7">
+        <v>2.44</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="6">
-        <v>115.1</v>
-      </c>
-      <c r="D22" s="6">
+      <c r="C22" s="5">
         <v>124.8</v>
       </c>
-      <c r="E22" s="7">
-        <v>9.699999999999999</v>
+      <c r="D22" s="5">
+        <v>117.65</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-7.15</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="6">
-        <v>-38.12</v>
-      </c>
-      <c r="D23" s="6">
+      <c r="C23" s="5">
         <v>-38.11</v>
       </c>
+      <c r="D23" s="5">
+        <v>-37.28</v>
+      </c>
       <c r="E23" s="7">
-        <v>0.01</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="6">
-        <v>5.41</v>
-      </c>
-      <c r="D24" s="6">
+      <c r="C24" s="5">
         <v>5.1</v>
       </c>
-      <c r="E24" s="8">
-        <v>-0.31</v>
+      <c r="D24" s="5">
+        <v>4.72</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-0.38</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C25" s="6">
-        <v>-18.08</v>
-      </c>
-      <c r="D25" s="6">
+      <c r="C25" s="5">
         <v>-17.83</v>
       </c>
-      <c r="E25" s="7">
-        <v>0.25</v>
+      <c r="D25" s="5">
+        <v>-19.18</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-1.35</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C26" s="6">
-        <v>28.29</v>
-      </c>
-      <c r="D26" s="6">
+      <c r="C26" s="5">
         <v>25.6</v>
       </c>
-      <c r="E26" s="8">
-        <v>-2.69</v>
+      <c r="D26" s="5">
+        <v>27.11</v>
+      </c>
+      <c r="E26" s="7">
+        <v>1.51</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="6">
-        <v>1.3</v>
-      </c>
-      <c r="D27" s="6">
+      <c r="C27" s="5">
         <v>-0.28</v>
       </c>
-      <c r="E27" s="8">
-        <v>-1.58</v>
+      <c r="D27" s="5">
+        <v>1.26</v>
+      </c>
+      <c r="E27" s="7">
+        <v>1.54</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C28" s="6">
-        <v>12.5</v>
-      </c>
-      <c r="D28" s="6">
+      <c r="C28" s="5">
         <v>10.7</v>
       </c>
-      <c r="E28" s="8">
-        <v>-1.8</v>
+      <c r="D28" s="5">
+        <v>13.36</v>
+      </c>
+      <c r="E28" s="7">
+        <v>2.66</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C29" s="6">
-        <v>-11.97</v>
-      </c>
-      <c r="D29" s="6">
+      <c r="C29" s="5">
         <v>-8.41</v>
       </c>
-      <c r="E29" s="7">
-        <v>3.56</v>
+      <c r="D29" s="5">
+        <v>-14.83</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-6.42</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C30" s="6">
-        <v>3.78</v>
-      </c>
-      <c r="D30" s="6">
+      <c r="C30" s="5">
         <v>3.95</v>
       </c>
+      <c r="D30" s="5">
+        <v>5.45</v>
+      </c>
       <c r="E30" s="7">
-        <v>0.17</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="6">
-        <v>13.5</v>
-      </c>
-      <c r="D31" s="6">
+      <c r="C31" s="5">
         <v>14.83</v>
       </c>
-      <c r="E31" s="7">
-        <v>1.33</v>
+      <c r="D31" s="5">
+        <v>14.16</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-0.67</v>
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="6">
-        <v>7.51</v>
-      </c>
-      <c r="D32" s="6">
+      <c r="C32" s="5">
         <v>9.4</v>
       </c>
-      <c r="E32" s="7">
-        <v>1.89</v>
+      <c r="D32" s="5">
+        <v>8.44</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-0.96</v>
       </c>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C33" s="6">
-        <v>18.55</v>
-      </c>
-      <c r="D33" s="6">
+      <c r="C33" s="5">
         <v>19.01</v>
+      </c>
+      <c r="D33" s="5">
+        <v>19.47</v>
       </c>
       <c r="E33" s="7">
         <v>0.46</v>
       </c>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C34" s="6">
-        <v>-3.79</v>
-      </c>
-      <c r="D34" s="6">
+      <c r="C34" s="5">
         <v>-4.49</v>
       </c>
-      <c r="E34" s="8">
-        <v>-0.7</v>
+      <c r="D34" s="5">
+        <v>-1.75</v>
+      </c>
+      <c r="E34" s="7">
+        <v>2.74</v>
       </c>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C35" s="6">
-        <v>-2.1</v>
-      </c>
-      <c r="D35" s="6">
+      <c r="C35" s="5">
         <v>-1.78</v>
       </c>
+      <c r="D35" s="5">
+        <v>-0.53</v>
+      </c>
       <c r="E35" s="7">
-        <v>0.32</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
+      <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C36" s="6">
-        <v>-27.78</v>
-      </c>
-      <c r="D36" s="6">
+      <c r="C36" s="5">
         <v>-25.3</v>
       </c>
-      <c r="E36" s="7">
-        <v>2.48</v>
+      <c r="D36" s="5">
+        <v>-27.35</v>
+      </c>
+      <c r="E36" s="6">
+        <v>-2.05</v>
       </c>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="6">
-        <v>-41.22</v>
-      </c>
-      <c r="D37" s="6">
+      <c r="C37" s="5">
         <v>-41.55</v>
       </c>
-      <c r="E37" s="8">
-        <v>-0.33</v>
+      <c r="D37" s="5">
+        <v>-41.42</v>
+      </c>
+      <c r="E37" s="7">
+        <v>0.13</v>
       </c>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C38" s="6">
-        <v>-7.6</v>
-      </c>
-      <c r="D38" s="6">
+      <c r="C38" s="5">
         <v>-7.56</v>
       </c>
+      <c r="D38" s="5">
+        <v>-7.38</v>
+      </c>
       <c r="E38" s="7">
-        <v>0.04</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C39" s="6">
-        <v>-22.13</v>
-      </c>
-      <c r="D39" s="6">
+      <c r="C39" s="5">
         <v>-21.25</v>
       </c>
-      <c r="E39" s="7">
-        <v>0.88</v>
+      <c r="D39" s="5">
+        <v>-21.34</v>
+      </c>
+      <c r="E39" s="6">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C40" s="6">
-        <v>-5.57</v>
-      </c>
-      <c r="D40" s="6">
+      <c r="C40" s="5">
         <v>-6.78</v>
       </c>
-      <c r="E40" s="8">
-        <v>-1.21</v>
+      <c r="D40" s="5">
+        <v>-5.51</v>
+      </c>
+      <c r="E40" s="7">
+        <v>1.27</v>
       </c>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
+      <c r="A41" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B41" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C41" s="6">
-        <v>-8.9</v>
-      </c>
-      <c r="D41" s="6">
+      <c r="C41" s="5">
         <v>-9.65</v>
       </c>
-      <c r="E41" s="8">
-        <v>-0.75</v>
+      <c r="D41" s="5">
+        <v>-8.050000000000001</v>
+      </c>
+      <c r="E41" s="7">
+        <v>1.6</v>
       </c>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
+      <c r="A42" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B42" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C42" s="6">
-        <v>11607</v>
-      </c>
-      <c r="D42" s="6">
+      <c r="C42" s="5">
         <v>11645</v>
       </c>
+      <c r="D42" s="5">
+        <v>11793</v>
+      </c>
       <c r="E42" s="7">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
+      <c r="B43" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="5">
+        <v>500.7</v>
+      </c>
+      <c r="D43" s="5">
+        <v>486.95</v>
+      </c>
+      <c r="E43" s="6">
+        <v>-13.75</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="5">
+        <v>353.55</v>
+      </c>
+      <c r="D44" s="5">
+        <v>354.35</v>
+      </c>
+      <c r="E44" s="7">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="5">
+        <v>2012</v>
+      </c>
+      <c r="D45" s="5">
+        <v>2016</v>
+      </c>
+      <c r="E45" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="5">
+        <v>11380</v>
+      </c>
+      <c r="D46" s="5">
+        <v>11368</v>
+      </c>
+      <c r="E46" s="6">
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="5">
+        <v>1080.2</v>
+      </c>
+      <c r="D47" s="5">
+        <v>1095</v>
+      </c>
+      <c r="E47" s="7">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="5">
+        <v>134.57</v>
+      </c>
+      <c r="D48" s="5">
+        <v>136.96</v>
+      </c>
+      <c r="E48" s="7">
+        <v>2.39</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49" s="5">
+        <v>43</v>
+      </c>
+      <c r="D49" s="5">
+        <v>29</v>
+      </c>
+      <c r="E49" s="6">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" s="5">
+        <v>29</v>
+      </c>
+      <c r="D50" s="5">
+        <v>43</v>
+      </c>
+      <c r="E50" s="7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="5">
+        <v>63.33</v>
+      </c>
+      <c r="D51" s="5">
+        <v>67.08</v>
+      </c>
+      <c r="E51" s="7">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="6">
-        <v>484.05</v>
-      </c>
-      <c r="D43" s="6">
-        <v>500.7</v>
-      </c>
-      <c r="E43" s="7">
-        <v>16.65</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
+      <c r="B52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="5">
+        <v>39.01</v>
+      </c>
+      <c r="D52" s="5">
+        <v>35.85</v>
+      </c>
+      <c r="E52" s="6">
+        <v>-3.16</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B44" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="6">
-        <v>355.55</v>
-      </c>
-      <c r="D44" s="6">
-        <v>353.55</v>
-      </c>
-      <c r="E44" s="8">
+      <c r="B53" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="5">
+        <v>53.79</v>
+      </c>
+      <c r="D53" s="5">
+        <v>54.29</v>
+      </c>
+      <c r="E53" s="7">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="5">
+        <v>57.84</v>
+      </c>
+      <c r="D54" s="5">
+        <v>58.49</v>
+      </c>
+      <c r="E54" s="7">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="5">
+        <v>57.7</v>
+      </c>
+      <c r="D55" s="5">
+        <v>57.24</v>
+      </c>
+      <c r="E55" s="6">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="5">
+        <v>51.47</v>
+      </c>
+      <c r="D56" s="5">
+        <v>55.08</v>
+      </c>
+      <c r="E56" s="7">
+        <v>3.61</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="5">
+        <v>40.03</v>
+      </c>
+      <c r="D57" s="5">
+        <v>46.9</v>
+      </c>
+      <c r="E57" s="7">
+        <v>6.87</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="5">
+        <v>-43.47</v>
+      </c>
+      <c r="D58" s="5">
+        <v>-58.53</v>
+      </c>
+      <c r="E58" s="6">
+        <v>-15.06</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="5">
+        <v>59.65</v>
+      </c>
+      <c r="D59" s="5">
+        <v>-37.85</v>
+      </c>
+      <c r="E59" s="6">
+        <v>-97.5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="5">
+        <v>-85.95</v>
+      </c>
+      <c r="D60" s="5">
+        <v>-87.95</v>
+      </c>
+      <c r="E60" s="6">
         <v>-2</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B45" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="6">
-        <v>2011.2</v>
-      </c>
-      <c r="D45" s="6">
-        <v>2012</v>
-      </c>
-      <c r="E45" s="7">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
+      <c r="B61" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="5">
+        <v>-36.26</v>
+      </c>
+      <c r="D61" s="5">
+        <v>-70.34</v>
+      </c>
+      <c r="E61" s="6">
+        <v>-34.08</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B46" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="6">
-        <v>11254</v>
-      </c>
-      <c r="D46" s="6">
-        <v>11380</v>
-      </c>
-      <c r="E46" s="7">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
+      <c r="B62" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="5">
+        <v>-52.16</v>
+      </c>
+      <c r="D62" s="5">
+        <v>-45.29</v>
+      </c>
+      <c r="E62" s="7">
+        <v>6.87</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B47" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="6">
-        <v>1094.3</v>
-      </c>
-      <c r="D47" s="6">
-        <v>1080.2</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-14.1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
+      <c r="B63" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="5">
+        <v>-68.72</v>
+      </c>
+      <c r="D63" s="5">
+        <v>-25.15</v>
+      </c>
+      <c r="E63" s="7">
+        <v>43.57</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B48" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="6">
-        <v>135.69</v>
-      </c>
-      <c r="D48" s="6">
-        <v>134.57</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-1.12</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C49" s="6">
-        <v>29</v>
-      </c>
-      <c r="D49" s="6">
-        <v>43</v>
-      </c>
-      <c r="E49" s="7">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C50" s="6">
-        <v>43</v>
-      </c>
-      <c r="D50" s="6">
-        <v>29</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="6">
-        <v>62.31</v>
-      </c>
-      <c r="D51" s="6">
-        <v>63.33</v>
-      </c>
-      <c r="E51" s="7">
-        <v>1.02</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="6">
-        <v>32.29</v>
-      </c>
-      <c r="D52" s="6">
-        <v>39.01</v>
-      </c>
-      <c r="E52" s="7">
-        <v>6.72</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="6">
-        <v>55.19</v>
-      </c>
-      <c r="D53" s="6">
-        <v>53.79</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="6">
-        <v>57.72</v>
-      </c>
-      <c r="D54" s="6">
-        <v>57.84</v>
-      </c>
-      <c r="E54" s="7">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="6">
-        <v>54.08</v>
-      </c>
-      <c r="D55" s="6">
-        <v>57.7</v>
-      </c>
-      <c r="E55" s="7">
-        <v>3.62</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="6">
-        <v>55.4</v>
-      </c>
-      <c r="D56" s="6">
-        <v>51.47</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-3.93</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="6">
-        <v>42.42</v>
-      </c>
-      <c r="D57" s="6">
-        <v>40.03</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-2.39</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B58" s="5" t="s">
+      <c r="B64" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C58" s="6">
-        <v>-40.39</v>
-      </c>
-      <c r="D58" s="6">
-        <v>-43.47</v>
-      </c>
-      <c r="E58" s="8">
-        <v>-3.08</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C59" s="6">
-        <v>10.87</v>
-      </c>
-      <c r="D59" s="6">
-        <v>59.65</v>
-      </c>
-      <c r="E59" s="7">
-        <v>48.78</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="6">
-        <v>-62.63</v>
-      </c>
-      <c r="D60" s="6">
-        <v>-85.95</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-23.32</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="6">
-        <v>-72.28</v>
-      </c>
-      <c r="D61" s="6">
-        <v>-36.26</v>
-      </c>
-      <c r="E61" s="7">
-        <v>36.02</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="6">
-        <v>-60.63</v>
-      </c>
-      <c r="D62" s="6">
-        <v>-52.16</v>
-      </c>
-      <c r="E62" s="7">
-        <v>8.470000000000001</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="6">
-        <v>-64.43000000000001</v>
-      </c>
-      <c r="D63" s="6">
-        <v>-68.72</v>
-      </c>
-      <c r="E63" s="8">
-        <v>-4.29</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="6">
-        <v>-63.9</v>
-      </c>
-      <c r="D64" s="6">
+      <c r="C64" s="5">
         <v>-67.7</v>
       </c>
-      <c r="E64" s="8">
-        <v>-3.8</v>
+      <c r="D64" s="5">
+        <v>-49.95</v>
+      </c>
+      <c r="E64" s="7">
+        <v>17.75</v>
       </c>
     </row>
   </sheetData>
@@ -2938,60 +2875,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>72</v>
+      <c r="B1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>68.8</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>7</v>
       </c>
-      <c r="D2" s="11">
-        <v>51.9</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>53.6</v>
+      </c>
+      <c r="E2" s="10">
         <v>90</v>
       </c>
-      <c r="F2" s="11">
-        <v>3.1</v>
-      </c>
-      <c r="G2" s="11">
-        <v>6.4</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>3.2</v>
+      </c>
+      <c r="G2" s="10">
+        <v>6.3</v>
+      </c>
+      <c r="H2" s="10">
         <v>57</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>60</v>
       </c>
     </row>
@@ -3093,49 +3030,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="14">
-        <v>0.2834</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.2415</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.174</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.1058</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.0613</v>
-      </c>
-      <c r="F2" s="14">
-        <v>-0.0067</v>
-      </c>
-      <c r="G2" s="14">
-        <v>-0.1816</v>
+      <c r="A2" s="13">
+        <v>0.2865</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.2411</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.1673</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.1087</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.0617</v>
+      </c>
+      <c r="F2" s="13">
+        <v>-0.0032</v>
+      </c>
+      <c r="G2" s="13">
+        <v>-0.1812</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="83">
   <si>
     <t>Symbol</t>
   </si>
@@ -172,7 +172,64 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>50 DMA &gt; 200 DMA</t>
+  </si>
+  <si>
+    <t>No → Yes</t>
+  </si>
+  <si>
+    <t>🟢 GOLDEN CROSS</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>52.2 → 47.2</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>52.2</t>
+  </si>
+  <si>
+    <t>47.2</t>
+  </si>
+  <si>
+    <t>55.3 → 48.1</t>
+  </si>
+  <si>
+    <t>55.3</t>
+  </si>
+  <si>
+    <t>48.1</t>
+  </si>
+  <si>
+    <t>55.1 → 49.9</t>
+  </si>
+  <si>
+    <t>55.1</t>
+  </si>
+  <si>
+    <t>49.9</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -258,14 +315,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -298,13 +355,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,14 +431,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -755,8 +814,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -896,58 +955,58 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>11793</v>
+        <v>11800</v>
       </c>
       <c r="D2">
-        <v>1.27</v>
+        <v>0.85</v>
       </c>
       <c r="E2">
         <v>11856</v>
       </c>
       <c r="F2">
-        <v>8469.309999999999</v>
+        <v>8506.780000000001</v>
       </c>
       <c r="G2">
-        <v>-0.53</v>
+        <v>-0.47</v>
       </c>
       <c r="H2">
-        <v>39.24</v>
+        <v>38.71</v>
       </c>
       <c r="I2">
-        <v>1.13</v>
+        <v>0.85</v>
       </c>
       <c r="J2">
-        <v>7.22</v>
+        <v>6.02</v>
       </c>
       <c r="K2">
-        <v>13.36</v>
+        <v>12.96</v>
       </c>
       <c r="L2">
-        <v>45.6</v>
+        <v>36.05</v>
       </c>
       <c r="M2">
-        <v>28.65</v>
+        <v>28.92</v>
       </c>
       <c r="N2">
         <v>85</v>
       </c>
       <c r="O2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="P2">
-        <v>11689</v>
+        <v>11709</v>
       </c>
       <c r="Q2">
-        <v>11585.8</v>
+        <v>11645.12</v>
       </c>
       <c r="R2">
-        <v>10721.46</v>
+        <v>10787.92</v>
       </c>
       <c r="S2">
-        <v>9742.799999999999</v>
+        <v>9773.16</v>
       </c>
       <c r="T2">
-        <v>21.04</v>
+        <v>20.74</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -962,43 +1021,43 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>67.08</v>
+        <v>65.33</v>
       </c>
       <c r="Z2">
-        <v>278.14</v>
+        <v>256.1</v>
       </c>
       <c r="AA2">
-        <v>321.15</v>
+        <v>298.84</v>
       </c>
       <c r="AB2">
-        <v>-43.01</v>
+        <v>-42.74</v>
       </c>
       <c r="AC2">
-        <v>11.84</v>
+        <v>21.52</v>
       </c>
       <c r="AD2">
-        <v>6.81</v>
+        <v>15.56</v>
       </c>
       <c r="AE2">
-        <v>207.56</v>
+        <v>197.65</v>
       </c>
       <c r="AF2">
-        <v>-58.53</v>
+        <v>-16.28</v>
       </c>
       <c r="AG2">
-        <v>11982.38</v>
+        <v>11922.7</v>
       </c>
       <c r="AH2">
-        <v>11189.22</v>
+        <v>11367.55</v>
       </c>
       <c r="AI2">
-        <v>11083.81</v>
+        <v>11181.55</v>
       </c>
       <c r="AJ2" t="s">
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>57.32</v>
+        <v>51.58</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1009,10 +1068,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>486.95</v>
+        <v>463.2</v>
       </c>
       <c r="D3">
-        <v>-2.75</v>
+        <v>-3.17</v>
       </c>
       <c r="E3">
         <v>670.25</v>
@@ -1021,46 +1080,46 @@
         <v>222.01</v>
       </c>
       <c r="G3">
-        <v>-27.35</v>
+        <v>-30.89</v>
       </c>
       <c r="H3">
-        <v>119.34</v>
+        <v>108.64</v>
       </c>
       <c r="I3">
-        <v>-7.71</v>
+        <v>-3.78</v>
       </c>
       <c r="J3">
-        <v>-8.050000000000001</v>
+        <v>-15.75</v>
       </c>
       <c r="K3">
-        <v>-14.83</v>
+        <v>-16.51</v>
       </c>
       <c r="L3">
-        <v>117.65</v>
+        <v>102.33</v>
       </c>
       <c r="M3">
-        <v>16.73</v>
+        <v>15.47</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="P3">
-        <v>490.74</v>
+        <v>482.65</v>
       </c>
       <c r="Q3">
-        <v>524.8200000000001</v>
+        <v>517.36</v>
       </c>
       <c r="R3">
-        <v>566.41</v>
+        <v>562.08</v>
       </c>
       <c r="S3">
-        <v>419.81</v>
+        <v>421.63</v>
       </c>
       <c r="T3">
-        <v>15.99</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1075,43 +1134,43 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>35.85</v>
+        <v>30.94</v>
       </c>
       <c r="Z3">
-        <v>-19.22</v>
+        <v>-22.35</v>
       </c>
       <c r="AA3">
-        <v>-15.8</v>
+        <v>-17.85</v>
       </c>
       <c r="AB3">
-        <v>-3.42</v>
+        <v>-4.5</v>
       </c>
       <c r="AC3">
-        <v>27.2</v>
+        <v>14.95</v>
       </c>
       <c r="AD3">
-        <v>15.77</v>
+        <v>24.25</v>
       </c>
       <c r="AE3">
-        <v>22.57</v>
+        <v>21.9</v>
       </c>
       <c r="AF3">
-        <v>-37.85</v>
+        <v>56</v>
       </c>
       <c r="AG3">
-        <v>568.23</v>
+        <v>569.51</v>
       </c>
       <c r="AH3">
-        <v>481.4</v>
+        <v>465.22</v>
       </c>
       <c r="AI3">
-        <v>553.0599999999999</v>
+        <v>536.87</v>
       </c>
       <c r="AJ3" t="s">
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>29.41</v>
+        <v>33.93</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1122,10 +1181,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>354.35</v>
+        <v>344.65</v>
       </c>
       <c r="D4">
-        <v>0.23</v>
+        <v>-1.99</v>
       </c>
       <c r="E4">
         <v>604.85</v>
@@ -1134,46 +1193,46 @@
         <v>303.75</v>
       </c>
       <c r="G4">
-        <v>-41.42</v>
+        <v>-43.02</v>
       </c>
       <c r="H4">
-        <v>16.66</v>
+        <v>13.47</v>
       </c>
       <c r="I4">
-        <v>-0.63</v>
+        <v>-4.9</v>
       </c>
       <c r="J4">
-        <v>7.33</v>
+        <v>4.79</v>
       </c>
       <c r="K4">
-        <v>5.45</v>
+        <v>2.68</v>
       </c>
       <c r="L4">
-        <v>-37.28</v>
+        <v>-42.15</v>
       </c>
       <c r="M4">
-        <v>-18.12</v>
+        <v>-20.08</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
       <c r="O4">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="P4">
-        <v>357.65</v>
+        <v>351.95</v>
       </c>
       <c r="Q4">
-        <v>349.97</v>
+        <v>351.87</v>
       </c>
       <c r="R4">
-        <v>335.59</v>
+        <v>337.2</v>
       </c>
       <c r="S4">
-        <v>391.58</v>
+        <v>390.02</v>
       </c>
       <c r="T4">
-        <v>-9.51</v>
+        <v>-11.63</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1188,34 +1247,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>54.29</v>
+        <v>47.25</v>
       </c>
       <c r="Z4">
-        <v>6.77</v>
+        <v>4.68</v>
       </c>
       <c r="AA4">
-        <v>7.54</v>
+        <v>6.71</v>
       </c>
       <c r="AB4">
-        <v>-0.77</v>
+        <v>-2.03</v>
       </c>
       <c r="AC4">
-        <v>7.48</v>
+        <v>0.68</v>
       </c>
       <c r="AD4">
-        <v>19.48</v>
+        <v>3.11</v>
       </c>
       <c r="AE4">
-        <v>13.01</v>
+        <v>12.56</v>
       </c>
       <c r="AF4">
-        <v>-87.95</v>
+        <v>-74.87</v>
       </c>
       <c r="AG4">
-        <v>382.56</v>
+        <v>381.38</v>
       </c>
       <c r="AH4">
-        <v>317.38</v>
+        <v>322.36</v>
       </c>
       <c r="AI4">
         <v>335.86</v>
@@ -1224,7 +1283,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>51.07</v>
+        <v>41.86</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1235,10 +1294,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>2016</v>
+        <v>2001.7</v>
       </c>
       <c r="D5">
-        <v>0.2</v>
+        <v>-1.52</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1247,88 +1306,88 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-7.38</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="H5">
-        <v>23.54</v>
+        <v>22.67</v>
       </c>
       <c r="I5">
-        <v>-0.44</v>
+        <v>-0.16</v>
       </c>
       <c r="J5">
-        <v>7.44</v>
+        <v>6.66</v>
       </c>
       <c r="K5">
-        <v>14.16</v>
+        <v>11.16</v>
       </c>
       <c r="L5">
-        <v>4.72</v>
+        <v>1.5</v>
       </c>
       <c r="M5">
-        <v>6.17</v>
+        <v>4.03</v>
       </c>
       <c r="N5">
         <v>57</v>
       </c>
       <c r="O5">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P5">
-        <v>2010.5</v>
+        <v>2014.68</v>
       </c>
       <c r="Q5">
-        <v>2005.69</v>
+        <v>2017.91</v>
       </c>
       <c r="R5">
-        <v>1894.82</v>
+        <v>1908.82</v>
       </c>
       <c r="S5">
-        <v>1908.98</v>
+        <v>1908.38</v>
       </c>
       <c r="T5">
-        <v>5.61</v>
+        <v>4.89</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
       </c>
       <c r="V5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="W5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="X5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y5">
-        <v>58.49</v>
+        <v>54.2</v>
       </c>
       <c r="Z5">
-        <v>34.6</v>
+        <v>30.09</v>
       </c>
       <c r="AA5">
-        <v>43.8</v>
+        <v>39.43</v>
       </c>
       <c r="AB5">
-        <v>-9.19</v>
+        <v>-9.34</v>
       </c>
       <c r="AC5">
-        <v>5.97</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="AD5">
-        <v>3.55</v>
+        <v>9.19</v>
       </c>
       <c r="AE5">
-        <v>38.72</v>
+        <v>37.86</v>
       </c>
       <c r="AF5">
-        <v>-70.34</v>
+        <v>-65.87</v>
       </c>
       <c r="AG5">
-        <v>2135.74</v>
+        <v>2123.41</v>
       </c>
       <c r="AH5">
-        <v>1875.63</v>
+        <v>1912.41</v>
       </c>
       <c r="AI5">
         <v>1958.53</v>
@@ -1337,7 +1396,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>20.13</v>
+        <v>16.44</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1348,58 +1407,58 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>11368</v>
+        <v>11120</v>
       </c>
       <c r="D6">
-        <v>-0.11</v>
+        <v>-1.77</v>
       </c>
       <c r="E6">
-        <v>14451.52</v>
+        <v>13632.57</v>
       </c>
       <c r="F6">
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-21.34</v>
+        <v>-18.43</v>
       </c>
       <c r="H6">
-        <v>29.98</v>
+        <v>27.14</v>
       </c>
       <c r="I6">
-        <v>-1.15</v>
+        <v>-3.09</v>
       </c>
       <c r="J6">
-        <v>9.050000000000001</v>
+        <v>4.13</v>
       </c>
       <c r="K6">
-        <v>8.44</v>
+        <v>3.88</v>
       </c>
       <c r="L6">
-        <v>-19.18</v>
+        <v>-18.93</v>
       </c>
       <c r="M6">
-        <v>24.11</v>
+        <v>23.75</v>
       </c>
       <c r="N6">
         <v>29</v>
       </c>
       <c r="O6">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="P6">
-        <v>11390.4</v>
+        <v>11288.4</v>
       </c>
       <c r="Q6">
-        <v>11292.7</v>
+        <v>11340.25</v>
       </c>
       <c r="R6">
-        <v>10851.26</v>
+        <v>10899.58</v>
       </c>
       <c r="S6">
-        <v>10756.97</v>
+        <v>10748.08</v>
       </c>
       <c r="T6">
-        <v>5.68</v>
+        <v>3.46</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1414,34 +1473,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>57.24</v>
+        <v>48.11</v>
       </c>
       <c r="Z6">
-        <v>182.65</v>
+        <v>134.72</v>
       </c>
       <c r="AA6">
-        <v>211.49</v>
+        <v>188.82</v>
       </c>
       <c r="AB6">
-        <v>-28.84</v>
+        <v>-54.11</v>
       </c>
       <c r="AC6">
-        <v>11.6</v>
+        <v>8.15</v>
       </c>
       <c r="AD6">
-        <v>13.13</v>
+        <v>11.36</v>
       </c>
       <c r="AE6">
-        <v>215.17</v>
+        <v>216.3</v>
       </c>
       <c r="AF6">
-        <v>-45.29</v>
+        <v>60.45</v>
       </c>
       <c r="AG6">
-        <v>11860.23</v>
+        <v>11776.9</v>
       </c>
       <c r="AH6">
-        <v>10725.17</v>
+        <v>10903.6</v>
       </c>
       <c r="AI6">
         <v>10787.84</v>
@@ -1450,7 +1509,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>32.58</v>
+        <v>29.72</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1461,10 +1520,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>1095</v>
+        <v>1077</v>
       </c>
       <c r="D7">
-        <v>1.37</v>
+        <v>-1.64</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1473,46 +1532,46 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-5.51</v>
+        <v>-7.06</v>
       </c>
       <c r="H7">
-        <v>36.61</v>
+        <v>34.36</v>
       </c>
       <c r="I7">
-        <v>0.39</v>
+        <v>-1.13</v>
       </c>
       <c r="J7">
-        <v>3.27</v>
+        <v>6.34</v>
       </c>
       <c r="K7">
-        <v>19.47</v>
+        <v>15.78</v>
       </c>
       <c r="L7">
-        <v>27.11</v>
+        <v>19.36</v>
       </c>
       <c r="M7">
-        <v>10.87</v>
+        <v>9.48</v>
       </c>
       <c r="N7">
         <v>71</v>
       </c>
       <c r="O7">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="P7">
-        <v>1089.16</v>
+        <v>1088.3</v>
       </c>
       <c r="Q7">
-        <v>1093.43</v>
+        <v>1098.97</v>
       </c>
       <c r="R7">
-        <v>1037.52</v>
+        <v>1045.18</v>
       </c>
       <c r="S7">
-        <v>974.79</v>
+        <v>975.15</v>
       </c>
       <c r="T7">
-        <v>12.33</v>
+        <v>10.44</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1527,34 +1586,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>55.08</v>
+        <v>49.85</v>
       </c>
       <c r="Z7">
-        <v>15.01</v>
+        <v>11.76</v>
       </c>
       <c r="AA7">
-        <v>21.57</v>
+        <v>18.41</v>
       </c>
       <c r="AB7">
-        <v>-6.56</v>
+        <v>-6.65</v>
       </c>
       <c r="AC7">
-        <v>8.48</v>
+        <v>10.18</v>
       </c>
       <c r="AD7">
-        <v>6.51</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AE7">
-        <v>24.89</v>
+        <v>23.74</v>
       </c>
       <c r="AF7">
-        <v>-25.15</v>
+        <v>-50.5</v>
       </c>
       <c r="AG7">
-        <v>1172.99</v>
+        <v>1165.77</v>
       </c>
       <c r="AH7">
-        <v>1013.86</v>
+        <v>1032.17</v>
       </c>
       <c r="AI7">
         <v>1067.72</v>
@@ -1563,7 +1622,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>22.55</v>
+        <v>21.68</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1574,10 +1633,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>136.96</v>
+        <v>135.68</v>
       </c>
       <c r="D8">
-        <v>1.78</v>
+        <v>-1.12</v>
       </c>
       <c r="E8">
         <v>148.95</v>
@@ -1586,25 +1645,25 @@
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>-8.050000000000001</v>
+        <v>-8.91</v>
       </c>
       <c r="H8">
-        <v>18.11</v>
+        <v>17.01</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="J8">
-        <v>-3.89</v>
+        <v>-1.97</v>
       </c>
       <c r="K8">
-        <v>-1.75</v>
+        <v>-1.01</v>
       </c>
       <c r="L8">
-        <v>1.26</v>
+        <v>-1.6</v>
       </c>
       <c r="M8">
-        <v>-0.32</v>
+        <v>-0.14</v>
       </c>
       <c r="N8">
         <v>43</v>
@@ -1613,19 +1672,19 @@
         <v>48</v>
       </c>
       <c r="P8">
-        <v>135.1</v>
+        <v>136.02</v>
       </c>
       <c r="Q8">
-        <v>139.09</v>
+        <v>138.78</v>
       </c>
       <c r="R8">
-        <v>137.27</v>
+        <v>137.4</v>
       </c>
       <c r="S8">
-        <v>133.62</v>
+        <v>133.6</v>
       </c>
       <c r="T8">
-        <v>2.5</v>
+        <v>1.56</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1640,34 +1699,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>46.9</v>
+        <v>43.89</v>
       </c>
       <c r="Z8">
-        <v>-0.91</v>
+        <v>-0.9</v>
       </c>
       <c r="AA8">
-        <v>-0.16</v>
+        <v>-0.42</v>
       </c>
       <c r="AB8">
-        <v>-0.75</v>
+        <v>-0.49</v>
       </c>
       <c r="AC8">
-        <v>24.21</v>
+        <v>39.07</v>
       </c>
       <c r="AD8">
-        <v>13.94</v>
+        <v>32.02</v>
       </c>
       <c r="AE8">
-        <v>4.11</v>
+        <v>4</v>
       </c>
       <c r="AF8">
-        <v>-49.95</v>
+        <v>-61.61</v>
       </c>
       <c r="AG8">
-        <v>145.58</v>
+        <v>145.44</v>
       </c>
       <c r="AH8">
-        <v>132.6</v>
+        <v>132.12</v>
       </c>
       <c r="AI8">
         <v>131.91</v>
@@ -1676,7 +1735,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>38.83</v>
+        <v>31.12</v>
       </c>
     </row>
   </sheetData>
@@ -1817,7 +1876,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1837,1025 +1896,1106 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>50</v>
       </c>
+      <c r="C2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="A5" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>55</v>
+      <c r="A6" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="5">
-        <v>11.93</v>
-      </c>
-      <c r="D7" s="5">
-        <v>7.22</v>
-      </c>
-      <c r="E7" s="6">
-        <v>-4.71</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="5">
-        <v>-4.67</v>
-      </c>
-      <c r="D8" s="5">
-        <v>-8.050000000000001</v>
-      </c>
-      <c r="E8" s="6">
-        <v>-3.38</v>
+      <c r="A7" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="5">
-        <v>6.12</v>
-      </c>
-      <c r="D9" s="5">
-        <v>7.33</v>
-      </c>
-      <c r="E9" s="7">
-        <v>1.21</v>
-      </c>
+      <c r="A9" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="7">
+        <v>3.69</v>
+      </c>
+      <c r="D11" s="7">
+        <v>6.02</v>
+      </c>
+      <c r="E11" s="8">
+        <v>2.33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7">
+        <v>-13.95</v>
+      </c>
+      <c r="D12" s="7">
+        <v>-15.75</v>
+      </c>
+      <c r="E12" s="9">
+        <v>-1.8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7">
+        <v>7.8</v>
+      </c>
+      <c r="D13" s="7">
+        <v>4.79</v>
+      </c>
+      <c r="E13" s="9">
+        <v>-3.01</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>5.86</v>
-      </c>
-      <c r="D10" s="5">
-        <v>7.44</v>
-      </c>
-      <c r="E10" s="7">
-        <v>1.58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="C14" s="7">
+        <v>7.57</v>
+      </c>
+      <c r="D14" s="7">
+        <v>6.66</v>
+      </c>
+      <c r="E14" s="9">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>8.94</v>
-      </c>
-      <c r="D11" s="5">
-        <v>9.050000000000001</v>
-      </c>
-      <c r="E11" s="7">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="C15" s="7">
+        <v>6.43</v>
+      </c>
+      <c r="D15" s="7">
+        <v>4.13</v>
+      </c>
+      <c r="E15" s="9">
+        <v>-2.3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C16" s="7">
+        <v>5.31</v>
+      </c>
+      <c r="D16" s="7">
+        <v>6.34</v>
+      </c>
+      <c r="E16" s="8">
         <v>1.03</v>
       </c>
-      <c r="D12" s="5">
-        <v>3.27</v>
-      </c>
-      <c r="E12" s="7">
-        <v>2.24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="5">
-        <v>-7.75</v>
-      </c>
-      <c r="D13" s="5">
-        <v>-3.89</v>
-      </c>
-      <c r="E13" s="7">
-        <v>3.86</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="C17" s="7">
+        <v>-0.97</v>
+      </c>
+      <c r="D17" s="7">
+        <v>-1.97</v>
+      </c>
+      <c r="E17" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C18" s="7">
+        <v>0</v>
+      </c>
+      <c r="D18" s="7">
+        <v>0.85</v>
+      </c>
+      <c r="E18" s="8">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>-4.44</v>
+      </c>
+      <c r="D19" s="7">
+        <v>-3.78</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7">
+        <v>-2.97</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-4.9</v>
+      </c>
+      <c r="E20" s="9">
+        <v>-1.93</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7">
+        <v>1.2</v>
+      </c>
+      <c r="D21" s="7">
+        <v>-0.16</v>
+      </c>
+      <c r="E21" s="9">
+        <v>-1.36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="7">
+        <v>-1.35</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-3.09</v>
+      </c>
+      <c r="E22" s="9">
+        <v>-1.74</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="7">
+        <v>0.74</v>
+      </c>
+      <c r="D23" s="7">
+        <v>-1.13</v>
+      </c>
+      <c r="E23" s="9">
+        <v>-1.87</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="7">
+        <v>2.29</v>
+      </c>
+      <c r="D24" s="7">
+        <v>1.15</v>
+      </c>
+      <c r="E24" s="9">
+        <v>-1.14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="7">
+        <v>38.15</v>
+      </c>
+      <c r="D25" s="7">
+        <v>36.05</v>
+      </c>
+      <c r="E25" s="9">
+        <v>-2.1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="7">
+        <v>112.03</v>
+      </c>
+      <c r="D26" s="7">
+        <v>102.33</v>
+      </c>
+      <c r="E26" s="9">
+        <v>-9.699999999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="7">
+        <v>-39.17</v>
+      </c>
+      <c r="D27" s="7">
+        <v>-42.15</v>
+      </c>
+      <c r="E27" s="9">
+        <v>-2.98</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="7">
+        <v>1.96</v>
+      </c>
+      <c r="D28" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="E28" s="9">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="7">
+        <v>-21.67</v>
+      </c>
+      <c r="D29" s="7">
+        <v>-18.93</v>
+      </c>
+      <c r="E29" s="8">
+        <v>2.74</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="7">
+        <v>20.97</v>
+      </c>
+      <c r="D30" s="7">
+        <v>19.36</v>
+      </c>
+      <c r="E30" s="9">
+        <v>-1.61</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="7">
+        <v>0.46</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-1.6</v>
+      </c>
+      <c r="E31" s="9">
+        <v>-2.06</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="7">
+        <v>13.09</v>
+      </c>
+      <c r="D32" s="7">
+        <v>12.96</v>
+      </c>
+      <c r="E32" s="9">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="7">
+        <v>-14.85</v>
+      </c>
+      <c r="D33" s="7">
+        <v>-16.51</v>
+      </c>
+      <c r="E33" s="9">
+        <v>-1.66</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="7">
+        <v>4.01</v>
+      </c>
+      <c r="D34" s="7">
+        <v>2.68</v>
+      </c>
+      <c r="E34" s="9">
+        <v>-1.33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="7">
+        <v>12.45</v>
+      </c>
+      <c r="D35" s="7">
+        <v>11.16</v>
+      </c>
+      <c r="E35" s="9">
+        <v>-1.29</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="7">
+        <v>6.37</v>
+      </c>
+      <c r="D36" s="7">
+        <v>3.88</v>
+      </c>
+      <c r="E36" s="9">
+        <v>-2.49</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="7">
+        <v>16.25</v>
+      </c>
+      <c r="D37" s="7">
+        <v>15.78</v>
+      </c>
+      <c r="E37" s="9">
         <v>-0.47</v>
       </c>
-      <c r="D14" s="5">
-        <v>1.13</v>
-      </c>
-      <c r="E14" s="7">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="7">
+        <v>-2.09</v>
+      </c>
+      <c r="D38" s="7">
+        <v>-1.01</v>
+      </c>
+      <c r="E38" s="8">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="7">
+        <v>-1.32</v>
+      </c>
+      <c r="D39" s="7">
+        <v>-0.47</v>
+      </c>
+      <c r="E39" s="8">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-6.98</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-7.71</v>
-      </c>
-      <c r="E15" s="6">
-        <v>-0.73</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B40" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="7">
+        <v>-28.63</v>
+      </c>
+      <c r="D40" s="7">
+        <v>-30.89</v>
+      </c>
+      <c r="E40" s="9">
+        <v>-2.26</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>-2.86</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.63</v>
-      </c>
-      <c r="E16" s="7">
-        <v>2.23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B41" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="7">
+        <v>-41.86</v>
+      </c>
+      <c r="D41" s="7">
+        <v>-43.02</v>
+      </c>
+      <c r="E41" s="9">
+        <v>-1.16</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-0.42</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.44</v>
-      </c>
-      <c r="E17" s="6">
-        <v>-0.02</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B42" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="7">
+        <v>-6.62</v>
+      </c>
+      <c r="D42" s="7">
+        <v>-8.039999999999999</v>
+      </c>
+      <c r="E42" s="9">
+        <v>-1.42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>-1.72</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-1.15</v>
-      </c>
-      <c r="E18" s="7">
-        <v>0.57</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B43" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="7">
+        <v>-17.48</v>
+      </c>
+      <c r="D43" s="7">
+        <v>-18.43</v>
+      </c>
+      <c r="E43" s="9">
+        <v>-0.95</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-1.28</v>
-      </c>
-      <c r="D19" s="5">
-        <v>0.39</v>
-      </c>
-      <c r="E19" s="7">
-        <v>1.67</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B44" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="7">
+        <v>-5.51</v>
+      </c>
+      <c r="D44" s="7">
+        <v>-7.06</v>
+      </c>
+      <c r="E44" s="9">
+        <v>-1.55</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-0.73</v>
-      </c>
-      <c r="D20" s="5">
-        <v>1</v>
-      </c>
-      <c r="E20" s="7">
-        <v>1.73</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B45" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="7">
+        <v>-7.88</v>
+      </c>
+      <c r="D45" s="7">
+        <v>-8.91</v>
+      </c>
+      <c r="E45" s="9">
+        <v>-1.03</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="5">
-        <v>43.16</v>
-      </c>
-      <c r="D21" s="5">
-        <v>45.6</v>
-      </c>
-      <c r="E21" s="7">
-        <v>2.44</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B46" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="7">
+        <v>11700</v>
+      </c>
+      <c r="D46" s="7">
+        <v>11800</v>
+      </c>
+      <c r="E46" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="5">
-        <v>124.8</v>
-      </c>
-      <c r="D22" s="5">
-        <v>117.65</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-7.15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B47" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="7">
+        <v>478.35</v>
+      </c>
+      <c r="D47" s="7">
+        <v>463.2</v>
+      </c>
+      <c r="E47" s="9">
+        <v>-15.15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="5">
-        <v>-38.11</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-37.28</v>
-      </c>
-      <c r="E23" s="7">
-        <v>0.83</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B48" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="7">
+        <v>351.65</v>
+      </c>
+      <c r="D48" s="7">
+        <v>344.65</v>
+      </c>
+      <c r="E48" s="9">
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="5">
-        <v>5.1</v>
-      </c>
-      <c r="D24" s="5">
-        <v>4.72</v>
-      </c>
-      <c r="E24" s="6">
-        <v>-0.38</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="B49" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="7">
+        <v>2032.5</v>
+      </c>
+      <c r="D49" s="7">
+        <v>2001.7</v>
+      </c>
+      <c r="E49" s="9">
+        <v>-30.8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>-17.83</v>
-      </c>
-      <c r="D25" s="5">
-        <v>-19.18</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-1.35</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="B50" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="7">
+        <v>11320</v>
+      </c>
+      <c r="D50" s="7">
+        <v>11120</v>
+      </c>
+      <c r="E50" s="9">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>25.6</v>
-      </c>
-      <c r="D26" s="5">
-        <v>27.11</v>
-      </c>
-      <c r="E26" s="7">
-        <v>1.51</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="B51" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="7">
+        <v>1095</v>
+      </c>
+      <c r="D51" s="7">
+        <v>1077</v>
+      </c>
+      <c r="E51" s="9">
+        <v>-18</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>-0.28</v>
-      </c>
-      <c r="D27" s="5">
-        <v>1.26</v>
-      </c>
-      <c r="E27" s="7">
-        <v>1.54</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="B52" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="7">
+        <v>137.21</v>
+      </c>
+      <c r="D52" s="7">
+        <v>135.68</v>
+      </c>
+      <c r="E52" s="9">
+        <v>-1.53</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="5">
-        <v>10.7</v>
-      </c>
-      <c r="D28" s="5">
-        <v>13.36</v>
-      </c>
-      <c r="E28" s="7">
-        <v>2.66</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="B53" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="7">
+        <v>62.74</v>
+      </c>
+      <c r="D53" s="7">
+        <v>65.33</v>
+      </c>
+      <c r="E53" s="8">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-8.41</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-14.83</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-6.42</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="B54" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="7">
+        <v>33.99</v>
+      </c>
+      <c r="D54" s="7">
+        <v>30.94</v>
+      </c>
+      <c r="E54" s="9">
+        <v>-3.05</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="5">
-        <v>3.95</v>
-      </c>
-      <c r="D30" s="5">
-        <v>5.45</v>
-      </c>
-      <c r="E30" s="7">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="B55" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="7">
+        <v>52.24</v>
+      </c>
+      <c r="D55" s="7">
+        <v>47.25</v>
+      </c>
+      <c r="E55" s="9">
+        <v>-4.99</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="5">
-        <v>14.83</v>
-      </c>
-      <c r="D31" s="5">
-        <v>14.16</v>
-      </c>
-      <c r="E31" s="6">
-        <v>-0.67</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="B56" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="7">
+        <v>61.13</v>
+      </c>
+      <c r="D56" s="7">
+        <v>54.2</v>
+      </c>
+      <c r="E56" s="9">
+        <v>-6.93</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="5">
-        <v>9.4</v>
-      </c>
-      <c r="D32" s="5">
-        <v>8.44</v>
-      </c>
-      <c r="E32" s="6">
-        <v>-0.96</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="B57" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="7">
+        <v>55.33</v>
+      </c>
+      <c r="D57" s="7">
+        <v>48.11</v>
+      </c>
+      <c r="E57" s="9">
+        <v>-7.22</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="5">
-        <v>19.01</v>
-      </c>
-      <c r="D33" s="5">
-        <v>19.47</v>
-      </c>
-      <c r="E33" s="7">
-        <v>0.46</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="B58" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="7">
+        <v>55.08</v>
+      </c>
+      <c r="D58" s="7">
+        <v>49.85</v>
+      </c>
+      <c r="E58" s="9">
+        <v>-5.23</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>-4.49</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-1.75</v>
-      </c>
-      <c r="E34" s="7">
-        <v>2.74</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="B59" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="7">
+        <v>47.58</v>
+      </c>
+      <c r="D59" s="7">
+        <v>43.89</v>
+      </c>
+      <c r="E59" s="9">
+        <v>-3.69</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-1.78</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-0.53</v>
-      </c>
-      <c r="E35" s="7">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="B60" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="7">
+        <v>-26.92</v>
+      </c>
+      <c r="D60" s="7">
+        <v>-16.28</v>
+      </c>
+      <c r="E60" s="8">
+        <v>10.64</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-25.3</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-27.35</v>
-      </c>
-      <c r="E36" s="6">
-        <v>-2.05</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
+      <c r="B61" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="7">
+        <v>-11.46</v>
+      </c>
+      <c r="D61" s="7">
+        <v>56</v>
+      </c>
+      <c r="E61" s="8">
+        <v>67.45999999999999</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="5">
-        <v>-41.55</v>
-      </c>
-      <c r="D37" s="5">
-        <v>-41.42</v>
-      </c>
-      <c r="E37" s="7">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
+      <c r="B62" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="7">
+        <v>-88.25</v>
+      </c>
+      <c r="D62" s="7">
+        <v>-74.87</v>
+      </c>
+      <c r="E62" s="8">
+        <v>13.38</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="5">
-        <v>-7.56</v>
-      </c>
-      <c r="D38" s="5">
-        <v>-7.38</v>
-      </c>
-      <c r="E38" s="7">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
+      <c r="B63" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="7">
+        <v>-39.81</v>
+      </c>
+      <c r="D63" s="7">
+        <v>-65.87</v>
+      </c>
+      <c r="E63" s="9">
+        <v>-26.06</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-21.25</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-21.34</v>
-      </c>
-      <c r="E39" s="6">
-        <v>-0.09</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
+      <c r="B64" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="7">
+        <v>-49.16</v>
+      </c>
+      <c r="D64" s="7">
+        <v>60.45</v>
+      </c>
+      <c r="E64" s="8">
+        <v>109.61</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="5">
-        <v>-6.78</v>
-      </c>
-      <c r="D40" s="5">
-        <v>-5.51</v>
-      </c>
-      <c r="E40" s="7">
-        <v>1.27</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
+      <c r="B65" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="7">
+        <v>-66.20999999999999</v>
+      </c>
+      <c r="D65" s="7">
+        <v>-50.5</v>
+      </c>
+      <c r="E65" s="8">
+        <v>15.71</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="5">
-        <v>-9.65</v>
-      </c>
-      <c r="D41" s="5">
-        <v>-8.050000000000001</v>
-      </c>
-      <c r="E41" s="7">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="5">
-        <v>11645</v>
-      </c>
-      <c r="D42" s="5">
-        <v>11793</v>
-      </c>
-      <c r="E42" s="7">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="5">
-        <v>500.7</v>
-      </c>
-      <c r="D43" s="5">
-        <v>486.95</v>
-      </c>
-      <c r="E43" s="6">
-        <v>-13.75</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="5">
-        <v>353.55</v>
-      </c>
-      <c r="D44" s="5">
-        <v>354.35</v>
-      </c>
-      <c r="E44" s="7">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="5">
-        <v>2012</v>
-      </c>
-      <c r="D45" s="5">
-        <v>2016</v>
-      </c>
-      <c r="E45" s="7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="5">
-        <v>11380</v>
-      </c>
-      <c r="D46" s="5">
-        <v>11368</v>
-      </c>
-      <c r="E46" s="6">
-        <v>-12</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="5">
-        <v>1080.2</v>
-      </c>
-      <c r="D47" s="5">
-        <v>1095</v>
-      </c>
-      <c r="E47" s="7">
-        <v>14.8</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="5">
-        <v>134.57</v>
-      </c>
-      <c r="D48" s="5">
-        <v>136.96</v>
-      </c>
-      <c r="E48" s="7">
-        <v>2.39</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C49" s="5">
-        <v>43</v>
-      </c>
-      <c r="D49" s="5">
-        <v>29</v>
-      </c>
-      <c r="E49" s="6">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C50" s="5">
-        <v>29</v>
-      </c>
-      <c r="D50" s="5">
-        <v>43</v>
-      </c>
-      <c r="E50" s="7">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="5">
-        <v>63.33</v>
-      </c>
-      <c r="D51" s="5">
-        <v>67.08</v>
-      </c>
-      <c r="E51" s="7">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="5">
-        <v>39.01</v>
-      </c>
-      <c r="D52" s="5">
-        <v>35.85</v>
-      </c>
-      <c r="E52" s="6">
-        <v>-3.16</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="5">
-        <v>53.79</v>
-      </c>
-      <c r="D53" s="5">
-        <v>54.29</v>
-      </c>
-      <c r="E53" s="7">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="5">
-        <v>57.84</v>
-      </c>
-      <c r="D54" s="5">
-        <v>58.49</v>
-      </c>
-      <c r="E54" s="7">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="5">
-        <v>57.7</v>
-      </c>
-      <c r="D55" s="5">
-        <v>57.24</v>
-      </c>
-      <c r="E55" s="6">
-        <v>-0.46</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="5">
-        <v>51.47</v>
-      </c>
-      <c r="D56" s="5">
-        <v>55.08</v>
-      </c>
-      <c r="E56" s="7">
-        <v>3.61</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="5">
-        <v>40.03</v>
-      </c>
-      <c r="D57" s="5">
-        <v>46.9</v>
-      </c>
-      <c r="E57" s="7">
-        <v>6.87</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B58" s="3" t="s">
+      <c r="B66" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C58" s="5">
-        <v>-43.47</v>
-      </c>
-      <c r="D58" s="5">
-        <v>-58.53</v>
-      </c>
-      <c r="E58" s="6">
-        <v>-15.06</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C59" s="5">
-        <v>59.65</v>
-      </c>
-      <c r="D59" s="5">
-        <v>-37.85</v>
-      </c>
-      <c r="E59" s="6">
-        <v>-97.5</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="5">
-        <v>-85.95</v>
-      </c>
-      <c r="D60" s="5">
-        <v>-87.95</v>
-      </c>
-      <c r="E60" s="6">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="5">
-        <v>-36.26</v>
-      </c>
-      <c r="D61" s="5">
-        <v>-70.34</v>
-      </c>
-      <c r="E61" s="6">
-        <v>-34.08</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="5">
-        <v>-52.16</v>
-      </c>
-      <c r="D62" s="5">
-        <v>-45.29</v>
-      </c>
-      <c r="E62" s="7">
-        <v>6.87</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="5">
-        <v>-68.72</v>
-      </c>
-      <c r="D63" s="5">
-        <v>-25.15</v>
-      </c>
-      <c r="E63" s="7">
-        <v>43.57</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="5">
-        <v>-67.7</v>
-      </c>
-      <c r="D64" s="5">
-        <v>-49.95</v>
-      </c>
-      <c r="E64" s="7">
-        <v>17.75</v>
+      <c r="C66" s="7">
+        <v>-37.97</v>
+      </c>
+      <c r="D66" s="7">
+        <v>-61.61</v>
+      </c>
+      <c r="E66" s="9">
+        <v>-23.64</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2875,61 +3015,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C1" s="8" t="s">
+      <c r="B1" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="12">
+        <v>68.8</v>
+      </c>
+      <c r="C2" s="13">
+        <v>7</v>
+      </c>
+      <c r="D2" s="12">
+        <v>48.5</v>
+      </c>
+      <c r="E2" s="12">
+        <v>90</v>
+      </c>
+      <c r="F2" s="12">
+        <v>1.5</v>
+      </c>
+      <c r="G2" s="12">
+        <v>4.1</v>
+      </c>
+      <c r="H2" s="12">
         <v>57</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="10">
-        <v>68.8</v>
-      </c>
-      <c r="C2" s="11">
-        <v>7</v>
-      </c>
-      <c r="D2" s="10">
-        <v>53.6</v>
-      </c>
-      <c r="E2" s="10">
-        <v>90</v>
-      </c>
-      <c r="F2" s="10">
-        <v>3.2</v>
-      </c>
-      <c r="G2" s="10">
-        <v>6.3</v>
-      </c>
-      <c r="H2" s="10">
-        <v>57</v>
-      </c>
-      <c r="I2" s="10">
-        <v>60</v>
+      <c r="I2" s="12">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -3030,49 +3170,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="14" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="13">
-        <v>0.2865</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.2411</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.1673</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.1087</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.0617</v>
-      </c>
-      <c r="F2" s="13">
-        <v>-0.0032</v>
-      </c>
-      <c r="G2" s="13">
-        <v>-0.1812</v>
+      <c r="A2" s="15">
+        <v>0.2892</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.2375</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.1547</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.09480000000000001</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.0403</v>
+      </c>
+      <c r="F2" s="15">
+        <v>-0.0014</v>
+      </c>
+      <c r="G2" s="15">
+        <v>-0.2008</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="76">
   <si>
     <t>Symbol</t>
   </si>
@@ -187,49 +187,28 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>50 DMA &gt; 200 DMA</t>
-  </si>
-  <si>
-    <t>No → Yes</t>
-  </si>
-  <si>
-    <t>🟢 GOLDEN CROSS</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>48.1 → 53.6</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>52.2 → 47.2</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>52.2</t>
-  </si>
-  <si>
-    <t>47.2</t>
-  </si>
-  <si>
-    <t>55.3 → 48.1</t>
-  </si>
-  <si>
-    <t>55.3</t>
-  </si>
-  <si>
     <t>48.1</t>
   </si>
   <si>
-    <t>55.1 → 49.9</t>
-  </si>
-  <si>
-    <t>55.1</t>
+    <t>53.6</t>
+  </si>
+  <si>
+    <t>49.9 → 52.6</t>
   </si>
   <si>
     <t>49.9</t>
+  </si>
+  <si>
+    <t>52.6</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -431,7 +410,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -439,7 +418,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -955,58 +933,58 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>11800</v>
+        <v>11927</v>
       </c>
       <c r="D2">
-        <v>0.85</v>
+        <v>1.08</v>
       </c>
       <c r="E2">
-        <v>11856</v>
+        <v>11927</v>
       </c>
       <c r="F2">
         <v>8506.780000000001</v>
       </c>
       <c r="G2">
-        <v>-0.47</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>38.71</v>
+        <v>40.21</v>
       </c>
       <c r="I2">
-        <v>0.85</v>
+        <v>2.76</v>
       </c>
       <c r="J2">
-        <v>6.02</v>
+        <v>6.65</v>
       </c>
       <c r="K2">
-        <v>12.96</v>
+        <v>11.9</v>
       </c>
       <c r="L2">
-        <v>36.05</v>
+        <v>37.01</v>
       </c>
       <c r="M2">
-        <v>28.92</v>
+        <v>29.37</v>
       </c>
       <c r="N2">
         <v>85</v>
       </c>
       <c r="O2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P2">
-        <v>11709</v>
+        <v>11773</v>
       </c>
       <c r="Q2">
-        <v>11645.12</v>
+        <v>11672.78</v>
       </c>
       <c r="R2">
-        <v>10787.92</v>
+        <v>10827.6</v>
       </c>
       <c r="S2">
-        <v>9773.16</v>
+        <v>9789.799999999999</v>
       </c>
       <c r="T2">
-        <v>20.74</v>
+        <v>21.83</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -1021,43 +999,43 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>65.33</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="Z2">
-        <v>256.1</v>
+        <v>257.91</v>
       </c>
       <c r="AA2">
-        <v>298.84</v>
+        <v>290.65</v>
       </c>
       <c r="AB2">
-        <v>-42.74</v>
+        <v>-32.74</v>
       </c>
       <c r="AC2">
-        <v>21.52</v>
+        <v>45.11</v>
       </c>
       <c r="AD2">
-        <v>15.56</v>
+        <v>26.65</v>
       </c>
       <c r="AE2">
-        <v>197.65</v>
+        <v>198.18</v>
       </c>
       <c r="AF2">
-        <v>-16.28</v>
+        <v>-37.43</v>
       </c>
       <c r="AG2">
-        <v>11922.7</v>
+        <v>11946.78</v>
       </c>
       <c r="AH2">
-        <v>11367.55</v>
+        <v>11398.77</v>
       </c>
       <c r="AI2">
-        <v>11181.55</v>
+        <v>11229.97</v>
       </c>
       <c r="AJ2" t="s">
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>51.58</v>
+        <v>51.62</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1068,10 +1046,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>463.2</v>
+        <v>455.05</v>
       </c>
       <c r="D3">
-        <v>-3.17</v>
+        <v>-1.76</v>
       </c>
       <c r="E3">
         <v>670.25</v>
@@ -1080,46 +1058,46 @@
         <v>222.01</v>
       </c>
       <c r="G3">
-        <v>-30.89</v>
+        <v>-32.11</v>
       </c>
       <c r="H3">
-        <v>108.64</v>
+        <v>104.97</v>
       </c>
       <c r="I3">
-        <v>-3.78</v>
+        <v>-5.99</v>
       </c>
       <c r="J3">
-        <v>-15.75</v>
+        <v>-15.86</v>
       </c>
       <c r="K3">
-        <v>-16.51</v>
+        <v>-18.85</v>
       </c>
       <c r="L3">
-        <v>102.33</v>
+        <v>97.08</v>
       </c>
       <c r="M3">
-        <v>15.47</v>
+        <v>14.71</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P3">
-        <v>482.65</v>
+        <v>476.85</v>
       </c>
       <c r="Q3">
-        <v>517.36</v>
+        <v>513.5700000000001</v>
       </c>
       <c r="R3">
-        <v>562.08</v>
+        <v>559.33</v>
       </c>
       <c r="S3">
-        <v>421.63</v>
+        <v>422.41</v>
       </c>
       <c r="T3">
-        <v>9.859999999999999</v>
+        <v>7.73</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1134,43 +1112,43 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>30.94</v>
+        <v>29.42</v>
       </c>
       <c r="Z3">
-        <v>-22.35</v>
+        <v>-24.24</v>
       </c>
       <c r="AA3">
-        <v>-17.85</v>
+        <v>-19.13</v>
       </c>
       <c r="AB3">
-        <v>-4.5</v>
+        <v>-5.12</v>
       </c>
       <c r="AC3">
-        <v>14.95</v>
+        <v>5.63</v>
       </c>
       <c r="AD3">
-        <v>24.25</v>
+        <v>17.06</v>
       </c>
       <c r="AE3">
-        <v>21.9</v>
+        <v>22.34</v>
       </c>
       <c r="AF3">
-        <v>56</v>
+        <v>59.15</v>
       </c>
       <c r="AG3">
-        <v>569.51</v>
+        <v>572.1900000000001</v>
       </c>
       <c r="AH3">
-        <v>465.22</v>
+        <v>454.94</v>
       </c>
       <c r="AI3">
-        <v>536.87</v>
+        <v>534.77</v>
       </c>
       <c r="AJ3" t="s">
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>33.93</v>
+        <v>37.26</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1181,10 +1159,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>344.65</v>
+        <v>334.35</v>
       </c>
       <c r="D4">
-        <v>-1.99</v>
+        <v>-2.99</v>
       </c>
       <c r="E4">
         <v>604.85</v>
@@ -1193,46 +1171,46 @@
         <v>303.75</v>
       </c>
       <c r="G4">
-        <v>-43.02</v>
+        <v>-44.72</v>
       </c>
       <c r="H4">
-        <v>13.47</v>
+        <v>10.07</v>
       </c>
       <c r="I4">
-        <v>-4.9</v>
+        <v>-5.96</v>
       </c>
       <c r="J4">
-        <v>4.79</v>
+        <v>1.5</v>
       </c>
       <c r="K4">
-        <v>2.68</v>
+        <v>0.12</v>
       </c>
       <c r="L4">
-        <v>-42.15</v>
+        <v>-43.72</v>
       </c>
       <c r="M4">
-        <v>-20.08</v>
+        <v>-21.05</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
       <c r="O4">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="P4">
-        <v>351.95</v>
+        <v>347.71</v>
       </c>
       <c r="Q4">
-        <v>351.87</v>
+        <v>352.23</v>
       </c>
       <c r="R4">
-        <v>337.2</v>
+        <v>337.48</v>
       </c>
       <c r="S4">
-        <v>390.02</v>
+        <v>389.17</v>
       </c>
       <c r="T4">
-        <v>-11.63</v>
+        <v>-14.09</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1247,43 +1225,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>47.25</v>
+        <v>41.04</v>
       </c>
       <c r="Z4">
-        <v>4.68</v>
+        <v>2.82</v>
       </c>
       <c r="AA4">
-        <v>6.71</v>
+        <v>5.93</v>
       </c>
       <c r="AB4">
-        <v>-2.03</v>
+        <v>-3.12</v>
       </c>
       <c r="AC4">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="AD4">
-        <v>3.11</v>
+        <v>0.62</v>
       </c>
       <c r="AE4">
-        <v>12.56</v>
+        <v>12.6</v>
       </c>
       <c r="AF4">
-        <v>-74.87</v>
+        <v>-57.75</v>
       </c>
       <c r="AG4">
-        <v>381.38</v>
+        <v>380.61</v>
       </c>
       <c r="AH4">
-        <v>322.36</v>
+        <v>323.86</v>
       </c>
       <c r="AI4">
-        <v>335.86</v>
+        <v>377.03</v>
       </c>
       <c r="AJ4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AK4">
-        <v>41.86</v>
+        <v>39.91</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1294,10 +1272,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>2001.7</v>
+        <v>2004</v>
       </c>
       <c r="D5">
-        <v>-1.52</v>
+        <v>0.11</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1306,25 +1284,25 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-8.039999999999999</v>
+        <v>-7.93</v>
       </c>
       <c r="H5">
-        <v>22.67</v>
+        <v>22.81</v>
       </c>
       <c r="I5">
-        <v>-0.16</v>
+        <v>-0.36</v>
       </c>
       <c r="J5">
-        <v>6.66</v>
+        <v>4.76</v>
       </c>
       <c r="K5">
-        <v>11.16</v>
+        <v>10.77</v>
       </c>
       <c r="L5">
-        <v>1.5</v>
+        <v>2.32</v>
       </c>
       <c r="M5">
-        <v>4.03</v>
+        <v>4.77</v>
       </c>
       <c r="N5">
         <v>57</v>
@@ -1333,19 +1311,19 @@
         <v>63</v>
       </c>
       <c r="P5">
-        <v>2014.68</v>
+        <v>2013.24</v>
       </c>
       <c r="Q5">
-        <v>2017.91</v>
+        <v>2021.72</v>
       </c>
       <c r="R5">
-        <v>1908.82</v>
+        <v>1913.9</v>
       </c>
       <c r="S5">
-        <v>1908.38</v>
+        <v>1908.08</v>
       </c>
       <c r="T5">
-        <v>4.89</v>
+        <v>5.03</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1360,34 +1338,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>54.2</v>
+        <v>54.61</v>
       </c>
       <c r="Z5">
-        <v>30.09</v>
+        <v>27.14</v>
       </c>
       <c r="AA5">
-        <v>39.43</v>
+        <v>36.98</v>
       </c>
       <c r="AB5">
-        <v>-9.34</v>
+        <v>-9.84</v>
       </c>
       <c r="AC5">
-        <v>9.949999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="AD5">
-        <v>9.19</v>
+        <v>9.83</v>
       </c>
       <c r="AE5">
-        <v>37.86</v>
+        <v>37.07</v>
       </c>
       <c r="AF5">
-        <v>-65.87</v>
+        <v>-68.81</v>
       </c>
       <c r="AG5">
-        <v>2123.41</v>
+        <v>2118.69</v>
       </c>
       <c r="AH5">
-        <v>1912.41</v>
+        <v>1924.74</v>
       </c>
       <c r="AI5">
         <v>1958.53</v>
@@ -1396,7 +1374,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>16.44</v>
+        <v>16.69</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1407,10 +1385,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>11120</v>
+        <v>11290</v>
       </c>
       <c r="D6">
-        <v>-1.77</v>
+        <v>1.53</v>
       </c>
       <c r="E6">
         <v>13632.57</v>
@@ -1419,46 +1397,46 @@
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-18.43</v>
+        <v>-17.18</v>
       </c>
       <c r="H6">
-        <v>27.14</v>
+        <v>29.09</v>
       </c>
       <c r="I6">
-        <v>-3.09</v>
+        <v>0.32</v>
       </c>
       <c r="J6">
-        <v>4.13</v>
+        <v>4.44</v>
       </c>
       <c r="K6">
-        <v>3.88</v>
+        <v>6.95</v>
       </c>
       <c r="L6">
-        <v>-18.93</v>
+        <v>-16.83</v>
       </c>
       <c r="M6">
-        <v>23.75</v>
+        <v>23.84</v>
       </c>
       <c r="N6">
         <v>29</v>
       </c>
       <c r="O6">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="P6">
-        <v>11288.4</v>
+        <v>11295.6</v>
       </c>
       <c r="Q6">
-        <v>11340.25</v>
+        <v>11363.2</v>
       </c>
       <c r="R6">
-        <v>10899.58</v>
+        <v>10919.66</v>
       </c>
       <c r="S6">
-        <v>10748.08</v>
+        <v>10738.84</v>
       </c>
       <c r="T6">
-        <v>3.46</v>
+        <v>5.13</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1473,34 +1451,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>48.11</v>
+        <v>53.64</v>
       </c>
       <c r="Z6">
-        <v>134.72</v>
+        <v>122.41</v>
       </c>
       <c r="AA6">
-        <v>188.82</v>
+        <v>175.54</v>
       </c>
       <c r="AB6">
-        <v>-54.11</v>
+        <v>-53.13</v>
       </c>
       <c r="AC6">
-        <v>8.15</v>
+        <v>12.5</v>
       </c>
       <c r="AD6">
-        <v>11.36</v>
+        <v>11.66</v>
       </c>
       <c r="AE6">
-        <v>216.3</v>
+        <v>235.06</v>
       </c>
       <c r="AF6">
-        <v>60.45</v>
+        <v>47.92</v>
       </c>
       <c r="AG6">
-        <v>11776.9</v>
+        <v>11729.78</v>
       </c>
       <c r="AH6">
-        <v>10903.6</v>
+        <v>10996.62</v>
       </c>
       <c r="AI6">
         <v>10787.84</v>
@@ -1509,7 +1487,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>29.72</v>
+        <v>33.52</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1520,10 +1498,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>1077</v>
+        <v>1087.4</v>
       </c>
       <c r="D7">
-        <v>-1.64</v>
+        <v>0.97</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1532,46 +1510,46 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-7.06</v>
+        <v>-6.16</v>
       </c>
       <c r="H7">
-        <v>34.36</v>
+        <v>35.66</v>
       </c>
       <c r="I7">
-        <v>-1.13</v>
+        <v>-0.63</v>
       </c>
       <c r="J7">
-        <v>6.34</v>
+        <v>3.73</v>
       </c>
       <c r="K7">
-        <v>15.78</v>
+        <v>16.78</v>
       </c>
       <c r="L7">
-        <v>19.36</v>
+        <v>22.48</v>
       </c>
       <c r="M7">
-        <v>9.48</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="N7">
         <v>71</v>
       </c>
       <c r="O7">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="P7">
-        <v>1088.3</v>
+        <v>1086.92</v>
       </c>
       <c r="Q7">
-        <v>1098.97</v>
+        <v>1100.92</v>
       </c>
       <c r="R7">
-        <v>1045.18</v>
+        <v>1048.08</v>
       </c>
       <c r="S7">
-        <v>975.15</v>
+        <v>975.38</v>
       </c>
       <c r="T7">
-        <v>10.44</v>
+        <v>11.48</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1586,34 +1564,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>49.85</v>
+        <v>52.64</v>
       </c>
       <c r="Z7">
-        <v>11.76</v>
+        <v>10.63</v>
       </c>
       <c r="AA7">
-        <v>18.41</v>
+        <v>16.85</v>
       </c>
       <c r="AB7">
-        <v>-6.65</v>
+        <v>-6.22</v>
       </c>
       <c r="AC7">
-        <v>10.18</v>
+        <v>9.67</v>
       </c>
       <c r="AD7">
-        <v>9.619999999999999</v>
+        <v>10.01</v>
       </c>
       <c r="AE7">
-        <v>23.74</v>
+        <v>23.55</v>
       </c>
       <c r="AF7">
-        <v>-50.5</v>
+        <v>-65.8</v>
       </c>
       <c r="AG7">
-        <v>1165.77</v>
+        <v>1163.65</v>
       </c>
       <c r="AH7">
-        <v>1032.17</v>
+        <v>1038.19</v>
       </c>
       <c r="AI7">
         <v>1067.72</v>
@@ -1622,7 +1600,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>21.68</v>
+        <v>23.78</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1633,10 +1611,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>135.68</v>
+        <v>135.11</v>
       </c>
       <c r="D8">
-        <v>-1.12</v>
+        <v>-0.42</v>
       </c>
       <c r="E8">
         <v>148.95</v>
@@ -1645,46 +1623,46 @@
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>-8.91</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="H8">
-        <v>17.01</v>
+        <v>16.51</v>
       </c>
       <c r="I8">
-        <v>1.15</v>
+        <v>-0.43</v>
       </c>
       <c r="J8">
-        <v>-1.97</v>
+        <v>-3.88</v>
       </c>
       <c r="K8">
-        <v>-1.01</v>
+        <v>-3.42</v>
       </c>
       <c r="L8">
-        <v>-1.6</v>
+        <v>-1.29</v>
       </c>
       <c r="M8">
-        <v>-0.14</v>
+        <v>-0.06</v>
       </c>
       <c r="N8">
         <v>43</v>
       </c>
       <c r="O8">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P8">
-        <v>136.02</v>
+        <v>135.91</v>
       </c>
       <c r="Q8">
-        <v>138.78</v>
+        <v>138.58</v>
       </c>
       <c r="R8">
-        <v>137.4</v>
+        <v>137.39</v>
       </c>
       <c r="S8">
         <v>133.6</v>
       </c>
       <c r="T8">
-        <v>1.56</v>
+        <v>1.13</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1699,34 +1677,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>43.89</v>
+        <v>42.57</v>
       </c>
       <c r="Z8">
-        <v>-0.9</v>
+        <v>-0.99</v>
       </c>
       <c r="AA8">
-        <v>-0.42</v>
+        <v>-0.53</v>
       </c>
       <c r="AB8">
-        <v>-0.49</v>
+        <v>-0.46</v>
       </c>
       <c r="AC8">
-        <v>39.07</v>
+        <v>33.17</v>
       </c>
       <c r="AD8">
-        <v>32.02</v>
+        <v>35</v>
       </c>
       <c r="AE8">
-        <v>4</v>
+        <v>3.87</v>
       </c>
       <c r="AF8">
-        <v>-61.61</v>
+        <v>-68.91</v>
       </c>
       <c r="AG8">
         <v>145.44</v>
       </c>
       <c r="AH8">
-        <v>132.12</v>
+        <v>131.73</v>
       </c>
       <c r="AI8">
         <v>131.91</v>
@@ -1735,7 +1713,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>31.12</v>
+        <v>28.98</v>
       </c>
     </row>
   </sheetData>
@@ -1876,7 +1854,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1916,7 +1894,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>55</v>
@@ -1928,1074 +1906,1014 @@
         <v>57</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>6.02</v>
+      </c>
+      <c r="D8" s="6">
+        <v>6.65</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-15.75</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-15.86</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>4.79</v>
+      </c>
+      <c r="D10" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-3.29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="4" t="s">
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>6.66</v>
+      </c>
+      <c r="D11" s="6">
+        <v>4.76</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-1.9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>4.13</v>
+      </c>
+      <c r="D12" s="6">
+        <v>4.44</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>6.34</v>
+      </c>
+      <c r="D13" s="6">
+        <v>3.73</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-2.61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-1.97</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-3.88</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-1.91</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6">
+        <v>0.85</v>
+      </c>
+      <c r="D15" s="6">
+        <v>2.76</v>
+      </c>
+      <c r="E15" s="7">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-3.78</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-5.99</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-2.21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-4.9</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-5.96</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-0.16</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-0.36</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-3.09</v>
+      </c>
+      <c r="D19" s="6">
+        <v>0.32</v>
+      </c>
+      <c r="E19" s="7">
+        <v>3.41</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-1.13</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-0.63</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>1.15</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-0.43</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-1.58</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="6">
+        <v>36.05</v>
+      </c>
+      <c r="D22" s="6">
+        <v>37.01</v>
+      </c>
+      <c r="E22" s="7">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="6">
+        <v>102.33</v>
+      </c>
+      <c r="D23" s="6">
+        <v>97.08</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-5.25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-42.15</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-43.72</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-1.57</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="D25" s="6">
+        <v>2.32</v>
+      </c>
+      <c r="E25" s="7">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-18.93</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-16.83</v>
+      </c>
+      <c r="E26" s="7">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>19.36</v>
+      </c>
+      <c r="D27" s="6">
+        <v>22.48</v>
+      </c>
+      <c r="E27" s="7">
+        <v>3.12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-1.6</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-1.29</v>
+      </c>
+      <c r="E28" s="7">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="6">
+        <v>12.96</v>
+      </c>
+      <c r="D29" s="6">
+        <v>11.9</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-16.51</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-18.85</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-2.34</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="6">
+        <v>2.68</v>
+      </c>
+      <c r="D31" s="6">
+        <v>0.12</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-2.56</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="6">
+        <v>11.16</v>
+      </c>
+      <c r="D32" s="6">
+        <v>10.77</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6">
+        <v>3.88</v>
+      </c>
+      <c r="D33" s="6">
+        <v>6.95</v>
+      </c>
+      <c r="E33" s="7">
+        <v>3.07</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>15.78</v>
+      </c>
+      <c r="D34" s="6">
+        <v>16.78</v>
+      </c>
+      <c r="E34" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-1.01</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-3.42</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-2.41</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-0.47</v>
+      </c>
+      <c r="D36" s="6">
+        <v>0</v>
+      </c>
+      <c r="E36" s="7">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-30.89</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-32.11</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-1.22</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-43.02</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-44.72</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-8.039999999999999</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-7.93</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-18.43</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-17.18</v>
+      </c>
+      <c r="E40" s="7">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-7.06</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-6.16</v>
+      </c>
+      <c r="E41" s="7">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-8.91</v>
+      </c>
+      <c r="D42" s="6">
+        <v>-9.289999999999999</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="6">
+        <v>11800</v>
+      </c>
+      <c r="D43" s="6">
+        <v>11927</v>
+      </c>
+      <c r="E43" s="7">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="6">
+        <v>463.2</v>
+      </c>
+      <c r="D44" s="6">
+        <v>455.05</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-8.15</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="6">
+        <v>344.65</v>
+      </c>
+      <c r="D45" s="6">
+        <v>334.35</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-10.3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="6">
+        <v>2001.7</v>
+      </c>
+      <c r="D46" s="6">
+        <v>2004</v>
+      </c>
+      <c r="E46" s="7">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="6">
+        <v>11120</v>
+      </c>
+      <c r="D47" s="6">
+        <v>11290</v>
+      </c>
+      <c r="E47" s="7">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="6">
+        <v>1077</v>
+      </c>
+      <c r="D48" s="6">
+        <v>1087.4</v>
+      </c>
+      <c r="E48" s="7">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="6">
+        <v>135.68</v>
+      </c>
+      <c r="D49" s="6">
+        <v>135.11</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="6">
+        <v>65.33</v>
+      </c>
+      <c r="D50" s="6">
+        <v>68.34999999999999</v>
+      </c>
+      <c r="E50" s="7">
+        <v>3.02</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="6">
+        <v>30.94</v>
+      </c>
+      <c r="D51" s="6">
+        <v>29.42</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-1.52</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="6">
+        <v>47.25</v>
+      </c>
+      <c r="D52" s="6">
+        <v>41.04</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-6.21</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="6">
+        <v>54.2</v>
+      </c>
+      <c r="D53" s="6">
+        <v>54.61</v>
+      </c>
+      <c r="E53" s="7">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="6">
+        <v>48.11</v>
+      </c>
+      <c r="D54" s="6">
+        <v>53.64</v>
+      </c>
+      <c r="E54" s="7">
+        <v>5.53</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="6">
+        <v>49.85</v>
+      </c>
+      <c r="D55" s="6">
+        <v>52.64</v>
+      </c>
+      <c r="E55" s="7">
+        <v>2.79</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="6">
+        <v>43.89</v>
+      </c>
+      <c r="D56" s="6">
+        <v>42.57</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-1.32</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C57" s="6">
+        <v>-16.28</v>
+      </c>
+      <c r="D57" s="6">
+        <v>-37.43</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-21.15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="6">
         <v>56</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
+      <c r="D58" s="6">
+        <v>59.15</v>
+      </c>
+      <c r="E58" s="7">
+        <v>3.15</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="5" t="s">
+      <c r="B59" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="6">
+        <v>-74.87</v>
+      </c>
+      <c r="D59" s="6">
+        <v>-57.75</v>
+      </c>
+      <c r="E59" s="7">
+        <v>17.12</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="6">
+        <v>-65.87</v>
+      </c>
+      <c r="D60" s="6">
+        <v>-68.81</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-2.94</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="B61" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="6">
+        <v>60.45</v>
+      </c>
+      <c r="D61" s="6">
+        <v>47.92</v>
+      </c>
+      <c r="E61" s="8">
+        <v>-12.53</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>3.69</v>
-      </c>
-      <c r="D11" s="7">
-        <v>6.02</v>
-      </c>
-      <c r="E11" s="8">
-        <v>2.33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>-13.95</v>
-      </c>
-      <c r="D12" s="7">
-        <v>-15.75</v>
-      </c>
-      <c r="E12" s="9">
-        <v>-1.8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>7.8</v>
-      </c>
-      <c r="D13" s="7">
-        <v>4.79</v>
-      </c>
-      <c r="E13" s="9">
-        <v>-3.01</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>7.57</v>
-      </c>
-      <c r="D14" s="7">
-        <v>6.66</v>
-      </c>
-      <c r="E14" s="9">
-        <v>-0.91</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="7">
-        <v>6.43</v>
-      </c>
-      <c r="D15" s="7">
-        <v>4.13</v>
-      </c>
-      <c r="E15" s="9">
-        <v>-2.3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="7">
-        <v>5.31</v>
-      </c>
-      <c r="D16" s="7">
-        <v>6.34</v>
-      </c>
-      <c r="E16" s="8">
-        <v>1.03</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B62" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="6">
+        <v>-50.5</v>
+      </c>
+      <c r="D62" s="6">
+        <v>-65.8</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-15.3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-0.97</v>
-      </c>
-      <c r="D17" s="7">
-        <v>-1.97</v>
-      </c>
-      <c r="E17" s="9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>0</v>
-      </c>
-      <c r="D18" s="7">
-        <v>0.85</v>
-      </c>
-      <c r="E18" s="8">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>-4.44</v>
-      </c>
-      <c r="D19" s="7">
-        <v>-3.78</v>
-      </c>
-      <c r="E19" s="8">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-2.97</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-4.9</v>
-      </c>
-      <c r="E20" s="9">
-        <v>-1.93</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>1.2</v>
-      </c>
-      <c r="D21" s="7">
-        <v>-0.16</v>
-      </c>
-      <c r="E21" s="9">
-        <v>-1.36</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="7">
-        <v>-1.35</v>
-      </c>
-      <c r="D22" s="7">
-        <v>-3.09</v>
-      </c>
-      <c r="E22" s="9">
-        <v>-1.74</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="7">
-        <v>0.74</v>
-      </c>
-      <c r="D23" s="7">
-        <v>-1.13</v>
-      </c>
-      <c r="E23" s="9">
-        <v>-1.87</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="7">
-        <v>2.29</v>
-      </c>
-      <c r="D24" s="7">
-        <v>1.15</v>
-      </c>
-      <c r="E24" s="9">
-        <v>-1.14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="7">
-        <v>38.15</v>
-      </c>
-      <c r="D25" s="7">
-        <v>36.05</v>
-      </c>
-      <c r="E25" s="9">
-        <v>-2.1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="7">
-        <v>112.03</v>
-      </c>
-      <c r="D26" s="7">
-        <v>102.33</v>
-      </c>
-      <c r="E26" s="9">
-        <v>-9.699999999999999</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="7">
-        <v>-39.17</v>
-      </c>
-      <c r="D27" s="7">
-        <v>-42.15</v>
-      </c>
-      <c r="E27" s="9">
-        <v>-2.98</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7">
-        <v>1.96</v>
-      </c>
-      <c r="D28" s="7">
-        <v>1.5</v>
-      </c>
-      <c r="E28" s="9">
-        <v>-0.46</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="7">
-        <v>-21.67</v>
-      </c>
-      <c r="D29" s="7">
-        <v>-18.93</v>
-      </c>
-      <c r="E29" s="8">
-        <v>2.74</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="7">
-        <v>20.97</v>
-      </c>
-      <c r="D30" s="7">
-        <v>19.36</v>
-      </c>
-      <c r="E30" s="9">
-        <v>-1.61</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="7">
-        <v>0.46</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-1.6</v>
-      </c>
-      <c r="E31" s="9">
-        <v>-2.06</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="7">
-        <v>13.09</v>
-      </c>
-      <c r="D32" s="7">
-        <v>12.96</v>
-      </c>
-      <c r="E32" s="9">
-        <v>-0.13</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="7">
-        <v>-14.85</v>
-      </c>
-      <c r="D33" s="7">
-        <v>-16.51</v>
-      </c>
-      <c r="E33" s="9">
-        <v>-1.66</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="7">
-        <v>4.01</v>
-      </c>
-      <c r="D34" s="7">
-        <v>2.68</v>
-      </c>
-      <c r="E34" s="9">
-        <v>-1.33</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="7">
-        <v>12.45</v>
-      </c>
-      <c r="D35" s="7">
-        <v>11.16</v>
-      </c>
-      <c r="E35" s="9">
-        <v>-1.29</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="7">
-        <v>6.37</v>
-      </c>
-      <c r="D36" s="7">
-        <v>3.88</v>
-      </c>
-      <c r="E36" s="9">
-        <v>-2.49</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="7">
-        <v>16.25</v>
-      </c>
-      <c r="D37" s="7">
-        <v>15.78</v>
-      </c>
-      <c r="E37" s="9">
-        <v>-0.47</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="7">
-        <v>-2.09</v>
-      </c>
-      <c r="D38" s="7">
-        <v>-1.01</v>
-      </c>
-      <c r="E38" s="8">
-        <v>1.08</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="7">
-        <v>-1.32</v>
-      </c>
-      <c r="D39" s="7">
-        <v>-0.47</v>
-      </c>
-      <c r="E39" s="8">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="7">
-        <v>-28.63</v>
-      </c>
-      <c r="D40" s="7">
-        <v>-30.89</v>
-      </c>
-      <c r="E40" s="9">
-        <v>-2.26</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="7">
-        <v>-41.86</v>
-      </c>
-      <c r="D41" s="7">
-        <v>-43.02</v>
-      </c>
-      <c r="E41" s="9">
-        <v>-1.16</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="7">
-        <v>-6.62</v>
-      </c>
-      <c r="D42" s="7">
-        <v>-8.039999999999999</v>
-      </c>
-      <c r="E42" s="9">
-        <v>-1.42</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="7">
-        <v>-17.48</v>
-      </c>
-      <c r="D43" s="7">
-        <v>-18.43</v>
-      </c>
-      <c r="E43" s="9">
-        <v>-0.95</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="7">
-        <v>-5.51</v>
-      </c>
-      <c r="D44" s="7">
-        <v>-7.06</v>
-      </c>
-      <c r="E44" s="9">
-        <v>-1.55</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="7">
-        <v>-7.88</v>
-      </c>
-      <c r="D45" s="7">
-        <v>-8.91</v>
-      </c>
-      <c r="E45" s="9">
-        <v>-1.03</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="7">
-        <v>11700</v>
-      </c>
-      <c r="D46" s="7">
-        <v>11800</v>
-      </c>
-      <c r="E46" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="7">
-        <v>478.35</v>
-      </c>
-      <c r="D47" s="7">
-        <v>463.2</v>
-      </c>
-      <c r="E47" s="9">
-        <v>-15.15</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="7">
-        <v>351.65</v>
-      </c>
-      <c r="D48" s="7">
-        <v>344.65</v>
-      </c>
-      <c r="E48" s="9">
-        <v>-7</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="7">
-        <v>2032.5</v>
-      </c>
-      <c r="D49" s="7">
-        <v>2001.7</v>
-      </c>
-      <c r="E49" s="9">
-        <v>-30.8</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="7">
-        <v>11320</v>
-      </c>
-      <c r="D50" s="7">
-        <v>11120</v>
-      </c>
-      <c r="E50" s="9">
-        <v>-200</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="7">
-        <v>1095</v>
-      </c>
-      <c r="D51" s="7">
-        <v>1077</v>
-      </c>
-      <c r="E51" s="9">
-        <v>-18</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="7">
-        <v>137.21</v>
-      </c>
-      <c r="D52" s="7">
-        <v>135.68</v>
-      </c>
-      <c r="E52" s="9">
-        <v>-1.53</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="7">
-        <v>62.74</v>
-      </c>
-      <c r="D53" s="7">
-        <v>65.33</v>
-      </c>
-      <c r="E53" s="8">
-        <v>2.59</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="7">
-        <v>33.99</v>
-      </c>
-      <c r="D54" s="7">
-        <v>30.94</v>
-      </c>
-      <c r="E54" s="9">
-        <v>-3.05</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="7">
-        <v>52.24</v>
-      </c>
-      <c r="D55" s="7">
-        <v>47.25</v>
-      </c>
-      <c r="E55" s="9">
-        <v>-4.99</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="7">
-        <v>61.13</v>
-      </c>
-      <c r="D56" s="7">
-        <v>54.2</v>
-      </c>
-      <c r="E56" s="9">
-        <v>-6.93</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="7">
-        <v>55.33</v>
-      </c>
-      <c r="D57" s="7">
-        <v>48.11</v>
-      </c>
-      <c r="E57" s="9">
-        <v>-7.22</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="7">
-        <v>55.08</v>
-      </c>
-      <c r="D58" s="7">
-        <v>49.85</v>
-      </c>
-      <c r="E58" s="9">
-        <v>-5.23</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="7">
-        <v>47.58</v>
-      </c>
-      <c r="D59" s="7">
-        <v>43.89</v>
-      </c>
-      <c r="E59" s="9">
-        <v>-3.69</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B60" s="6" t="s">
+      <c r="B63" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C60" s="7">
-        <v>-26.92</v>
-      </c>
-      <c r="D60" s="7">
-        <v>-16.28</v>
-      </c>
-      <c r="E60" s="8">
-        <v>10.64</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="7">
-        <v>-11.46</v>
-      </c>
-      <c r="D61" s="7">
-        <v>56</v>
-      </c>
-      <c r="E61" s="8">
-        <v>67.45999999999999</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="7">
-        <v>-88.25</v>
-      </c>
-      <c r="D62" s="7">
-        <v>-74.87</v>
-      </c>
-      <c r="E62" s="8">
-        <v>13.38</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="7">
-        <v>-39.81</v>
-      </c>
-      <c r="D63" s="7">
-        <v>-65.87</v>
-      </c>
-      <c r="E63" s="9">
-        <v>-26.06</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="7">
-        <v>-49.16</v>
-      </c>
-      <c r="D64" s="7">
-        <v>60.45</v>
-      </c>
-      <c r="E64" s="8">
-        <v>109.61</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="7">
-        <v>-66.20999999999999</v>
-      </c>
-      <c r="D65" s="7">
-        <v>-50.5</v>
-      </c>
-      <c r="E65" s="8">
-        <v>15.71</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="7">
-        <v>-37.97</v>
-      </c>
-      <c r="D66" s="7">
+      <c r="C63" s="6">
         <v>-61.61</v>
       </c>
-      <c r="E66" s="9">
-        <v>-23.64</v>
+      <c r="D63" s="6">
+        <v>-68.91</v>
+      </c>
+      <c r="E63" s="8">
+        <v>-7.3</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3015,60 +2933,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="I1" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="C1" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>82</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="11">
         <v>68.8</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="12">
         <v>7</v>
       </c>
-      <c r="D2" s="12">
-        <v>48.5</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="11">
+        <v>48.9</v>
+      </c>
+      <c r="E2" s="11">
         <v>90</v>
       </c>
-      <c r="F2" s="12">
-        <v>1.5</v>
-      </c>
-      <c r="G2" s="12">
-        <v>4.1</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="F2" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="G2" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="H2" s="11">
         <v>57</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>70</v>
       </c>
     </row>
@@ -3170,49 +3088,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="15">
-        <v>0.2892</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.2375</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.1547</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.09480000000000001</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0.0403</v>
-      </c>
-      <c r="F2" s="15">
-        <v>-0.0014</v>
-      </c>
-      <c r="G2" s="15">
-        <v>-0.2008</v>
+      <c r="A2" s="14">
+        <v>0.2937</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.2384</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.1471</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.098</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.04769999999999999</v>
+      </c>
+      <c r="F2" s="14">
+        <v>-0.0005999999999999999</v>
+      </c>
+      <c r="G2" s="14">
+        <v>-0.2105</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="73">
   <si>
     <t>Symbol</t>
   </si>
@@ -187,28 +187,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>48.1 → 53.6</t>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>29.4 → 33.1</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>48.1</t>
-  </si>
-  <si>
-    <t>53.6</t>
-  </si>
-  <si>
-    <t>49.9 → 52.6</t>
-  </si>
-  <si>
-    <t>49.9</t>
-  </si>
-  <si>
-    <t>52.6</t>
+    <t>29.4</t>
+  </si>
+  <si>
+    <t>33.1</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -420,8 +411,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -933,10 +924,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>11927</v>
+        <v>11724</v>
       </c>
       <c r="D2">
-        <v>1.08</v>
+        <v>-1.7</v>
       </c>
       <c r="E2">
         <v>11927</v>
@@ -945,46 +936,46 @@
         <v>8506.780000000001</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>-1.7</v>
       </c>
       <c r="H2">
-        <v>40.21</v>
+        <v>37.82</v>
       </c>
       <c r="I2">
-        <v>2.76</v>
+        <v>0.68</v>
       </c>
       <c r="J2">
-        <v>6.65</v>
+        <v>3.08</v>
       </c>
       <c r="K2">
-        <v>11.9</v>
+        <v>10</v>
       </c>
       <c r="L2">
-        <v>37.01</v>
+        <v>36.9</v>
       </c>
       <c r="M2">
-        <v>29.37</v>
+        <v>28.91</v>
       </c>
       <c r="N2">
         <v>85</v>
       </c>
       <c r="O2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="P2">
-        <v>11773</v>
+        <v>11788.8</v>
       </c>
       <c r="Q2">
-        <v>11672.78</v>
+        <v>11692.08</v>
       </c>
       <c r="R2">
-        <v>10827.6</v>
+        <v>10863.3</v>
       </c>
       <c r="S2">
-        <v>9789.799999999999</v>
+        <v>9805.42</v>
       </c>
       <c r="T2">
-        <v>21.83</v>
+        <v>19.57</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -999,34 +990,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>68.34999999999999</v>
+        <v>59.45</v>
       </c>
       <c r="Z2">
-        <v>257.91</v>
+        <v>240.2</v>
       </c>
       <c r="AA2">
-        <v>290.65</v>
+        <v>280.56</v>
       </c>
       <c r="AB2">
-        <v>-32.74</v>
+        <v>-40.36</v>
       </c>
       <c r="AC2">
-        <v>45.11</v>
+        <v>43.64</v>
       </c>
       <c r="AD2">
-        <v>26.65</v>
+        <v>36.76</v>
       </c>
       <c r="AE2">
-        <v>198.18</v>
+        <v>198.52</v>
       </c>
       <c r="AF2">
-        <v>-37.43</v>
+        <v>-33.06</v>
       </c>
       <c r="AG2">
-        <v>11946.78</v>
+        <v>11916.73</v>
       </c>
       <c r="AH2">
-        <v>11398.77</v>
+        <v>11467.42</v>
       </c>
       <c r="AI2">
         <v>11229.97</v>
@@ -1035,7 +1026,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>51.62</v>
+        <v>51.65</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1046,10 +1037,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>455.05</v>
+        <v>463.5</v>
       </c>
       <c r="D3">
-        <v>-1.76</v>
+        <v>1.86</v>
       </c>
       <c r="E3">
         <v>670.25</v>
@@ -1058,46 +1049,46 @@
         <v>222.01</v>
       </c>
       <c r="G3">
-        <v>-32.11</v>
+        <v>-30.85</v>
       </c>
       <c r="H3">
-        <v>104.97</v>
+        <v>108.77</v>
       </c>
       <c r="I3">
-        <v>-5.99</v>
+        <v>-7.43</v>
       </c>
       <c r="J3">
-        <v>-15.86</v>
+        <v>-12.7</v>
       </c>
       <c r="K3">
-        <v>-18.85</v>
+        <v>-17.34</v>
       </c>
       <c r="L3">
-        <v>97.08</v>
+        <v>102.34</v>
       </c>
       <c r="M3">
-        <v>14.71</v>
+        <v>15.14</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P3">
-        <v>476.85</v>
+        <v>469.41</v>
       </c>
       <c r="Q3">
-        <v>513.5700000000001</v>
+        <v>509.92</v>
       </c>
       <c r="R3">
-        <v>559.33</v>
+        <v>556.6</v>
       </c>
       <c r="S3">
-        <v>422.41</v>
+        <v>423.22</v>
       </c>
       <c r="T3">
-        <v>7.73</v>
+        <v>9.52</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1112,43 +1103,43 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>29.42</v>
+        <v>33.1</v>
       </c>
       <c r="Z3">
-        <v>-24.24</v>
+        <v>-24.78</v>
       </c>
       <c r="AA3">
-        <v>-19.13</v>
+        <v>-20.26</v>
       </c>
       <c r="AB3">
-        <v>-5.12</v>
+        <v>-4.52</v>
       </c>
       <c r="AC3">
-        <v>5.63</v>
+        <v>6.65</v>
       </c>
       <c r="AD3">
-        <v>17.06</v>
+        <v>9.07</v>
       </c>
       <c r="AE3">
-        <v>22.34</v>
+        <v>21.78</v>
       </c>
       <c r="AF3">
-        <v>59.15</v>
+        <v>-26.55</v>
       </c>
       <c r="AG3">
-        <v>572.1900000000001</v>
+        <v>571.54</v>
       </c>
       <c r="AH3">
-        <v>454.94</v>
+        <v>448.29</v>
       </c>
       <c r="AI3">
-        <v>534.77</v>
+        <v>527.59</v>
       </c>
       <c r="AJ3" t="s">
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>37.26</v>
+        <v>40.15</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1159,10 +1150,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>334.35</v>
+        <v>340.6</v>
       </c>
       <c r="D4">
-        <v>-2.99</v>
+        <v>1.87</v>
       </c>
       <c r="E4">
         <v>604.85</v>
@@ -1171,46 +1162,46 @@
         <v>303.75</v>
       </c>
       <c r="G4">
-        <v>-44.72</v>
+        <v>-43.69</v>
       </c>
       <c r="H4">
-        <v>10.07</v>
+        <v>12.13</v>
       </c>
       <c r="I4">
-        <v>-5.96</v>
+        <v>-3.66</v>
       </c>
       <c r="J4">
-        <v>1.5</v>
+        <v>4.14</v>
       </c>
       <c r="K4">
-        <v>0.12</v>
+        <v>1.99</v>
       </c>
       <c r="L4">
-        <v>-43.72</v>
+        <v>-42.68</v>
       </c>
       <c r="M4">
-        <v>-21.05</v>
+        <v>-20.78</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
       <c r="O4">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P4">
-        <v>347.71</v>
+        <v>345.12</v>
       </c>
       <c r="Q4">
-        <v>352.23</v>
+        <v>352.74</v>
       </c>
       <c r="R4">
-        <v>337.48</v>
+        <v>337.83</v>
       </c>
       <c r="S4">
-        <v>389.17</v>
+        <v>388.38</v>
       </c>
       <c r="T4">
-        <v>-14.09</v>
+        <v>-12.3</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1225,34 +1216,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>41.04</v>
+        <v>45.7</v>
       </c>
       <c r="Z4">
-        <v>2.82</v>
+        <v>1.82</v>
       </c>
       <c r="AA4">
-        <v>5.93</v>
+        <v>5.11</v>
       </c>
       <c r="AB4">
-        <v>-3.12</v>
+        <v>-3.29</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>5.61</v>
       </c>
       <c r="AD4">
-        <v>0.62</v>
+        <v>2.1</v>
       </c>
       <c r="AE4">
-        <v>12.6</v>
+        <v>12.67</v>
       </c>
       <c r="AF4">
-        <v>-57.75</v>
+        <v>-73.59999999999999</v>
       </c>
       <c r="AG4">
-        <v>380.61</v>
+        <v>379.82</v>
       </c>
       <c r="AH4">
-        <v>323.86</v>
+        <v>325.65</v>
       </c>
       <c r="AI4">
         <v>377.03</v>
@@ -1261,7 +1252,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>39.91</v>
+        <v>37.21</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1272,10 +1263,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>2004</v>
+        <v>2010</v>
       </c>
       <c r="D5">
-        <v>0.11</v>
+        <v>0.3</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1284,22 +1275,22 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-7.93</v>
+        <v>-7.65</v>
       </c>
       <c r="H5">
-        <v>22.81</v>
+        <v>23.18</v>
       </c>
       <c r="I5">
-        <v>-0.36</v>
+        <v>-0.1</v>
       </c>
       <c r="J5">
-        <v>4.76</v>
+        <v>4.26</v>
       </c>
       <c r="K5">
-        <v>10.77</v>
+        <v>11.1</v>
       </c>
       <c r="L5">
-        <v>2.32</v>
+        <v>1.52</v>
       </c>
       <c r="M5">
         <v>4.77</v>
@@ -1308,22 +1299,22 @@
         <v>57</v>
       </c>
       <c r="O5">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P5">
-        <v>2013.24</v>
+        <v>2012.84</v>
       </c>
       <c r="Q5">
-        <v>2021.72</v>
+        <v>2026</v>
       </c>
       <c r="R5">
-        <v>1913.9</v>
+        <v>1918.35</v>
       </c>
       <c r="S5">
-        <v>1908.08</v>
+        <v>1907.62</v>
       </c>
       <c r="T5">
-        <v>5.03</v>
+        <v>5.37</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1338,34 +1329,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>54.61</v>
+        <v>55.73</v>
       </c>
       <c r="Z5">
-        <v>27.14</v>
+        <v>24.99</v>
       </c>
       <c r="AA5">
-        <v>36.98</v>
+        <v>34.58</v>
       </c>
       <c r="AB5">
-        <v>-9.84</v>
+        <v>-9.59</v>
       </c>
       <c r="AC5">
-        <v>7.9</v>
+        <v>7.41</v>
       </c>
       <c r="AD5">
-        <v>9.83</v>
+        <v>8.42</v>
       </c>
       <c r="AE5">
-        <v>37.07</v>
+        <v>35.91</v>
       </c>
       <c r="AF5">
-        <v>-68.81</v>
+        <v>-56.7</v>
       </c>
       <c r="AG5">
-        <v>2118.69</v>
+        <v>2111.8</v>
       </c>
       <c r="AH5">
-        <v>1924.74</v>
+        <v>1940.19</v>
       </c>
       <c r="AI5">
         <v>1958.53</v>
@@ -1374,7 +1365,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>16.69</v>
+        <v>14.73</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1385,58 +1376,58 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>11290</v>
+        <v>11540</v>
       </c>
       <c r="D6">
-        <v>1.53</v>
+        <v>2.21</v>
       </c>
       <c r="E6">
-        <v>13632.57</v>
+        <v>13595.75</v>
       </c>
       <c r="F6">
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-17.18</v>
+        <v>-15.12</v>
       </c>
       <c r="H6">
-        <v>29.09</v>
+        <v>31.95</v>
       </c>
       <c r="I6">
-        <v>0.32</v>
+        <v>1.41</v>
       </c>
       <c r="J6">
-        <v>4.44</v>
+        <v>6.55</v>
       </c>
       <c r="K6">
-        <v>6.95</v>
+        <v>9.32</v>
       </c>
       <c r="L6">
-        <v>-16.83</v>
+        <v>-15.35</v>
       </c>
       <c r="M6">
-        <v>23.84</v>
+        <v>24.53</v>
       </c>
       <c r="N6">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="O6">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="P6">
-        <v>11295.6</v>
+        <v>11327.6</v>
       </c>
       <c r="Q6">
-        <v>11363.2</v>
+        <v>11392.75</v>
       </c>
       <c r="R6">
-        <v>10919.66</v>
+        <v>10941.18</v>
       </c>
       <c r="S6">
-        <v>10738.84</v>
+        <v>10733.64</v>
       </c>
       <c r="T6">
-        <v>5.13</v>
+        <v>7.51</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1451,34 +1442,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>53.64</v>
+        <v>60.34</v>
       </c>
       <c r="Z6">
-        <v>122.41</v>
+        <v>131.31</v>
       </c>
       <c r="AA6">
-        <v>175.54</v>
+        <v>166.69</v>
       </c>
       <c r="AB6">
-        <v>-53.13</v>
+        <v>-35.38</v>
       </c>
       <c r="AC6">
-        <v>12.5</v>
+        <v>31.33</v>
       </c>
       <c r="AD6">
-        <v>11.66</v>
+        <v>17.33</v>
       </c>
       <c r="AE6">
-        <v>235.06</v>
+        <v>240.91</v>
       </c>
       <c r="AF6">
-        <v>47.92</v>
+        <v>-21.7</v>
       </c>
       <c r="AG6">
-        <v>11729.78</v>
+        <v>11710.82</v>
       </c>
       <c r="AH6">
-        <v>10996.62</v>
+        <v>11074.68</v>
       </c>
       <c r="AI6">
         <v>10787.84</v>
@@ -1487,7 +1478,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>33.52</v>
+        <v>30.94</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1498,10 +1489,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>1087.4</v>
+        <v>1085</v>
       </c>
       <c r="D7">
-        <v>0.97</v>
+        <v>-0.22</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1510,46 +1501,46 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-6.16</v>
+        <v>-6.37</v>
       </c>
       <c r="H7">
-        <v>35.66</v>
+        <v>35.36</v>
       </c>
       <c r="I7">
-        <v>-0.63</v>
+        <v>0.44</v>
       </c>
       <c r="J7">
-        <v>3.73</v>
+        <v>3.49</v>
       </c>
       <c r="K7">
-        <v>16.78</v>
+        <v>16.52</v>
       </c>
       <c r="L7">
-        <v>22.48</v>
+        <v>21.15</v>
       </c>
       <c r="M7">
-        <v>9.800000000000001</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="N7">
         <v>71</v>
       </c>
       <c r="O7">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="P7">
-        <v>1086.92</v>
+        <v>1087.88</v>
       </c>
       <c r="Q7">
-        <v>1100.92</v>
+        <v>1102.45</v>
       </c>
       <c r="R7">
-        <v>1048.08</v>
+        <v>1050.59</v>
       </c>
       <c r="S7">
-        <v>975.38</v>
+        <v>975.47</v>
       </c>
       <c r="T7">
-        <v>11.48</v>
+        <v>11.23</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1564,34 +1555,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>52.64</v>
+        <v>51.92</v>
       </c>
       <c r="Z7">
-        <v>10.63</v>
+        <v>9.44</v>
       </c>
       <c r="AA7">
-        <v>16.85</v>
+        <v>15.37</v>
       </c>
       <c r="AB7">
-        <v>-6.22</v>
+        <v>-5.93</v>
       </c>
       <c r="AC7">
-        <v>9.67</v>
+        <v>13.95</v>
       </c>
       <c r="AD7">
-        <v>10.01</v>
+        <v>11.27</v>
       </c>
       <c r="AE7">
-        <v>23.55</v>
+        <v>22.77</v>
       </c>
       <c r="AF7">
-        <v>-65.8</v>
+        <v>-58.88</v>
       </c>
       <c r="AG7">
-        <v>1163.65</v>
+        <v>1161.81</v>
       </c>
       <c r="AH7">
-        <v>1038.19</v>
+        <v>1043.09</v>
       </c>
       <c r="AI7">
         <v>1067.72</v>
@@ -1600,7 +1591,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>23.78</v>
+        <v>23.65</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1611,10 +1602,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>135.11</v>
+        <v>137.03</v>
       </c>
       <c r="D8">
-        <v>-0.42</v>
+        <v>1.42</v>
       </c>
       <c r="E8">
         <v>148.95</v>
@@ -1623,46 +1614,46 @@
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>-9.289999999999999</v>
+        <v>-8</v>
       </c>
       <c r="H8">
-        <v>16.51</v>
+        <v>18.17</v>
       </c>
       <c r="I8">
-        <v>-0.43</v>
+        <v>1.83</v>
       </c>
       <c r="J8">
-        <v>-3.88</v>
+        <v>-1.49</v>
       </c>
       <c r="K8">
-        <v>-3.42</v>
+        <v>-2.05</v>
       </c>
       <c r="L8">
-        <v>-1.29</v>
+        <v>-0.28</v>
       </c>
       <c r="M8">
-        <v>-0.06</v>
+        <v>0.14</v>
       </c>
       <c r="N8">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="O8">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="P8">
-        <v>135.91</v>
+        <v>136.4</v>
       </c>
       <c r="Q8">
-        <v>138.58</v>
+        <v>138.47</v>
       </c>
       <c r="R8">
-        <v>137.39</v>
+        <v>137.42</v>
       </c>
       <c r="S8">
-        <v>133.6</v>
+        <v>133.62</v>
       </c>
       <c r="T8">
-        <v>1.13</v>
+        <v>2.56</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1677,34 +1668,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>42.57</v>
+        <v>48.23</v>
       </c>
       <c r="Z8">
-        <v>-0.99</v>
+        <v>-0.89</v>
       </c>
       <c r="AA8">
-        <v>-0.53</v>
+        <v>-0.6</v>
       </c>
       <c r="AB8">
-        <v>-0.46</v>
+        <v>-0.29</v>
       </c>
       <c r="AC8">
-        <v>33.17</v>
+        <v>34.35</v>
       </c>
       <c r="AD8">
-        <v>35</v>
+        <v>35.53</v>
       </c>
       <c r="AE8">
-        <v>3.87</v>
+        <v>3.9</v>
       </c>
       <c r="AF8">
-        <v>-68.91</v>
+        <v>-54.11</v>
       </c>
       <c r="AG8">
-        <v>145.44</v>
+        <v>145.34</v>
       </c>
       <c r="AH8">
-        <v>131.73</v>
+        <v>131.59</v>
       </c>
       <c r="AI8">
         <v>131.91</v>
@@ -1713,7 +1704,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>28.98</v>
+        <v>25.43</v>
       </c>
     </row>
   </sheetData>
@@ -1854,7 +1845,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1894,7 +1885,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>55</v>
@@ -1912,1008 +1903,1022 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C4" s="4" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+      <c r="E6" s="3" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>67</v>
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>6.65</v>
+      </c>
+      <c r="D7" s="6">
+        <v>3.08</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-3.57</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>6.02</v>
+        <v>-15.86</v>
       </c>
       <c r="D8" s="6">
-        <v>6.65</v>
-      </c>
-      <c r="E8" s="7">
-        <v>0.63</v>
+        <v>-12.7</v>
+      </c>
+      <c r="E8" s="8">
+        <v>3.16</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-15.75</v>
+        <v>1.5</v>
       </c>
       <c r="D9" s="6">
-        <v>-15.86</v>
+        <v>4.14</v>
       </c>
       <c r="E9" s="8">
-        <v>-0.11</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>4.79</v>
+        <v>4.76</v>
       </c>
       <c r="D10" s="6">
-        <v>1.5</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-3.29</v>
+        <v>4.26</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-0.5</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>6.66</v>
+        <v>4.44</v>
       </c>
       <c r="D11" s="6">
-        <v>4.76</v>
+        <v>6.55</v>
       </c>
       <c r="E11" s="8">
-        <v>-1.9</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>4.13</v>
+        <v>3.73</v>
       </c>
       <c r="D12" s="6">
-        <v>4.44</v>
+        <v>3.49</v>
       </c>
       <c r="E12" s="7">
-        <v>0.31</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>6.34</v>
+        <v>-3.88</v>
       </c>
       <c r="D13" s="6">
-        <v>3.73</v>
+        <v>-1.49</v>
       </c>
       <c r="E13" s="8">
-        <v>-2.61</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C14" s="6">
-        <v>-1.97</v>
+        <v>2.76</v>
       </c>
       <c r="D14" s="6">
-        <v>-3.88</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-1.91</v>
+        <v>0.68</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-2.08</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>0.85</v>
+        <v>-5.99</v>
       </c>
       <c r="D15" s="6">
-        <v>2.76</v>
+        <v>-7.43</v>
       </c>
       <c r="E15" s="7">
-        <v>1.91</v>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-3.78</v>
+        <v>-5.96</v>
       </c>
       <c r="D16" s="6">
-        <v>-5.99</v>
+        <v>-3.66</v>
       </c>
       <c r="E16" s="8">
-        <v>-2.21</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-4.9</v>
+        <v>-0.36</v>
       </c>
       <c r="D17" s="6">
-        <v>-5.96</v>
+        <v>-0.1</v>
       </c>
       <c r="E17" s="8">
-        <v>-1.06</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-0.16</v>
+        <v>0.32</v>
       </c>
       <c r="D18" s="6">
-        <v>-0.36</v>
+        <v>1.41</v>
       </c>
       <c r="E18" s="8">
-        <v>-0.2</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-3.09</v>
+        <v>-0.63</v>
       </c>
       <c r="D19" s="6">
-        <v>0.32</v>
-      </c>
-      <c r="E19" s="7">
-        <v>3.41</v>
+        <v>0.44</v>
+      </c>
+      <c r="E19" s="8">
+        <v>1.07</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>-1.13</v>
+        <v>-0.43</v>
       </c>
       <c r="D20" s="6">
-        <v>-0.63</v>
-      </c>
-      <c r="E20" s="7">
-        <v>0.5</v>
+        <v>1.83</v>
+      </c>
+      <c r="E20" s="8">
+        <v>2.26</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C21" s="6">
-        <v>1.15</v>
+        <v>37.01</v>
       </c>
       <c r="D21" s="6">
-        <v>-0.43</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-1.58</v>
+        <v>36.9</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.11</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C22" s="6">
-        <v>36.05</v>
+        <v>97.08</v>
       </c>
       <c r="D22" s="6">
-        <v>37.01</v>
-      </c>
-      <c r="E22" s="7">
-        <v>0.96</v>
+        <v>102.34</v>
+      </c>
+      <c r="E22" s="8">
+        <v>5.26</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C23" s="6">
-        <v>102.33</v>
+        <v>-43.72</v>
       </c>
       <c r="D23" s="6">
-        <v>97.08</v>
+        <v>-42.68</v>
       </c>
       <c r="E23" s="8">
-        <v>-5.25</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C24" s="6">
-        <v>-42.15</v>
+        <v>2.32</v>
       </c>
       <c r="D24" s="6">
-        <v>-43.72</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-1.57</v>
+        <v>1.52</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-0.8</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>1.5</v>
+        <v>-16.83</v>
       </c>
       <c r="D25" s="6">
-        <v>2.32</v>
-      </c>
-      <c r="E25" s="7">
-        <v>0.82</v>
+        <v>-15.35</v>
+      </c>
+      <c r="E25" s="8">
+        <v>1.48</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>-18.93</v>
+        <v>22.48</v>
       </c>
       <c r="D26" s="6">
-        <v>-16.83</v>
+        <v>21.15</v>
       </c>
       <c r="E26" s="7">
-        <v>2.1</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>19.36</v>
+        <v>-1.29</v>
       </c>
       <c r="D27" s="6">
-        <v>22.48</v>
-      </c>
-      <c r="E27" s="7">
-        <v>3.12</v>
+        <v>-0.28</v>
+      </c>
+      <c r="E27" s="8">
+        <v>1.01</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C28" s="6">
-        <v>-1.6</v>
+        <v>11.9</v>
       </c>
       <c r="D28" s="6">
-        <v>-1.29</v>
+        <v>10</v>
       </c>
       <c r="E28" s="7">
-        <v>0.31</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C29" s="6">
-        <v>12.96</v>
+        <v>-18.85</v>
       </c>
       <c r="D29" s="6">
-        <v>11.9</v>
+        <v>-17.34</v>
       </c>
       <c r="E29" s="8">
-        <v>-1.06</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C30" s="6">
-        <v>-16.51</v>
+        <v>0.12</v>
       </c>
       <c r="D30" s="6">
-        <v>-18.85</v>
+        <v>1.99</v>
       </c>
       <c r="E30" s="8">
-        <v>-2.34</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C31" s="6">
-        <v>2.68</v>
+        <v>10.77</v>
       </c>
       <c r="D31" s="6">
-        <v>0.12</v>
+        <v>11.1</v>
       </c>
       <c r="E31" s="8">
-        <v>-2.56</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C32" s="6">
-        <v>11.16</v>
+        <v>6.95</v>
       </c>
       <c r="D32" s="6">
-        <v>10.77</v>
+        <v>9.32</v>
       </c>
       <c r="E32" s="8">
-        <v>-0.39</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C33" s="6">
-        <v>3.88</v>
+        <v>16.78</v>
       </c>
       <c r="D33" s="6">
-        <v>6.95</v>
+        <v>16.52</v>
       </c>
       <c r="E33" s="7">
-        <v>3.07</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>15.78</v>
+        <v>-3.42</v>
       </c>
       <c r="D34" s="6">
-        <v>16.78</v>
-      </c>
-      <c r="E34" s="7">
-        <v>1</v>
+        <v>-2.05</v>
+      </c>
+      <c r="E34" s="8">
+        <v>1.37</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C35" s="6">
-        <v>-1.01</v>
+        <v>0</v>
       </c>
       <c r="D35" s="6">
-        <v>-3.42</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-2.41</v>
+        <v>-1.7</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-1.7</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C36" s="6">
-        <v>-0.47</v>
+        <v>-32.11</v>
       </c>
       <c r="D36" s="6">
-        <v>0</v>
-      </c>
-      <c r="E36" s="7">
-        <v>0.47</v>
+        <v>-30.85</v>
+      </c>
+      <c r="E36" s="8">
+        <v>1.26</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C37" s="6">
-        <v>-30.89</v>
+        <v>-44.72</v>
       </c>
       <c r="D37" s="6">
-        <v>-32.11</v>
+        <v>-43.69</v>
       </c>
       <c r="E37" s="8">
-        <v>-1.22</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C38" s="6">
-        <v>-43.02</v>
+        <v>-7.93</v>
       </c>
       <c r="D38" s="6">
-        <v>-44.72</v>
+        <v>-7.65</v>
       </c>
       <c r="E38" s="8">
-        <v>-1.7</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C39" s="6">
-        <v>-8.039999999999999</v>
+        <v>-17.18</v>
       </c>
       <c r="D39" s="6">
-        <v>-7.93</v>
-      </c>
-      <c r="E39" s="7">
-        <v>0.11</v>
+        <v>-15.12</v>
+      </c>
+      <c r="E39" s="8">
+        <v>2.06</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C40" s="6">
-        <v>-18.43</v>
+        <v>-6.16</v>
       </c>
       <c r="D40" s="6">
-        <v>-17.18</v>
+        <v>-6.37</v>
       </c>
       <c r="E40" s="7">
-        <v>1.25</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C41" s="6">
-        <v>-7.06</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="D41" s="6">
-        <v>-6.16</v>
-      </c>
-      <c r="E41" s="7">
-        <v>0.9</v>
+        <v>-8</v>
+      </c>
+      <c r="E41" s="8">
+        <v>1.29</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C42" s="6">
-        <v>-8.91</v>
+        <v>11927</v>
       </c>
       <c r="D42" s="6">
-        <v>-9.289999999999999</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-0.38</v>
+        <v>11724</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-203</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C43" s="6">
-        <v>11800</v>
+        <v>455.05</v>
       </c>
       <c r="D43" s="6">
-        <v>11927</v>
-      </c>
-      <c r="E43" s="7">
-        <v>127</v>
+        <v>463.5</v>
+      </c>
+      <c r="E43" s="8">
+        <v>8.449999999999999</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C44" s="6">
-        <v>463.2</v>
+        <v>334.35</v>
       </c>
       <c r="D44" s="6">
-        <v>455.05</v>
+        <v>340.6</v>
       </c>
       <c r="E44" s="8">
-        <v>-8.15</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C45" s="6">
-        <v>344.65</v>
+        <v>2004</v>
       </c>
       <c r="D45" s="6">
-        <v>334.35</v>
+        <v>2010</v>
       </c>
       <c r="E45" s="8">
-        <v>-10.3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C46" s="6">
-        <v>2001.7</v>
+        <v>11290</v>
       </c>
       <c r="D46" s="6">
-        <v>2004</v>
-      </c>
-      <c r="E46" s="7">
-        <v>2.3</v>
+        <v>11540</v>
+      </c>
+      <c r="E46" s="8">
+        <v>250</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C47" s="6">
-        <v>11120</v>
+        <v>1087.4</v>
       </c>
       <c r="D47" s="6">
-        <v>11290</v>
+        <v>1085</v>
       </c>
       <c r="E47" s="7">
-        <v>170</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C48" s="6">
-        <v>1077</v>
+        <v>135.11</v>
       </c>
       <c r="D48" s="6">
-        <v>1087.4</v>
-      </c>
-      <c r="E48" s="7">
-        <v>10.4</v>
+        <v>137.03</v>
+      </c>
+      <c r="E48" s="8">
+        <v>1.92</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49" s="6">
+        <v>29</v>
+      </c>
+      <c r="D49" s="6">
         <v>43</v>
       </c>
-      <c r="B49" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="6">
-        <v>135.68</v>
-      </c>
-      <c r="D49" s="6">
-        <v>135.11</v>
-      </c>
       <c r="E49" s="8">
-        <v>-0.57</v>
+        <v>14</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C50" s="6">
-        <v>65.33</v>
+        <v>43</v>
       </c>
       <c r="D50" s="6">
-        <v>68.34999999999999</v>
+        <v>29</v>
       </c>
       <c r="E50" s="7">
-        <v>3.02</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C51" s="6">
-        <v>30.94</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="D51" s="6">
-        <v>29.42</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-1.52</v>
+        <v>59.45</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-8.9</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C52" s="6">
-        <v>47.25</v>
+        <v>29.42</v>
       </c>
       <c r="D52" s="6">
-        <v>41.04</v>
+        <v>33.1</v>
       </c>
       <c r="E52" s="8">
-        <v>-6.21</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C53" s="6">
-        <v>54.2</v>
+        <v>41.04</v>
       </c>
       <c r="D53" s="6">
-        <v>54.61</v>
-      </c>
-      <c r="E53" s="7">
-        <v>0.41</v>
+        <v>45.7</v>
+      </c>
+      <c r="E53" s="8">
+        <v>4.66</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C54" s="6">
-        <v>48.11</v>
+        <v>54.61</v>
       </c>
       <c r="D54" s="6">
-        <v>53.64</v>
-      </c>
-      <c r="E54" s="7">
-        <v>5.53</v>
+        <v>55.73</v>
+      </c>
+      <c r="E54" s="8">
+        <v>1.12</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C55" s="6">
-        <v>49.85</v>
+        <v>53.64</v>
       </c>
       <c r="D55" s="6">
-        <v>52.64</v>
-      </c>
-      <c r="E55" s="7">
-        <v>2.79</v>
+        <v>60.34</v>
+      </c>
+      <c r="E55" s="8">
+        <v>6.7</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C56" s="6">
-        <v>43.89</v>
+        <v>52.64</v>
       </c>
       <c r="D56" s="6">
-        <v>42.57</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-1.32</v>
+        <v>51.92</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-0.72</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C57" s="6">
-        <v>-16.28</v>
+        <v>42.57</v>
       </c>
       <c r="D57" s="6">
-        <v>-37.43</v>
+        <v>48.23</v>
       </c>
       <c r="E57" s="8">
-        <v>-21.15</v>
+        <v>5.66</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C58" s="6">
-        <v>56</v>
+        <v>-37.43</v>
       </c>
       <c r="D58" s="6">
-        <v>59.15</v>
-      </c>
-      <c r="E58" s="7">
-        <v>3.15</v>
+        <v>-33.06</v>
+      </c>
+      <c r="E58" s="8">
+        <v>4.37</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C59" s="6">
-        <v>-74.87</v>
+        <v>59.15</v>
       </c>
       <c r="D59" s="6">
-        <v>-57.75</v>
+        <v>-26.55</v>
       </c>
       <c r="E59" s="7">
-        <v>17.12</v>
+        <v>-85.7</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C60" s="6">
-        <v>-65.87</v>
+        <v>-57.75</v>
       </c>
       <c r="D60" s="6">
-        <v>-68.81</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-2.94</v>
+        <v>-73.59999999999999</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-15.85</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C61" s="6">
-        <v>60.45</v>
+        <v>-68.81</v>
       </c>
       <c r="D61" s="6">
-        <v>47.92</v>
+        <v>-56.7</v>
       </c>
       <c r="E61" s="8">
-        <v>-12.53</v>
+        <v>12.11</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C62" s="6">
-        <v>-50.5</v>
+        <v>47.92</v>
       </c>
       <c r="D62" s="6">
-        <v>-65.8</v>
-      </c>
-      <c r="E62" s="8">
-        <v>-15.3</v>
+        <v>-21.7</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-69.62</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C63" s="6">
-        <v>-61.61</v>
+        <v>-65.8</v>
       </c>
       <c r="D63" s="6">
+        <v>-58.88</v>
+      </c>
+      <c r="E63" s="8">
+        <v>6.92</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="6">
         <v>-68.91</v>
       </c>
-      <c r="E63" s="8">
-        <v>-7.3</v>
+      <c r="D64" s="6">
+        <v>-54.11</v>
+      </c>
+      <c r="E64" s="8">
+        <v>14.8</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2937,28 +2942,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>72</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2972,16 +2977,16 @@
         <v>7</v>
       </c>
       <c r="D2" s="11">
-        <v>48.9</v>
+        <v>50.6</v>
       </c>
       <c r="E2" s="11">
         <v>90</v>
       </c>
       <c r="F2" s="11">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="G2" s="11">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="H2" s="11">
         <v>57</v>
@@ -3112,25 +3117,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="14">
-        <v>0.2937</v>
+        <v>0.2891</v>
       </c>
       <c r="B2" s="14">
-        <v>0.2384</v>
+        <v>0.2453</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1471</v>
+        <v>0.1514</v>
       </c>
       <c r="D2" s="14">
-        <v>0.098</v>
+        <v>0.09789999999999999</v>
       </c>
       <c r="E2" s="14">
         <v>0.04769999999999999</v>
       </c>
       <c r="F2" s="14">
-        <v>-0.0005999999999999999</v>
+        <v>0.0014</v>
       </c>
       <c r="G2" s="14">
-        <v>-0.2105</v>
+        <v>-0.2078</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="64">
   <si>
     <t>Symbol</t>
   </si>
@@ -172,34 +172,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>29.4 → 33.1</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>29.4</t>
-  </si>
-  <si>
-    <t>33.1</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -401,18 +374,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -924,10 +896,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>11724</v>
+        <v>11720</v>
       </c>
       <c r="D2">
-        <v>-1.7</v>
+        <v>-0.03</v>
       </c>
       <c r="E2">
         <v>11927</v>
@@ -936,46 +908,46 @@
         <v>8506.780000000001</v>
       </c>
       <c r="G2">
-        <v>-1.7</v>
+        <v>-1.74</v>
       </c>
       <c r="H2">
-        <v>37.82</v>
+        <v>37.77</v>
       </c>
       <c r="I2">
-        <v>0.68</v>
+        <v>-0.62</v>
       </c>
       <c r="J2">
-        <v>3.08</v>
+        <v>3.37</v>
       </c>
       <c r="K2">
-        <v>10</v>
+        <v>12.05</v>
       </c>
       <c r="L2">
-        <v>36.9</v>
+        <v>36.93</v>
       </c>
       <c r="M2">
-        <v>28.91</v>
+        <v>28.85</v>
       </c>
       <c r="N2">
         <v>85</v>
       </c>
       <c r="O2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P2">
-        <v>11788.8</v>
+        <v>11774.2</v>
       </c>
       <c r="Q2">
-        <v>11692.08</v>
+        <v>11706.48</v>
       </c>
       <c r="R2">
-        <v>10863.3</v>
+        <v>10896.86</v>
       </c>
       <c r="S2">
-        <v>9805.42</v>
+        <v>9820.76</v>
       </c>
       <c r="T2">
-        <v>19.57</v>
+        <v>19.34</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -990,34 +962,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>59.45</v>
+        <v>59.28</v>
       </c>
       <c r="Z2">
-        <v>240.2</v>
+        <v>223.26</v>
       </c>
       <c r="AA2">
-        <v>280.56</v>
+        <v>269.1</v>
       </c>
       <c r="AB2">
-        <v>-40.36</v>
+        <v>-45.84</v>
       </c>
       <c r="AC2">
-        <v>43.64</v>
+        <v>33.33</v>
       </c>
       <c r="AD2">
-        <v>36.76</v>
+        <v>40.69</v>
       </c>
       <c r="AE2">
-        <v>198.52</v>
+        <v>198.91</v>
       </c>
       <c r="AF2">
-        <v>-33.06</v>
+        <v>-7.83</v>
       </c>
       <c r="AG2">
-        <v>11916.73</v>
+        <v>11894.95</v>
       </c>
       <c r="AH2">
-        <v>11467.42</v>
+        <v>11518</v>
       </c>
       <c r="AI2">
         <v>11229.97</v>
@@ -1026,7 +998,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>51.65</v>
+        <v>46.49</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1037,10 +1009,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>463.5</v>
+        <v>450.6</v>
       </c>
       <c r="D3">
-        <v>1.86</v>
+        <v>-2.78</v>
       </c>
       <c r="E3">
         <v>670.25</v>
@@ -1049,46 +1021,46 @@
         <v>222.01</v>
       </c>
       <c r="G3">
-        <v>-30.85</v>
+        <v>-32.77</v>
       </c>
       <c r="H3">
-        <v>108.77</v>
+        <v>102.96</v>
       </c>
       <c r="I3">
-        <v>-7.43</v>
+        <v>-7.46</v>
       </c>
       <c r="J3">
-        <v>-12.7</v>
+        <v>-16.01</v>
       </c>
       <c r="K3">
-        <v>-17.34</v>
+        <v>-18.49</v>
       </c>
       <c r="L3">
-        <v>102.34</v>
+        <v>98.93000000000001</v>
       </c>
       <c r="M3">
-        <v>15.14</v>
+        <v>14.61</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="P3">
-        <v>469.41</v>
+        <v>462.14</v>
       </c>
       <c r="Q3">
-        <v>509.92</v>
+        <v>505.54</v>
       </c>
       <c r="R3">
-        <v>556.6</v>
+        <v>553.55</v>
       </c>
       <c r="S3">
-        <v>423.22</v>
+        <v>423.99</v>
       </c>
       <c r="T3">
-        <v>9.52</v>
+        <v>6.28</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1103,43 +1075,43 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>33.1</v>
+        <v>30.49</v>
       </c>
       <c r="Z3">
-        <v>-24.78</v>
+        <v>-25.95</v>
       </c>
       <c r="AA3">
-        <v>-20.26</v>
+        <v>-21.4</v>
       </c>
       <c r="AB3">
-        <v>-4.52</v>
+        <v>-4.55</v>
       </c>
       <c r="AC3">
-        <v>6.65</v>
+        <v>8.57</v>
       </c>
       <c r="AD3">
-        <v>9.07</v>
+        <v>6.95</v>
       </c>
       <c r="AE3">
-        <v>21.78</v>
+        <v>21.56</v>
       </c>
       <c r="AF3">
-        <v>-26.55</v>
+        <v>36.73</v>
       </c>
       <c r="AG3">
-        <v>571.54</v>
+        <v>571.05</v>
       </c>
       <c r="AH3">
-        <v>448.29</v>
+        <v>440.04</v>
       </c>
       <c r="AI3">
-        <v>527.59</v>
+        <v>521.85</v>
       </c>
       <c r="AJ3" t="s">
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>40.15</v>
+        <v>43.33</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1150,10 +1122,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>340.6</v>
+        <v>334.8</v>
       </c>
       <c r="D4">
-        <v>1.87</v>
+        <v>-1.7</v>
       </c>
       <c r="E4">
         <v>604.85</v>
@@ -1162,46 +1134,46 @@
         <v>303.75</v>
       </c>
       <c r="G4">
-        <v>-43.69</v>
+        <v>-44.65</v>
       </c>
       <c r="H4">
-        <v>12.13</v>
+        <v>10.22</v>
       </c>
       <c r="I4">
-        <v>-3.66</v>
+        <v>-5.52</v>
       </c>
       <c r="J4">
-        <v>4.14</v>
+        <v>1.29</v>
       </c>
       <c r="K4">
-        <v>1.99</v>
+        <v>6.47</v>
       </c>
       <c r="L4">
-        <v>-42.68</v>
+        <v>-42.69</v>
       </c>
       <c r="M4">
-        <v>-20.78</v>
+        <v>-21.11</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
       <c r="O4">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P4">
-        <v>345.12</v>
+        <v>341.21</v>
       </c>
       <c r="Q4">
-        <v>352.74</v>
+        <v>353.01</v>
       </c>
       <c r="R4">
-        <v>337.83</v>
+        <v>337.97</v>
       </c>
       <c r="S4">
-        <v>388.38</v>
+        <v>387.55</v>
       </c>
       <c r="T4">
-        <v>-12.3</v>
+        <v>-13.61</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1216,43 +1188,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>45.7</v>
+        <v>42.36</v>
       </c>
       <c r="Z4">
-        <v>1.82</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AA4">
-        <v>5.11</v>
+        <v>4.2</v>
       </c>
       <c r="AB4">
-        <v>-3.29</v>
+        <v>-3.64</v>
       </c>
       <c r="AC4">
-        <v>5.61</v>
+        <v>7.62</v>
       </c>
       <c r="AD4">
-        <v>2.1</v>
+        <v>4.41</v>
       </c>
       <c r="AE4">
-        <v>12.67</v>
+        <v>12.4</v>
       </c>
       <c r="AF4">
-        <v>-73.59999999999999</v>
+        <v>-89.22</v>
       </c>
       <c r="AG4">
-        <v>379.82</v>
+        <v>379.18</v>
       </c>
       <c r="AH4">
-        <v>325.65</v>
+        <v>326.85</v>
       </c>
       <c r="AI4">
-        <v>377.03</v>
+        <v>375.36</v>
       </c>
       <c r="AJ4" t="s">
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>37.21</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1263,10 +1235,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="D5">
-        <v>0.3</v>
+        <v>0.05</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1275,46 +1247,46 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-7.65</v>
+        <v>-7.61</v>
       </c>
       <c r="H5">
-        <v>23.18</v>
+        <v>23.24</v>
       </c>
       <c r="I5">
-        <v>-0.1</v>
+        <v>-0.25</v>
       </c>
       <c r="J5">
-        <v>4.26</v>
+        <v>4.5</v>
       </c>
       <c r="K5">
-        <v>11.1</v>
+        <v>12.75</v>
       </c>
       <c r="L5">
-        <v>1.52</v>
+        <v>2.29</v>
       </c>
       <c r="M5">
-        <v>4.77</v>
+        <v>4.47</v>
       </c>
       <c r="N5">
         <v>57</v>
       </c>
       <c r="O5">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="P5">
-        <v>2012.84</v>
+        <v>2011.84</v>
       </c>
       <c r="Q5">
-        <v>2026</v>
+        <v>2031.08</v>
       </c>
       <c r="R5">
-        <v>1918.35</v>
+        <v>1923.28</v>
       </c>
       <c r="S5">
-        <v>1907.62</v>
+        <v>1907.09</v>
       </c>
       <c r="T5">
-        <v>5.37</v>
+        <v>5.45</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1329,34 +1301,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>55.73</v>
+        <v>55.93</v>
       </c>
       <c r="Z5">
-        <v>24.99</v>
+        <v>23.1</v>
       </c>
       <c r="AA5">
-        <v>34.58</v>
+        <v>32.28</v>
       </c>
       <c r="AB5">
-        <v>-9.59</v>
+        <v>-9.18</v>
       </c>
       <c r="AC5">
-        <v>7.41</v>
+        <v>14.94</v>
       </c>
       <c r="AD5">
-        <v>8.42</v>
+        <v>10.08</v>
       </c>
       <c r="AE5">
-        <v>35.91</v>
+        <v>35.42</v>
       </c>
       <c r="AF5">
-        <v>-56.7</v>
+        <v>-58.3</v>
       </c>
       <c r="AG5">
-        <v>2111.8</v>
+        <v>2097.7</v>
       </c>
       <c r="AH5">
-        <v>1940.19</v>
+        <v>1964.45</v>
       </c>
       <c r="AI5">
         <v>1958.53</v>
@@ -1365,7 +1337,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>14.73</v>
+        <v>14.18</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1376,10 +1348,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>11540</v>
+        <v>11399</v>
       </c>
       <c r="D6">
-        <v>2.21</v>
+        <v>-1.22</v>
       </c>
       <c r="E6">
         <v>13595.75</v>
@@ -1388,25 +1360,25 @@
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-15.12</v>
+        <v>-16.16</v>
       </c>
       <c r="H6">
-        <v>31.95</v>
+        <v>30.33</v>
       </c>
       <c r="I6">
-        <v>1.41</v>
+        <v>0.27</v>
       </c>
       <c r="J6">
-        <v>6.55</v>
+        <v>4.11</v>
       </c>
       <c r="K6">
-        <v>9.32</v>
+        <v>10.02</v>
       </c>
       <c r="L6">
-        <v>-15.35</v>
+        <v>-15.43</v>
       </c>
       <c r="M6">
-        <v>24.53</v>
+        <v>23.91</v>
       </c>
       <c r="N6">
         <v>43</v>
@@ -1415,19 +1387,19 @@
         <v>50</v>
       </c>
       <c r="P6">
-        <v>11327.6</v>
+        <v>11333.8</v>
       </c>
       <c r="Q6">
-        <v>11392.75</v>
+        <v>11414.2</v>
       </c>
       <c r="R6">
-        <v>10941.18</v>
+        <v>10959.16</v>
       </c>
       <c r="S6">
-        <v>10733.64</v>
+        <v>10727.56</v>
       </c>
       <c r="T6">
-        <v>7.51</v>
+        <v>6.26</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1442,34 +1414,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>60.34</v>
+        <v>55.47</v>
       </c>
       <c r="Z6">
-        <v>131.31</v>
+        <v>125.54</v>
       </c>
       <c r="AA6">
-        <v>166.69</v>
+        <v>158.46</v>
       </c>
       <c r="AB6">
-        <v>-35.38</v>
+        <v>-32.92</v>
       </c>
       <c r="AC6">
-        <v>31.33</v>
+        <v>44.32</v>
       </c>
       <c r="AD6">
-        <v>17.33</v>
+        <v>29.38</v>
       </c>
       <c r="AE6">
-        <v>240.91</v>
+        <v>238.63</v>
       </c>
       <c r="AF6">
-        <v>-21.7</v>
+        <v>29.5</v>
       </c>
       <c r="AG6">
-        <v>11710.82</v>
+        <v>11662.42</v>
       </c>
       <c r="AH6">
-        <v>11074.68</v>
+        <v>11165.98</v>
       </c>
       <c r="AI6">
         <v>10787.84</v>
@@ -1478,7 +1450,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>30.94</v>
+        <v>28.71</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1489,10 +1461,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="D7">
-        <v>-0.22</v>
+        <v>-0.18</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1501,46 +1473,46 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-6.37</v>
+        <v>-6.54</v>
       </c>
       <c r="H7">
-        <v>35.36</v>
+        <v>35.11</v>
       </c>
       <c r="I7">
-        <v>0.44</v>
+        <v>-1.1</v>
       </c>
       <c r="J7">
-        <v>3.49</v>
+        <v>2.71</v>
       </c>
       <c r="K7">
-        <v>16.52</v>
+        <v>19.24</v>
       </c>
       <c r="L7">
-        <v>21.15</v>
+        <v>21.07</v>
       </c>
       <c r="M7">
-        <v>9.789999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="N7">
         <v>71</v>
       </c>
       <c r="O7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P7">
-        <v>1087.88</v>
+        <v>1085.48</v>
       </c>
       <c r="Q7">
-        <v>1102.45</v>
+        <v>1103.93</v>
       </c>
       <c r="R7">
-        <v>1050.59</v>
+        <v>1053.08</v>
       </c>
       <c r="S7">
-        <v>975.47</v>
+        <v>975.46</v>
       </c>
       <c r="T7">
-        <v>11.23</v>
+        <v>11.02</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1555,34 +1527,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>51.92</v>
+        <v>51.29</v>
       </c>
       <c r="Z7">
-        <v>9.44</v>
+        <v>8.24</v>
       </c>
       <c r="AA7">
-        <v>15.37</v>
+        <v>13.94</v>
       </c>
       <c r="AB7">
-        <v>-5.93</v>
+        <v>-5.71</v>
       </c>
       <c r="AC7">
-        <v>13.95</v>
+        <v>20.49</v>
       </c>
       <c r="AD7">
-        <v>11.27</v>
+        <v>14.7</v>
       </c>
       <c r="AE7">
-        <v>22.77</v>
+        <v>22.86</v>
       </c>
       <c r="AF7">
-        <v>-58.88</v>
+        <v>-33.04</v>
       </c>
       <c r="AG7">
-        <v>1161.81</v>
+        <v>1159.51</v>
       </c>
       <c r="AH7">
-        <v>1043.09</v>
+        <v>1048.34</v>
       </c>
       <c r="AI7">
         <v>1067.72</v>
@@ -1591,7 +1563,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>23.65</v>
+        <v>20.88</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1602,10 +1574,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>137.03</v>
+        <v>136.26</v>
       </c>
       <c r="D8">
-        <v>1.42</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E8">
         <v>148.95</v>
@@ -1614,46 +1586,46 @@
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>-8</v>
+        <v>-8.52</v>
       </c>
       <c r="H8">
-        <v>18.17</v>
+        <v>17.51</v>
       </c>
       <c r="I8">
-        <v>1.83</v>
+        <v>-0.51</v>
       </c>
       <c r="J8">
-        <v>-1.49</v>
+        <v>-2.27</v>
       </c>
       <c r="K8">
-        <v>-2.05</v>
+        <v>-3.51</v>
       </c>
       <c r="L8">
-        <v>-0.28</v>
+        <v>-0.42</v>
       </c>
       <c r="M8">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="N8">
         <v>29</v>
       </c>
       <c r="O8">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="P8">
-        <v>136.4</v>
+        <v>136.26</v>
       </c>
       <c r="Q8">
-        <v>138.47</v>
+        <v>138.28</v>
       </c>
       <c r="R8">
-        <v>137.42</v>
+        <v>137.46</v>
       </c>
       <c r="S8">
-        <v>133.62</v>
+        <v>133.61</v>
       </c>
       <c r="T8">
-        <v>2.56</v>
+        <v>1.98</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1668,34 +1640,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>48.23</v>
+        <v>46.26</v>
       </c>
       <c r="Z8">
-        <v>-0.89</v>
+        <v>-0.86</v>
       </c>
       <c r="AA8">
-        <v>-0.6</v>
+        <v>-0.65</v>
       </c>
       <c r="AB8">
-        <v>-0.29</v>
+        <v>-0.21</v>
       </c>
       <c r="AC8">
-        <v>34.35</v>
+        <v>43.54</v>
       </c>
       <c r="AD8">
-        <v>35.53</v>
+        <v>37.02</v>
       </c>
       <c r="AE8">
-        <v>3.9</v>
+        <v>3.83</v>
       </c>
       <c r="AF8">
-        <v>-54.11</v>
+        <v>-63</v>
       </c>
       <c r="AG8">
-        <v>145.34</v>
+        <v>145.19</v>
       </c>
       <c r="AH8">
-        <v>131.59</v>
+        <v>131.37</v>
       </c>
       <c r="AI8">
         <v>131.91</v>
@@ -1704,7 +1676,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>25.43</v>
+        <v>22.55</v>
       </c>
     </row>
   </sheetData>
@@ -1845,7 +1817,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1865,47 +1837,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1913,1006 +1850,972 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>64</v>
+      <c r="B6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>6.65</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>3.08</v>
       </c>
-      <c r="E7" s="7">
-        <v>-3.57</v>
+      <c r="D7" s="5">
+        <v>3.37</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.29</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-15.86</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>-12.7</v>
       </c>
-      <c r="E8" s="8">
-        <v>3.16</v>
+      <c r="D8" s="5">
+        <v>-16.01</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-3.31</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>1.5</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>4.14</v>
       </c>
-      <c r="E9" s="8">
-        <v>2.64</v>
+      <c r="D9" s="5">
+        <v>1.29</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-2.85</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>4.76</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>4.26</v>
       </c>
-      <c r="E10" s="7">
-        <v>-0.5</v>
+      <c r="D10" s="5">
+        <v>4.5</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0.24</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>4.44</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>6.55</v>
       </c>
-      <c r="E11" s="8">
-        <v>2.11</v>
+      <c r="D11" s="5">
+        <v>4.11</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-2.44</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="6">
-        <v>3.73</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>3.49</v>
       </c>
+      <c r="D12" s="5">
+        <v>2.71</v>
+      </c>
       <c r="E12" s="7">
-        <v>-0.24</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="6">
-        <v>-3.88</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>-1.49</v>
       </c>
-      <c r="E13" s="8">
-        <v>2.39</v>
+      <c r="D13" s="5">
+        <v>-2.27</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-0.78</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="6">
-        <v>2.76</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" s="5">
         <v>0.68</v>
       </c>
+      <c r="D14" s="5">
+        <v>-0.62</v>
+      </c>
       <c r="E14" s="7">
-        <v>-2.08</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="6">
-        <v>-5.99</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C15" s="5">
         <v>-7.43</v>
       </c>
+      <c r="D15" s="5">
+        <v>-7.46</v>
+      </c>
       <c r="E15" s="7">
-        <v>-1.44</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="6">
-        <v>-5.96</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C16" s="5">
         <v>-3.66</v>
       </c>
-      <c r="E16" s="8">
-        <v>2.3</v>
+      <c r="D16" s="5">
+        <v>-5.52</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-1.86</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="6">
-        <v>-0.36</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C17" s="5">
         <v>-0.1</v>
       </c>
-      <c r="E17" s="8">
-        <v>0.26</v>
+      <c r="D17" s="5">
+        <v>-0.25</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-0.15</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="6">
-        <v>0.32</v>
-      </c>
-      <c r="D18" s="6">
+      <c r="C18" s="5">
         <v>1.41</v>
       </c>
-      <c r="E18" s="8">
-        <v>1.09</v>
+      <c r="D18" s="5">
+        <v>0.27</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-1.14</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="5">
+        <v>0.44</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-1.1</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-1.54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5">
+        <v>1.83</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-0.51</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-2.34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>36.9</v>
+      </c>
+      <c r="D21" s="5">
+        <v>36.93</v>
+      </c>
+      <c r="E21" s="6">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="5">
+        <v>102.34</v>
+      </c>
+      <c r="D22" s="5">
+        <v>98.93000000000001</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-3.41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5">
+        <v>-42.68</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-42.69</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5">
+        <v>1.52</v>
+      </c>
+      <c r="D24" s="5">
+        <v>2.29</v>
+      </c>
+      <c r="E24" s="6">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-15.35</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-15.43</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-0.08</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>21.15</v>
+      </c>
+      <c r="D26" s="5">
+        <v>21.07</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-0.08</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-0.28</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-0.42</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="5">
+        <v>10</v>
+      </c>
+      <c r="D28" s="5">
+        <v>12.05</v>
+      </c>
+      <c r="E28" s="6">
+        <v>2.05</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-17.34</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-18.49</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-1.15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="5">
+        <v>1.99</v>
+      </c>
+      <c r="D30" s="5">
+        <v>6.47</v>
+      </c>
+      <c r="E30" s="6">
+        <v>4.48</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="5">
+        <v>11.1</v>
+      </c>
+      <c r="D31" s="5">
+        <v>12.75</v>
+      </c>
+      <c r="E31" s="6">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="5">
+        <v>9.32</v>
+      </c>
+      <c r="D32" s="5">
+        <v>10.02</v>
+      </c>
+      <c r="E32" s="6">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="5">
+        <v>16.52</v>
+      </c>
+      <c r="D33" s="5">
+        <v>19.24</v>
+      </c>
+      <c r="E33" s="6">
+        <v>2.72</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>-2.05</v>
+      </c>
+      <c r="D34" s="5">
+        <v>-3.51</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-1.46</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-1.7</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-1.74</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-30.85</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-32.77</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-1.92</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="5">
+        <v>-43.69</v>
+      </c>
+      <c r="D37" s="5">
+        <v>-44.65</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-0.96</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="5">
+        <v>-7.65</v>
+      </c>
+      <c r="D38" s="5">
+        <v>-7.61</v>
+      </c>
+      <c r="E38" s="6">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="5">
+        <v>-15.12</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-16.16</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-1.04</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="5">
+        <v>-6.37</v>
+      </c>
+      <c r="D40" s="5">
+        <v>-6.54</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="5">
+        <v>-8</v>
+      </c>
+      <c r="D41" s="5">
+        <v>-8.52</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-0.52</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="5">
+        <v>11724</v>
+      </c>
+      <c r="D42" s="5">
+        <v>11720</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="5">
+        <v>463.5</v>
+      </c>
+      <c r="D43" s="5">
+        <v>450.6</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-12.9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="5">
+        <v>340.6</v>
+      </c>
+      <c r="D44" s="5">
+        <v>334.8</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-5.8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="5">
+        <v>2010</v>
+      </c>
+      <c r="D45" s="5">
+        <v>2011</v>
+      </c>
+      <c r="E45" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="5">
+        <v>11540</v>
+      </c>
+      <c r="D46" s="5">
+        <v>11399</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-141</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="5">
+        <v>1085</v>
+      </c>
+      <c r="D47" s="5">
+        <v>1083</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="5">
+        <v>137.03</v>
+      </c>
+      <c r="D48" s="5">
+        <v>136.26</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-0.77</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="5">
+        <v>59.45</v>
+      </c>
+      <c r="D49" s="5">
+        <v>59.28</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="5">
+        <v>33.1</v>
+      </c>
+      <c r="D50" s="5">
+        <v>30.49</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-2.61</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="5">
+        <v>45.7</v>
+      </c>
+      <c r="D51" s="5">
+        <v>42.36</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-3.34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="5">
+        <v>55.73</v>
+      </c>
+      <c r="D52" s="5">
+        <v>55.93</v>
+      </c>
+      <c r="E52" s="6">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="5">
+        <v>60.34</v>
+      </c>
+      <c r="D53" s="5">
+        <v>55.47</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-4.87</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="5">
+        <v>51.92</v>
+      </c>
+      <c r="D54" s="5">
+        <v>51.29</v>
+      </c>
+      <c r="E54" s="7">
         <v>-0.63</v>
       </c>
-      <c r="D19" s="6">
-        <v>0.44</v>
-      </c>
-      <c r="E19" s="8">
-        <v>1.07</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-0.43</v>
-      </c>
-      <c r="D20" s="6">
-        <v>1.83</v>
-      </c>
-      <c r="E20" s="8">
-        <v>2.26</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="5">
+        <v>48.23</v>
+      </c>
+      <c r="D55" s="5">
+        <v>46.26</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-1.97</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>37.01</v>
-      </c>
-      <c r="D21" s="6">
-        <v>36.9</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B56" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" s="5">
+        <v>-33.06</v>
+      </c>
+      <c r="D56" s="5">
+        <v>-7.83</v>
+      </c>
+      <c r="E56" s="6">
+        <v>25.23</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="6">
-        <v>97.08</v>
-      </c>
-      <c r="D22" s="6">
-        <v>102.34</v>
-      </c>
-      <c r="E22" s="8">
-        <v>5.26</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B57" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C57" s="5">
+        <v>-26.55</v>
+      </c>
+      <c r="D57" s="5">
+        <v>36.73</v>
+      </c>
+      <c r="E57" s="6">
+        <v>63.28</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-43.72</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-42.68</v>
-      </c>
-      <c r="E23" s="8">
-        <v>1.04</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B58" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="5">
+        <v>-73.59999999999999</v>
+      </c>
+      <c r="D58" s="5">
+        <v>-89.22</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-15.62</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6">
-        <v>2.32</v>
-      </c>
-      <c r="D24" s="6">
-        <v>1.52</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-0.8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="5">
+        <v>-56.7</v>
+      </c>
+      <c r="D59" s="5">
+        <v>-58.3</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-1.6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-16.83</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-15.35</v>
-      </c>
-      <c r="E25" s="8">
-        <v>1.48</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B60" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="5">
+        <v>-21.7</v>
+      </c>
+      <c r="D60" s="5">
+        <v>29.5</v>
+      </c>
+      <c r="E60" s="6">
+        <v>51.2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>22.48</v>
-      </c>
-      <c r="D26" s="6">
-        <v>21.15</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-1.33</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B61" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="5">
+        <v>-58.88</v>
+      </c>
+      <c r="D61" s="5">
+        <v>-33.04</v>
+      </c>
+      <c r="E61" s="6">
+        <v>25.84</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-1.29</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-0.28</v>
-      </c>
-      <c r="E27" s="8">
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="6">
-        <v>11.9</v>
-      </c>
-      <c r="D28" s="6">
-        <v>10</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-1.9</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-18.85</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-17.34</v>
-      </c>
-      <c r="E29" s="8">
-        <v>1.51</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="6">
-        <v>0.12</v>
-      </c>
-      <c r="D30" s="6">
-        <v>1.99</v>
-      </c>
-      <c r="E30" s="8">
-        <v>1.87</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="6">
-        <v>10.77</v>
-      </c>
-      <c r="D31" s="6">
-        <v>11.1</v>
-      </c>
-      <c r="E31" s="8">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="6">
-        <v>6.95</v>
-      </c>
-      <c r="D32" s="6">
-        <v>9.32</v>
-      </c>
-      <c r="E32" s="8">
-        <v>2.37</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="6">
-        <v>16.78</v>
-      </c>
-      <c r="D33" s="6">
-        <v>16.52</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-0.26</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-3.42</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-2.05</v>
-      </c>
-      <c r="E34" s="8">
-        <v>1.37</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="6">
-        <v>0</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-1.7</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-1.7</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-32.11</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-30.85</v>
-      </c>
-      <c r="E36" s="8">
-        <v>1.26</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-44.72</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-43.69</v>
-      </c>
-      <c r="E37" s="8">
-        <v>1.03</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-7.93</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-7.65</v>
-      </c>
-      <c r="E38" s="8">
-        <v>0.28</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-17.18</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-15.12</v>
-      </c>
-      <c r="E39" s="8">
-        <v>2.06</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-6.16</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-6.37</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-0.21</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-9.289999999999999</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-8</v>
-      </c>
-      <c r="E41" s="8">
-        <v>1.29</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="6">
-        <v>11927</v>
-      </c>
-      <c r="D42" s="6">
-        <v>11724</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-203</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="6">
-        <v>455.05</v>
-      </c>
-      <c r="D43" s="6">
-        <v>463.5</v>
-      </c>
-      <c r="E43" s="8">
-        <v>8.449999999999999</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="6">
-        <v>334.35</v>
-      </c>
-      <c r="D44" s="6">
-        <v>340.6</v>
-      </c>
-      <c r="E44" s="8">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="6">
-        <v>2004</v>
-      </c>
-      <c r="D45" s="6">
-        <v>2010</v>
-      </c>
-      <c r="E45" s="8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="6">
-        <v>11290</v>
-      </c>
-      <c r="D46" s="6">
-        <v>11540</v>
-      </c>
-      <c r="E46" s="8">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="6">
-        <v>1087.4</v>
-      </c>
-      <c r="D47" s="6">
-        <v>1085</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-2.4</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="6">
-        <v>135.11</v>
-      </c>
-      <c r="D48" s="6">
-        <v>137.03</v>
-      </c>
-      <c r="E48" s="8">
-        <v>1.92</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C49" s="6">
-        <v>29</v>
-      </c>
-      <c r="D49" s="6">
-        <v>43</v>
-      </c>
-      <c r="E49" s="8">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C50" s="6">
-        <v>43</v>
-      </c>
-      <c r="D50" s="6">
-        <v>29</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="6">
-        <v>68.34999999999999</v>
-      </c>
-      <c r="D51" s="6">
-        <v>59.45</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-8.9</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="6">
-        <v>29.42</v>
-      </c>
-      <c r="D52" s="6">
-        <v>33.1</v>
-      </c>
-      <c r="E52" s="8">
-        <v>3.68</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="6">
-        <v>41.04</v>
-      </c>
-      <c r="D53" s="6">
-        <v>45.7</v>
-      </c>
-      <c r="E53" s="8">
-        <v>4.66</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="6">
-        <v>54.61</v>
-      </c>
-      <c r="D54" s="6">
-        <v>55.73</v>
-      </c>
-      <c r="E54" s="8">
-        <v>1.12</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="6">
-        <v>53.64</v>
-      </c>
-      <c r="D55" s="6">
-        <v>60.34</v>
-      </c>
-      <c r="E55" s="8">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="6">
-        <v>52.64</v>
-      </c>
-      <c r="D56" s="6">
-        <v>51.92</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-0.72</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="6">
-        <v>42.57</v>
-      </c>
-      <c r="D57" s="6">
-        <v>48.23</v>
-      </c>
-      <c r="E57" s="8">
-        <v>5.66</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B58" s="5" t="s">
+      <c r="B62" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C58" s="6">
-        <v>-37.43</v>
-      </c>
-      <c r="D58" s="6">
-        <v>-33.06</v>
-      </c>
-      <c r="E58" s="8">
-        <v>4.37</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C59" s="6">
-        <v>59.15</v>
-      </c>
-      <c r="D59" s="6">
-        <v>-26.55</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-85.7</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="6">
-        <v>-57.75</v>
-      </c>
-      <c r="D60" s="6">
-        <v>-73.59999999999999</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-15.85</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="6">
-        <v>-68.81</v>
-      </c>
-      <c r="D61" s="6">
-        <v>-56.7</v>
-      </c>
-      <c r="E61" s="8">
-        <v>12.11</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="6">
-        <v>47.92</v>
-      </c>
-      <c r="D62" s="6">
-        <v>-21.7</v>
+      <c r="C62" s="5">
+        <v>-54.11</v>
+      </c>
+      <c r="D62" s="5">
+        <v>-63</v>
       </c>
       <c r="E62" s="7">
-        <v>-69.62</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="6">
-        <v>-65.8</v>
-      </c>
-      <c r="D63" s="6">
-        <v>-58.88</v>
-      </c>
-      <c r="E63" s="8">
-        <v>6.92</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="6">
-        <v>-68.91</v>
-      </c>
-      <c r="D64" s="6">
-        <v>-54.11</v>
-      </c>
-      <c r="E64" s="8">
-        <v>14.8</v>
+        <v>-8.890000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2938,60 +2841,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>72</v>
+      <c r="B1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>68.8</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>7</v>
       </c>
-      <c r="D2" s="11">
-        <v>50.6</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>48.7</v>
+      </c>
+      <c r="E2" s="10">
         <v>90</v>
       </c>
-      <c r="F2" s="11">
-        <v>1</v>
-      </c>
-      <c r="G2" s="11">
-        <v>4.2</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-0.3</v>
+      </c>
+      <c r="G2" s="10">
+        <v>5.5</v>
+      </c>
+      <c r="H2" s="10">
         <v>57</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>70</v>
       </c>
     </row>
@@ -3093,49 +2996,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="14">
-        <v>0.2891</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.2453</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.1514</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.09789999999999999</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.04769999999999999</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.0014</v>
-      </c>
-      <c r="G2" s="14">
-        <v>-0.2078</v>
+      <c r="A2" s="13">
+        <v>0.2885</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.2391</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.1461</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.0964</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.0447</v>
+      </c>
+      <c r="F2" s="13">
+        <v>0.001</v>
+      </c>
+      <c r="G2" s="13">
+        <v>-0.2111</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="64">
   <si>
     <t>Symbol</t>
   </si>
@@ -896,10 +896,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>11720</v>
+        <v>11910</v>
       </c>
       <c r="D2">
-        <v>-0.03</v>
+        <v>1.62</v>
       </c>
       <c r="E2">
         <v>11927</v>
@@ -908,46 +908,46 @@
         <v>8506.780000000001</v>
       </c>
       <c r="G2">
-        <v>-1.74</v>
+        <v>-0.14</v>
       </c>
       <c r="H2">
-        <v>37.77</v>
+        <v>40.01</v>
       </c>
       <c r="I2">
-        <v>-0.62</v>
+        <v>1.79</v>
       </c>
       <c r="J2">
-        <v>3.37</v>
+        <v>4.18</v>
       </c>
       <c r="K2">
-        <v>12.05</v>
+        <v>14.78</v>
       </c>
       <c r="L2">
-        <v>36.93</v>
+        <v>38.02</v>
       </c>
       <c r="M2">
-        <v>28.85</v>
+        <v>29.16</v>
       </c>
       <c r="N2">
         <v>85</v>
       </c>
       <c r="O2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P2">
-        <v>11774.2</v>
+        <v>11816.2</v>
       </c>
       <c r="Q2">
-        <v>11706.48</v>
+        <v>11725.95</v>
       </c>
       <c r="R2">
-        <v>10896.86</v>
+        <v>10933.52</v>
       </c>
       <c r="S2">
-        <v>9820.76</v>
+        <v>9836.459999999999</v>
       </c>
       <c r="T2">
-        <v>19.34</v>
+        <v>21.08</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -962,43 +962,43 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>59.28</v>
+        <v>64.31999999999999</v>
       </c>
       <c r="Z2">
-        <v>223.26</v>
+        <v>222.61</v>
       </c>
       <c r="AA2">
-        <v>269.1</v>
+        <v>259.8</v>
       </c>
       <c r="AB2">
-        <v>-45.84</v>
+        <v>-37.19</v>
       </c>
       <c r="AC2">
-        <v>33.33</v>
+        <v>18.5</v>
       </c>
       <c r="AD2">
-        <v>40.69</v>
+        <v>31.82</v>
       </c>
       <c r="AE2">
-        <v>198.91</v>
+        <v>202.85</v>
       </c>
       <c r="AF2">
-        <v>-7.83</v>
+        <v>14.69</v>
       </c>
       <c r="AG2">
-        <v>11894.95</v>
+        <v>11914</v>
       </c>
       <c r="AH2">
-        <v>11518</v>
+        <v>11537.9</v>
       </c>
       <c r="AI2">
-        <v>11229.97</v>
+        <v>11262.96</v>
       </c>
       <c r="AJ2" t="s">
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>46.49</v>
+        <v>45.48</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1009,10 +1009,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>450.6</v>
+        <v>477.45</v>
       </c>
       <c r="D3">
-        <v>-2.78</v>
+        <v>5.96</v>
       </c>
       <c r="E3">
         <v>670.25</v>
@@ -1021,46 +1021,46 @@
         <v>222.01</v>
       </c>
       <c r="G3">
-        <v>-32.77</v>
+        <v>-28.77</v>
       </c>
       <c r="H3">
-        <v>102.96</v>
+        <v>115.06</v>
       </c>
       <c r="I3">
-        <v>-7.46</v>
+        <v>-0.19</v>
       </c>
       <c r="J3">
-        <v>-16.01</v>
+        <v>-11.27</v>
       </c>
       <c r="K3">
-        <v>-18.49</v>
+        <v>-14.6</v>
       </c>
       <c r="L3">
-        <v>98.93000000000001</v>
+        <v>108.88</v>
       </c>
       <c r="M3">
-        <v>14.61</v>
+        <v>15.76</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="P3">
-        <v>462.14</v>
+        <v>461.96</v>
       </c>
       <c r="Q3">
-        <v>505.54</v>
+        <v>503.21</v>
       </c>
       <c r="R3">
-        <v>553.55</v>
+        <v>550.6900000000001</v>
       </c>
       <c r="S3">
-        <v>423.99</v>
+        <v>424.97</v>
       </c>
       <c r="T3">
-        <v>6.28</v>
+        <v>12.35</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1075,34 +1075,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>30.49</v>
+        <v>40.95</v>
       </c>
       <c r="Z3">
-        <v>-25.95</v>
+        <v>-24.43</v>
       </c>
       <c r="AA3">
-        <v>-21.4</v>
+        <v>-22</v>
       </c>
       <c r="AB3">
-        <v>-4.55</v>
+        <v>-2.42</v>
       </c>
       <c r="AC3">
-        <v>8.57</v>
+        <v>31.7</v>
       </c>
       <c r="AD3">
-        <v>6.95</v>
+        <v>15.64</v>
       </c>
       <c r="AE3">
-        <v>21.56</v>
+        <v>22.19</v>
       </c>
       <c r="AF3">
-        <v>36.73</v>
+        <v>117.37</v>
       </c>
       <c r="AG3">
-        <v>571.05</v>
+        <v>569.25</v>
       </c>
       <c r="AH3">
-        <v>440.04</v>
+        <v>437.17</v>
       </c>
       <c r="AI3">
         <v>521.85</v>
@@ -1111,7 +1111,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>43.33</v>
+        <v>41.55</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1122,10 +1122,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>334.8</v>
+        <v>332.75</v>
       </c>
       <c r="D4">
-        <v>-1.7</v>
+        <v>-0.61</v>
       </c>
       <c r="E4">
         <v>604.85</v>
@@ -1134,46 +1134,46 @@
         <v>303.75</v>
       </c>
       <c r="G4">
-        <v>-44.65</v>
+        <v>-44.99</v>
       </c>
       <c r="H4">
-        <v>10.22</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="I4">
-        <v>-5.52</v>
+        <v>-5.37</v>
       </c>
       <c r="J4">
-        <v>1.29</v>
+        <v>1.06</v>
       </c>
       <c r="K4">
-        <v>6.47</v>
+        <v>5.53</v>
       </c>
       <c r="L4">
-        <v>-42.69</v>
+        <v>-43.58</v>
       </c>
       <c r="M4">
-        <v>-21.11</v>
+        <v>-21.65</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
       <c r="O4">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="P4">
-        <v>341.21</v>
+        <v>337.43</v>
       </c>
       <c r="Q4">
         <v>353.01</v>
       </c>
       <c r="R4">
-        <v>337.97</v>
+        <v>338.04</v>
       </c>
       <c r="S4">
-        <v>387.55</v>
+        <v>386.69</v>
       </c>
       <c r="T4">
-        <v>-13.61</v>
+        <v>-13.95</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1188,43 +1188,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>42.36</v>
+        <v>41.21</v>
       </c>
       <c r="Z4">
-        <v>0.5600000000000001</v>
+        <v>-0.6</v>
       </c>
       <c r="AA4">
-        <v>4.2</v>
+        <v>3.24</v>
       </c>
       <c r="AB4">
-        <v>-3.64</v>
+        <v>-3.84</v>
       </c>
       <c r="AC4">
-        <v>7.62</v>
+        <v>7.88</v>
       </c>
       <c r="AD4">
-        <v>4.41</v>
+        <v>7.04</v>
       </c>
       <c r="AE4">
-        <v>12.4</v>
+        <v>12.11</v>
       </c>
       <c r="AF4">
-        <v>-89.22</v>
+        <v>-85.98999999999999</v>
       </c>
       <c r="AG4">
-        <v>379.18</v>
+        <v>379.2</v>
       </c>
       <c r="AH4">
-        <v>326.85</v>
+        <v>326.81</v>
       </c>
       <c r="AI4">
-        <v>375.36</v>
+        <v>370.1</v>
       </c>
       <c r="AJ4" t="s">
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>35.6</v>
+        <v>35.42</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1235,10 +1235,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>2011</v>
+        <v>2002</v>
       </c>
       <c r="D5">
-        <v>0.05</v>
+        <v>-0.45</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1247,46 +1247,46 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-7.61</v>
+        <v>-8.02</v>
       </c>
       <c r="H5">
-        <v>23.24</v>
+        <v>22.69</v>
       </c>
       <c r="I5">
-        <v>-0.25</v>
+        <v>-1.5</v>
       </c>
       <c r="J5">
-        <v>4.5</v>
+        <v>4.85</v>
       </c>
       <c r="K5">
-        <v>12.75</v>
+        <v>13.82</v>
       </c>
       <c r="L5">
-        <v>2.29</v>
+        <v>1.95</v>
       </c>
       <c r="M5">
-        <v>4.47</v>
+        <v>3.91</v>
       </c>
       <c r="N5">
         <v>57</v>
       </c>
       <c r="O5">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P5">
-        <v>2011.84</v>
+        <v>2005.74</v>
       </c>
       <c r="Q5">
-        <v>2031.08</v>
+        <v>2029.72</v>
       </c>
       <c r="R5">
-        <v>1923.28</v>
+        <v>1927.89</v>
       </c>
       <c r="S5">
-        <v>1907.09</v>
+        <v>1907.15</v>
       </c>
       <c r="T5">
-        <v>5.45</v>
+        <v>4.97</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1301,34 +1301,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>55.93</v>
+        <v>53.63</v>
       </c>
       <c r="Z5">
-        <v>23.1</v>
+        <v>20.64</v>
       </c>
       <c r="AA5">
-        <v>32.28</v>
+        <v>29.95</v>
       </c>
       <c r="AB5">
-        <v>-9.18</v>
+        <v>-9.32</v>
       </c>
       <c r="AC5">
-        <v>14.94</v>
+        <v>14.21</v>
       </c>
       <c r="AD5">
-        <v>10.08</v>
+        <v>12.19</v>
       </c>
       <c r="AE5">
-        <v>35.42</v>
+        <v>35.21</v>
       </c>
       <c r="AF5">
-        <v>-58.3</v>
+        <v>-62.26</v>
       </c>
       <c r="AG5">
-        <v>2097.7</v>
+        <v>2097.6</v>
       </c>
       <c r="AH5">
-        <v>1964.45</v>
+        <v>1961.84</v>
       </c>
       <c r="AI5">
         <v>1958.53</v>
@@ -1337,7 +1337,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>14.18</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1348,10 +1348,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>11399</v>
+        <v>11340</v>
       </c>
       <c r="D6">
-        <v>-1.22</v>
+        <v>-0.52</v>
       </c>
       <c r="E6">
         <v>13595.75</v>
@@ -1360,46 +1360,46 @@
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-16.16</v>
+        <v>-16.59</v>
       </c>
       <c r="H6">
-        <v>30.33</v>
+        <v>29.66</v>
       </c>
       <c r="I6">
-        <v>0.27</v>
+        <v>0.18</v>
       </c>
       <c r="J6">
-        <v>4.11</v>
+        <v>3.37</v>
       </c>
       <c r="K6">
-        <v>10.02</v>
+        <v>10.42</v>
       </c>
       <c r="L6">
-        <v>-15.43</v>
+        <v>-14.09</v>
       </c>
       <c r="M6">
-        <v>23.91</v>
+        <v>23.55</v>
       </c>
       <c r="N6">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="O6">
         <v>50</v>
       </c>
       <c r="P6">
-        <v>11333.8</v>
+        <v>11337.8</v>
       </c>
       <c r="Q6">
-        <v>11414.2</v>
+        <v>11414.05</v>
       </c>
       <c r="R6">
-        <v>10959.16</v>
+        <v>10972.44</v>
       </c>
       <c r="S6">
-        <v>10727.56</v>
+        <v>10723.48</v>
       </c>
       <c r="T6">
-        <v>6.26</v>
+        <v>5.75</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1414,34 +1414,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>55.47</v>
+        <v>53.53</v>
       </c>
       <c r="Z6">
-        <v>125.54</v>
+        <v>114.89</v>
       </c>
       <c r="AA6">
-        <v>158.46</v>
+        <v>149.75</v>
       </c>
       <c r="AB6">
-        <v>-32.92</v>
+        <v>-34.86</v>
       </c>
       <c r="AC6">
-        <v>44.32</v>
+        <v>44.11</v>
       </c>
       <c r="AD6">
-        <v>29.38</v>
+        <v>39.92</v>
       </c>
       <c r="AE6">
-        <v>238.63</v>
+        <v>234.37</v>
       </c>
       <c r="AF6">
-        <v>29.5</v>
+        <v>-27.6</v>
       </c>
       <c r="AG6">
-        <v>11662.42</v>
+        <v>11662.46</v>
       </c>
       <c r="AH6">
-        <v>11165.98</v>
+        <v>11165.64</v>
       </c>
       <c r="AI6">
         <v>10787.84</v>
@@ -1450,7 +1450,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>28.71</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1461,10 +1461,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>1083</v>
+        <v>1079.9</v>
       </c>
       <c r="D7">
-        <v>-0.18</v>
+        <v>-0.29</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1473,46 +1473,46 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-6.54</v>
+        <v>-6.81</v>
       </c>
       <c r="H7">
-        <v>35.11</v>
+        <v>34.73</v>
       </c>
       <c r="I7">
-        <v>-1.1</v>
+        <v>-1.38</v>
       </c>
       <c r="J7">
-        <v>2.71</v>
+        <v>2.51</v>
       </c>
       <c r="K7">
-        <v>19.24</v>
+        <v>21.47</v>
       </c>
       <c r="L7">
-        <v>21.07</v>
+        <v>19.88</v>
       </c>
       <c r="M7">
-        <v>9.640000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="N7">
         <v>71</v>
       </c>
       <c r="O7">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P7">
-        <v>1085.48</v>
+        <v>1082.46</v>
       </c>
       <c r="Q7">
-        <v>1103.93</v>
+        <v>1100.86</v>
       </c>
       <c r="R7">
-        <v>1053.08</v>
+        <v>1055.5</v>
       </c>
       <c r="S7">
-        <v>975.46</v>
+        <v>975.83</v>
       </c>
       <c r="T7">
-        <v>11.02</v>
+        <v>10.66</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1527,34 +1527,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>51.29</v>
+        <v>50.28</v>
       </c>
       <c r="Z7">
-        <v>8.24</v>
+        <v>6.95</v>
       </c>
       <c r="AA7">
-        <v>13.94</v>
+        <v>12.55</v>
       </c>
       <c r="AB7">
-        <v>-5.71</v>
+        <v>-5.59</v>
       </c>
       <c r="AC7">
-        <v>20.49</v>
+        <v>18.48</v>
       </c>
       <c r="AD7">
-        <v>14.7</v>
+        <v>17.64</v>
       </c>
       <c r="AE7">
-        <v>22.86</v>
+        <v>22.46</v>
       </c>
       <c r="AF7">
-        <v>-33.04</v>
+        <v>-41.14</v>
       </c>
       <c r="AG7">
-        <v>1159.51</v>
+        <v>1154.52</v>
       </c>
       <c r="AH7">
-        <v>1048.34</v>
+        <v>1047.2</v>
       </c>
       <c r="AI7">
         <v>1067.72</v>
@@ -1563,7 +1563,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>20.88</v>
+        <v>21.23</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1574,10 +1574,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>136.26</v>
+        <v>137.27</v>
       </c>
       <c r="D8">
-        <v>-0.5600000000000001</v>
+        <v>0.74</v>
       </c>
       <c r="E8">
         <v>148.95</v>
@@ -1586,46 +1586,46 @@
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>-8.52</v>
+        <v>-7.84</v>
       </c>
       <c r="H8">
-        <v>17.51</v>
+        <v>18.38</v>
       </c>
       <c r="I8">
-        <v>-0.51</v>
+        <v>0.04</v>
       </c>
       <c r="J8">
-        <v>-2.27</v>
+        <v>-1.89</v>
       </c>
       <c r="K8">
-        <v>-3.51</v>
+        <v>-1.08</v>
       </c>
       <c r="L8">
-        <v>-0.42</v>
+        <v>2.92</v>
       </c>
       <c r="M8">
-        <v>0.1</v>
+        <v>0.17</v>
       </c>
       <c r="N8">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="O8">
         <v>52</v>
       </c>
       <c r="P8">
-        <v>136.26</v>
+        <v>136.27</v>
       </c>
       <c r="Q8">
-        <v>138.28</v>
+        <v>138.08</v>
       </c>
       <c r="R8">
-        <v>137.46</v>
+        <v>137.47</v>
       </c>
       <c r="S8">
-        <v>133.61</v>
+        <v>133.62</v>
       </c>
       <c r="T8">
-        <v>1.98</v>
+        <v>2.73</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1640,34 +1640,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>46.26</v>
+        <v>49.19</v>
       </c>
       <c r="Z8">
-        <v>-0.86</v>
+        <v>-0.75</v>
       </c>
       <c r="AA8">
-        <v>-0.65</v>
+        <v>-0.67</v>
       </c>
       <c r="AB8">
-        <v>-0.21</v>
+        <v>-0.08</v>
       </c>
       <c r="AC8">
-        <v>43.54</v>
+        <v>63.89</v>
       </c>
       <c r="AD8">
-        <v>37.02</v>
+        <v>47.26</v>
       </c>
       <c r="AE8">
-        <v>3.83</v>
+        <v>3.73</v>
       </c>
       <c r="AF8">
-        <v>-63</v>
+        <v>-74.95</v>
       </c>
       <c r="AG8">
-        <v>145.19</v>
+        <v>144.84</v>
       </c>
       <c r="AH8">
-        <v>131.37</v>
+        <v>131.31</v>
       </c>
       <c r="AI8">
         <v>131.91</v>
@@ -1676,7 +1676,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>22.55</v>
+        <v>20.09</v>
       </c>
     </row>
   </sheetData>
@@ -1817,7 +1817,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1874,13 +1874,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>3.08</v>
+        <v>3.37</v>
       </c>
       <c r="D7" s="5">
-        <v>3.37</v>
+        <v>4.18</v>
       </c>
       <c r="E7" s="6">
-        <v>0.29</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1891,13 +1891,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-12.7</v>
+        <v>-16.01</v>
       </c>
       <c r="D8" s="5">
-        <v>-16.01</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-3.31</v>
+        <v>-11.27</v>
+      </c>
+      <c r="E8" s="6">
+        <v>4.74</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1908,13 +1908,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>4.14</v>
+        <v>1.29</v>
       </c>
       <c r="D9" s="5">
-        <v>1.29</v>
+        <v>1.06</v>
       </c>
       <c r="E9" s="7">
-        <v>-2.85</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1925,13 +1925,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>4.26</v>
+        <v>4.5</v>
       </c>
       <c r="D10" s="5">
-        <v>4.5</v>
+        <v>4.85</v>
       </c>
       <c r="E10" s="6">
-        <v>0.24</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1942,13 +1942,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>6.55</v>
+        <v>4.11</v>
       </c>
       <c r="D11" s="5">
-        <v>4.11</v>
+        <v>3.37</v>
       </c>
       <c r="E11" s="7">
-        <v>-2.44</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1959,13 +1959,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="5">
-        <v>3.49</v>
+        <v>2.71</v>
       </c>
       <c r="D12" s="5">
-        <v>2.71</v>
+        <v>2.51</v>
       </c>
       <c r="E12" s="7">
-        <v>-0.78</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1976,13 +1976,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="5">
-        <v>-1.49</v>
+        <v>-2.27</v>
       </c>
       <c r="D13" s="5">
-        <v>-2.27</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-0.78</v>
+        <v>-1.89</v>
+      </c>
+      <c r="E13" s="6">
+        <v>0.38</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1993,13 +1993,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="5">
-        <v>0.68</v>
+        <v>-0.62</v>
       </c>
       <c r="D14" s="5">
-        <v>-0.62</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-1.3</v>
+        <v>1.79</v>
+      </c>
+      <c r="E14" s="6">
+        <v>2.41</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2010,13 +2010,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="5">
-        <v>-7.43</v>
+        <v>-7.46</v>
       </c>
       <c r="D15" s="5">
-        <v>-7.46</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-0.03</v>
+        <v>-0.19</v>
+      </c>
+      <c r="E15" s="6">
+        <v>7.27</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2027,13 +2027,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>-3.66</v>
+        <v>-5.52</v>
       </c>
       <c r="D16" s="5">
-        <v>-5.52</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-1.86</v>
+        <v>-5.37</v>
+      </c>
+      <c r="E16" s="6">
+        <v>0.15</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2044,13 +2044,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="5">
-        <v>-0.1</v>
+        <v>-0.25</v>
       </c>
       <c r="D17" s="5">
-        <v>-0.25</v>
+        <v>-1.5</v>
       </c>
       <c r="E17" s="7">
-        <v>-0.15</v>
+        <v>-1.25</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2061,13 +2061,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="5">
-        <v>1.41</v>
+        <v>0.27</v>
       </c>
       <c r="D18" s="5">
-        <v>0.27</v>
+        <v>0.18</v>
       </c>
       <c r="E18" s="7">
-        <v>-1.14</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2078,13 +2078,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="5">
-        <v>0.44</v>
+        <v>-1.1</v>
       </c>
       <c r="D19" s="5">
-        <v>-1.1</v>
+        <v>-1.38</v>
       </c>
       <c r="E19" s="7">
-        <v>-1.54</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2095,13 +2095,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="5">
-        <v>1.83</v>
+        <v>-0.51</v>
       </c>
       <c r="D20" s="5">
-        <v>-0.51</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-2.34</v>
+        <v>0.04</v>
+      </c>
+      <c r="E20" s="6">
+        <v>0.55</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2112,13 +2112,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="5">
-        <v>36.9</v>
+        <v>36.93</v>
       </c>
       <c r="D21" s="5">
-        <v>36.93</v>
+        <v>38.02</v>
       </c>
       <c r="E21" s="6">
-        <v>0.03</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2129,13 +2129,13 @@
         <v>11</v>
       </c>
       <c r="C22" s="5">
-        <v>102.34</v>
+        <v>98.93000000000001</v>
       </c>
       <c r="D22" s="5">
-        <v>98.93000000000001</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-3.41</v>
+        <v>108.88</v>
+      </c>
+      <c r="E22" s="6">
+        <v>9.949999999999999</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2146,13 +2146,13 @@
         <v>11</v>
       </c>
       <c r="C23" s="5">
-        <v>-42.68</v>
+        <v>-42.69</v>
       </c>
       <c r="D23" s="5">
-        <v>-42.69</v>
+        <v>-43.58</v>
       </c>
       <c r="E23" s="7">
-        <v>-0.01</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2163,13 +2163,13 @@
         <v>11</v>
       </c>
       <c r="C24" s="5">
-        <v>1.52</v>
+        <v>2.29</v>
       </c>
       <c r="D24" s="5">
-        <v>2.29</v>
-      </c>
-      <c r="E24" s="6">
-        <v>0.77</v>
+        <v>1.95</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-0.34</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2180,13 +2180,13 @@
         <v>11</v>
       </c>
       <c r="C25" s="5">
-        <v>-15.35</v>
+        <v>-15.43</v>
       </c>
       <c r="D25" s="5">
-        <v>-15.43</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-0.08</v>
+        <v>-14.09</v>
+      </c>
+      <c r="E25" s="6">
+        <v>1.34</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2197,13 +2197,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="5">
-        <v>21.15</v>
+        <v>21.07</v>
       </c>
       <c r="D26" s="5">
-        <v>21.07</v>
+        <v>19.88</v>
       </c>
       <c r="E26" s="7">
-        <v>-0.08</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2214,13 +2214,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="5">
-        <v>-0.28</v>
+        <v>-0.42</v>
       </c>
       <c r="D27" s="5">
-        <v>-0.42</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-0.14</v>
+        <v>2.92</v>
+      </c>
+      <c r="E27" s="6">
+        <v>3.34</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2231,13 +2231,13 @@
         <v>10</v>
       </c>
       <c r="C28" s="5">
-        <v>10</v>
+        <v>12.05</v>
       </c>
       <c r="D28" s="5">
-        <v>12.05</v>
+        <v>14.78</v>
       </c>
       <c r="E28" s="6">
-        <v>2.05</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2248,13 +2248,13 @@
         <v>10</v>
       </c>
       <c r="C29" s="5">
-        <v>-17.34</v>
+        <v>-18.49</v>
       </c>
       <c r="D29" s="5">
-        <v>-18.49</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-1.15</v>
+        <v>-14.6</v>
+      </c>
+      <c r="E29" s="6">
+        <v>3.89</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2265,13 +2265,13 @@
         <v>10</v>
       </c>
       <c r="C30" s="5">
-        <v>1.99</v>
+        <v>6.47</v>
       </c>
       <c r="D30" s="5">
-        <v>6.47</v>
-      </c>
-      <c r="E30" s="6">
-        <v>4.48</v>
+        <v>5.53</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2282,13 +2282,13 @@
         <v>10</v>
       </c>
       <c r="C31" s="5">
-        <v>11.1</v>
+        <v>12.75</v>
       </c>
       <c r="D31" s="5">
-        <v>12.75</v>
+        <v>13.82</v>
       </c>
       <c r="E31" s="6">
-        <v>1.65</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2299,13 +2299,13 @@
         <v>10</v>
       </c>
       <c r="C32" s="5">
-        <v>9.32</v>
+        <v>10.02</v>
       </c>
       <c r="D32" s="5">
-        <v>10.02</v>
+        <v>10.42</v>
       </c>
       <c r="E32" s="6">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2316,13 +2316,13 @@
         <v>10</v>
       </c>
       <c r="C33" s="5">
-        <v>16.52</v>
+        <v>19.24</v>
       </c>
       <c r="D33" s="5">
-        <v>19.24</v>
+        <v>21.47</v>
       </c>
       <c r="E33" s="6">
-        <v>2.72</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2333,13 +2333,13 @@
         <v>10</v>
       </c>
       <c r="C34" s="5">
-        <v>-2.05</v>
+        <v>-3.51</v>
       </c>
       <c r="D34" s="5">
-        <v>-3.51</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-1.46</v>
+        <v>-1.08</v>
+      </c>
+      <c r="E34" s="6">
+        <v>2.43</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2350,13 +2350,13 @@
         <v>6</v>
       </c>
       <c r="C35" s="5">
-        <v>-1.7</v>
+        <v>-1.74</v>
       </c>
       <c r="D35" s="5">
-        <v>-1.74</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-0.04</v>
+        <v>-0.14</v>
+      </c>
+      <c r="E35" s="6">
+        <v>1.6</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2367,13 +2367,13 @@
         <v>6</v>
       </c>
       <c r="C36" s="5">
-        <v>-30.85</v>
+        <v>-32.77</v>
       </c>
       <c r="D36" s="5">
-        <v>-32.77</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-1.92</v>
+        <v>-28.77</v>
+      </c>
+      <c r="E36" s="6">
+        <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2384,13 +2384,13 @@
         <v>6</v>
       </c>
       <c r="C37" s="5">
-        <v>-43.69</v>
+        <v>-44.65</v>
       </c>
       <c r="D37" s="5">
-        <v>-44.65</v>
+        <v>-44.99</v>
       </c>
       <c r="E37" s="7">
-        <v>-0.96</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2401,13 +2401,13 @@
         <v>6</v>
       </c>
       <c r="C38" s="5">
-        <v>-7.65</v>
+        <v>-7.61</v>
       </c>
       <c r="D38" s="5">
-        <v>-7.61</v>
-      </c>
-      <c r="E38" s="6">
-        <v>0.04</v>
+        <v>-8.02</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-0.41</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2418,13 +2418,13 @@
         <v>6</v>
       </c>
       <c r="C39" s="5">
-        <v>-15.12</v>
+        <v>-16.16</v>
       </c>
       <c r="D39" s="5">
-        <v>-16.16</v>
+        <v>-16.59</v>
       </c>
       <c r="E39" s="7">
-        <v>-1.04</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2435,13 +2435,13 @@
         <v>6</v>
       </c>
       <c r="C40" s="5">
-        <v>-6.37</v>
+        <v>-6.54</v>
       </c>
       <c r="D40" s="5">
-        <v>-6.54</v>
+        <v>-6.81</v>
       </c>
       <c r="E40" s="7">
-        <v>-0.17</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2452,13 +2452,13 @@
         <v>6</v>
       </c>
       <c r="C41" s="5">
-        <v>-8</v>
+        <v>-8.52</v>
       </c>
       <c r="D41" s="5">
-        <v>-8.52</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-0.52</v>
+        <v>-7.84</v>
+      </c>
+      <c r="E41" s="6">
+        <v>0.68</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2469,13 +2469,13 @@
         <v>2</v>
       </c>
       <c r="C42" s="5">
-        <v>11724</v>
+        <v>11720</v>
       </c>
       <c r="D42" s="5">
-        <v>11720</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-4</v>
+        <v>11910</v>
+      </c>
+      <c r="E42" s="6">
+        <v>190</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2486,13 +2486,13 @@
         <v>2</v>
       </c>
       <c r="C43" s="5">
-        <v>463.5</v>
+        <v>450.6</v>
       </c>
       <c r="D43" s="5">
-        <v>450.6</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-12.9</v>
+        <v>477.45</v>
+      </c>
+      <c r="E43" s="6">
+        <v>26.85</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2503,13 +2503,13 @@
         <v>2</v>
       </c>
       <c r="C44" s="5">
-        <v>340.6</v>
+        <v>334.8</v>
       </c>
       <c r="D44" s="5">
-        <v>334.8</v>
+        <v>332.75</v>
       </c>
       <c r="E44" s="7">
-        <v>-5.8</v>
+        <v>-2.05</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2520,13 +2520,13 @@
         <v>2</v>
       </c>
       <c r="C45" s="5">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="D45" s="5">
-        <v>2011</v>
-      </c>
-      <c r="E45" s="6">
-        <v>1</v>
+        <v>2002</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-9</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2537,13 +2537,13 @@
         <v>2</v>
       </c>
       <c r="C46" s="5">
-        <v>11540</v>
+        <v>11399</v>
       </c>
       <c r="D46" s="5">
-        <v>11399</v>
+        <v>11340</v>
       </c>
       <c r="E46" s="7">
-        <v>-141</v>
+        <v>-59</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2554,13 +2554,13 @@
         <v>2</v>
       </c>
       <c r="C47" s="5">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="D47" s="5">
-        <v>1083</v>
+        <v>1079.9</v>
       </c>
       <c r="E47" s="7">
-        <v>-2</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2571,251 +2571,285 @@
         <v>2</v>
       </c>
       <c r="C48" s="5">
-        <v>137.03</v>
+        <v>136.26</v>
       </c>
       <c r="D48" s="5">
-        <v>136.26</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-0.77</v>
+        <v>137.27</v>
+      </c>
+      <c r="E48" s="6">
+        <v>1.01</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C49" s="5">
-        <v>59.45</v>
+        <v>43</v>
       </c>
       <c r="D49" s="5">
-        <v>59.28</v>
+        <v>29</v>
       </c>
       <c r="E49" s="7">
-        <v>-0.17</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C50" s="5">
-        <v>33.1</v>
+        <v>29</v>
       </c>
       <c r="D50" s="5">
-        <v>30.49</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-2.61</v>
+        <v>43</v>
+      </c>
+      <c r="E50" s="6">
+        <v>14</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C51" s="5">
-        <v>45.7</v>
+        <v>59.28</v>
       </c>
       <c r="D51" s="5">
-        <v>42.36</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-3.34</v>
+        <v>64.31999999999999</v>
+      </c>
+      <c r="E51" s="6">
+        <v>5.04</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C52" s="5">
-        <v>55.73</v>
+        <v>30.49</v>
       </c>
       <c r="D52" s="5">
-        <v>55.93</v>
+        <v>40.95</v>
       </c>
       <c r="E52" s="6">
-        <v>0.2</v>
+        <v>10.46</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C53" s="5">
-        <v>60.34</v>
+        <v>42.36</v>
       </c>
       <c r="D53" s="5">
-        <v>55.47</v>
+        <v>41.21</v>
       </c>
       <c r="E53" s="7">
-        <v>-4.87</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C54" s="5">
-        <v>51.92</v>
+        <v>55.93</v>
       </c>
       <c r="D54" s="5">
-        <v>51.29</v>
+        <v>53.63</v>
       </c>
       <c r="E54" s="7">
-        <v>-0.63</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C55" s="5">
-        <v>48.23</v>
+        <v>55.47</v>
       </c>
       <c r="D55" s="5">
-        <v>46.26</v>
+        <v>53.53</v>
       </c>
       <c r="E55" s="7">
-        <v>-1.97</v>
+        <v>-1.94</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C56" s="5">
-        <v>-33.06</v>
+        <v>51.29</v>
       </c>
       <c r="D56" s="5">
-        <v>-7.83</v>
-      </c>
-      <c r="E56" s="6">
-        <v>25.23</v>
+        <v>50.28</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-1.01</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C57" s="5">
-        <v>-26.55</v>
+        <v>46.26</v>
       </c>
       <c r="D57" s="5">
-        <v>36.73</v>
+        <v>49.19</v>
       </c>
       <c r="E57" s="6">
-        <v>63.28</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C58" s="5">
-        <v>-73.59999999999999</v>
+        <v>-7.83</v>
       </c>
       <c r="D58" s="5">
-        <v>-89.22</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-15.62</v>
+        <v>14.69</v>
+      </c>
+      <c r="E58" s="6">
+        <v>22.52</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C59" s="5">
-        <v>-56.7</v>
+        <v>36.73</v>
       </c>
       <c r="D59" s="5">
-        <v>-58.3</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-1.6</v>
+        <v>117.37</v>
+      </c>
+      <c r="E59" s="6">
+        <v>80.64</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C60" s="5">
-        <v>-21.7</v>
+        <v>-89.22</v>
       </c>
       <c r="D60" s="5">
-        <v>29.5</v>
+        <v>-85.98999999999999</v>
       </c>
       <c r="E60" s="6">
-        <v>51.2</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C61" s="5">
-        <v>-58.88</v>
+        <v>-58.3</v>
       </c>
       <c r="D61" s="5">
-        <v>-33.04</v>
-      </c>
-      <c r="E61" s="6">
-        <v>25.84</v>
+        <v>-62.26</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-3.96</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C62" s="5">
-        <v>-54.11</v>
+        <v>29.5</v>
       </c>
       <c r="D62" s="5">
+        <v>-27.6</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-57.1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="5">
+        <v>-33.04</v>
+      </c>
+      <c r="D63" s="5">
+        <v>-41.14</v>
+      </c>
+      <c r="E63" s="7">
+        <v>-8.1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="5">
         <v>-63</v>
       </c>
-      <c r="E62" s="7">
-        <v>-8.890000000000001</v>
+      <c r="D64" s="5">
+        <v>-74.95</v>
+      </c>
+      <c r="E64" s="7">
+        <v>-11.95</v>
       </c>
     </row>
   </sheetData>
@@ -2880,16 +2914,16 @@
         <v>7</v>
       </c>
       <c r="D2" s="10">
-        <v>48.7</v>
+        <v>50.4</v>
       </c>
       <c r="E2" s="10">
         <v>90</v>
       </c>
       <c r="F2" s="10">
-        <v>-0.3</v>
+        <v>0.4</v>
       </c>
       <c r="G2" s="10">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="H2" s="10">
         <v>57</v>
@@ -3020,25 +3054,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="13">
-        <v>0.2885</v>
+        <v>0.2916</v>
       </c>
       <c r="B2" s="13">
-        <v>0.2391</v>
+        <v>0.2355</v>
       </c>
       <c r="C2" s="13">
-        <v>0.1461</v>
+        <v>0.1576</v>
       </c>
       <c r="D2" s="13">
-        <v>0.0964</v>
+        <v>0.0897</v>
       </c>
       <c r="E2" s="13">
-        <v>0.0447</v>
+        <v>0.0391</v>
       </c>
       <c r="F2" s="13">
-        <v>0.001</v>
+        <v>0.0017</v>
       </c>
       <c r="G2" s="13">
-        <v>-0.2111</v>
+        <v>-0.2165</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="73">
   <si>
     <t>Symbol</t>
   </si>
@@ -172,7 +172,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>50.3 → 43.4</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>50.3</t>
+  </si>
+  <si>
+    <t>43.4</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -258,14 +285,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -298,13 +325,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,17 +401,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -896,58 +924,58 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>11910</v>
+        <v>12130</v>
       </c>
       <c r="D2">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="E2">
-        <v>11927</v>
+        <v>12130</v>
       </c>
       <c r="F2">
         <v>8506.780000000001</v>
       </c>
       <c r="G2">
-        <v>-0.14</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>40.01</v>
+        <v>42.59</v>
       </c>
       <c r="I2">
-        <v>1.79</v>
+        <v>2.8</v>
       </c>
       <c r="J2">
-        <v>4.18</v>
+        <v>5.29</v>
       </c>
       <c r="K2">
-        <v>14.78</v>
+        <v>17.98</v>
       </c>
       <c r="L2">
-        <v>38.02</v>
+        <v>41.53</v>
       </c>
       <c r="M2">
-        <v>29.16</v>
+        <v>29.54</v>
       </c>
       <c r="N2">
         <v>85</v>
       </c>
       <c r="O2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P2">
-        <v>11816.2</v>
+        <v>11882.2</v>
       </c>
       <c r="Q2">
-        <v>11725.95</v>
+        <v>11739.65</v>
       </c>
       <c r="R2">
-        <v>10933.52</v>
+        <v>10974.8</v>
       </c>
       <c r="S2">
-        <v>9836.459999999999</v>
+        <v>9853.379999999999</v>
       </c>
       <c r="T2">
-        <v>21.08</v>
+        <v>23.1</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -962,43 +990,43 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>64.31999999999999</v>
+        <v>69.08</v>
       </c>
       <c r="Z2">
-        <v>222.61</v>
+        <v>237.11</v>
       </c>
       <c r="AA2">
-        <v>259.8</v>
+        <v>255.26</v>
       </c>
       <c r="AB2">
-        <v>-37.19</v>
+        <v>-18.15</v>
       </c>
       <c r="AC2">
-        <v>18.5</v>
+        <v>51.83</v>
       </c>
       <c r="AD2">
-        <v>31.82</v>
+        <v>34.55</v>
       </c>
       <c r="AE2">
-        <v>202.85</v>
+        <v>206.43</v>
       </c>
       <c r="AF2">
-        <v>14.69</v>
+        <v>56.3</v>
       </c>
       <c r="AG2">
-        <v>11914</v>
+        <v>11995.35</v>
       </c>
       <c r="AH2">
-        <v>11537.9</v>
+        <v>11483.95</v>
       </c>
       <c r="AI2">
-        <v>11262.96</v>
+        <v>11384.21</v>
       </c>
       <c r="AJ2" t="s">
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>45.48</v>
+        <v>46.72</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1009,10 +1037,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>477.45</v>
+        <v>474.05</v>
       </c>
       <c r="D3">
-        <v>5.96</v>
+        <v>-0.71</v>
       </c>
       <c r="E3">
         <v>670.25</v>
@@ -1021,46 +1049,46 @@
         <v>222.01</v>
       </c>
       <c r="G3">
-        <v>-28.77</v>
+        <v>-29.27</v>
       </c>
       <c r="H3">
-        <v>115.06</v>
+        <v>113.53</v>
       </c>
       <c r="I3">
-        <v>-0.19</v>
+        <v>2.34</v>
       </c>
       <c r="J3">
-        <v>-11.27</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="K3">
-        <v>-14.6</v>
+        <v>-17.07</v>
       </c>
       <c r="L3">
-        <v>108.88</v>
+        <v>106.55</v>
       </c>
       <c r="M3">
-        <v>15.76</v>
+        <v>15.98</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P3">
-        <v>461.96</v>
+        <v>464.13</v>
       </c>
       <c r="Q3">
-        <v>503.21</v>
+        <v>500.72</v>
       </c>
       <c r="R3">
-        <v>550.6900000000001</v>
+        <v>547.67</v>
       </c>
       <c r="S3">
-        <v>424.97</v>
+        <v>425.96</v>
       </c>
       <c r="T3">
-        <v>12.35</v>
+        <v>11.29</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1075,34 +1103,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>40.95</v>
+        <v>40.12</v>
       </c>
       <c r="Z3">
-        <v>-24.43</v>
+        <v>-23.23</v>
       </c>
       <c r="AA3">
-        <v>-22</v>
+        <v>-22.25</v>
       </c>
       <c r="AB3">
-        <v>-2.42</v>
+        <v>-0.98</v>
       </c>
       <c r="AC3">
-        <v>31.7</v>
+        <v>47.67</v>
       </c>
       <c r="AD3">
-        <v>15.64</v>
+        <v>29.32</v>
       </c>
       <c r="AE3">
-        <v>22.19</v>
+        <v>21.46</v>
       </c>
       <c r="AF3">
-        <v>117.37</v>
+        <v>18.04</v>
       </c>
       <c r="AG3">
-        <v>569.25</v>
+        <v>567.25</v>
       </c>
       <c r="AH3">
-        <v>437.17</v>
+        <v>434.2</v>
       </c>
       <c r="AI3">
         <v>521.85</v>
@@ -1111,7 +1139,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>41.55</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1122,10 +1150,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>332.75</v>
+        <v>324.8</v>
       </c>
       <c r="D4">
-        <v>-0.61</v>
+        <v>-2.39</v>
       </c>
       <c r="E4">
         <v>604.85</v>
@@ -1134,25 +1162,25 @@
         <v>303.75</v>
       </c>
       <c r="G4">
-        <v>-44.99</v>
+        <v>-46.3</v>
       </c>
       <c r="H4">
-        <v>9.550000000000001</v>
+        <v>6.93</v>
       </c>
       <c r="I4">
-        <v>-5.37</v>
+        <v>-5.76</v>
       </c>
       <c r="J4">
-        <v>1.06</v>
+        <v>-2.43</v>
       </c>
       <c r="K4">
-        <v>5.53</v>
+        <v>3.8</v>
       </c>
       <c r="L4">
-        <v>-43.58</v>
+        <v>-43.42</v>
       </c>
       <c r="M4">
-        <v>-21.65</v>
+        <v>-22.03</v>
       </c>
       <c r="N4">
         <v>15</v>
@@ -1161,19 +1189,19 @@
         <v>18</v>
       </c>
       <c r="P4">
-        <v>337.43</v>
+        <v>333.46</v>
       </c>
       <c r="Q4">
-        <v>353.01</v>
+        <v>352.36</v>
       </c>
       <c r="R4">
-        <v>338.04</v>
+        <v>338.02</v>
       </c>
       <c r="S4">
-        <v>386.69</v>
+        <v>385.78</v>
       </c>
       <c r="T4">
-        <v>-13.95</v>
+        <v>-15.81</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1188,43 +1216,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>41.21</v>
+        <v>37.01</v>
       </c>
       <c r="Z4">
-        <v>-0.6</v>
+        <v>-2.14</v>
       </c>
       <c r="AA4">
-        <v>3.24</v>
+        <v>2.17</v>
       </c>
       <c r="AB4">
-        <v>-3.84</v>
+        <v>-4.3</v>
       </c>
       <c r="AC4">
-        <v>7.88</v>
+        <v>2.27</v>
       </c>
       <c r="AD4">
-        <v>7.04</v>
+        <v>5.92</v>
       </c>
       <c r="AE4">
-        <v>12.11</v>
+        <v>11.9</v>
       </c>
       <c r="AF4">
-        <v>-85.98999999999999</v>
+        <v>-87.65000000000001</v>
       </c>
       <c r="AG4">
-        <v>379.2</v>
+        <v>380.69</v>
       </c>
       <c r="AH4">
-        <v>326.81</v>
+        <v>324.04</v>
       </c>
       <c r="AI4">
-        <v>370.1</v>
+        <v>363.71</v>
       </c>
       <c r="AJ4" t="s">
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>35.42</v>
+        <v>36.78</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1235,10 +1263,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>2002</v>
+        <v>2021</v>
       </c>
       <c r="D5">
-        <v>-0.45</v>
+        <v>0.95</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1247,46 +1275,46 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-8.02</v>
+        <v>-7.15</v>
       </c>
       <c r="H5">
-        <v>22.69</v>
+        <v>23.85</v>
       </c>
       <c r="I5">
-        <v>-1.5</v>
+        <v>0.96</v>
       </c>
       <c r="J5">
-        <v>4.85</v>
+        <v>-0.4</v>
       </c>
       <c r="K5">
-        <v>13.82</v>
+        <v>16.06</v>
       </c>
       <c r="L5">
-        <v>1.95</v>
+        <v>5.03</v>
       </c>
       <c r="M5">
-        <v>3.91</v>
+        <v>3.38</v>
       </c>
       <c r="N5">
         <v>57</v>
       </c>
       <c r="O5">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="P5">
-        <v>2005.74</v>
+        <v>2009.6</v>
       </c>
       <c r="Q5">
-        <v>2029.72</v>
+        <v>2025.97</v>
       </c>
       <c r="R5">
-        <v>1927.89</v>
+        <v>1932.92</v>
       </c>
       <c r="S5">
-        <v>1907.15</v>
+        <v>1907.08</v>
       </c>
       <c r="T5">
-        <v>4.97</v>
+        <v>5.97</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1301,34 +1329,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>53.63</v>
+        <v>57.6</v>
       </c>
       <c r="Z5">
-        <v>20.64</v>
+        <v>19.99</v>
       </c>
       <c r="AA5">
-        <v>29.95</v>
+        <v>27.96</v>
       </c>
       <c r="AB5">
-        <v>-9.32</v>
+        <v>-7.97</v>
       </c>
       <c r="AC5">
-        <v>14.21</v>
+        <v>25.15</v>
       </c>
       <c r="AD5">
-        <v>12.19</v>
+        <v>18.1</v>
       </c>
       <c r="AE5">
-        <v>35.21</v>
+        <v>36.48</v>
       </c>
       <c r="AF5">
-        <v>-62.26</v>
+        <v>-40.75</v>
       </c>
       <c r="AG5">
-        <v>2097.6</v>
+        <v>2086.3</v>
       </c>
       <c r="AH5">
-        <v>1961.84</v>
+        <v>1965.64</v>
       </c>
       <c r="AI5">
         <v>1958.53</v>
@@ -1337,7 +1365,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>15.63</v>
+        <v>18.39</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1348,10 +1376,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>11340</v>
+        <v>11644</v>
       </c>
       <c r="D6">
-        <v>-0.52</v>
+        <v>2.68</v>
       </c>
       <c r="E6">
         <v>13595.75</v>
@@ -1360,46 +1388,46 @@
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-16.59</v>
+        <v>-14.36</v>
       </c>
       <c r="H6">
-        <v>29.66</v>
+        <v>33.14</v>
       </c>
       <c r="I6">
-        <v>0.18</v>
+        <v>4.71</v>
       </c>
       <c r="J6">
-        <v>3.37</v>
+        <v>2.65</v>
       </c>
       <c r="K6">
-        <v>10.42</v>
+        <v>13.71</v>
       </c>
       <c r="L6">
-        <v>-14.09</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="M6">
-        <v>23.55</v>
+        <v>23.5</v>
       </c>
       <c r="N6">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="O6">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="P6">
-        <v>11337.8</v>
+        <v>11442.6</v>
       </c>
       <c r="Q6">
-        <v>11414.05</v>
+        <v>11416.3</v>
       </c>
       <c r="R6">
-        <v>10972.44</v>
+        <v>10991.78</v>
       </c>
       <c r="S6">
-        <v>10723.48</v>
+        <v>10721.71</v>
       </c>
       <c r="T6">
-        <v>5.75</v>
+        <v>8.6</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1414,34 +1442,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>53.53</v>
+        <v>61.1</v>
       </c>
       <c r="Z6">
-        <v>114.89</v>
+        <v>129.48</v>
       </c>
       <c r="AA6">
-        <v>149.75</v>
+        <v>145.69</v>
       </c>
       <c r="AB6">
-        <v>-34.86</v>
+        <v>-16.22</v>
       </c>
       <c r="AC6">
-        <v>44.11</v>
+        <v>45.45</v>
       </c>
       <c r="AD6">
-        <v>39.92</v>
+        <v>44.63</v>
       </c>
       <c r="AE6">
-        <v>234.37</v>
+        <v>247.2</v>
       </c>
       <c r="AF6">
-        <v>-27.6</v>
+        <v>15.65</v>
       </c>
       <c r="AG6">
-        <v>11662.46</v>
+        <v>11672.46</v>
       </c>
       <c r="AH6">
-        <v>11165.64</v>
+        <v>11160.14</v>
       </c>
       <c r="AI6">
         <v>10787.84</v>
@@ -1450,7 +1478,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>28</v>
+        <v>25.21</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1461,10 +1489,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>1079.9</v>
+        <v>1057</v>
       </c>
       <c r="D7">
-        <v>-0.29</v>
+        <v>-2.12</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1473,46 +1501,46 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-6.81</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="H7">
-        <v>34.73</v>
+        <v>31.87</v>
       </c>
       <c r="I7">
-        <v>-1.38</v>
+        <v>-1.86</v>
       </c>
       <c r="J7">
-        <v>2.51</v>
+        <v>-7.38</v>
       </c>
       <c r="K7">
-        <v>21.47</v>
+        <v>19.84</v>
       </c>
       <c r="L7">
-        <v>19.88</v>
+        <v>20.63</v>
       </c>
       <c r="M7">
-        <v>8.970000000000001</v>
+        <v>7.44</v>
       </c>
       <c r="N7">
         <v>71</v>
       </c>
       <c r="O7">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="P7">
-        <v>1082.46</v>
+        <v>1078.46</v>
       </c>
       <c r="Q7">
-        <v>1100.86</v>
+        <v>1096.06</v>
       </c>
       <c r="R7">
-        <v>1055.5</v>
+        <v>1057.41</v>
       </c>
       <c r="S7">
-        <v>975.83</v>
+        <v>976.05</v>
       </c>
       <c r="T7">
-        <v>10.66</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1527,43 +1555,43 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>50.28</v>
+        <v>43.42</v>
       </c>
       <c r="Z7">
-        <v>6.95</v>
+        <v>4.04</v>
       </c>
       <c r="AA7">
-        <v>12.55</v>
+        <v>10.84</v>
       </c>
       <c r="AB7">
-        <v>-5.59</v>
+        <v>-6.8</v>
       </c>
       <c r="AC7">
-        <v>18.48</v>
+        <v>9.1</v>
       </c>
       <c r="AD7">
-        <v>17.64</v>
+        <v>16.02</v>
       </c>
       <c r="AE7">
-        <v>22.46</v>
+        <v>22.85</v>
       </c>
       <c r="AF7">
-        <v>-41.14</v>
+        <v>-6.46</v>
       </c>
       <c r="AG7">
-        <v>1154.52</v>
+        <v>1147.19</v>
       </c>
       <c r="AH7">
-        <v>1047.2</v>
+        <v>1044.93</v>
       </c>
       <c r="AI7">
-        <v>1067.72</v>
+        <v>1131.04</v>
       </c>
       <c r="AJ7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AK7">
-        <v>21.23</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1574,10 +1602,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>137.27</v>
+        <v>137.38</v>
       </c>
       <c r="D8">
-        <v>0.74</v>
+        <v>0.08</v>
       </c>
       <c r="E8">
         <v>148.95</v>
@@ -1586,46 +1614,46 @@
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>-7.84</v>
+        <v>-7.77</v>
       </c>
       <c r="H8">
-        <v>18.38</v>
+        <v>18.47</v>
       </c>
       <c r="I8">
-        <v>0.04</v>
+        <v>1.25</v>
       </c>
       <c r="J8">
-        <v>-1.89</v>
+        <v>-2.86</v>
       </c>
       <c r="K8">
-        <v>-1.08</v>
+        <v>-2.42</v>
       </c>
       <c r="L8">
-        <v>2.92</v>
+        <v>5.42</v>
       </c>
       <c r="M8">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="N8">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="O8">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P8">
-        <v>136.27</v>
+        <v>136.61</v>
       </c>
       <c r="Q8">
-        <v>138.08</v>
+        <v>137.76</v>
       </c>
       <c r="R8">
-        <v>137.47</v>
+        <v>137.5</v>
       </c>
       <c r="S8">
-        <v>133.62</v>
+        <v>133.66</v>
       </c>
       <c r="T8">
-        <v>2.73</v>
+        <v>2.79</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1640,34 +1668,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>49.19</v>
+        <v>49.51</v>
       </c>
       <c r="Z8">
-        <v>-0.75</v>
+        <v>-0.65</v>
       </c>
       <c r="AA8">
         <v>-0.67</v>
       </c>
       <c r="AB8">
-        <v>-0.08</v>
+        <v>0.02</v>
       </c>
       <c r="AC8">
-        <v>63.89</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="AD8">
-        <v>47.26</v>
+        <v>62.62</v>
       </c>
       <c r="AE8">
-        <v>3.73</v>
+        <v>3.81</v>
       </c>
       <c r="AF8">
-        <v>-74.95</v>
+        <v>-46.01</v>
       </c>
       <c r="AG8">
-        <v>144.84</v>
+        <v>144.01</v>
       </c>
       <c r="AH8">
-        <v>131.31</v>
+        <v>131.52</v>
       </c>
       <c r="AI8">
         <v>131.91</v>
@@ -1676,7 +1704,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>20.09</v>
+        <v>21.15</v>
       </c>
     </row>
   </sheetData>
@@ -1837,12 +1865,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>50</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1850,1006 +1913,1006 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>55</v>
+      <c r="B6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="6">
+        <v>4.18</v>
+      </c>
+      <c r="D7" s="6">
+        <v>5.29</v>
+      </c>
+      <c r="E7" s="7">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-11.27</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-9.550000000000001</v>
+      </c>
+      <c r="E8" s="7">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>1.06</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-2.43</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-3.49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>4.85</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-0.4</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-5.25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
         <v>3.37</v>
       </c>
-      <c r="D7" s="5">
-        <v>4.18</v>
-      </c>
-      <c r="E7" s="6">
-        <v>0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="D11" s="6">
+        <v>2.65</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>2.51</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-7.38</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-9.890000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-1.89</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-2.86</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-0.97</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="6">
+        <v>1.79</v>
+      </c>
+      <c r="D14" s="6">
+        <v>2.8</v>
+      </c>
+      <c r="E14" s="7">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="5">
-        <v>-16.01</v>
-      </c>
-      <c r="D8" s="5">
-        <v>-11.27</v>
-      </c>
-      <c r="E8" s="6">
-        <v>4.74</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-0.19</v>
+      </c>
+      <c r="D15" s="6">
+        <v>2.34</v>
+      </c>
+      <c r="E15" s="7">
+        <v>2.53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="5">
-        <v>1.29</v>
-      </c>
-      <c r="D9" s="5">
-        <v>1.06</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-0.23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-5.37</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-5.76</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="5">
-        <v>4.5</v>
-      </c>
-      <c r="D10" s="5">
-        <v>4.85</v>
-      </c>
-      <c r="E10" s="6">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-1.5</v>
+      </c>
+      <c r="D17" s="6">
+        <v>0.96</v>
+      </c>
+      <c r="E17" s="7">
+        <v>2.46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="5">
-        <v>4.11</v>
-      </c>
-      <c r="D11" s="5">
-        <v>3.37</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-0.74</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.18</v>
+      </c>
+      <c r="D18" s="6">
+        <v>4.71</v>
+      </c>
+      <c r="E18" s="7">
+        <v>4.53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="5">
-        <v>2.71</v>
-      </c>
-      <c r="D12" s="5">
-        <v>2.51</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-1.38</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-1.86</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="5">
-        <v>-2.27</v>
-      </c>
-      <c r="D13" s="5">
-        <v>-1.89</v>
-      </c>
-      <c r="E13" s="6">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>0.04</v>
+      </c>
+      <c r="D20" s="6">
+        <v>1.25</v>
+      </c>
+      <c r="E20" s="7">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="5">
-        <v>-0.62</v>
-      </c>
-      <c r="D14" s="5">
-        <v>1.79</v>
-      </c>
-      <c r="E14" s="6">
-        <v>2.41</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>38.02</v>
+      </c>
+      <c r="D21" s="6">
+        <v>41.53</v>
+      </c>
+      <c r="E21" s="7">
+        <v>3.51</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-7.46</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-0.19</v>
-      </c>
-      <c r="E15" s="6">
-        <v>7.27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="6">
+        <v>108.88</v>
+      </c>
+      <c r="D22" s="6">
+        <v>106.55</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-2.33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>-5.52</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-5.37</v>
-      </c>
-      <c r="E16" s="6">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-43.58</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-43.42</v>
+      </c>
+      <c r="E23" s="7">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-0.25</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-1.5</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-1.25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>1.95</v>
+      </c>
+      <c r="D24" s="6">
+        <v>5.03</v>
+      </c>
+      <c r="E24" s="7">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>0.27</v>
-      </c>
-      <c r="D18" s="5">
-        <v>0.18</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-0.09</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-14.09</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-9.970000000000001</v>
+      </c>
+      <c r="E25" s="7">
+        <v>4.12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-1.1</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-1.38</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.28</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>19.88</v>
+      </c>
+      <c r="D26" s="6">
+        <v>20.63</v>
+      </c>
+      <c r="E26" s="7">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-0.51</v>
-      </c>
-      <c r="D20" s="5">
-        <v>0.04</v>
-      </c>
-      <c r="E20" s="6">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>2.92</v>
+      </c>
+      <c r="D27" s="6">
+        <v>5.42</v>
+      </c>
+      <c r="E27" s="7">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="5">
-        <v>36.93</v>
-      </c>
-      <c r="D21" s="5">
-        <v>38.02</v>
-      </c>
-      <c r="E21" s="6">
-        <v>1.09</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="6">
+        <v>14.78</v>
+      </c>
+      <c r="D28" s="6">
+        <v>17.98</v>
+      </c>
+      <c r="E28" s="7">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="5">
-        <v>98.93000000000001</v>
-      </c>
-      <c r="D22" s="5">
-        <v>108.88</v>
-      </c>
-      <c r="E22" s="6">
-        <v>9.949999999999999</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-14.6</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-17.07</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-2.47</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="5">
-        <v>-42.69</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-43.58</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-0.89</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="6">
+        <v>5.53</v>
+      </c>
+      <c r="D30" s="6">
+        <v>3.8</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-1.73</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="5">
-        <v>2.29</v>
-      </c>
-      <c r="D24" s="5">
-        <v>1.95</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-0.34</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="B31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="6">
+        <v>13.82</v>
+      </c>
+      <c r="D31" s="6">
+        <v>16.06</v>
+      </c>
+      <c r="E31" s="7">
+        <v>2.24</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>-15.43</v>
-      </c>
-      <c r="D25" s="5">
-        <v>-14.09</v>
-      </c>
-      <c r="E25" s="6">
-        <v>1.34</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="B32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="6">
+        <v>10.42</v>
+      </c>
+      <c r="D32" s="6">
+        <v>13.71</v>
+      </c>
+      <c r="E32" s="7">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>21.07</v>
-      </c>
-      <c r="D26" s="5">
-        <v>19.88</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-1.19</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6">
+        <v>21.47</v>
+      </c>
+      <c r="D33" s="6">
+        <v>19.84</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-1.63</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>-0.42</v>
-      </c>
-      <c r="D27" s="5">
-        <v>2.92</v>
-      </c>
-      <c r="E27" s="6">
-        <v>3.34</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-1.08</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-2.42</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-1.34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="5">
-        <v>12.05</v>
-      </c>
-      <c r="D28" s="5">
-        <v>14.78</v>
-      </c>
-      <c r="E28" s="6">
-        <v>2.73</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="B35" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-0.14</v>
+      </c>
+      <c r="D35" s="6">
+        <v>0</v>
+      </c>
+      <c r="E35" s="7">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-18.49</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-14.6</v>
-      </c>
-      <c r="E29" s="6">
-        <v>3.89</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="B36" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-28.77</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-29.27</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="5">
-        <v>6.47</v>
-      </c>
-      <c r="D30" s="5">
-        <v>5.53</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-0.9399999999999999</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="B37" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-44.99</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-46.3</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-1.31</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="5">
-        <v>12.75</v>
-      </c>
-      <c r="D31" s="5">
-        <v>13.82</v>
-      </c>
-      <c r="E31" s="6">
-        <v>1.07</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="B38" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-8.02</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-7.15</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="5">
-        <v>10.02</v>
-      </c>
-      <c r="D32" s="5">
-        <v>10.42</v>
-      </c>
-      <c r="E32" s="6">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="B39" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-16.59</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-14.36</v>
+      </c>
+      <c r="E39" s="7">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="5">
-        <v>19.24</v>
-      </c>
-      <c r="D33" s="5">
-        <v>21.47</v>
-      </c>
-      <c r="E33" s="6">
-        <v>2.23</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="B40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-6.81</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-8.779999999999999</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-1.97</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>-3.51</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-1.08</v>
-      </c>
-      <c r="E34" s="6">
-        <v>2.43</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="B41" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-7.84</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-7.77</v>
+      </c>
+      <c r="E41" s="7">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-1.74</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-0.14</v>
-      </c>
-      <c r="E35" s="6">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="B42" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="6">
+        <v>11910</v>
+      </c>
+      <c r="D42" s="6">
+        <v>12130</v>
+      </c>
+      <c r="E42" s="7">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-32.77</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-28.77</v>
-      </c>
-      <c r="E36" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
+      <c r="B43" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="6">
+        <v>477.45</v>
+      </c>
+      <c r="D43" s="6">
+        <v>474.05</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-3.4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="5">
-        <v>-44.65</v>
-      </c>
-      <c r="D37" s="5">
-        <v>-44.99</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-0.34</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
+      <c r="B44" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="6">
+        <v>332.75</v>
+      </c>
+      <c r="D44" s="6">
+        <v>324.8</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-7.95</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="5">
-        <v>-7.61</v>
-      </c>
-      <c r="D38" s="5">
-        <v>-8.02</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-0.41</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
+      <c r="B45" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="6">
+        <v>2002</v>
+      </c>
+      <c r="D45" s="6">
+        <v>2021</v>
+      </c>
+      <c r="E45" s="7">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-16.16</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-16.59</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-0.43</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
+      <c r="B46" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="6">
+        <v>11340</v>
+      </c>
+      <c r="D46" s="6">
+        <v>11644</v>
+      </c>
+      <c r="E46" s="7">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="5">
-        <v>-6.54</v>
-      </c>
-      <c r="D40" s="5">
-        <v>-6.81</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-0.27</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
+      <c r="B47" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="6">
+        <v>1079.9</v>
+      </c>
+      <c r="D47" s="6">
+        <v>1057</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-22.9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="5">
-        <v>-8.52</v>
-      </c>
-      <c r="D41" s="5">
-        <v>-7.84</v>
-      </c>
-      <c r="E41" s="6">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
+      <c r="B48" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="6">
+        <v>137.27</v>
+      </c>
+      <c r="D48" s="6">
+        <v>137.38</v>
+      </c>
+      <c r="E48" s="7">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49" s="6">
+        <v>29</v>
+      </c>
+      <c r="D49" s="6">
+        <v>43</v>
+      </c>
+      <c r="E49" s="7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" s="6">
+        <v>43</v>
+      </c>
+      <c r="D50" s="6">
+        <v>29</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="5">
-        <v>11720</v>
-      </c>
-      <c r="D42" s="5">
-        <v>11910</v>
-      </c>
-      <c r="E42" s="6">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
+      <c r="B51" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="6">
+        <v>64.31999999999999</v>
+      </c>
+      <c r="D51" s="6">
+        <v>69.08</v>
+      </c>
+      <c r="E51" s="7">
+        <v>4.76</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="5">
-        <v>450.6</v>
-      </c>
-      <c r="D43" s="5">
-        <v>477.45</v>
-      </c>
-      <c r="E43" s="6">
-        <v>26.85</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
+      <c r="B52" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="6">
+        <v>40.95</v>
+      </c>
+      <c r="D52" s="6">
+        <v>40.12</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-0.83</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="5">
-        <v>334.8</v>
-      </c>
-      <c r="D44" s="5">
-        <v>332.75</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-2.05</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
+      <c r="B53" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="6">
+        <v>41.21</v>
+      </c>
+      <c r="D53" s="6">
+        <v>37.01</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-4.2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="5">
-        <v>2011</v>
-      </c>
-      <c r="D45" s="5">
-        <v>2002</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-9</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
+      <c r="B54" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="6">
+        <v>53.63</v>
+      </c>
+      <c r="D54" s="6">
+        <v>57.6</v>
+      </c>
+      <c r="E54" s="7">
+        <v>3.97</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="5">
-        <v>11399</v>
-      </c>
-      <c r="D46" s="5">
-        <v>11340</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-59</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
+      <c r="B55" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="6">
+        <v>53.53</v>
+      </c>
+      <c r="D55" s="6">
+        <v>61.1</v>
+      </c>
+      <c r="E55" s="7">
+        <v>7.57</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="5">
-        <v>1083</v>
-      </c>
-      <c r="D47" s="5">
-        <v>1079.9</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-3.1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
+      <c r="B56" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="6">
+        <v>50.28</v>
+      </c>
+      <c r="D56" s="6">
+        <v>43.42</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-6.86</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="5">
-        <v>136.26</v>
-      </c>
-      <c r="D48" s="5">
-        <v>137.27</v>
-      </c>
-      <c r="E48" s="6">
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
+      <c r="B57" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="6">
+        <v>49.19</v>
+      </c>
+      <c r="D57" s="6">
+        <v>49.51</v>
+      </c>
+      <c r="E57" s="7">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="6">
+        <v>14.69</v>
+      </c>
+      <c r="D58" s="6">
+        <v>56.3</v>
+      </c>
+      <c r="E58" s="7">
+        <v>41.61</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="6">
+        <v>117.37</v>
+      </c>
+      <c r="D59" s="6">
+        <v>18.04</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-99.33</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="6">
+        <v>-85.98999999999999</v>
+      </c>
+      <c r="D60" s="6">
+        <v>-87.65000000000001</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-1.66</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="6">
+        <v>-62.26</v>
+      </c>
+      <c r="D61" s="6">
+        <v>-40.75</v>
+      </c>
+      <c r="E61" s="7">
+        <v>21.51</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C49" s="5">
+      <c r="B62" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="6">
+        <v>-27.6</v>
+      </c>
+      <c r="D62" s="6">
+        <v>15.65</v>
+      </c>
+      <c r="E62" s="7">
+        <v>43.25</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="6">
+        <v>-41.14</v>
+      </c>
+      <c r="D63" s="6">
+        <v>-6.46</v>
+      </c>
+      <c r="E63" s="7">
+        <v>34.68</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D49" s="5">
-        <v>29</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C50" s="5">
-        <v>29</v>
-      </c>
-      <c r="D50" s="5">
-        <v>43</v>
-      </c>
-      <c r="E50" s="6">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="5">
-        <v>59.28</v>
-      </c>
-      <c r="D51" s="5">
-        <v>64.31999999999999</v>
-      </c>
-      <c r="E51" s="6">
-        <v>5.04</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="5">
-        <v>30.49</v>
-      </c>
-      <c r="D52" s="5">
-        <v>40.95</v>
-      </c>
-      <c r="E52" s="6">
-        <v>10.46</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="5">
-        <v>42.36</v>
-      </c>
-      <c r="D53" s="5">
-        <v>41.21</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-1.15</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="5">
-        <v>55.93</v>
-      </c>
-      <c r="D54" s="5">
-        <v>53.63</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-2.3</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="5">
-        <v>55.47</v>
-      </c>
-      <c r="D55" s="5">
-        <v>53.53</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-1.94</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="5">
-        <v>51.29</v>
-      </c>
-      <c r="D56" s="5">
-        <v>50.28</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-1.01</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="5">
-        <v>46.26</v>
-      </c>
-      <c r="D57" s="5">
-        <v>49.19</v>
-      </c>
-      <c r="E57" s="6">
-        <v>2.93</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B58" s="3" t="s">
+      <c r="B64" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C58" s="5">
-        <v>-7.83</v>
-      </c>
-      <c r="D58" s="5">
-        <v>14.69</v>
-      </c>
-      <c r="E58" s="6">
-        <v>22.52</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C59" s="5">
-        <v>36.73</v>
-      </c>
-      <c r="D59" s="5">
-        <v>117.37</v>
-      </c>
-      <c r="E59" s="6">
-        <v>80.64</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="5">
-        <v>-89.22</v>
-      </c>
-      <c r="D60" s="5">
-        <v>-85.98999999999999</v>
-      </c>
-      <c r="E60" s="6">
-        <v>3.23</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="5">
-        <v>-58.3</v>
-      </c>
-      <c r="D61" s="5">
-        <v>-62.26</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-3.96</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="5">
-        <v>29.5</v>
-      </c>
-      <c r="D62" s="5">
-        <v>-27.6</v>
-      </c>
-      <c r="E62" s="7">
-        <v>-57.1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="5">
-        <v>-33.04</v>
-      </c>
-      <c r="D63" s="5">
-        <v>-41.14</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-8.1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="5">
-        <v>-63</v>
-      </c>
-      <c r="D64" s="5">
+      <c r="C64" s="6">
         <v>-74.95</v>
       </c>
+      <c r="D64" s="6">
+        <v>-46.01</v>
+      </c>
       <c r="E64" s="7">
-        <v>-11.95</v>
+        <v>28.94</v>
       </c>
     </row>
   </sheetData>
@@ -2875,60 +2938,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C1" s="8" t="s">
+      <c r="B1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="11">
+        <v>68.8</v>
+      </c>
+      <c r="C2" s="12">
+        <v>7</v>
+      </c>
+      <c r="D2" s="11">
+        <v>51.1</v>
+      </c>
+      <c r="E2" s="11">
+        <v>90</v>
+      </c>
+      <c r="F2" s="11">
+        <v>-2.1</v>
+      </c>
+      <c r="G2" s="11">
+        <v>7.4</v>
+      </c>
+      <c r="H2" s="11">
         <v>57</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="10">
-        <v>68.8</v>
-      </c>
-      <c r="C2" s="11">
-        <v>7</v>
-      </c>
-      <c r="D2" s="10">
-        <v>50.4</v>
-      </c>
-      <c r="E2" s="10">
-        <v>90</v>
-      </c>
-      <c r="F2" s="10">
-        <v>0.4</v>
-      </c>
-      <c r="G2" s="10">
-        <v>7.2</v>
-      </c>
-      <c r="H2" s="10">
-        <v>57</v>
-      </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>70</v>
       </c>
     </row>
@@ -3030,49 +3093,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="13">
-        <v>0.2916</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.2355</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.1576</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.0897</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.0391</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0.0017</v>
-      </c>
-      <c r="G2" s="13">
-        <v>-0.2165</v>
+      <c r="A2" s="14">
+        <v>0.2954</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.235</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.1598</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.07440000000000001</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.0338</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.0023</v>
+      </c>
+      <c r="G2" s="14">
+        <v>-0.2203</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="80">
   <si>
     <t>Symbol</t>
   </si>
@@ -187,19 +187,40 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>RSI Overbought Entry</t>
+  </si>
+  <si>
+    <t>69.1 → 73.1</t>
+  </si>
+  <si>
+    <t>⚠️ CAUTION</t>
+  </si>
+  <si>
+    <t>69.1</t>
+  </si>
+  <si>
+    <t>73.1</t>
+  </si>
+  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>50.3 → 43.4</t>
+    <t>57.6 → 46.5</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
   </si>
   <si>
-    <t>50.3</t>
-  </si>
-  <si>
-    <t>43.4</t>
+    <t>57.6</t>
+  </si>
+  <si>
+    <t>46.5</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -251,7 +272,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -285,6 +306,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -298,7 +326,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -320,6 +348,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4A6FA5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -401,7 +435,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -409,14 +443,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -425,7 +460,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -924,13 +959,13 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>12130</v>
+        <v>12361</v>
       </c>
       <c r="D2">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="E2">
-        <v>12130</v>
+        <v>12361</v>
       </c>
       <c r="F2">
         <v>8506.780000000001</v>
@@ -939,43 +974,43 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>42.59</v>
+        <v>45.31</v>
       </c>
       <c r="I2">
-        <v>2.8</v>
+        <v>3.64</v>
       </c>
       <c r="J2">
-        <v>5.29</v>
+        <v>4.26</v>
       </c>
       <c r="K2">
-        <v>17.98</v>
+        <v>20.49</v>
       </c>
       <c r="L2">
-        <v>41.53</v>
+        <v>44.25</v>
       </c>
       <c r="M2">
-        <v>29.54</v>
+        <v>29.82</v>
       </c>
       <c r="N2">
         <v>85</v>
       </c>
       <c r="O2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="P2">
-        <v>11882.2</v>
+        <v>11969</v>
       </c>
       <c r="Q2">
-        <v>11739.65</v>
+        <v>11777.7</v>
       </c>
       <c r="R2">
-        <v>10974.8</v>
+        <v>11018.2</v>
       </c>
       <c r="S2">
-        <v>9853.379999999999</v>
+        <v>9871.459999999999</v>
       </c>
       <c r="T2">
-        <v>23.1</v>
+        <v>25.22</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -990,43 +1025,43 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>69.08</v>
+        <v>73.14</v>
       </c>
       <c r="Z2">
-        <v>237.11</v>
+        <v>264.2</v>
       </c>
       <c r="AA2">
-        <v>255.26</v>
+        <v>257.05</v>
       </c>
       <c r="AB2">
-        <v>-18.15</v>
+        <v>7.14</v>
       </c>
       <c r="AC2">
+        <v>85.16</v>
+      </c>
+      <c r="AD2">
         <v>51.83</v>
       </c>
-      <c r="AD2">
-        <v>34.55</v>
-      </c>
       <c r="AE2">
-        <v>206.43</v>
+        <v>218.83</v>
       </c>
       <c r="AF2">
-        <v>56.3</v>
+        <v>111.41</v>
       </c>
       <c r="AG2">
-        <v>11995.35</v>
+        <v>12147.11</v>
       </c>
       <c r="AH2">
-        <v>11483.95</v>
+        <v>11408.29</v>
       </c>
       <c r="AI2">
-        <v>11384.21</v>
+        <v>11623.52</v>
       </c>
       <c r="AJ2" t="s">
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>46.72</v>
+        <v>50.18</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1037,10 +1072,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>474.05</v>
+        <v>471.95</v>
       </c>
       <c r="D3">
-        <v>-0.71</v>
+        <v>-0.44</v>
       </c>
       <c r="E3">
         <v>670.25</v>
@@ -1049,25 +1084,25 @@
         <v>222.01</v>
       </c>
       <c r="G3">
-        <v>-29.27</v>
+        <v>-29.59</v>
       </c>
       <c r="H3">
-        <v>113.53</v>
+        <v>112.58</v>
       </c>
       <c r="I3">
-        <v>2.34</v>
+        <v>3.71</v>
       </c>
       <c r="J3">
-        <v>-9.550000000000001</v>
+        <v>-9.9</v>
       </c>
       <c r="K3">
-        <v>-17.07</v>
+        <v>-15.03</v>
       </c>
       <c r="L3">
-        <v>106.55</v>
+        <v>101.39</v>
       </c>
       <c r="M3">
-        <v>15.98</v>
+        <v>15.86</v>
       </c>
       <c r="N3">
         <v>99</v>
@@ -1076,19 +1111,19 @@
         <v>88</v>
       </c>
       <c r="P3">
-        <v>464.13</v>
+        <v>467.51</v>
       </c>
       <c r="Q3">
-        <v>500.72</v>
+        <v>497.11</v>
       </c>
       <c r="R3">
-        <v>547.67</v>
+        <v>544.71</v>
       </c>
       <c r="S3">
-        <v>425.96</v>
+        <v>426.97</v>
       </c>
       <c r="T3">
-        <v>11.29</v>
+        <v>10.53</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1103,34 +1138,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>40.12</v>
+        <v>39.59</v>
       </c>
       <c r="Z3">
-        <v>-23.23</v>
+        <v>-22.19</v>
       </c>
       <c r="AA3">
-        <v>-22.25</v>
+        <v>-22.24</v>
       </c>
       <c r="AB3">
-        <v>-0.98</v>
+        <v>0.05</v>
       </c>
       <c r="AC3">
-        <v>47.67</v>
+        <v>72.78</v>
       </c>
       <c r="AD3">
-        <v>29.32</v>
+        <v>50.72</v>
       </c>
       <c r="AE3">
-        <v>21.46</v>
+        <v>21.57</v>
       </c>
       <c r="AF3">
-        <v>18.04</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="AG3">
-        <v>567.25</v>
+        <v>561.5</v>
       </c>
       <c r="AH3">
-        <v>434.2</v>
+        <v>432.72</v>
       </c>
       <c r="AI3">
         <v>521.85</v>
@@ -1139,7 +1174,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>39.1</v>
+        <v>34.24</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1150,10 +1185,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>324.8</v>
+        <v>325.85</v>
       </c>
       <c r="D4">
-        <v>-2.39</v>
+        <v>0.32</v>
       </c>
       <c r="E4">
         <v>604.85</v>
@@ -1162,25 +1197,25 @@
         <v>303.75</v>
       </c>
       <c r="G4">
-        <v>-46.3</v>
+        <v>-46.13</v>
       </c>
       <c r="H4">
-        <v>6.93</v>
+        <v>7.28</v>
       </c>
       <c r="I4">
-        <v>-5.76</v>
+        <v>-2.54</v>
       </c>
       <c r="J4">
-        <v>-2.43</v>
+        <v>-3.49</v>
       </c>
       <c r="K4">
-        <v>3.8</v>
+        <v>5.54</v>
       </c>
       <c r="L4">
-        <v>-43.42</v>
+        <v>-43.15</v>
       </c>
       <c r="M4">
-        <v>-22.03</v>
+        <v>-21.57</v>
       </c>
       <c r="N4">
         <v>15</v>
@@ -1189,19 +1224,19 @@
         <v>18</v>
       </c>
       <c r="P4">
-        <v>333.46</v>
+        <v>331.76</v>
       </c>
       <c r="Q4">
-        <v>352.36</v>
+        <v>351.17</v>
       </c>
       <c r="R4">
-        <v>338.02</v>
+        <v>337.94</v>
       </c>
       <c r="S4">
-        <v>385.78</v>
+        <v>384.89</v>
       </c>
       <c r="T4">
-        <v>-15.81</v>
+        <v>-15.34</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1216,43 +1251,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>37.01</v>
+        <v>37.91</v>
       </c>
       <c r="Z4">
-        <v>-2.14</v>
+        <v>-3.23</v>
       </c>
       <c r="AA4">
-        <v>2.17</v>
+        <v>1.09</v>
       </c>
       <c r="AB4">
-        <v>-4.3</v>
+        <v>-4.32</v>
       </c>
       <c r="AC4">
-        <v>2.27</v>
+        <v>1.55</v>
       </c>
       <c r="AD4">
-        <v>5.92</v>
+        <v>3.9</v>
       </c>
       <c r="AE4">
-        <v>11.9</v>
+        <v>11.59</v>
       </c>
       <c r="AF4">
-        <v>-87.65000000000001</v>
+        <v>-86.58</v>
       </c>
       <c r="AG4">
-        <v>380.69</v>
+        <v>381.88</v>
       </c>
       <c r="AH4">
-        <v>324.04</v>
+        <v>320.47</v>
       </c>
       <c r="AI4">
-        <v>363.71</v>
+        <v>361.57</v>
       </c>
       <c r="AJ4" t="s">
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>36.78</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1263,10 +1298,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>2021</v>
+        <v>1972</v>
       </c>
       <c r="D5">
-        <v>0.95</v>
+        <v>-2.42</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1275,46 +1310,46 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-7.15</v>
+        <v>-9.4</v>
       </c>
       <c r="H5">
-        <v>23.85</v>
+        <v>20.85</v>
       </c>
       <c r="I5">
-        <v>0.96</v>
+        <v>-1.6</v>
       </c>
       <c r="J5">
-        <v>-0.4</v>
+        <v>-5.92</v>
       </c>
       <c r="K5">
-        <v>16.06</v>
+        <v>13.7</v>
       </c>
       <c r="L5">
-        <v>5.03</v>
+        <v>2.84</v>
       </c>
       <c r="M5">
-        <v>3.38</v>
+        <v>3.32</v>
       </c>
       <c r="N5">
         <v>57</v>
       </c>
       <c r="O5">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="P5">
-        <v>2009.6</v>
+        <v>2003.2</v>
       </c>
       <c r="Q5">
-        <v>2025.97</v>
+        <v>2019.32</v>
       </c>
       <c r="R5">
-        <v>1932.92</v>
+        <v>1936.71</v>
       </c>
       <c r="S5">
-        <v>1907.08</v>
+        <v>1906.66</v>
       </c>
       <c r="T5">
-        <v>5.97</v>
+        <v>3.43</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1329,34 +1364,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>57.6</v>
+        <v>46.54</v>
       </c>
       <c r="Z5">
-        <v>19.99</v>
+        <v>15.35</v>
       </c>
       <c r="AA5">
-        <v>27.96</v>
+        <v>25.44</v>
       </c>
       <c r="AB5">
-        <v>-7.97</v>
+        <v>-10.09</v>
       </c>
       <c r="AC5">
-        <v>25.15</v>
+        <v>17.62</v>
       </c>
       <c r="AD5">
-        <v>18.1</v>
+        <v>18.99</v>
       </c>
       <c r="AE5">
-        <v>36.48</v>
+        <v>38.22</v>
       </c>
       <c r="AF5">
-        <v>-40.75</v>
+        <v>-26.99</v>
       </c>
       <c r="AG5">
-        <v>2086.3</v>
+        <v>2071.78</v>
       </c>
       <c r="AH5">
-        <v>1965.64</v>
+        <v>1966.86</v>
       </c>
       <c r="AI5">
         <v>1958.53</v>
@@ -1365,7 +1400,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>18.39</v>
+        <v>21.51</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1376,10 +1411,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>11644</v>
+        <v>11310</v>
       </c>
       <c r="D6">
-        <v>2.68</v>
+        <v>-2.87</v>
       </c>
       <c r="E6">
         <v>13595.75</v>
@@ -1388,46 +1423,46 @@
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-14.36</v>
+        <v>-16.81</v>
       </c>
       <c r="H6">
-        <v>33.14</v>
+        <v>29.32</v>
       </c>
       <c r="I6">
-        <v>4.71</v>
+        <v>0.18</v>
       </c>
       <c r="J6">
-        <v>2.65</v>
+        <v>-2.49</v>
       </c>
       <c r="K6">
-        <v>13.71</v>
+        <v>10.99</v>
       </c>
       <c r="L6">
-        <v>-9.970000000000001</v>
+        <v>-12.34</v>
       </c>
       <c r="M6">
-        <v>23.5</v>
+        <v>22.89</v>
       </c>
       <c r="N6">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="O6">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="P6">
-        <v>11442.6</v>
+        <v>11446.6</v>
       </c>
       <c r="Q6">
-        <v>11416.3</v>
+        <v>11408.05</v>
       </c>
       <c r="R6">
-        <v>10991.78</v>
+        <v>11000.08</v>
       </c>
       <c r="S6">
-        <v>10721.71</v>
+        <v>10718.36</v>
       </c>
       <c r="T6">
-        <v>8.6</v>
+        <v>5.52</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1442,34 +1477,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>61.1</v>
+        <v>51.23</v>
       </c>
       <c r="Z6">
-        <v>129.48</v>
+        <v>112.79</v>
       </c>
       <c r="AA6">
-        <v>145.69</v>
+        <v>139.11</v>
       </c>
       <c r="AB6">
-        <v>-16.22</v>
+        <v>-26.32</v>
       </c>
       <c r="AC6">
-        <v>45.45</v>
+        <v>39.06</v>
       </c>
       <c r="AD6">
-        <v>44.63</v>
+        <v>42.87</v>
       </c>
       <c r="AE6">
-        <v>247.2</v>
+        <v>255.4</v>
       </c>
       <c r="AF6">
-        <v>15.65</v>
+        <v>6.45</v>
       </c>
       <c r="AG6">
-        <v>11672.46</v>
+        <v>11666.86</v>
       </c>
       <c r="AH6">
-        <v>11160.14</v>
+        <v>11149.24</v>
       </c>
       <c r="AI6">
         <v>10787.84</v>
@@ -1478,7 +1513,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>25.21</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1489,10 +1524,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>1057</v>
+        <v>1053.9</v>
       </c>
       <c r="D7">
-        <v>-2.12</v>
+        <v>-0.29</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1501,25 +1536,25 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-8.779999999999999</v>
+        <v>-9.050000000000001</v>
       </c>
       <c r="H7">
-        <v>31.87</v>
+        <v>31.48</v>
       </c>
       <c r="I7">
-        <v>-1.86</v>
+        <v>-3.08</v>
       </c>
       <c r="J7">
-        <v>-7.38</v>
+        <v>-8.59</v>
       </c>
       <c r="K7">
-        <v>19.84</v>
+        <v>20.2</v>
       </c>
       <c r="L7">
-        <v>20.63</v>
+        <v>20.19</v>
       </c>
       <c r="M7">
-        <v>7.44</v>
+        <v>7.39</v>
       </c>
       <c r="N7">
         <v>71</v>
@@ -1528,19 +1563,19 @@
         <v>74</v>
       </c>
       <c r="P7">
-        <v>1078.46</v>
+        <v>1071.76</v>
       </c>
       <c r="Q7">
-        <v>1096.06</v>
+        <v>1091.31</v>
       </c>
       <c r="R7">
-        <v>1057.41</v>
+        <v>1059.12</v>
       </c>
       <c r="S7">
-        <v>976.05</v>
+        <v>976.3</v>
       </c>
       <c r="T7">
-        <v>8.289999999999999</v>
+        <v>7.95</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1555,43 +1590,43 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>43.42</v>
+        <v>42.58</v>
       </c>
       <c r="Z7">
-        <v>4.04</v>
+        <v>1.47</v>
       </c>
       <c r="AA7">
-        <v>10.84</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="AB7">
-        <v>-6.8</v>
+        <v>-7.5</v>
       </c>
       <c r="AC7">
-        <v>9.1</v>
+        <v>2.55</v>
       </c>
       <c r="AD7">
-        <v>16.02</v>
+        <v>10.04</v>
       </c>
       <c r="AE7">
-        <v>22.85</v>
+        <v>22.64</v>
       </c>
       <c r="AF7">
-        <v>-6.46</v>
+        <v>-18.07</v>
       </c>
       <c r="AG7">
-        <v>1147.19</v>
+        <v>1139.3</v>
       </c>
       <c r="AH7">
-        <v>1044.93</v>
+        <v>1043.31</v>
       </c>
       <c r="AI7">
-        <v>1131.04</v>
+        <v>1124.93</v>
       </c>
       <c r="AJ7" t="s">
         <v>48</v>
       </c>
       <c r="AK7">
-        <v>23.2</v>
+        <v>25.45</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1602,10 +1637,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>137.38</v>
+        <v>136.03</v>
       </c>
       <c r="D8">
-        <v>0.08</v>
+        <v>-0.98</v>
       </c>
       <c r="E8">
         <v>148.95</v>
@@ -1614,88 +1649,88 @@
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>-7.77</v>
+        <v>-8.67</v>
       </c>
       <c r="H8">
-        <v>18.47</v>
+        <v>17.31</v>
       </c>
       <c r="I8">
-        <v>1.25</v>
+        <v>0.68</v>
       </c>
       <c r="J8">
-        <v>-2.86</v>
+        <v>-5.27</v>
       </c>
       <c r="K8">
-        <v>-2.42</v>
+        <v>-2.59</v>
       </c>
       <c r="L8">
-        <v>5.42</v>
+        <v>5.61</v>
       </c>
       <c r="M8">
-        <v>0.23</v>
+        <v>0.15</v>
       </c>
       <c r="N8">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="O8">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="P8">
-        <v>136.61</v>
+        <v>136.79</v>
       </c>
       <c r="Q8">
-        <v>137.76</v>
+        <v>137.45</v>
       </c>
       <c r="R8">
-        <v>137.5</v>
+        <v>137.46</v>
       </c>
       <c r="S8">
-        <v>133.66</v>
+        <v>133.67</v>
       </c>
       <c r="T8">
-        <v>2.79</v>
+        <v>1.76</v>
       </c>
       <c r="U8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="V8" t="s">
         <v>45</v>
       </c>
       <c r="W8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="X8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y8">
-        <v>49.51</v>
+        <v>45.68</v>
       </c>
       <c r="Z8">
-        <v>-0.65</v>
+        <v>-0.67</v>
       </c>
       <c r="AA8">
         <v>-0.67</v>
       </c>
       <c r="AB8">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AC8">
-        <v>80.43000000000001</v>
+        <v>83.98999999999999</v>
       </c>
       <c r="AD8">
-        <v>62.62</v>
+        <v>76.11</v>
       </c>
       <c r="AE8">
-        <v>3.81</v>
+        <v>3.74</v>
       </c>
       <c r="AF8">
-        <v>-46.01</v>
+        <v>-63.86</v>
       </c>
       <c r="AG8">
-        <v>144.01</v>
+        <v>143.37</v>
       </c>
       <c r="AH8">
-        <v>131.52</v>
+        <v>131.54</v>
       </c>
       <c r="AI8">
         <v>131.91</v>
@@ -1704,7 +1739,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>21.15</v>
+        <v>22.06</v>
       </c>
     </row>
   </sheetData>
@@ -1845,7 +1880,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1885,7 +1920,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>55</v>
@@ -1903,1022 +1938,1065 @@
         <v>59</v>
       </c>
     </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="A5" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="B9" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>4.18</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C10" s="7">
         <v>5.29</v>
       </c>
-      <c r="E7" s="7">
-        <v>1.11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="D10" s="7">
+        <v>4.26</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-1.03</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-11.27</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C11" s="7">
         <v>-9.550000000000001</v>
       </c>
-      <c r="E8" s="7">
-        <v>1.72</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="D11" s="7">
+        <v>-9.9</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>1.06</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C12" s="7">
         <v>-2.43</v>
       </c>
-      <c r="E9" s="8">
+      <c r="D12" s="7">
         <v>-3.49</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="E12" s="8">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>4.85</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C13" s="7">
         <v>-0.4</v>
       </c>
-      <c r="E10" s="8">
-        <v>-5.25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="D13" s="7">
+        <v>-5.92</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-5.52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>3.37</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C14" s="7">
         <v>2.65</v>
       </c>
-      <c r="E11" s="8">
-        <v>-0.72</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="D14" s="7">
+        <v>-2.49</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-5.14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C15" s="7">
+        <v>-7.38</v>
+      </c>
+      <c r="D15" s="7">
+        <v>-8.59</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-1.21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-2.86</v>
+      </c>
+      <c r="D16" s="7">
+        <v>-5.27</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-2.41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="7">
+        <v>2.8</v>
+      </c>
+      <c r="D17" s="7">
+        <v>3.64</v>
+      </c>
+      <c r="E17" s="9">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="7">
+        <v>2.34</v>
+      </c>
+      <c r="D18" s="7">
+        <v>3.71</v>
+      </c>
+      <c r="E18" s="9">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>-5.76</v>
+      </c>
+      <c r="D19" s="7">
+        <v>-2.54</v>
+      </c>
+      <c r="E19" s="9">
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7">
+        <v>0.96</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-1.6</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-2.56</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7">
+        <v>4.71</v>
+      </c>
+      <c r="D21" s="7">
+        <v>0.18</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-4.53</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="7">
+        <v>-1.86</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-3.08</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-1.22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="7">
+        <v>1.25</v>
+      </c>
+      <c r="D23" s="7">
+        <v>0.68</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="7">
+        <v>41.53</v>
+      </c>
+      <c r="D24" s="7">
+        <v>44.25</v>
+      </c>
+      <c r="E24" s="9">
+        <v>2.72</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="7">
+        <v>106.55</v>
+      </c>
+      <c r="D25" s="7">
+        <v>101.39</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-5.16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="7">
+        <v>-43.42</v>
+      </c>
+      <c r="D26" s="7">
+        <v>-43.15</v>
+      </c>
+      <c r="E26" s="9">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="7">
+        <v>5.03</v>
+      </c>
+      <c r="D27" s="7">
+        <v>2.84</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-2.19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="7">
+        <v>-9.970000000000001</v>
+      </c>
+      <c r="D28" s="7">
+        <v>-12.34</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-2.37</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="7">
+        <v>20.63</v>
+      </c>
+      <c r="D29" s="7">
+        <v>20.19</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="7">
+        <v>5.42</v>
+      </c>
+      <c r="D30" s="7">
+        <v>5.61</v>
+      </c>
+      <c r="E30" s="9">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="7">
+        <v>17.98</v>
+      </c>
+      <c r="D31" s="7">
+        <v>20.49</v>
+      </c>
+      <c r="E31" s="9">
         <v>2.51</v>
       </c>
-      <c r="D12" s="6">
-        <v>-7.38</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-9.890000000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="7">
+        <v>-17.07</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-15.03</v>
+      </c>
+      <c r="E32" s="9">
+        <v>2.04</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="7">
+        <v>3.8</v>
+      </c>
+      <c r="D33" s="7">
+        <v>5.54</v>
+      </c>
+      <c r="E33" s="9">
+        <v>1.74</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="7">
+        <v>16.06</v>
+      </c>
+      <c r="D34" s="7">
+        <v>13.7</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-2.36</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="7">
+        <v>13.71</v>
+      </c>
+      <c r="D35" s="7">
+        <v>10.99</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-2.72</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="7">
+        <v>19.84</v>
+      </c>
+      <c r="D36" s="7">
+        <v>20.2</v>
+      </c>
+      <c r="E36" s="9">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-1.89</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-2.86</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-0.97</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="7">
+        <v>-2.42</v>
+      </c>
+      <c r="D37" s="7">
+        <v>-2.59</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="7">
+        <v>-29.27</v>
+      </c>
+      <c r="D38" s="7">
+        <v>-29.59</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="7">
+        <v>-46.3</v>
+      </c>
+      <c r="D39" s="7">
+        <v>-46.13</v>
+      </c>
+      <c r="E39" s="9">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="7">
+        <v>-7.15</v>
+      </c>
+      <c r="D40" s="7">
+        <v>-9.4</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-2.25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="7">
+        <v>-14.36</v>
+      </c>
+      <c r="D41" s="7">
+        <v>-16.81</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-2.45</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="7">
+        <v>-8.779999999999999</v>
+      </c>
+      <c r="D42" s="7">
+        <v>-9.050000000000001</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-0.27</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="7">
+        <v>-7.77</v>
+      </c>
+      <c r="D43" s="7">
+        <v>-8.67</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="6">
-        <v>1.79</v>
-      </c>
-      <c r="D14" s="6">
-        <v>2.8</v>
-      </c>
-      <c r="E14" s="7">
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B44" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="7">
+        <v>12130</v>
+      </c>
+      <c r="D44" s="7">
+        <v>12361</v>
+      </c>
+      <c r="E44" s="9">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-0.19</v>
-      </c>
-      <c r="D15" s="6">
-        <v>2.34</v>
-      </c>
-      <c r="E15" s="7">
-        <v>2.53</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B45" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="7">
+        <v>474.05</v>
+      </c>
+      <c r="D45" s="7">
+        <v>471.95</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-2.1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-5.37</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-5.76</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-0.39</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B46" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="7">
+        <v>324.8</v>
+      </c>
+      <c r="D46" s="7">
+        <v>325.85</v>
+      </c>
+      <c r="E46" s="9">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-1.5</v>
-      </c>
-      <c r="D17" s="6">
-        <v>0.96</v>
-      </c>
-      <c r="E17" s="7">
-        <v>2.46</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B47" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="7">
+        <v>2021</v>
+      </c>
+      <c r="D47" s="7">
+        <v>1972</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-49</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>0.18</v>
-      </c>
-      <c r="D18" s="6">
-        <v>4.71</v>
-      </c>
-      <c r="E18" s="7">
-        <v>4.53</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B48" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="7">
+        <v>11644</v>
+      </c>
+      <c r="D48" s="7">
+        <v>11310</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-334</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-1.38</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-1.86</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-0.48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B49" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="7">
+        <v>1057</v>
+      </c>
+      <c r="D49" s="7">
+        <v>1053.9</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-3.1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>0.04</v>
-      </c>
-      <c r="D20" s="6">
-        <v>1.25</v>
-      </c>
-      <c r="E20" s="7">
-        <v>1.21</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B50" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="7">
+        <v>137.38</v>
+      </c>
+      <c r="D50" s="7">
+        <v>136.03</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-1.35</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51" s="7">
+        <v>43</v>
+      </c>
+      <c r="D51" s="7">
+        <v>29</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52" s="7">
+        <v>29</v>
+      </c>
+      <c r="D52" s="7">
+        <v>43</v>
+      </c>
+      <c r="E52" s="9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>38.02</v>
-      </c>
-      <c r="D21" s="6">
-        <v>41.53</v>
-      </c>
-      <c r="E21" s="7">
-        <v>3.51</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B53" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="7">
+        <v>69.08</v>
+      </c>
+      <c r="D53" s="7">
+        <v>73.14</v>
+      </c>
+      <c r="E53" s="9">
+        <v>4.06</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="6">
-        <v>108.88</v>
-      </c>
-      <c r="D22" s="6">
-        <v>106.55</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-2.33</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B54" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="7">
+        <v>40.12</v>
+      </c>
+      <c r="D54" s="7">
+        <v>39.59</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-43.58</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-43.42</v>
-      </c>
-      <c r="E23" s="7">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B55" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="7">
+        <v>37.01</v>
+      </c>
+      <c r="D55" s="7">
+        <v>37.91</v>
+      </c>
+      <c r="E55" s="9">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6">
-        <v>1.95</v>
-      </c>
-      <c r="D24" s="6">
-        <v>5.03</v>
-      </c>
-      <c r="E24" s="7">
-        <v>3.08</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B56" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="7">
+        <v>57.6</v>
+      </c>
+      <c r="D56" s="7">
+        <v>46.54</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-11.06</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-14.09</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-9.970000000000001</v>
-      </c>
-      <c r="E25" s="7">
-        <v>4.12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B57" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="7">
+        <v>61.1</v>
+      </c>
+      <c r="D57" s="7">
+        <v>51.23</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-9.869999999999999</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>19.88</v>
-      </c>
-      <c r="D26" s="6">
-        <v>20.63</v>
-      </c>
-      <c r="E26" s="7">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B58" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="7">
+        <v>43.42</v>
+      </c>
+      <c r="D58" s="7">
+        <v>42.58</v>
+      </c>
+      <c r="E58" s="8">
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>2.92</v>
-      </c>
-      <c r="D27" s="6">
-        <v>5.42</v>
-      </c>
-      <c r="E27" s="7">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B59" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="7">
+        <v>49.51</v>
+      </c>
+      <c r="D59" s="7">
+        <v>45.68</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-3.83</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="6">
-        <v>14.78</v>
-      </c>
-      <c r="D28" s="6">
-        <v>17.98</v>
-      </c>
-      <c r="E28" s="7">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B60" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="7">
+        <v>56.3</v>
+      </c>
+      <c r="D60" s="7">
+        <v>111.41</v>
+      </c>
+      <c r="E60" s="9">
+        <v>55.11</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-14.6</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-17.07</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-2.47</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B61" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="7">
+        <v>18.04</v>
+      </c>
+      <c r="D61" s="7">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="E61" s="9">
+        <v>58.06</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="6">
-        <v>5.53</v>
-      </c>
-      <c r="D30" s="6">
-        <v>3.8</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-1.73</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="B62" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="7">
+        <v>-87.65000000000001</v>
+      </c>
+      <c r="D62" s="7">
+        <v>-86.58</v>
+      </c>
+      <c r="E62" s="9">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="6">
-        <v>13.82</v>
-      </c>
-      <c r="D31" s="6">
-        <v>16.06</v>
-      </c>
-      <c r="E31" s="7">
-        <v>2.24</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="B63" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="7">
+        <v>-40.75</v>
+      </c>
+      <c r="D63" s="7">
+        <v>-26.99</v>
+      </c>
+      <c r="E63" s="9">
+        <v>13.76</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="6">
-        <v>10.42</v>
-      </c>
-      <c r="D32" s="6">
-        <v>13.71</v>
-      </c>
-      <c r="E32" s="7">
-        <v>3.29</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="B64" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="7">
+        <v>15.65</v>
+      </c>
+      <c r="D64" s="7">
+        <v>6.45</v>
+      </c>
+      <c r="E64" s="8">
+        <v>-9.199999999999999</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="6">
-        <v>21.47</v>
-      </c>
-      <c r="D33" s="6">
-        <v>19.84</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-1.63</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="B65" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="7">
+        <v>-6.46</v>
+      </c>
+      <c r="D65" s="7">
+        <v>-18.07</v>
+      </c>
+      <c r="E65" s="8">
+        <v>-11.61</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-1.08</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-2.42</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-1.34</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-0.14</v>
-      </c>
-      <c r="D35" s="6">
-        <v>0</v>
-      </c>
-      <c r="E35" s="7">
-        <v>0.14</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-28.77</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-29.27</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-44.99</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-46.3</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-1.31</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-8.02</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-7.15</v>
-      </c>
-      <c r="E38" s="7">
-        <v>0.87</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-16.59</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-14.36</v>
-      </c>
-      <c r="E39" s="7">
-        <v>2.23</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-6.81</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-8.779999999999999</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-1.97</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-7.84</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-7.77</v>
-      </c>
-      <c r="E41" s="7">
-        <v>0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="6">
-        <v>11910</v>
-      </c>
-      <c r="D42" s="6">
-        <v>12130</v>
-      </c>
-      <c r="E42" s="7">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="6">
-        <v>477.45</v>
-      </c>
-      <c r="D43" s="6">
-        <v>474.05</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-3.4</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="6">
-        <v>332.75</v>
-      </c>
-      <c r="D44" s="6">
-        <v>324.8</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-7.95</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="6">
-        <v>2002</v>
-      </c>
-      <c r="D45" s="6">
-        <v>2021</v>
-      </c>
-      <c r="E45" s="7">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="6">
-        <v>11340</v>
-      </c>
-      <c r="D46" s="6">
-        <v>11644</v>
-      </c>
-      <c r="E46" s="7">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="6">
-        <v>1079.9</v>
-      </c>
-      <c r="D47" s="6">
-        <v>1057</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-22.9</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="6">
-        <v>137.27</v>
-      </c>
-      <c r="D48" s="6">
-        <v>137.38</v>
-      </c>
-      <c r="E48" s="7">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C49" s="6">
-        <v>29</v>
-      </c>
-      <c r="D49" s="6">
-        <v>43</v>
-      </c>
-      <c r="E49" s="7">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C50" s="6">
-        <v>43</v>
-      </c>
-      <c r="D50" s="6">
-        <v>29</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="6">
-        <v>64.31999999999999</v>
-      </c>
-      <c r="D51" s="6">
-        <v>69.08</v>
-      </c>
-      <c r="E51" s="7">
-        <v>4.76</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="6">
-        <v>40.95</v>
-      </c>
-      <c r="D52" s="6">
-        <v>40.12</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-0.83</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="6">
-        <v>41.21</v>
-      </c>
-      <c r="D53" s="6">
-        <v>37.01</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-4.2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="6">
-        <v>53.63</v>
-      </c>
-      <c r="D54" s="6">
-        <v>57.6</v>
-      </c>
-      <c r="E54" s="7">
-        <v>3.97</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="6">
-        <v>53.53</v>
-      </c>
-      <c r="D55" s="6">
-        <v>61.1</v>
-      </c>
-      <c r="E55" s="7">
-        <v>7.57</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="6">
-        <v>50.28</v>
-      </c>
-      <c r="D56" s="6">
-        <v>43.42</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-6.86</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="6">
-        <v>49.19</v>
-      </c>
-      <c r="D57" s="6">
-        <v>49.51</v>
-      </c>
-      <c r="E57" s="7">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B58" s="5" t="s">
+      <c r="B66" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C58" s="6">
-        <v>14.69</v>
-      </c>
-      <c r="D58" s="6">
-        <v>56.3</v>
-      </c>
-      <c r="E58" s="7">
-        <v>41.61</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C59" s="6">
-        <v>117.37</v>
-      </c>
-      <c r="D59" s="6">
-        <v>18.04</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-99.33</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="6">
-        <v>-85.98999999999999</v>
-      </c>
-      <c r="D60" s="6">
-        <v>-87.65000000000001</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-1.66</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="6">
-        <v>-62.26</v>
-      </c>
-      <c r="D61" s="6">
-        <v>-40.75</v>
-      </c>
-      <c r="E61" s="7">
-        <v>21.51</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="6">
-        <v>-27.6</v>
-      </c>
-      <c r="D62" s="6">
-        <v>15.65</v>
-      </c>
-      <c r="E62" s="7">
-        <v>43.25</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="6">
-        <v>-41.14</v>
-      </c>
-      <c r="D63" s="6">
-        <v>-6.46</v>
-      </c>
-      <c r="E63" s="7">
-        <v>34.68</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="6">
-        <v>-74.95</v>
-      </c>
-      <c r="D64" s="6">
+      <c r="C66" s="7">
         <v>-46.01</v>
       </c>
-      <c r="E64" s="7">
-        <v>28.94</v>
+      <c r="D66" s="7">
+        <v>-63.86</v>
+      </c>
+      <c r="E66" s="8">
+        <v>-17.85</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2938,61 +3016,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>72</v>
       </c>
+      <c r="C1" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="12">
         <v>68.8</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="13">
         <v>7</v>
       </c>
-      <c r="D2" s="11">
-        <v>51.1</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="12">
+        <v>48.1</v>
+      </c>
+      <c r="E2" s="12">
         <v>90</v>
       </c>
-      <c r="F2" s="11">
-        <v>-2.1</v>
-      </c>
-      <c r="G2" s="11">
-        <v>7.4</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="12">
+        <v>-4.5</v>
+      </c>
+      <c r="G2" s="12">
+        <v>7.6</v>
+      </c>
+      <c r="H2" s="12">
         <v>57</v>
       </c>
-      <c r="I2" s="11">
-        <v>70</v>
+      <c r="I2" s="12">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -3093,49 +3171,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="14" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="14">
-        <v>0.2954</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.235</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.1598</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.07440000000000001</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.0338</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.0023</v>
-      </c>
-      <c r="G2" s="14">
-        <v>-0.2203</v>
+      <c r="A2" s="15">
+        <v>0.2982</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.2289</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.1586</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.07389999999999999</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.0332</v>
+      </c>
+      <c r="F2" s="15">
+        <v>0.0015</v>
+      </c>
+      <c r="G2" s="15">
+        <v>-0.2157</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="82">
   <si>
     <t>Symbol</t>
   </si>
@@ -187,40 +187,46 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Overbought Entry</t>
-  </si>
-  <si>
-    <t>69.1 → 73.1</t>
-  </si>
-  <si>
-    <t>⚠️ CAUTION</t>
-  </si>
-  <si>
-    <t>69.1</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>46.5 → 50.3</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>46.5</t>
+  </si>
+  <si>
+    <t>50.3</t>
+  </si>
+  <si>
+    <t>RSI Overbought Exit</t>
+  </si>
+  <si>
+    <t>73.1 → 64.1</t>
+  </si>
+  <si>
+    <t>🔵 COOLING</t>
   </si>
   <si>
     <t>73.1</t>
   </si>
   <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>57.6 → 46.5</t>
+    <t>64.1</t>
+  </si>
+  <si>
+    <t>51.2 → 46.2</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
   </si>
   <si>
-    <t>57.6</t>
-  </si>
-  <si>
-    <t>46.5</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
+    <t>51.2</t>
+  </si>
+  <si>
+    <t>46.2</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -306,7 +312,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F4E79"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -314,13 +327,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -353,19 +359,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -435,7 +441,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -444,9 +450,10 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -819,7 +826,8 @@
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
     <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="19" width="10.7109375" customWidth="1"/>
+    <col min="17" max="18" width="10.7109375" customWidth="1"/>
+    <col min="19" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -959,10 +967,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>12361</v>
+        <v>12130</v>
       </c>
       <c r="D2">
-        <v>1.9</v>
+        <v>-1.87</v>
       </c>
       <c r="E2">
         <v>12361</v>
@@ -971,46 +979,46 @@
         <v>8506.780000000001</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>-1.87</v>
       </c>
       <c r="H2">
-        <v>45.31</v>
+        <v>42.59</v>
       </c>
       <c r="I2">
-        <v>3.64</v>
+        <v>3.46</v>
       </c>
       <c r="J2">
-        <v>4.26</v>
+        <v>4.57</v>
       </c>
       <c r="K2">
-        <v>20.49</v>
+        <v>17.06</v>
       </c>
       <c r="L2">
-        <v>44.25</v>
+        <v>42.51</v>
       </c>
       <c r="M2">
-        <v>29.82</v>
+        <v>29.59</v>
       </c>
       <c r="N2">
         <v>85</v>
       </c>
       <c r="O2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P2">
-        <v>11969</v>
+        <v>12050.2</v>
       </c>
       <c r="Q2">
-        <v>11777.7</v>
+        <v>11794.2</v>
       </c>
       <c r="R2">
-        <v>11018.2</v>
+        <v>11060.3</v>
       </c>
       <c r="S2">
-        <v>9871.459999999999</v>
+        <v>9888.51</v>
       </c>
       <c r="T2">
-        <v>25.22</v>
+        <v>22.67</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -1025,34 +1033,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>73.14</v>
+        <v>64.08</v>
       </c>
       <c r="Z2">
-        <v>264.2</v>
+        <v>263.98</v>
       </c>
       <c r="AA2">
-        <v>257.05</v>
+        <v>258.44</v>
       </c>
       <c r="AB2">
-        <v>7.14</v>
+        <v>5.54</v>
       </c>
       <c r="AC2">
-        <v>85.16</v>
+        <v>78.22</v>
       </c>
       <c r="AD2">
-        <v>51.83</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="AE2">
-        <v>218.83</v>
+        <v>234.34</v>
       </c>
       <c r="AF2">
-        <v>111.41</v>
+        <v>36.56</v>
       </c>
       <c r="AG2">
-        <v>12147.11</v>
+        <v>12195.87</v>
       </c>
       <c r="AH2">
-        <v>11408.29</v>
+        <v>11392.53</v>
       </c>
       <c r="AI2">
         <v>11623.52</v>
@@ -1061,7 +1069,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>50.18</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1072,10 +1080,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>471.95</v>
+        <v>484.55</v>
       </c>
       <c r="D3">
-        <v>-0.44</v>
+        <v>2.67</v>
       </c>
       <c r="E3">
         <v>670.25</v>
@@ -1084,46 +1092,46 @@
         <v>222.01</v>
       </c>
       <c r="G3">
-        <v>-29.59</v>
+        <v>-27.71</v>
       </c>
       <c r="H3">
-        <v>112.58</v>
+        <v>118.26</v>
       </c>
       <c r="I3">
-        <v>3.71</v>
+        <v>4.54</v>
       </c>
       <c r="J3">
-        <v>-9.9</v>
+        <v>-10.96</v>
       </c>
       <c r="K3">
-        <v>-15.03</v>
+        <v>-13.29</v>
       </c>
       <c r="L3">
-        <v>101.39</v>
+        <v>106.7</v>
       </c>
       <c r="M3">
-        <v>15.86</v>
+        <v>16.13</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P3">
-        <v>467.51</v>
+        <v>471.72</v>
       </c>
       <c r="Q3">
-        <v>497.11</v>
+        <v>494.82</v>
       </c>
       <c r="R3">
-        <v>544.71</v>
+        <v>542.77</v>
       </c>
       <c r="S3">
-        <v>426.97</v>
+        <v>428.04</v>
       </c>
       <c r="T3">
-        <v>10.53</v>
+        <v>13.2</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1138,34 +1146,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>39.59</v>
+        <v>44.34</v>
       </c>
       <c r="Z3">
-        <v>-22.19</v>
+        <v>-20.12</v>
       </c>
       <c r="AA3">
-        <v>-22.24</v>
+        <v>-21.81</v>
       </c>
       <c r="AB3">
-        <v>0.05</v>
+        <v>1.69</v>
       </c>
       <c r="AC3">
-        <v>72.78</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="AD3">
-        <v>50.72</v>
+        <v>67.81</v>
       </c>
       <c r="AE3">
-        <v>21.57</v>
+        <v>22.34</v>
       </c>
       <c r="AF3">
-        <v>76.09999999999999</v>
+        <v>242.05</v>
       </c>
       <c r="AG3">
-        <v>561.5</v>
+        <v>557.46</v>
       </c>
       <c r="AH3">
-        <v>432.72</v>
+        <v>432.17</v>
       </c>
       <c r="AI3">
         <v>521.85</v>
@@ -1174,7 +1182,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>34.24</v>
+        <v>30.66</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1185,10 +1193,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>325.85</v>
+        <v>323.6</v>
       </c>
       <c r="D4">
-        <v>0.32</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="E4">
         <v>604.85</v>
@@ -1197,46 +1205,46 @@
         <v>303.75</v>
       </c>
       <c r="G4">
-        <v>-46.13</v>
+        <v>-46.5</v>
       </c>
       <c r="H4">
-        <v>7.28</v>
+        <v>6.53</v>
       </c>
       <c r="I4">
-        <v>-2.54</v>
+        <v>-4.99</v>
       </c>
       <c r="J4">
-        <v>-3.49</v>
+        <v>-7.46</v>
       </c>
       <c r="K4">
-        <v>5.54</v>
+        <v>6.53</v>
       </c>
       <c r="L4">
-        <v>-43.15</v>
+        <v>-43.13</v>
       </c>
       <c r="M4">
-        <v>-21.57</v>
+        <v>-21.69</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
       <c r="O4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P4">
-        <v>331.76</v>
+        <v>328.36</v>
       </c>
       <c r="Q4">
-        <v>351.17</v>
+        <v>349.95</v>
       </c>
       <c r="R4">
         <v>337.94</v>
       </c>
       <c r="S4">
-        <v>384.89</v>
+        <v>383.97</v>
       </c>
       <c r="T4">
-        <v>-15.34</v>
+        <v>-15.72</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1251,43 +1259,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>37.91</v>
+        <v>36.7</v>
       </c>
       <c r="Z4">
-        <v>-3.23</v>
+        <v>-4.23</v>
       </c>
       <c r="AA4">
-        <v>1.09</v>
+        <v>0.02</v>
       </c>
       <c r="AB4">
-        <v>-4.32</v>
+        <v>-4.26</v>
       </c>
       <c r="AC4">
-        <v>1.55</v>
+        <v>1.29</v>
       </c>
       <c r="AD4">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="AE4">
-        <v>11.59</v>
+        <v>11.25</v>
       </c>
       <c r="AF4">
-        <v>-86.58</v>
+        <v>-89.34</v>
       </c>
       <c r="AG4">
-        <v>381.88</v>
+        <v>383.03</v>
       </c>
       <c r="AH4">
-        <v>320.47</v>
+        <v>316.86</v>
       </c>
       <c r="AI4">
-        <v>361.57</v>
+        <v>357.31</v>
       </c>
       <c r="AJ4" t="s">
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>38.1</v>
+        <v>39.95</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1298,10 +1306,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1972</v>
+        <v>1990</v>
       </c>
       <c r="D5">
-        <v>-2.42</v>
+        <v>0.91</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1310,46 +1318,46 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-9.4</v>
+        <v>-8.57</v>
       </c>
       <c r="H5">
-        <v>20.85</v>
+        <v>21.95</v>
       </c>
       <c r="I5">
-        <v>-1.6</v>
+        <v>-1</v>
       </c>
       <c r="J5">
-        <v>-5.92</v>
+        <v>-5.46</v>
       </c>
       <c r="K5">
-        <v>13.7</v>
+        <v>16.39</v>
       </c>
       <c r="L5">
-        <v>2.84</v>
+        <v>4</v>
       </c>
       <c r="M5">
-        <v>3.32</v>
+        <v>3.61</v>
       </c>
       <c r="N5">
         <v>57</v>
       </c>
       <c r="O5">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="P5">
-        <v>2003.2</v>
+        <v>1999.2</v>
       </c>
       <c r="Q5">
-        <v>2019.32</v>
+        <v>2014.52</v>
       </c>
       <c r="R5">
-        <v>1936.71</v>
+        <v>1941.21</v>
       </c>
       <c r="S5">
-        <v>1906.66</v>
+        <v>1906.28</v>
       </c>
       <c r="T5">
-        <v>3.43</v>
+        <v>4.39</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1364,34 +1372,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>46.54</v>
+        <v>50.31</v>
       </c>
       <c r="Z5">
-        <v>15.35</v>
+        <v>12.97</v>
       </c>
       <c r="AA5">
-        <v>25.44</v>
+        <v>22.94</v>
       </c>
       <c r="AB5">
-        <v>-10.09</v>
+        <v>-9.98</v>
       </c>
       <c r="AC5">
-        <v>17.62</v>
+        <v>26.24</v>
       </c>
       <c r="AD5">
-        <v>18.99</v>
+        <v>23.01</v>
       </c>
       <c r="AE5">
-        <v>38.22</v>
+        <v>39.12</v>
       </c>
       <c r="AF5">
-        <v>-26.99</v>
+        <v>-25.53</v>
       </c>
       <c r="AG5">
-        <v>2071.78</v>
+        <v>2058.11</v>
       </c>
       <c r="AH5">
-        <v>1966.86</v>
+        <v>1970.93</v>
       </c>
       <c r="AI5">
         <v>1958.53</v>
@@ -1400,7 +1408,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>21.51</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1411,10 +1419,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>11310</v>
+        <v>11100</v>
       </c>
       <c r="D6">
-        <v>-2.87</v>
+        <v>-1.86</v>
       </c>
       <c r="E6">
         <v>13595.75</v>
@@ -1423,25 +1431,25 @@
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-16.81</v>
+        <v>-18.36</v>
       </c>
       <c r="H6">
-        <v>29.32</v>
+        <v>26.92</v>
       </c>
       <c r="I6">
-        <v>0.18</v>
+        <v>-3.81</v>
       </c>
       <c r="J6">
-        <v>-2.49</v>
+        <v>-3.27</v>
       </c>
       <c r="K6">
-        <v>10.99</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="L6">
-        <v>-12.34</v>
+        <v>-12.65</v>
       </c>
       <c r="M6">
-        <v>22.89</v>
+        <v>22.73</v>
       </c>
       <c r="N6">
         <v>29</v>
@@ -1450,19 +1458,19 @@
         <v>49</v>
       </c>
       <c r="P6">
-        <v>11446.6</v>
+        <v>11358.6</v>
       </c>
       <c r="Q6">
-        <v>11408.05</v>
+        <v>11388.25</v>
       </c>
       <c r="R6">
-        <v>11000.08</v>
+        <v>11009.78</v>
       </c>
       <c r="S6">
-        <v>10718.36</v>
+        <v>10711</v>
       </c>
       <c r="T6">
-        <v>5.52</v>
+        <v>3.63</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1477,34 +1485,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>51.23</v>
+        <v>46.17</v>
       </c>
       <c r="Z6">
-        <v>112.79</v>
+        <v>81.68000000000001</v>
       </c>
       <c r="AA6">
-        <v>139.11</v>
+        <v>127.63</v>
       </c>
       <c r="AB6">
-        <v>-26.32</v>
+        <v>-45.95</v>
       </c>
       <c r="AC6">
-        <v>39.06</v>
+        <v>29.5</v>
       </c>
       <c r="AD6">
-        <v>42.87</v>
+        <v>38</v>
       </c>
       <c r="AE6">
-        <v>255.4</v>
+        <v>255.09</v>
       </c>
       <c r="AF6">
-        <v>6.45</v>
+        <v>-22.54</v>
       </c>
       <c r="AG6">
-        <v>11666.86</v>
+        <v>11677.53</v>
       </c>
       <c r="AH6">
-        <v>11149.24</v>
+        <v>11098.97</v>
       </c>
       <c r="AI6">
         <v>10787.84</v>
@@ -1513,7 +1521,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>22.8</v>
+        <v>22.45</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1524,10 +1532,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>1053.9</v>
+        <v>1055.9</v>
       </c>
       <c r="D7">
-        <v>-0.29</v>
+        <v>0.19</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1536,46 +1544,46 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-9.050000000000001</v>
+        <v>-8.880000000000001</v>
       </c>
       <c r="H7">
-        <v>31.48</v>
+        <v>31.73</v>
       </c>
       <c r="I7">
-        <v>-3.08</v>
+        <v>-2.68</v>
       </c>
       <c r="J7">
-        <v>-8.59</v>
+        <v>-8.1</v>
       </c>
       <c r="K7">
-        <v>20.2</v>
+        <v>20.76</v>
       </c>
       <c r="L7">
-        <v>20.19</v>
+        <v>20.28</v>
       </c>
       <c r="M7">
-        <v>7.39</v>
+        <v>7.49</v>
       </c>
       <c r="N7">
         <v>71</v>
       </c>
       <c r="O7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P7">
-        <v>1071.76</v>
+        <v>1065.94</v>
       </c>
       <c r="Q7">
-        <v>1091.31</v>
+        <v>1086.16</v>
       </c>
       <c r="R7">
-        <v>1059.12</v>
+        <v>1060.99</v>
       </c>
       <c r="S7">
-        <v>976.3</v>
+        <v>976.48</v>
       </c>
       <c r="T7">
-        <v>7.95</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1590,43 +1598,43 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>42.58</v>
+        <v>43.35</v>
       </c>
       <c r="Z7">
-        <v>1.47</v>
+        <v>-0.41</v>
       </c>
       <c r="AA7">
-        <v>8.970000000000001</v>
+        <v>7.09</v>
       </c>
       <c r="AB7">
         <v>-7.5</v>
       </c>
       <c r="AC7">
-        <v>2.55</v>
+        <v>1.99</v>
       </c>
       <c r="AD7">
-        <v>10.04</v>
+        <v>4.55</v>
       </c>
       <c r="AE7">
-        <v>22.64</v>
+        <v>22.9</v>
       </c>
       <c r="AF7">
-        <v>-18.07</v>
+        <v>14.41</v>
       </c>
       <c r="AG7">
-        <v>1139.3</v>
+        <v>1124.85</v>
       </c>
       <c r="AH7">
-        <v>1043.31</v>
+        <v>1047.47</v>
       </c>
       <c r="AI7">
-        <v>1124.93</v>
+        <v>1116.59</v>
       </c>
       <c r="AJ7" t="s">
         <v>48</v>
       </c>
       <c r="AK7">
-        <v>25.45</v>
+        <v>28.62</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1637,10 +1645,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>136.03</v>
+        <v>134.18</v>
       </c>
       <c r="D8">
-        <v>-0.98</v>
+        <v>-1.36</v>
       </c>
       <c r="E8">
         <v>148.95</v>
@@ -1649,46 +1657,46 @@
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>-8.67</v>
+        <v>-9.92</v>
       </c>
       <c r="H8">
-        <v>17.31</v>
+        <v>15.71</v>
       </c>
       <c r="I8">
-        <v>0.68</v>
+        <v>-2.08</v>
       </c>
       <c r="J8">
-        <v>-5.27</v>
+        <v>-5.67</v>
       </c>
       <c r="K8">
-        <v>-2.59</v>
+        <v>-3.93</v>
       </c>
       <c r="L8">
-        <v>5.61</v>
+        <v>5.03</v>
       </c>
       <c r="M8">
-        <v>0.15</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="N8">
         <v>43</v>
       </c>
       <c r="O8">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="P8">
-        <v>136.79</v>
+        <v>136.22</v>
       </c>
       <c r="Q8">
-        <v>137.45</v>
+        <v>137.05</v>
       </c>
       <c r="R8">
-        <v>137.46</v>
+        <v>137.44</v>
       </c>
       <c r="S8">
-        <v>133.67</v>
+        <v>133.68</v>
       </c>
       <c r="T8">
-        <v>1.76</v>
+        <v>0.38</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1703,34 +1711,34 @@
         <v>2</v>
       </c>
       <c r="Y8">
-        <v>45.68</v>
+        <v>40.99</v>
       </c>
       <c r="Z8">
-        <v>-0.67</v>
+        <v>-0.82</v>
       </c>
       <c r="AA8">
-        <v>-0.67</v>
+        <v>-0.7</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="AC8">
-        <v>83.98999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="AD8">
-        <v>76.11</v>
+        <v>76.58</v>
       </c>
       <c r="AE8">
-        <v>3.74</v>
+        <v>3.64</v>
       </c>
       <c r="AF8">
-        <v>-63.86</v>
+        <v>-70.48</v>
       </c>
       <c r="AG8">
-        <v>143.37</v>
+        <v>142.7</v>
       </c>
       <c r="AH8">
-        <v>131.54</v>
+        <v>131.41</v>
       </c>
       <c r="AI8">
         <v>131.91</v>
@@ -1739,7 +1747,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>22.06</v>
+        <v>19.19</v>
       </c>
     </row>
   </sheetData>
@@ -1880,7 +1888,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1920,7 +1928,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>55</v>
@@ -1940,7 +1948,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>60</v>
@@ -1959,1044 +1967,1007 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="8">
+        <v>4.26</v>
+      </c>
+      <c r="D9" s="8">
+        <v>4.57</v>
+      </c>
+      <c r="E9" s="9">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="8">
+        <v>-9.9</v>
+      </c>
+      <c r="D10" s="8">
+        <v>-10.96</v>
+      </c>
+      <c r="E10" s="10">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="8">
+        <v>-3.49</v>
+      </c>
+      <c r="D11" s="8">
+        <v>-7.46</v>
+      </c>
+      <c r="E11" s="10">
+        <v>-3.97</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="8">
+        <v>-5.92</v>
+      </c>
+      <c r="D12" s="8">
+        <v>-5.46</v>
+      </c>
+      <c r="E12" s="9">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="8">
+        <v>-2.49</v>
+      </c>
+      <c r="D13" s="8">
+        <v>-3.27</v>
+      </c>
+      <c r="E13" s="10">
+        <v>-0.78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="8">
+        <v>-8.59</v>
+      </c>
+      <c r="D14" s="8">
+        <v>-8.1</v>
+      </c>
+      <c r="E14" s="9">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="5" t="s">
+      <c r="B15" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="8">
+        <v>-5.27</v>
+      </c>
+      <c r="D15" s="8">
+        <v>-5.67</v>
+      </c>
+      <c r="E15" s="10">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="8">
+        <v>3.64</v>
+      </c>
+      <c r="D16" s="8">
+        <v>3.46</v>
+      </c>
+      <c r="E16" s="10">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="8">
+        <v>3.71</v>
+      </c>
+      <c r="D17" s="8">
+        <v>4.54</v>
+      </c>
+      <c r="E17" s="9">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="8">
+        <v>-2.54</v>
+      </c>
+      <c r="D18" s="8">
+        <v>-4.99</v>
+      </c>
+      <c r="E18" s="10">
+        <v>-2.45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="8">
+        <v>-1.6</v>
+      </c>
+      <c r="D19" s="8">
+        <v>-1</v>
+      </c>
+      <c r="E19" s="9">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="8">
+        <v>0.18</v>
+      </c>
+      <c r="D20" s="8">
+        <v>-3.81</v>
+      </c>
+      <c r="E20" s="10">
+        <v>-3.99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="8">
+        <v>-3.08</v>
+      </c>
+      <c r="D21" s="8">
+        <v>-2.68</v>
+      </c>
+      <c r="E21" s="9">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="B22" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="8">
+        <v>0.68</v>
+      </c>
+      <c r="D22" s="8">
+        <v>-2.08</v>
+      </c>
+      <c r="E22" s="10">
+        <v>-2.76</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="8">
+        <v>44.25</v>
+      </c>
+      <c r="D23" s="8">
+        <v>42.51</v>
+      </c>
+      <c r="E23" s="10">
+        <v>-1.74</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="8">
+        <v>101.39</v>
+      </c>
+      <c r="D24" s="8">
+        <v>106.7</v>
+      </c>
+      <c r="E24" s="9">
+        <v>5.31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="8">
+        <v>-43.15</v>
+      </c>
+      <c r="D25" s="8">
+        <v>-43.13</v>
+      </c>
+      <c r="E25" s="9">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="8">
+        <v>2.84</v>
+      </c>
+      <c r="D26" s="8">
+        <v>4</v>
+      </c>
+      <c r="E26" s="9">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="8">
+        <v>-12.34</v>
+      </c>
+      <c r="D27" s="8">
+        <v>-12.65</v>
+      </c>
+      <c r="E27" s="10">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="8">
+        <v>20.19</v>
+      </c>
+      <c r="D28" s="8">
+        <v>20.28</v>
+      </c>
+      <c r="E28" s="9">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="8">
+        <v>5.61</v>
+      </c>
+      <c r="D29" s="8">
+        <v>5.03</v>
+      </c>
+      <c r="E29" s="10">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="8">
+        <v>20.49</v>
+      </c>
+      <c r="D30" s="8">
+        <v>17.06</v>
+      </c>
+      <c r="E30" s="10">
+        <v>-3.43</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="8">
+        <v>-15.03</v>
+      </c>
+      <c r="D31" s="8">
+        <v>-13.29</v>
+      </c>
+      <c r="E31" s="9">
+        <v>1.74</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="8">
+        <v>5.54</v>
+      </c>
+      <c r="D32" s="8">
+        <v>6.53</v>
+      </c>
+      <c r="E32" s="9">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="8">
+        <v>13.7</v>
+      </c>
+      <c r="D33" s="8">
+        <v>16.39</v>
+      </c>
+      <c r="E33" s="9">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="8">
+        <v>10.99</v>
+      </c>
+      <c r="D34" s="8">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="E34" s="10">
+        <v>-1.38</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="8">
+        <v>20.2</v>
+      </c>
+      <c r="D35" s="8">
+        <v>20.76</v>
+      </c>
+      <c r="E35" s="9">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="8">
+        <v>-2.59</v>
+      </c>
+      <c r="D36" s="8">
+        <v>-3.93</v>
+      </c>
+      <c r="E36" s="10">
+        <v>-1.34</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="8">
         <v>0</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="D37" s="8">
+        <v>-1.87</v>
+      </c>
+      <c r="E37" s="10">
+        <v>-1.87</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="8">
+        <v>-29.59</v>
+      </c>
+      <c r="D38" s="8">
+        <v>-27.71</v>
+      </c>
+      <c r="E38" s="9">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="8">
+        <v>-46.13</v>
+      </c>
+      <c r="D39" s="8">
+        <v>-46.5</v>
+      </c>
+      <c r="E39" s="10">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="8">
+        <v>-9.4</v>
+      </c>
+      <c r="D40" s="8">
+        <v>-8.57</v>
+      </c>
+      <c r="E40" s="9">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="8">
+        <v>-16.81</v>
+      </c>
+      <c r="D41" s="8">
+        <v>-18.36</v>
+      </c>
+      <c r="E41" s="10">
+        <v>-1.55</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="8">
+        <v>-9.050000000000001</v>
+      </c>
+      <c r="D42" s="8">
+        <v>-8.880000000000001</v>
+      </c>
+      <c r="E42" s="9">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="8">
+        <v>-8.67</v>
+      </c>
+      <c r="D43" s="8">
+        <v>-9.92</v>
+      </c>
+      <c r="E43" s="10">
+        <v>-1.25</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>5.29</v>
-      </c>
-      <c r="D10" s="7">
-        <v>4.26</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-1.03</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B44" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="8">
+        <v>12361</v>
+      </c>
+      <c r="D44" s="8">
+        <v>12130</v>
+      </c>
+      <c r="E44" s="10">
+        <v>-231</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>-9.550000000000001</v>
-      </c>
-      <c r="D11" s="7">
-        <v>-9.9</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-0.35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B45" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="8">
+        <v>471.95</v>
+      </c>
+      <c r="D45" s="8">
+        <v>484.55</v>
+      </c>
+      <c r="E45" s="9">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>-2.43</v>
-      </c>
-      <c r="D12" s="7">
-        <v>-3.49</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-1.06</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B46" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="8">
+        <v>325.85</v>
+      </c>
+      <c r="D46" s="8">
+        <v>323.6</v>
+      </c>
+      <c r="E46" s="10">
+        <v>-2.25</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>-0.4</v>
-      </c>
-      <c r="D13" s="7">
-        <v>-5.92</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-5.52</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B47" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="8">
+        <v>1972</v>
+      </c>
+      <c r="D47" s="8">
+        <v>1990</v>
+      </c>
+      <c r="E47" s="9">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>2.65</v>
-      </c>
-      <c r="D14" s="7">
-        <v>-2.49</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-5.14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B48" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="8">
+        <v>11310</v>
+      </c>
+      <c r="D48" s="8">
+        <v>11100</v>
+      </c>
+      <c r="E48" s="10">
+        <v>-210</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="7">
-        <v>-7.38</v>
-      </c>
-      <c r="D15" s="7">
-        <v>-8.59</v>
-      </c>
-      <c r="E15" s="8">
+      <c r="B49" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="8">
+        <v>1053.9</v>
+      </c>
+      <c r="D49" s="8">
+        <v>1055.9</v>
+      </c>
+      <c r="E49" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="8">
+        <v>136.03</v>
+      </c>
+      <c r="D50" s="8">
+        <v>134.18</v>
+      </c>
+      <c r="E50" s="10">
+        <v>-1.85</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="8">
+        <v>73.14</v>
+      </c>
+      <c r="D51" s="8">
+        <v>64.08</v>
+      </c>
+      <c r="E51" s="10">
+        <v>-9.06</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="8">
+        <v>39.59</v>
+      </c>
+      <c r="D52" s="8">
+        <v>44.34</v>
+      </c>
+      <c r="E52" s="9">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="8">
+        <v>37.91</v>
+      </c>
+      <c r="D53" s="8">
+        <v>36.7</v>
+      </c>
+      <c r="E53" s="10">
         <v>-1.21</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+    <row r="54" spans="1:5">
+      <c r="A54" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="8">
+        <v>46.54</v>
+      </c>
+      <c r="D54" s="8">
+        <v>50.31</v>
+      </c>
+      <c r="E54" s="9">
+        <v>3.77</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="8">
+        <v>51.23</v>
+      </c>
+      <c r="D55" s="8">
+        <v>46.17</v>
+      </c>
+      <c r="E55" s="10">
+        <v>-5.06</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="8">
+        <v>42.58</v>
+      </c>
+      <c r="D56" s="8">
+        <v>43.35</v>
+      </c>
+      <c r="E56" s="9">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-2.86</v>
-      </c>
-      <c r="D16" s="7">
-        <v>-5.27</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-2.41</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B57" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="8">
+        <v>45.68</v>
+      </c>
+      <c r="D57" s="8">
+        <v>40.99</v>
+      </c>
+      <c r="E57" s="10">
+        <v>-4.69</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <v>2.8</v>
-      </c>
-      <c r="D17" s="7">
-        <v>3.64</v>
-      </c>
-      <c r="E17" s="9">
-        <v>0.84</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B58" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="8">
+        <v>111.41</v>
+      </c>
+      <c r="D58" s="8">
+        <v>36.56</v>
+      </c>
+      <c r="E58" s="10">
+        <v>-74.84999999999999</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>2.34</v>
-      </c>
-      <c r="D18" s="7">
-        <v>3.71</v>
-      </c>
-      <c r="E18" s="9">
-        <v>1.37</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B59" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="8">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="D59" s="8">
+        <v>242.05</v>
+      </c>
+      <c r="E59" s="9">
+        <v>165.95</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>-5.76</v>
-      </c>
-      <c r="D19" s="7">
-        <v>-2.54</v>
-      </c>
-      <c r="E19" s="9">
-        <v>3.22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B60" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="8">
+        <v>-86.58</v>
+      </c>
+      <c r="D60" s="8">
+        <v>-89.34</v>
+      </c>
+      <c r="E60" s="10">
+        <v>-2.76</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>0.96</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-1.6</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-2.56</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B61" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="8">
+        <v>-26.99</v>
+      </c>
+      <c r="D61" s="8">
+        <v>-25.53</v>
+      </c>
+      <c r="E61" s="9">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>4.71</v>
-      </c>
-      <c r="D21" s="7">
-        <v>0.18</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-4.53</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B62" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="8">
+        <v>6.45</v>
+      </c>
+      <c r="D62" s="8">
+        <v>-22.54</v>
+      </c>
+      <c r="E62" s="10">
+        <v>-28.99</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="7">
-        <v>-1.86</v>
-      </c>
-      <c r="D22" s="7">
-        <v>-3.08</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-1.22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B63" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="8">
+        <v>-18.07</v>
+      </c>
+      <c r="D63" s="8">
+        <v>14.41</v>
+      </c>
+      <c r="E63" s="9">
+        <v>32.48</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="7">
-        <v>1.25</v>
-      </c>
-      <c r="D23" s="7">
-        <v>0.68</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-0.57</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="7">
-        <v>41.53</v>
-      </c>
-      <c r="D24" s="7">
-        <v>44.25</v>
-      </c>
-      <c r="E24" s="9">
-        <v>2.72</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="7">
-        <v>106.55</v>
-      </c>
-      <c r="D25" s="7">
-        <v>101.39</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-5.16</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="7">
-        <v>-43.42</v>
-      </c>
-      <c r="D26" s="7">
-        <v>-43.15</v>
-      </c>
-      <c r="E26" s="9">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="7">
-        <v>5.03</v>
-      </c>
-      <c r="D27" s="7">
-        <v>2.84</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-2.19</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7">
-        <v>-9.970000000000001</v>
-      </c>
-      <c r="D28" s="7">
-        <v>-12.34</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-2.37</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="7">
-        <v>20.63</v>
-      </c>
-      <c r="D29" s="7">
-        <v>20.19</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-0.44</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="7">
-        <v>5.42</v>
-      </c>
-      <c r="D30" s="7">
-        <v>5.61</v>
-      </c>
-      <c r="E30" s="9">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="7">
-        <v>17.98</v>
-      </c>
-      <c r="D31" s="7">
-        <v>20.49</v>
-      </c>
-      <c r="E31" s="9">
-        <v>2.51</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-17.07</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-15.03</v>
-      </c>
-      <c r="E32" s="9">
-        <v>2.04</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="7">
-        <v>3.8</v>
-      </c>
-      <c r="D33" s="7">
-        <v>5.54</v>
-      </c>
-      <c r="E33" s="9">
-        <v>1.74</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="7">
-        <v>16.06</v>
-      </c>
-      <c r="D34" s="7">
-        <v>13.7</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-2.36</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="7">
-        <v>13.71</v>
-      </c>
-      <c r="D35" s="7">
-        <v>10.99</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-2.72</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="7">
-        <v>19.84</v>
-      </c>
-      <c r="D36" s="7">
-        <v>20.2</v>
-      </c>
-      <c r="E36" s="9">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="7">
-        <v>-2.42</v>
-      </c>
-      <c r="D37" s="7">
-        <v>-2.59</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="7">
-        <v>-29.27</v>
-      </c>
-      <c r="D38" s="7">
-        <v>-29.59</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-0.32</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="7">
-        <v>-46.3</v>
-      </c>
-      <c r="D39" s="7">
-        <v>-46.13</v>
-      </c>
-      <c r="E39" s="9">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="7">
-        <v>-7.15</v>
-      </c>
-      <c r="D40" s="7">
-        <v>-9.4</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-2.25</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="7">
-        <v>-14.36</v>
-      </c>
-      <c r="D41" s="7">
-        <v>-16.81</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-2.45</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="7">
-        <v>-8.779999999999999</v>
-      </c>
-      <c r="D42" s="7">
-        <v>-9.050000000000001</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-0.27</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="7">
-        <v>-7.77</v>
-      </c>
-      <c r="D43" s="7">
-        <v>-8.67</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="7">
-        <v>12130</v>
-      </c>
-      <c r="D44" s="7">
-        <v>12361</v>
-      </c>
-      <c r="E44" s="9">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="7">
-        <v>474.05</v>
-      </c>
-      <c r="D45" s="7">
-        <v>471.95</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-2.1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="7">
-        <v>324.8</v>
-      </c>
-      <c r="D46" s="7">
-        <v>325.85</v>
-      </c>
-      <c r="E46" s="9">
-        <v>1.05</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="7">
-        <v>2021</v>
-      </c>
-      <c r="D47" s="7">
-        <v>1972</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-49</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="7">
-        <v>11644</v>
-      </c>
-      <c r="D48" s="7">
-        <v>11310</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-334</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="7">
-        <v>1057</v>
-      </c>
-      <c r="D49" s="7">
-        <v>1053.9</v>
-      </c>
-      <c r="E49" s="8">
-        <v>-3.1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="7">
-        <v>137.38</v>
-      </c>
-      <c r="D50" s="7">
-        <v>136.03</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-1.35</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C51" s="7">
-        <v>43</v>
-      </c>
-      <c r="D51" s="7">
-        <v>29</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C52" s="7">
-        <v>29</v>
-      </c>
-      <c r="D52" s="7">
-        <v>43</v>
-      </c>
-      <c r="E52" s="9">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="7">
-        <v>69.08</v>
-      </c>
-      <c r="D53" s="7">
-        <v>73.14</v>
-      </c>
-      <c r="E53" s="9">
-        <v>4.06</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="7">
-        <v>40.12</v>
-      </c>
-      <c r="D54" s="7">
-        <v>39.59</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-0.53</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="7">
-        <v>37.01</v>
-      </c>
-      <c r="D55" s="7">
-        <v>37.91</v>
-      </c>
-      <c r="E55" s="9">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="7">
-        <v>57.6</v>
-      </c>
-      <c r="D56" s="7">
-        <v>46.54</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-11.06</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="7">
-        <v>61.1</v>
-      </c>
-      <c r="D57" s="7">
-        <v>51.23</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-9.869999999999999</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="7">
-        <v>43.42</v>
-      </c>
-      <c r="D58" s="7">
-        <v>42.58</v>
-      </c>
-      <c r="E58" s="8">
-        <v>-0.84</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="7">
-        <v>49.51</v>
-      </c>
-      <c r="D59" s="7">
-        <v>45.68</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-3.83</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B60" s="6" t="s">
+      <c r="B64" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C60" s="7">
-        <v>56.3</v>
-      </c>
-      <c r="D60" s="7">
-        <v>111.41</v>
-      </c>
-      <c r="E60" s="9">
-        <v>55.11</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="7">
-        <v>18.04</v>
-      </c>
-      <c r="D61" s="7">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="E61" s="9">
-        <v>58.06</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="7">
-        <v>-87.65000000000001</v>
-      </c>
-      <c r="D62" s="7">
-        <v>-86.58</v>
-      </c>
-      <c r="E62" s="9">
-        <v>1.07</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="7">
-        <v>-40.75</v>
-      </c>
-      <c r="D63" s="7">
-        <v>-26.99</v>
-      </c>
-      <c r="E63" s="9">
-        <v>13.76</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="7">
-        <v>15.65</v>
-      </c>
-      <c r="D64" s="7">
-        <v>6.45</v>
-      </c>
-      <c r="E64" s="8">
-        <v>-9.199999999999999</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="7">
-        <v>-6.46</v>
-      </c>
-      <c r="D65" s="7">
-        <v>-18.07</v>
-      </c>
-      <c r="E65" s="8">
-        <v>-11.61</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="7">
-        <v>-46.01</v>
-      </c>
-      <c r="D66" s="7">
+      <c r="C64" s="8">
         <v>-63.86</v>
       </c>
-      <c r="E66" s="8">
-        <v>-17.85</v>
+      <c r="D64" s="8">
+        <v>-70.48</v>
+      </c>
+      <c r="E64" s="10">
+        <v>-6.62</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3016,60 +2987,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="D1" s="10" t="s">
+      <c r="B1" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="C1" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="D1" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="E1" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="F1" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="G1" s="11" t="s">
         <v>79</v>
       </c>
+      <c r="H1" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="13">
         <v>68.8</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="14">
         <v>7</v>
       </c>
-      <c r="D2" s="12">
-        <v>48.1</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="13">
+        <v>46.6</v>
+      </c>
+      <c r="E2" s="13">
         <v>90</v>
       </c>
-      <c r="F2" s="12">
-        <v>-4.5</v>
-      </c>
-      <c r="G2" s="12">
+      <c r="F2" s="13">
+        <v>-5.2</v>
+      </c>
+      <c r="G2" s="13">
         <v>7.6</v>
       </c>
-      <c r="H2" s="12">
+      <c r="H2" s="13">
         <v>57</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="13">
         <v>60</v>
       </c>
     </row>
@@ -3171,49 +3142,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="15" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="15">
-        <v>0.2982</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.2289</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.1586</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.07389999999999999</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0.0332</v>
-      </c>
-      <c r="F2" s="15">
-        <v>0.0015</v>
-      </c>
-      <c r="G2" s="15">
-        <v>-0.2157</v>
+      <c r="A2" s="16">
+        <v>0.2959</v>
+      </c>
+      <c r="B2" s="16">
+        <v>0.2273</v>
+      </c>
+      <c r="C2" s="16">
+        <v>0.1613</v>
+      </c>
+      <c r="D2" s="16">
+        <v>0.07490000000000001</v>
+      </c>
+      <c r="E2" s="16">
+        <v>0.0361</v>
+      </c>
+      <c r="F2" s="16">
+        <v>-0.0007000000000000001</v>
+      </c>
+      <c r="G2" s="16">
+        <v>-0.2169</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="78">
   <si>
     <t>Symbol</t>
   </si>
@@ -190,43 +190,31 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>46.5 → 50.3</t>
+    <t>44.3 → 52.2</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>46.5</t>
-  </si>
-  <si>
-    <t>50.3</t>
-  </si>
-  <si>
-    <t>RSI Overbought Exit</t>
-  </si>
-  <si>
-    <t>73.1 → 64.1</t>
-  </si>
-  <si>
-    <t>🔵 COOLING</t>
-  </si>
-  <si>
-    <t>73.1</t>
-  </si>
-  <si>
-    <t>64.1</t>
-  </si>
-  <si>
-    <t>51.2 → 46.2</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>51.2</t>
-  </si>
-  <si>
-    <t>46.2</t>
+    <t>44.3</t>
+  </si>
+  <si>
+    <t>52.2</t>
+  </si>
+  <si>
+    <t>Left 52W High Zone</t>
+  </si>
+  <si>
+    <t>-1.9% → -3.6%</t>
+  </si>
+  <si>
+    <t>⚪ NEUTRAL</t>
+  </si>
+  <si>
+    <t>-1.9%</t>
+  </si>
+  <si>
+    <t>-3.6%</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -441,7 +429,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -450,11 +438,10 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -826,8 +813,7 @@
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
     <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="18" width="10.7109375" customWidth="1"/>
-    <col min="19" max="19" width="9.7109375" customWidth="1"/>
+    <col min="17" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -967,10 +953,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>12130</v>
+        <v>11920</v>
       </c>
       <c r="D2">
-        <v>-1.87</v>
+        <v>-1.73</v>
       </c>
       <c r="E2">
         <v>12361</v>
@@ -979,46 +965,46 @@
         <v>8506.780000000001</v>
       </c>
       <c r="G2">
-        <v>-1.87</v>
+        <v>-3.57</v>
       </c>
       <c r="H2">
-        <v>42.59</v>
+        <v>40.12</v>
       </c>
       <c r="I2">
-        <v>3.46</v>
+        <v>1.71</v>
       </c>
       <c r="J2">
-        <v>4.57</v>
+        <v>1.02</v>
       </c>
       <c r="K2">
-        <v>17.06</v>
+        <v>15.26</v>
       </c>
       <c r="L2">
-        <v>42.51</v>
+        <v>34.8</v>
       </c>
       <c r="M2">
-        <v>29.59</v>
+        <v>28.88</v>
       </c>
       <c r="N2">
         <v>85</v>
       </c>
       <c r="O2">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="P2">
-        <v>12050.2</v>
+        <v>12090.2</v>
       </c>
       <c r="Q2">
-        <v>11794.2</v>
+        <v>11809.2</v>
       </c>
       <c r="R2">
-        <v>11060.3</v>
+        <v>11103.7</v>
       </c>
       <c r="S2">
-        <v>9888.51</v>
+        <v>9904.01</v>
       </c>
       <c r="T2">
-        <v>22.67</v>
+        <v>20.36</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -1033,34 +1019,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>64.08</v>
+        <v>57.16</v>
       </c>
       <c r="Z2">
-        <v>263.98</v>
+        <v>244.05</v>
       </c>
       <c r="AA2">
-        <v>258.44</v>
+        <v>255.56</v>
       </c>
       <c r="AB2">
-        <v>5.54</v>
+        <v>-11.51</v>
       </c>
       <c r="AC2">
-        <v>78.22</v>
+        <v>44.88</v>
       </c>
       <c r="AD2">
-        <v>71.73999999999999</v>
+        <v>69.42</v>
       </c>
       <c r="AE2">
-        <v>234.34</v>
+        <v>236.96</v>
       </c>
       <c r="AF2">
-        <v>36.56</v>
+        <v>23.8</v>
       </c>
       <c r="AG2">
-        <v>12195.87</v>
+        <v>12205.85</v>
       </c>
       <c r="AH2">
-        <v>11392.53</v>
+        <v>11412.55</v>
       </c>
       <c r="AI2">
         <v>11623.52</v>
@@ -1069,7 +1055,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>49</v>
+        <v>47.86</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1080,10 +1066,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>484.55</v>
+        <v>508.95</v>
       </c>
       <c r="D3">
-        <v>2.67</v>
+        <v>5.04</v>
       </c>
       <c r="E3">
         <v>670.25</v>
@@ -1092,46 +1078,46 @@
         <v>222.01</v>
       </c>
       <c r="G3">
-        <v>-27.71</v>
+        <v>-24.07</v>
       </c>
       <c r="H3">
-        <v>118.26</v>
+        <v>129.25</v>
       </c>
       <c r="I3">
-        <v>4.54</v>
+        <v>12.95</v>
       </c>
       <c r="J3">
-        <v>-10.96</v>
+        <v>-4.04</v>
       </c>
       <c r="K3">
-        <v>-13.29</v>
+        <v>-7.81</v>
       </c>
       <c r="L3">
-        <v>106.7</v>
+        <v>113.47</v>
       </c>
       <c r="M3">
-        <v>16.13</v>
+        <v>17.71</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="P3">
-        <v>471.72</v>
+        <v>483.39</v>
       </c>
       <c r="Q3">
-        <v>494.82</v>
+        <v>493.64</v>
       </c>
       <c r="R3">
-        <v>542.77</v>
+        <v>541.15</v>
       </c>
       <c r="S3">
-        <v>428.04</v>
+        <v>429.18</v>
       </c>
       <c r="T3">
-        <v>13.2</v>
+        <v>18.59</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1146,34 +1132,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>44.34</v>
+        <v>52.18</v>
       </c>
       <c r="Z3">
-        <v>-20.12</v>
+        <v>-16.32</v>
       </c>
       <c r="AA3">
-        <v>-21.81</v>
+        <v>-20.71</v>
       </c>
       <c r="AB3">
-        <v>1.69</v>
+        <v>4.39</v>
       </c>
       <c r="AC3">
-        <v>82.98999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="AD3">
-        <v>67.81</v>
+        <v>83.16</v>
       </c>
       <c r="AE3">
-        <v>22.34</v>
+        <v>22.71</v>
       </c>
       <c r="AF3">
-        <v>242.05</v>
+        <v>102.38</v>
       </c>
       <c r="AG3">
-        <v>557.46</v>
+        <v>554.13</v>
       </c>
       <c r="AH3">
-        <v>432.17</v>
+        <v>433.14</v>
       </c>
       <c r="AI3">
         <v>521.85</v>
@@ -1182,7 +1168,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>30.66</v>
+        <v>30.27</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1193,10 +1179,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>323.6</v>
+        <v>334.2</v>
       </c>
       <c r="D4">
-        <v>-0.6899999999999999</v>
+        <v>3.28</v>
       </c>
       <c r="E4">
         <v>604.85</v>
@@ -1205,46 +1191,46 @@
         <v>303.75</v>
       </c>
       <c r="G4">
-        <v>-46.5</v>
+        <v>-44.75</v>
       </c>
       <c r="H4">
-        <v>6.53</v>
+        <v>10.02</v>
       </c>
       <c r="I4">
-        <v>-4.99</v>
+        <v>-0.18</v>
       </c>
       <c r="J4">
-        <v>-7.46</v>
+        <v>-3.99</v>
       </c>
       <c r="K4">
-        <v>6.53</v>
+        <v>7.29</v>
       </c>
       <c r="L4">
-        <v>-43.13</v>
+        <v>-41.47</v>
       </c>
       <c r="M4">
-        <v>-21.69</v>
+        <v>-21.45</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
       <c r="O4">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="P4">
-        <v>328.36</v>
+        <v>328.24</v>
       </c>
       <c r="Q4">
-        <v>349.95</v>
+        <v>347.53</v>
       </c>
       <c r="R4">
-        <v>337.94</v>
+        <v>338.13</v>
       </c>
       <c r="S4">
-        <v>383.97</v>
+        <v>383.13</v>
       </c>
       <c r="T4">
-        <v>-15.72</v>
+        <v>-12.77</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1259,34 +1245,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>36.7</v>
+        <v>45.52</v>
       </c>
       <c r="Z4">
-        <v>-4.23</v>
+        <v>-4.12</v>
       </c>
       <c r="AA4">
-        <v>0.02</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AB4">
-        <v>-4.26</v>
+        <v>-3.32</v>
       </c>
       <c r="AC4">
-        <v>1.29</v>
+        <v>13.81</v>
       </c>
       <c r="AD4">
-        <v>1.7</v>
+        <v>5.55</v>
       </c>
       <c r="AE4">
-        <v>11.25</v>
+        <v>11.34</v>
       </c>
       <c r="AF4">
-        <v>-89.34</v>
+        <v>-83.34</v>
       </c>
       <c r="AG4">
-        <v>383.03</v>
+        <v>377.52</v>
       </c>
       <c r="AH4">
-        <v>316.86</v>
+        <v>317.55</v>
       </c>
       <c r="AI4">
         <v>357.31</v>
@@ -1295,7 +1281,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>39.95</v>
+        <v>36.29</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1306,10 +1292,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1990</v>
+        <v>1992.1</v>
       </c>
       <c r="D5">
-        <v>0.91</v>
+        <v>0.11</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1318,46 +1304,46 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-8.57</v>
+        <v>-8.48</v>
       </c>
       <c r="H5">
-        <v>21.95</v>
+        <v>22.08</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="J5">
-        <v>-5.46</v>
+        <v>-4.5</v>
       </c>
       <c r="K5">
-        <v>16.39</v>
+        <v>16.96</v>
       </c>
       <c r="L5">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="M5">
-        <v>3.61</v>
+        <v>3.59</v>
       </c>
       <c r="N5">
         <v>57</v>
       </c>
       <c r="O5">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P5">
-        <v>1999.2</v>
+        <v>1995.42</v>
       </c>
       <c r="Q5">
-        <v>2014.52</v>
+        <v>2009.82</v>
       </c>
       <c r="R5">
-        <v>1941.21</v>
+        <v>1945.45</v>
       </c>
       <c r="S5">
-        <v>1906.28</v>
+        <v>1905.84</v>
       </c>
       <c r="T5">
-        <v>4.39</v>
+        <v>4.53</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1372,34 +1358,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>50.31</v>
+        <v>50.75</v>
       </c>
       <c r="Z5">
-        <v>12.97</v>
+        <v>11.12</v>
       </c>
       <c r="AA5">
-        <v>22.94</v>
+        <v>20.58</v>
       </c>
       <c r="AB5">
-        <v>-9.98</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="AC5">
-        <v>26.24</v>
+        <v>18.24</v>
       </c>
       <c r="AD5">
-        <v>23.01</v>
+        <v>20.7</v>
       </c>
       <c r="AE5">
-        <v>39.12</v>
+        <v>38.33</v>
       </c>
       <c r="AF5">
-        <v>-25.53</v>
+        <v>-52.33</v>
       </c>
       <c r="AG5">
-        <v>2058.11</v>
+        <v>2038.77</v>
       </c>
       <c r="AH5">
-        <v>1970.93</v>
+        <v>1980.88</v>
       </c>
       <c r="AI5">
         <v>1958.53</v>
@@ -1408,7 +1394,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>25.85</v>
+        <v>27.86</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1419,10 +1405,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>11100</v>
+        <v>11165</v>
       </c>
       <c r="D6">
-        <v>-1.86</v>
+        <v>0.59</v>
       </c>
       <c r="E6">
         <v>13595.75</v>
@@ -1431,46 +1417,46 @@
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-18.36</v>
+        <v>-17.88</v>
       </c>
       <c r="H6">
-        <v>26.92</v>
+        <v>27.66</v>
       </c>
       <c r="I6">
-        <v>-3.81</v>
+        <v>-2.05</v>
       </c>
       <c r="J6">
-        <v>-3.27</v>
+        <v>-2.88</v>
       </c>
       <c r="K6">
-        <v>9.609999999999999</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="L6">
-        <v>-12.65</v>
+        <v>-10.55</v>
       </c>
       <c r="M6">
-        <v>22.73</v>
+        <v>22.49</v>
       </c>
       <c r="N6">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="O6">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P6">
-        <v>11358.6</v>
+        <v>11311.8</v>
       </c>
       <c r="Q6">
-        <v>11388.25</v>
+        <v>11377.15</v>
       </c>
       <c r="R6">
-        <v>11009.78</v>
+        <v>11021.42</v>
       </c>
       <c r="S6">
-        <v>10711</v>
+        <v>10706.21</v>
       </c>
       <c r="T6">
-        <v>3.63</v>
+        <v>4.29</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1485,34 +1471,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>46.17</v>
+        <v>47.89</v>
       </c>
       <c r="Z6">
-        <v>81.68000000000001</v>
+        <v>61.56</v>
       </c>
       <c r="AA6">
-        <v>127.63</v>
+        <v>114.41</v>
       </c>
       <c r="AB6">
-        <v>-45.95</v>
+        <v>-52.85</v>
       </c>
       <c r="AC6">
-        <v>29.5</v>
+        <v>10.02</v>
       </c>
       <c r="AD6">
-        <v>38</v>
+        <v>26.19</v>
       </c>
       <c r="AE6">
-        <v>255.09</v>
+        <v>253.44</v>
       </c>
       <c r="AF6">
-        <v>-22.54</v>
+        <v>172.12</v>
       </c>
       <c r="AG6">
-        <v>11677.53</v>
+        <v>11683.18</v>
       </c>
       <c r="AH6">
-        <v>11098.97</v>
+        <v>11071.12</v>
       </c>
       <c r="AI6">
         <v>10787.84</v>
@@ -1521,7 +1507,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>22.45</v>
+        <v>22.56</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1532,10 +1518,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>1055.9</v>
+        <v>1049</v>
       </c>
       <c r="D7">
-        <v>0.19</v>
+        <v>-0.65</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1544,46 +1530,46 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-8.880000000000001</v>
+        <v>-9.48</v>
       </c>
       <c r="H7">
-        <v>31.73</v>
+        <v>30.87</v>
       </c>
       <c r="I7">
-        <v>-2.68</v>
+        <v>-3.14</v>
       </c>
       <c r="J7">
-        <v>-8.1</v>
+        <v>-9.48</v>
       </c>
       <c r="K7">
-        <v>20.76</v>
+        <v>17.94</v>
       </c>
       <c r="L7">
-        <v>20.28</v>
+        <v>17.95</v>
       </c>
       <c r="M7">
-        <v>7.49</v>
+        <v>7.28</v>
       </c>
       <c r="N7">
         <v>71</v>
       </c>
       <c r="O7">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="P7">
-        <v>1065.94</v>
+        <v>1059.14</v>
       </c>
       <c r="Q7">
-        <v>1086.16</v>
+        <v>1081.37</v>
       </c>
       <c r="R7">
-        <v>1060.99</v>
+        <v>1062.15</v>
       </c>
       <c r="S7">
-        <v>976.48</v>
+        <v>976.59</v>
       </c>
       <c r="T7">
-        <v>8.130000000000001</v>
+        <v>7.41</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1598,34 +1584,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>43.35</v>
+        <v>41.3</v>
       </c>
       <c r="Z7">
-        <v>-0.41</v>
+        <v>-2.42</v>
       </c>
       <c r="AA7">
-        <v>7.09</v>
+        <v>5.19</v>
       </c>
       <c r="AB7">
-        <v>-7.5</v>
+        <v>-7.61</v>
       </c>
       <c r="AC7">
         <v>1.99</v>
       </c>
       <c r="AD7">
-        <v>4.55</v>
+        <v>2.18</v>
       </c>
       <c r="AE7">
-        <v>22.9</v>
+        <v>22.44</v>
       </c>
       <c r="AF7">
-        <v>14.41</v>
+        <v>25.12</v>
       </c>
       <c r="AG7">
-        <v>1124.85</v>
+        <v>1112.47</v>
       </c>
       <c r="AH7">
-        <v>1047.47</v>
+        <v>1050.27</v>
       </c>
       <c r="AI7">
         <v>1116.59</v>
@@ -1634,7 +1620,7 @@
         <v>48</v>
       </c>
       <c r="AK7">
-        <v>28.62</v>
+        <v>31.37</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1645,10 +1631,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>134.18</v>
+        <v>132.97</v>
       </c>
       <c r="D8">
-        <v>-1.36</v>
+        <v>-0.9</v>
       </c>
       <c r="E8">
         <v>148.95</v>
@@ -1657,46 +1643,46 @@
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>-9.92</v>
+        <v>-10.73</v>
       </c>
       <c r="H8">
-        <v>15.71</v>
+        <v>14.67</v>
       </c>
       <c r="I8">
-        <v>-2.08</v>
+        <v>-2.41</v>
       </c>
       <c r="J8">
-        <v>-5.67</v>
+        <v>-6.47</v>
       </c>
       <c r="K8">
-        <v>-3.93</v>
+        <v>-4.31</v>
       </c>
       <c r="L8">
-        <v>5.03</v>
+        <v>-0.64</v>
       </c>
       <c r="M8">
-        <v>-0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="N8">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="O8">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="P8">
-        <v>136.22</v>
+        <v>135.57</v>
       </c>
       <c r="Q8">
-        <v>137.05</v>
+        <v>136.54</v>
       </c>
       <c r="R8">
-        <v>137.44</v>
+        <v>137.42</v>
       </c>
       <c r="S8">
-        <v>133.68</v>
+        <v>133.67</v>
       </c>
       <c r="T8">
-        <v>0.38</v>
+        <v>-0.52</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1708,37 +1694,37 @@
         <v>46</v>
       </c>
       <c r="X8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y8">
-        <v>40.99</v>
+        <v>38.23</v>
       </c>
       <c r="Z8">
-        <v>-0.82</v>
+        <v>-1.03</v>
       </c>
       <c r="AA8">
-        <v>-0.7</v>
+        <v>-0.76</v>
       </c>
       <c r="AB8">
-        <v>-0.12</v>
+        <v>-0.26</v>
       </c>
       <c r="AC8">
-        <v>65.3</v>
+        <v>33.62</v>
       </c>
       <c r="AD8">
-        <v>76.58</v>
+        <v>60.97</v>
       </c>
       <c r="AE8">
         <v>3.64</v>
       </c>
       <c r="AF8">
-        <v>-70.48</v>
+        <v>-71.15000000000001</v>
       </c>
       <c r="AG8">
-        <v>142.7</v>
+        <v>141.64</v>
       </c>
       <c r="AH8">
-        <v>131.41</v>
+        <v>131.43</v>
       </c>
       <c r="AI8">
         <v>131.91</v>
@@ -1747,7 +1733,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>19.19</v>
+        <v>19.04</v>
       </c>
     </row>
   </sheetData>
@@ -1888,7 +1874,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1928,7 +1914,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>55</v>
@@ -1966,1008 +1952,1022 @@
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="6" t="s">
+    <row r="6" spans="1:6">
+      <c r="A6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="7">
+        <v>4.57</v>
+      </c>
+      <c r="D8" s="7">
+        <v>1.02</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-3.55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-10.96</v>
+      </c>
+      <c r="D9" s="7">
+        <v>-4.04</v>
+      </c>
+      <c r="E9" s="9">
+        <v>6.92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="7">
+        <v>-7.46</v>
+      </c>
+      <c r="D10" s="7">
+        <v>-3.99</v>
+      </c>
+      <c r="E10" s="9">
+        <v>3.47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="7">
+        <v>-5.46</v>
+      </c>
+      <c r="D11" s="7">
+        <v>-4.5</v>
+      </c>
+      <c r="E11" s="9">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" s="6" t="s">
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7">
+        <v>-3.27</v>
+      </c>
+      <c r="D12" s="7">
+        <v>-2.88</v>
+      </c>
+      <c r="E12" s="9">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7">
+        <v>-8.1</v>
+      </c>
+      <c r="D13" s="7">
+        <v>-9.48</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-1.38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7">
+        <v>-5.67</v>
+      </c>
+      <c r="D14" s="7">
+        <v>-6.47</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="7">
+        <v>3.46</v>
+      </c>
+      <c r="D15" s="7">
+        <v>1.71</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-1.75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="7">
+        <v>4.54</v>
+      </c>
+      <c r="D16" s="7">
+        <v>12.95</v>
+      </c>
+      <c r="E16" s="9">
+        <v>8.41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-4.99</v>
+      </c>
+      <c r="D17" s="7">
+        <v>-0.18</v>
+      </c>
+      <c r="E17" s="9">
+        <v>4.81</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-1</v>
+      </c>
+      <c r="D18" s="7">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="E18" s="9">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>-3.81</v>
+      </c>
+      <c r="D19" s="7">
+        <v>-2.05</v>
+      </c>
+      <c r="E19" s="9">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7">
+        <v>-2.68</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-3.14</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-2.08</v>
+      </c>
+      <c r="D21" s="7">
+        <v>-2.41</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="7">
+        <v>42.51</v>
+      </c>
+      <c r="D22" s="7">
+        <v>34.8</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-7.71</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="7">
+        <v>106.7</v>
+      </c>
+      <c r="D23" s="7">
+        <v>113.47</v>
+      </c>
+      <c r="E23" s="9">
+        <v>6.77</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="7">
+        <v>-43.13</v>
+      </c>
+      <c r="D24" s="7">
+        <v>-41.47</v>
+      </c>
+      <c r="E24" s="9">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="7">
+        <v>4</v>
+      </c>
+      <c r="D25" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="7">
+        <v>-12.65</v>
+      </c>
+      <c r="D26" s="7">
+        <v>-10.55</v>
+      </c>
+      <c r="E26" s="9">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="7">
+        <v>20.28</v>
+      </c>
+      <c r="D27" s="7">
+        <v>17.95</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-2.33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="7">
+        <v>5.03</v>
+      </c>
+      <c r="D28" s="7">
+        <v>-0.64</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-5.67</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="7">
+        <v>17.06</v>
+      </c>
+      <c r="D29" s="7">
+        <v>15.26</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-1.8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="7">
+        <v>-13.29</v>
+      </c>
+      <c r="D30" s="7">
+        <v>-7.81</v>
+      </c>
+      <c r="E30" s="9">
+        <v>5.48</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="7">
+        <v>6.53</v>
+      </c>
+      <c r="D31" s="7">
+        <v>7.29</v>
+      </c>
+      <c r="E31" s="9">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="7">
+        <v>16.39</v>
+      </c>
+      <c r="D32" s="7">
+        <v>16.96</v>
+      </c>
+      <c r="E32" s="9">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="7">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="D33" s="7">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="7">
+        <v>20.76</v>
+      </c>
+      <c r="D34" s="7">
+        <v>17.94</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-2.82</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="7">
+        <v>-3.93</v>
+      </c>
+      <c r="D35" s="7">
+        <v>-4.31</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="7">
+        <v>-1.87</v>
+      </c>
+      <c r="D36" s="7">
+        <v>-3.57</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="7">
+        <v>-27.71</v>
+      </c>
+      <c r="D37" s="7">
+        <v>-24.07</v>
+      </c>
+      <c r="E37" s="9">
+        <v>3.64</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="7">
+        <v>-46.5</v>
+      </c>
+      <c r="D38" s="7">
+        <v>-44.75</v>
+      </c>
+      <c r="E38" s="9">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="7">
+        <v>-8.57</v>
+      </c>
+      <c r="D39" s="7">
+        <v>-8.48</v>
+      </c>
+      <c r="E39" s="9">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="7">
+        <v>-18.36</v>
+      </c>
+      <c r="D40" s="7">
+        <v>-17.88</v>
+      </c>
+      <c r="E40" s="9">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="7">
+        <v>-8.880000000000001</v>
+      </c>
+      <c r="D41" s="7">
+        <v>-9.48</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="7">
+        <v>-9.92</v>
+      </c>
+      <c r="D42" s="7">
+        <v>-10.73</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="7">
+        <v>12130</v>
+      </c>
+      <c r="D43" s="7">
+        <v>11920</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-210</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="7">
+        <v>484.55</v>
+      </c>
+      <c r="D44" s="7">
+        <v>508.95</v>
+      </c>
+      <c r="E44" s="9">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="7">
+        <v>323.6</v>
+      </c>
+      <c r="D45" s="7">
+        <v>334.2</v>
+      </c>
+      <c r="E45" s="9">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="7">
+        <v>1990</v>
+      </c>
+      <c r="D46" s="7">
+        <v>1992.1</v>
+      </c>
+      <c r="E46" s="9">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="7">
+        <v>11100</v>
+      </c>
+      <c r="D47" s="7">
+        <v>11165</v>
+      </c>
+      <c r="E47" s="9">
         <v>65</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="7" t="s">
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="7">
+        <v>1055.9</v>
+      </c>
+      <c r="D48" s="7">
+        <v>1049</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-6.9</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="7">
+        <v>134.18</v>
+      </c>
+      <c r="D49" s="7">
+        <v>132.97</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-1.21</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" s="7">
+        <v>29</v>
+      </c>
+      <c r="D50" s="7">
+        <v>43</v>
+      </c>
+      <c r="E50" s="9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51" s="7">
+        <v>43</v>
+      </c>
+      <c r="D51" s="7">
+        <v>29</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="8">
-        <v>4.26</v>
-      </c>
-      <c r="D9" s="8">
-        <v>4.57</v>
-      </c>
-      <c r="E9" s="9">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="7" t="s">
+      <c r="B52" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="7">
+        <v>64.08</v>
+      </c>
+      <c r="D52" s="7">
+        <v>57.16</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-6.92</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="8">
-        <v>-9.9</v>
-      </c>
-      <c r="D10" s="8">
-        <v>-10.96</v>
-      </c>
-      <c r="E10" s="10">
-        <v>-1.06</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="7" t="s">
+      <c r="B53" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="7">
+        <v>44.34</v>
+      </c>
+      <c r="D53" s="7">
+        <v>52.18</v>
+      </c>
+      <c r="E53" s="9">
+        <v>7.84</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="8">
-        <v>-3.49</v>
-      </c>
-      <c r="D11" s="8">
-        <v>-7.46</v>
-      </c>
-      <c r="E11" s="10">
-        <v>-3.97</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="7" t="s">
+      <c r="B54" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="7">
+        <v>36.7</v>
+      </c>
+      <c r="D54" s="7">
+        <v>45.52</v>
+      </c>
+      <c r="E54" s="9">
+        <v>8.82</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="8">
-        <v>-5.92</v>
-      </c>
-      <c r="D12" s="8">
-        <v>-5.46</v>
-      </c>
-      <c r="E12" s="9">
-        <v>0.46</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="7" t="s">
+      <c r="B55" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="7">
+        <v>50.31</v>
+      </c>
+      <c r="D55" s="7">
+        <v>50.75</v>
+      </c>
+      <c r="E55" s="9">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="8">
-        <v>-2.49</v>
-      </c>
-      <c r="D13" s="8">
-        <v>-3.27</v>
-      </c>
-      <c r="E13" s="10">
-        <v>-0.78</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="7" t="s">
+      <c r="B56" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="7">
+        <v>46.17</v>
+      </c>
+      <c r="D56" s="7">
+        <v>47.89</v>
+      </c>
+      <c r="E56" s="9">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="8">
-        <v>-8.59</v>
-      </c>
-      <c r="D14" s="8">
-        <v>-8.1</v>
-      </c>
-      <c r="E14" s="9">
-        <v>0.49</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="7" t="s">
+      <c r="B57" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="7">
+        <v>43.35</v>
+      </c>
+      <c r="D57" s="7">
+        <v>41.3</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-2.05</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="8">
-        <v>-5.27</v>
-      </c>
-      <c r="D15" s="8">
-        <v>-5.67</v>
-      </c>
-      <c r="E15" s="10">
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="7" t="s">
+      <c r="B58" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="7">
+        <v>40.99</v>
+      </c>
+      <c r="D58" s="7">
+        <v>38.23</v>
+      </c>
+      <c r="E58" s="8">
+        <v>-2.76</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="8">
-        <v>3.64</v>
-      </c>
-      <c r="D16" s="8">
-        <v>3.46</v>
-      </c>
-      <c r="E16" s="10">
-        <v>-0.18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="7" t="s">
+      <c r="B59" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="7">
+        <v>36.56</v>
+      </c>
+      <c r="D59" s="7">
+        <v>23.8</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-12.76</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="8">
-        <v>3.71</v>
-      </c>
-      <c r="D17" s="8">
-        <v>4.54</v>
-      </c>
-      <c r="E17" s="9">
-        <v>0.83</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="7" t="s">
+      <c r="B60" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="7">
+        <v>242.05</v>
+      </c>
+      <c r="D60" s="7">
+        <v>102.38</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-139.67</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="8">
-        <v>-2.54</v>
-      </c>
-      <c r="D18" s="8">
-        <v>-4.99</v>
-      </c>
-      <c r="E18" s="10">
-        <v>-2.45</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="7" t="s">
+      <c r="B61" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="7">
+        <v>-89.34</v>
+      </c>
+      <c r="D61" s="7">
+        <v>-83.34</v>
+      </c>
+      <c r="E61" s="9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="8">
-        <v>-1.6</v>
-      </c>
-      <c r="D19" s="8">
-        <v>-1</v>
-      </c>
-      <c r="E19" s="9">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="7" t="s">
+      <c r="B62" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="7">
+        <v>-25.53</v>
+      </c>
+      <c r="D62" s="7">
+        <v>-52.33</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-26.8</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="8">
-        <v>0.18</v>
-      </c>
-      <c r="D20" s="8">
-        <v>-3.81</v>
-      </c>
-      <c r="E20" s="10">
-        <v>-3.99</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="7" t="s">
+      <c r="B63" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="7">
+        <v>-22.54</v>
+      </c>
+      <c r="D63" s="7">
+        <v>172.12</v>
+      </c>
+      <c r="E63" s="9">
+        <v>194.66</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="8">
-        <v>-3.08</v>
-      </c>
-      <c r="D21" s="8">
-        <v>-2.68</v>
-      </c>
-      <c r="E21" s="9">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="7" t="s">
+      <c r="B64" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="7">
+        <v>14.41</v>
+      </c>
+      <c r="D64" s="7">
+        <v>25.12</v>
+      </c>
+      <c r="E64" s="9">
+        <v>10.71</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="8">
-        <v>0.68</v>
-      </c>
-      <c r="D22" s="8">
-        <v>-2.08</v>
-      </c>
-      <c r="E22" s="10">
-        <v>-2.76</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="8">
-        <v>44.25</v>
-      </c>
-      <c r="D23" s="8">
-        <v>42.51</v>
-      </c>
-      <c r="E23" s="10">
-        <v>-1.74</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="8">
-        <v>101.39</v>
-      </c>
-      <c r="D24" s="8">
-        <v>106.7</v>
-      </c>
-      <c r="E24" s="9">
-        <v>5.31</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="8">
-        <v>-43.15</v>
-      </c>
-      <c r="D25" s="8">
-        <v>-43.13</v>
-      </c>
-      <c r="E25" s="9">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="8">
-        <v>2.84</v>
-      </c>
-      <c r="D26" s="8">
-        <v>4</v>
-      </c>
-      <c r="E26" s="9">
-        <v>1.16</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="8">
-        <v>-12.34</v>
-      </c>
-      <c r="D27" s="8">
-        <v>-12.65</v>
-      </c>
-      <c r="E27" s="10">
-        <v>-0.31</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="8">
-        <v>20.19</v>
-      </c>
-      <c r="D28" s="8">
-        <v>20.28</v>
-      </c>
-      <c r="E28" s="9">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="8">
-        <v>5.61</v>
-      </c>
-      <c r="D29" s="8">
-        <v>5.03</v>
-      </c>
-      <c r="E29" s="10">
-        <v>-0.58</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="8">
-        <v>20.49</v>
-      </c>
-      <c r="D30" s="8">
-        <v>17.06</v>
-      </c>
-      <c r="E30" s="10">
-        <v>-3.43</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="8">
-        <v>-15.03</v>
-      </c>
-      <c r="D31" s="8">
-        <v>-13.29</v>
-      </c>
-      <c r="E31" s="9">
-        <v>1.74</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="8">
-        <v>5.54</v>
-      </c>
-      <c r="D32" s="8">
-        <v>6.53</v>
-      </c>
-      <c r="E32" s="9">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="8">
-        <v>13.7</v>
-      </c>
-      <c r="D33" s="8">
-        <v>16.39</v>
-      </c>
-      <c r="E33" s="9">
-        <v>2.69</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="8">
-        <v>10.99</v>
-      </c>
-      <c r="D34" s="8">
-        <v>9.609999999999999</v>
-      </c>
-      <c r="E34" s="10">
-        <v>-1.38</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="8">
-        <v>20.2</v>
-      </c>
-      <c r="D35" s="8">
-        <v>20.76</v>
-      </c>
-      <c r="E35" s="9">
-        <v>0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="8">
-        <v>-2.59</v>
-      </c>
-      <c r="D36" s="8">
-        <v>-3.93</v>
-      </c>
-      <c r="E36" s="10">
-        <v>-1.34</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="8">
-        <v>0</v>
-      </c>
-      <c r="D37" s="8">
-        <v>-1.87</v>
-      </c>
-      <c r="E37" s="10">
-        <v>-1.87</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="8">
-        <v>-29.59</v>
-      </c>
-      <c r="D38" s="8">
-        <v>-27.71</v>
-      </c>
-      <c r="E38" s="9">
-        <v>1.88</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="8">
-        <v>-46.13</v>
-      </c>
-      <c r="D39" s="8">
-        <v>-46.5</v>
-      </c>
-      <c r="E39" s="10">
-        <v>-0.37</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="8">
-        <v>-9.4</v>
-      </c>
-      <c r="D40" s="8">
-        <v>-8.57</v>
-      </c>
-      <c r="E40" s="9">
-        <v>0.83</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="8">
-        <v>-16.81</v>
-      </c>
-      <c r="D41" s="8">
-        <v>-18.36</v>
-      </c>
-      <c r="E41" s="10">
-        <v>-1.55</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="8">
-        <v>-9.050000000000001</v>
-      </c>
-      <c r="D42" s="8">
-        <v>-8.880000000000001</v>
-      </c>
-      <c r="E42" s="9">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="8">
-        <v>-8.67</v>
-      </c>
-      <c r="D43" s="8">
-        <v>-9.92</v>
-      </c>
-      <c r="E43" s="10">
-        <v>-1.25</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="8">
-        <v>12361</v>
-      </c>
-      <c r="D44" s="8">
-        <v>12130</v>
-      </c>
-      <c r="E44" s="10">
-        <v>-231</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="8">
-        <v>471.95</v>
-      </c>
-      <c r="D45" s="8">
-        <v>484.55</v>
-      </c>
-      <c r="E45" s="9">
-        <v>12.6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="8">
-        <v>325.85</v>
-      </c>
-      <c r="D46" s="8">
-        <v>323.6</v>
-      </c>
-      <c r="E46" s="10">
-        <v>-2.25</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="8">
-        <v>1972</v>
-      </c>
-      <c r="D47" s="8">
-        <v>1990</v>
-      </c>
-      <c r="E47" s="9">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="8">
-        <v>11310</v>
-      </c>
-      <c r="D48" s="8">
-        <v>11100</v>
-      </c>
-      <c r="E48" s="10">
-        <v>-210</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="8">
-        <v>1053.9</v>
-      </c>
-      <c r="D49" s="8">
-        <v>1055.9</v>
-      </c>
-      <c r="E49" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="8">
-        <v>136.03</v>
-      </c>
-      <c r="D50" s="8">
-        <v>134.18</v>
-      </c>
-      <c r="E50" s="10">
-        <v>-1.85</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="8">
-        <v>73.14</v>
-      </c>
-      <c r="D51" s="8">
-        <v>64.08</v>
-      </c>
-      <c r="E51" s="10">
-        <v>-9.06</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="8">
-        <v>39.59</v>
-      </c>
-      <c r="D52" s="8">
-        <v>44.34</v>
-      </c>
-      <c r="E52" s="9">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B53" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="8">
-        <v>37.91</v>
-      </c>
-      <c r="D53" s="8">
-        <v>36.7</v>
-      </c>
-      <c r="E53" s="10">
-        <v>-1.21</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="8">
-        <v>46.54</v>
-      </c>
-      <c r="D54" s="8">
-        <v>50.31</v>
-      </c>
-      <c r="E54" s="9">
-        <v>3.77</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="8">
-        <v>51.23</v>
-      </c>
-      <c r="D55" s="8">
-        <v>46.17</v>
-      </c>
-      <c r="E55" s="10">
-        <v>-5.06</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B56" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="8">
-        <v>42.58</v>
-      </c>
-      <c r="D56" s="8">
-        <v>43.35</v>
-      </c>
-      <c r="E56" s="9">
-        <v>0.77</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="8">
-        <v>45.68</v>
-      </c>
-      <c r="D57" s="8">
-        <v>40.99</v>
-      </c>
-      <c r="E57" s="10">
-        <v>-4.69</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B58" s="7" t="s">
+      <c r="B65" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C58" s="8">
-        <v>111.41</v>
-      </c>
-      <c r="D58" s="8">
-        <v>36.56</v>
-      </c>
-      <c r="E58" s="10">
-        <v>-74.84999999999999</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C59" s="8">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="D59" s="8">
-        <v>242.05</v>
-      </c>
-      <c r="E59" s="9">
-        <v>165.95</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="8">
-        <v>-86.58</v>
-      </c>
-      <c r="D60" s="8">
-        <v>-89.34</v>
-      </c>
-      <c r="E60" s="10">
-        <v>-2.76</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B61" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="8">
-        <v>-26.99</v>
-      </c>
-      <c r="D61" s="8">
-        <v>-25.53</v>
-      </c>
-      <c r="E61" s="9">
-        <v>1.46</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="8">
-        <v>6.45</v>
-      </c>
-      <c r="D62" s="8">
-        <v>-22.54</v>
-      </c>
-      <c r="E62" s="10">
-        <v>-28.99</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B63" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="8">
-        <v>-18.07</v>
-      </c>
-      <c r="D63" s="8">
-        <v>14.41</v>
-      </c>
-      <c r="E63" s="9">
-        <v>32.48</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B64" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="8">
-        <v>-63.86</v>
-      </c>
-      <c r="D64" s="8">
+      <c r="C65" s="7">
         <v>-70.48</v>
       </c>
-      <c r="E64" s="10">
-        <v>-6.62</v>
+      <c r="D65" s="7">
+        <v>-71.15000000000001</v>
+      </c>
+      <c r="E65" s="8">
+        <v>-0.67</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2987,60 +2987,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="G1" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="H1" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="I1" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="F1" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>81</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="13">
-        <v>68.8</v>
-      </c>
-      <c r="C2" s="14">
+      <c r="B2" s="12">
+        <v>60.8</v>
+      </c>
+      <c r="C2" s="13">
         <v>7</v>
       </c>
-      <c r="D2" s="13">
-        <v>46.6</v>
-      </c>
-      <c r="E2" s="13">
-        <v>90</v>
-      </c>
-      <c r="F2" s="13">
-        <v>-5.2</v>
-      </c>
-      <c r="G2" s="13">
-        <v>7.6</v>
-      </c>
-      <c r="H2" s="13">
+      <c r="D2" s="12">
+        <v>47.6</v>
+      </c>
+      <c r="E2" s="12">
+        <v>70</v>
+      </c>
+      <c r="F2" s="12">
+        <v>-4.3</v>
+      </c>
+      <c r="G2" s="12">
+        <v>7.8</v>
+      </c>
+      <c r="H2" s="12">
         <v>57</v>
       </c>
-      <c r="I2" s="13">
+      <c r="I2" s="12">
         <v>60</v>
       </c>
     </row>
@@ -3142,49 +3142,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="14" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="16">
-        <v>0.2959</v>
-      </c>
-      <c r="B2" s="16">
-        <v>0.2273</v>
-      </c>
-      <c r="C2" s="16">
-        <v>0.1613</v>
-      </c>
-      <c r="D2" s="16">
-        <v>0.07490000000000001</v>
-      </c>
-      <c r="E2" s="16">
-        <v>0.0361</v>
-      </c>
-      <c r="F2" s="16">
-        <v>-0.0007000000000000001</v>
-      </c>
-      <c r="G2" s="16">
-        <v>-0.2169</v>
+      <c r="A2" s="15">
+        <v>0.2888</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.2249</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.1771</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.0728</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.0359</v>
+      </c>
+      <c r="F2" s="15">
+        <v>0.0005</v>
+      </c>
+      <c r="G2" s="15">
+        <v>-0.2145</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="73">
   <si>
     <t>Symbol</t>
   </si>
@@ -190,31 +190,16 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>44.3 → 52.2</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>44.3</t>
-  </si>
-  <si>
-    <t>52.2</t>
-  </si>
-  <si>
-    <t>Left 52W High Zone</t>
-  </si>
-  <si>
-    <t>-1.9% → -3.6%</t>
-  </si>
-  <si>
-    <t>⚪ NEUTRAL</t>
-  </si>
-  <si>
-    <t>-1.9%</t>
-  </si>
-  <si>
-    <t>-3.6%</t>
+    <t>50.8 → 46.1</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>50.8</t>
+  </si>
+  <si>
+    <t>46.1</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -266,7 +251,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -300,27 +285,20 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -347,19 +325,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -429,7 +401,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -437,15 +409,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -454,7 +425,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -953,10 +924,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>11920</v>
+        <v>11919</v>
       </c>
       <c r="D2">
-        <v>-1.73</v>
+        <v>-0.01</v>
       </c>
       <c r="E2">
         <v>12361</v>
@@ -965,25 +936,25 @@
         <v>8506.780000000001</v>
       </c>
       <c r="G2">
-        <v>-3.57</v>
+        <v>-3.58</v>
       </c>
       <c r="H2">
-        <v>40.12</v>
+        <v>40.11</v>
       </c>
       <c r="I2">
-        <v>1.71</v>
+        <v>0.08</v>
       </c>
       <c r="J2">
-        <v>1.02</v>
+        <v>2.57</v>
       </c>
       <c r="K2">
-        <v>15.26</v>
+        <v>16.5</v>
       </c>
       <c r="L2">
-        <v>34.8</v>
+        <v>33.84</v>
       </c>
       <c r="M2">
-        <v>28.88</v>
+        <v>28.76</v>
       </c>
       <c r="N2">
         <v>85</v>
@@ -992,19 +963,19 @@
         <v>80</v>
       </c>
       <c r="P2">
-        <v>12090.2</v>
+        <v>12092</v>
       </c>
       <c r="Q2">
-        <v>11809.2</v>
+        <v>11822.05</v>
       </c>
       <c r="R2">
-        <v>11103.7</v>
+        <v>11145.22</v>
       </c>
       <c r="S2">
-        <v>9904.01</v>
+        <v>9919.620000000001</v>
       </c>
       <c r="T2">
-        <v>20.36</v>
+        <v>20.16</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -1019,34 +990,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>57.16</v>
+        <v>57.12</v>
       </c>
       <c r="Z2">
-        <v>244.05</v>
+        <v>225.57</v>
       </c>
       <c r="AA2">
-        <v>255.56</v>
+        <v>249.56</v>
       </c>
       <c r="AB2">
-        <v>-11.51</v>
+        <v>-23.99</v>
       </c>
       <c r="AC2">
+        <v>11.55</v>
+      </c>
+      <c r="AD2">
         <v>44.88</v>
       </c>
-      <c r="AD2">
-        <v>69.42</v>
-      </c>
       <c r="AE2">
-        <v>236.96</v>
+        <v>230.89</v>
       </c>
       <c r="AF2">
-        <v>23.8</v>
+        <v>-36.23</v>
       </c>
       <c r="AG2">
-        <v>12205.85</v>
+        <v>12215.26</v>
       </c>
       <c r="AH2">
-        <v>11412.55</v>
+        <v>11428.84</v>
       </c>
       <c r="AI2">
         <v>11623.52</v>
@@ -1055,7 +1026,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>47.86</v>
+        <v>45.68</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1066,10 +1037,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>508.95</v>
+        <v>517.55</v>
       </c>
       <c r="D3">
-        <v>5.04</v>
+        <v>1.69</v>
       </c>
       <c r="E3">
         <v>670.25</v>
@@ -1078,46 +1049,46 @@
         <v>222.01</v>
       </c>
       <c r="G3">
-        <v>-24.07</v>
+        <v>-22.78</v>
       </c>
       <c r="H3">
-        <v>129.25</v>
+        <v>133.12</v>
       </c>
       <c r="I3">
-        <v>12.95</v>
+        <v>8.4</v>
       </c>
       <c r="J3">
-        <v>-4.04</v>
+        <v>-2.83</v>
       </c>
       <c r="K3">
-        <v>-7.81</v>
+        <v>-10.05</v>
       </c>
       <c r="L3">
-        <v>113.47</v>
+        <v>113.45</v>
       </c>
       <c r="M3">
-        <v>17.71</v>
+        <v>18.15</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P3">
-        <v>483.39</v>
+        <v>491.41</v>
       </c>
       <c r="Q3">
-        <v>493.64</v>
+        <v>492.64</v>
       </c>
       <c r="R3">
-        <v>541.15</v>
+        <v>539.9299999999999</v>
       </c>
       <c r="S3">
-        <v>429.18</v>
+        <v>430.36</v>
       </c>
       <c r="T3">
-        <v>18.59</v>
+        <v>20.26</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1132,34 +1103,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>52.18</v>
+        <v>54.61</v>
       </c>
       <c r="Z3">
-        <v>-16.32</v>
+        <v>-12.47</v>
       </c>
       <c r="AA3">
-        <v>-20.71</v>
+        <v>-19.07</v>
       </c>
       <c r="AB3">
-        <v>4.39</v>
+        <v>6.59</v>
       </c>
       <c r="AC3">
-        <v>93.7</v>
+        <v>100</v>
       </c>
       <c r="AD3">
-        <v>83.16</v>
+        <v>92.23</v>
       </c>
       <c r="AE3">
-        <v>22.71</v>
+        <v>21.96</v>
       </c>
       <c r="AF3">
-        <v>102.38</v>
+        <v>53.36</v>
       </c>
       <c r="AG3">
-        <v>554.13</v>
+        <v>550.71</v>
       </c>
       <c r="AH3">
-        <v>433.14</v>
+        <v>434.57</v>
       </c>
       <c r="AI3">
         <v>521.85</v>
@@ -1168,7 +1139,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>30.27</v>
+        <v>31.13</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1179,10 +1150,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>334.2</v>
+        <v>331.15</v>
       </c>
       <c r="D4">
-        <v>3.28</v>
+        <v>-0.91</v>
       </c>
       <c r="E4">
         <v>604.85</v>
@@ -1191,46 +1162,46 @@
         <v>303.75</v>
       </c>
       <c r="G4">
-        <v>-44.75</v>
+        <v>-45.25</v>
       </c>
       <c r="H4">
-        <v>10.02</v>
+        <v>9.02</v>
       </c>
       <c r="I4">
-        <v>-0.18</v>
+        <v>-0.48</v>
       </c>
       <c r="J4">
-        <v>-3.99</v>
+        <v>-13.42</v>
       </c>
       <c r="K4">
-        <v>7.29</v>
+        <v>8.08</v>
       </c>
       <c r="L4">
-        <v>-41.47</v>
+        <v>-42.07</v>
       </c>
       <c r="M4">
-        <v>-21.45</v>
+        <v>-22.86</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
       <c r="O4">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="P4">
-        <v>328.24</v>
+        <v>327.92</v>
       </c>
       <c r="Q4">
-        <v>347.53</v>
+        <v>345.53</v>
       </c>
       <c r="R4">
-        <v>338.13</v>
+        <v>338.31</v>
       </c>
       <c r="S4">
-        <v>383.13</v>
+        <v>382.3</v>
       </c>
       <c r="T4">
-        <v>-12.77</v>
+        <v>-13.38</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1245,34 +1216,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>45.52</v>
+        <v>43.63</v>
       </c>
       <c r="Z4">
-        <v>-4.12</v>
+        <v>-4.23</v>
       </c>
       <c r="AA4">
-        <v>-0.8100000000000001</v>
+        <v>-1.49</v>
       </c>
       <c r="AB4">
-        <v>-3.32</v>
+        <v>-2.74</v>
       </c>
       <c r="AC4">
-        <v>13.81</v>
+        <v>25.01</v>
       </c>
       <c r="AD4">
-        <v>5.55</v>
+        <v>13.37</v>
       </c>
       <c r="AE4">
-        <v>11.34</v>
+        <v>11.04</v>
       </c>
       <c r="AF4">
-        <v>-83.34</v>
+        <v>-91.58</v>
       </c>
       <c r="AG4">
-        <v>377.52</v>
+        <v>374.19</v>
       </c>
       <c r="AH4">
-        <v>317.55</v>
+        <v>316.87</v>
       </c>
       <c r="AI4">
         <v>357.31</v>
@@ -1281,7 +1252,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>36.29</v>
+        <v>32.56</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1292,10 +1263,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1992.1</v>
+        <v>1970</v>
       </c>
       <c r="D5">
-        <v>0.11</v>
+        <v>-1.11</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1304,46 +1275,46 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-8.48</v>
+        <v>-9.49</v>
       </c>
       <c r="H5">
-        <v>22.08</v>
+        <v>20.73</v>
       </c>
       <c r="I5">
-        <v>-0.9399999999999999</v>
+        <v>-1.6</v>
       </c>
       <c r="J5">
-        <v>-4.5</v>
+        <v>-5.56</v>
       </c>
       <c r="K5">
-        <v>16.96</v>
+        <v>17.64</v>
       </c>
       <c r="L5">
-        <v>2.5</v>
+        <v>0.72</v>
       </c>
       <c r="M5">
-        <v>3.59</v>
+        <v>3.35</v>
       </c>
       <c r="N5">
         <v>57</v>
       </c>
       <c r="O5">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="P5">
-        <v>1995.42</v>
+        <v>1989.02</v>
       </c>
       <c r="Q5">
-        <v>2009.82</v>
+        <v>2007.88</v>
       </c>
       <c r="R5">
-        <v>1945.45</v>
+        <v>1949.55</v>
       </c>
       <c r="S5">
-        <v>1905.84</v>
+        <v>1905.44</v>
       </c>
       <c r="T5">
-        <v>4.53</v>
+        <v>3.39</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1358,34 +1329,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>50.75</v>
+        <v>46.15</v>
       </c>
       <c r="Z5">
-        <v>11.12</v>
+        <v>7.79</v>
       </c>
       <c r="AA5">
-        <v>20.58</v>
+        <v>18.02</v>
       </c>
       <c r="AB5">
-        <v>-9.449999999999999</v>
+        <v>-10.23</v>
       </c>
       <c r="AC5">
         <v>18.24</v>
       </c>
       <c r="AD5">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="AE5">
-        <v>38.33</v>
+        <v>37.32</v>
       </c>
       <c r="AF5">
-        <v>-52.33</v>
+        <v>-47.11</v>
       </c>
       <c r="AG5">
-        <v>2038.77</v>
+        <v>2041.87</v>
       </c>
       <c r="AH5">
-        <v>1980.88</v>
+        <v>1973.89</v>
       </c>
       <c r="AI5">
         <v>1958.53</v>
@@ -1394,7 +1365,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>27.86</v>
+        <v>29.61</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1405,10 +1376,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>11165</v>
+        <v>11162</v>
       </c>
       <c r="D6">
-        <v>0.59</v>
+        <v>-0.03</v>
       </c>
       <c r="E6">
         <v>13595.75</v>
@@ -1417,43 +1388,43 @@
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-17.88</v>
+        <v>-17.9</v>
       </c>
       <c r="H6">
-        <v>27.66</v>
+        <v>27.62</v>
       </c>
       <c r="I6">
-        <v>-2.05</v>
+        <v>-1.57</v>
       </c>
       <c r="J6">
-        <v>-2.88</v>
+        <v>-1.98</v>
       </c>
       <c r="K6">
-        <v>9.470000000000001</v>
+        <v>13.11</v>
       </c>
       <c r="L6">
-        <v>-10.55</v>
+        <v>-11.12</v>
       </c>
       <c r="M6">
-        <v>22.49</v>
+        <v>23.1</v>
       </c>
       <c r="N6">
         <v>43</v>
       </c>
       <c r="O6">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="P6">
-        <v>11311.8</v>
+        <v>11276.2</v>
       </c>
       <c r="Q6">
-        <v>11377.15</v>
+        <v>11372.1</v>
       </c>
       <c r="R6">
-        <v>11021.42</v>
+        <v>11032.68</v>
       </c>
       <c r="S6">
-        <v>10706.21</v>
+        <v>10702.66</v>
       </c>
       <c r="T6">
         <v>4.29</v>
@@ -1471,34 +1442,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>47.89</v>
+        <v>47.81</v>
       </c>
       <c r="Z6">
-        <v>61.56</v>
+        <v>44.85</v>
       </c>
       <c r="AA6">
-        <v>114.41</v>
+        <v>100.5</v>
       </c>
       <c r="AB6">
-        <v>-52.85</v>
+        <v>-55.65</v>
       </c>
       <c r="AC6">
-        <v>10.02</v>
+        <v>7.08</v>
       </c>
       <c r="AD6">
-        <v>26.19</v>
+        <v>15.53</v>
       </c>
       <c r="AE6">
-        <v>253.44</v>
+        <v>253.55</v>
       </c>
       <c r="AF6">
-        <v>172.12</v>
+        <v>-19</v>
       </c>
       <c r="AG6">
-        <v>11683.18</v>
+        <v>11689.2</v>
       </c>
       <c r="AH6">
-        <v>11071.12</v>
+        <v>11055</v>
       </c>
       <c r="AI6">
         <v>10787.84</v>
@@ -1507,7 +1478,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>22.56</v>
+        <v>20.65</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1518,10 +1489,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>1049</v>
+        <v>1060.5</v>
       </c>
       <c r="D7">
-        <v>-0.65</v>
+        <v>1.1</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1530,46 +1501,46 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-9.48</v>
+        <v>-8.48</v>
       </c>
       <c r="H7">
-        <v>30.87</v>
+        <v>32.31</v>
       </c>
       <c r="I7">
-        <v>-3.14</v>
+        <v>-1.8</v>
       </c>
       <c r="J7">
-        <v>-9.48</v>
+        <v>-7.36</v>
       </c>
       <c r="K7">
-        <v>17.94</v>
+        <v>21.74</v>
       </c>
       <c r="L7">
-        <v>17.95</v>
+        <v>19.14</v>
       </c>
       <c r="M7">
-        <v>7.28</v>
+        <v>7.57</v>
       </c>
       <c r="N7">
         <v>71</v>
       </c>
       <c r="O7">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="P7">
-        <v>1059.14</v>
+        <v>1055.26</v>
       </c>
       <c r="Q7">
-        <v>1081.37</v>
+        <v>1080.5</v>
       </c>
       <c r="R7">
-        <v>1062.15</v>
+        <v>1063.75</v>
       </c>
       <c r="S7">
-        <v>976.59</v>
+        <v>976.83</v>
       </c>
       <c r="T7">
-        <v>7.41</v>
+        <v>8.57</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1584,34 +1555,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>41.3</v>
+        <v>45.89</v>
       </c>
       <c r="Z7">
-        <v>-2.42</v>
+        <v>-3.05</v>
       </c>
       <c r="AA7">
-        <v>5.19</v>
+        <v>3.54</v>
       </c>
       <c r="AB7">
-        <v>-7.61</v>
+        <v>-6.6</v>
       </c>
       <c r="AC7">
-        <v>1.99</v>
+        <v>12.84</v>
       </c>
       <c r="AD7">
-        <v>2.18</v>
+        <v>5.61</v>
       </c>
       <c r="AE7">
-        <v>22.44</v>
+        <v>21.88</v>
       </c>
       <c r="AF7">
-        <v>25.12</v>
+        <v>10.9</v>
       </c>
       <c r="AG7">
-        <v>1112.47</v>
+        <v>1112.95</v>
       </c>
       <c r="AH7">
-        <v>1050.27</v>
+        <v>1048.04</v>
       </c>
       <c r="AI7">
         <v>1116.59</v>
@@ -1620,7 +1591,7 @@
         <v>48</v>
       </c>
       <c r="AK7">
-        <v>31.37</v>
+        <v>32.54</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1631,10 +1602,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>132.97</v>
+        <v>134.44</v>
       </c>
       <c r="D8">
-        <v>-0.9</v>
+        <v>1.11</v>
       </c>
       <c r="E8">
         <v>148.95</v>
@@ -1643,25 +1614,25 @@
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>-10.73</v>
+        <v>-9.74</v>
       </c>
       <c r="H8">
-        <v>14.67</v>
+        <v>15.94</v>
       </c>
       <c r="I8">
-        <v>-2.41</v>
+        <v>-2.06</v>
       </c>
       <c r="J8">
-        <v>-6.47</v>
+        <v>-6.18</v>
       </c>
       <c r="K8">
-        <v>-4.31</v>
+        <v>-1.98</v>
       </c>
       <c r="L8">
-        <v>-0.64</v>
+        <v>0.49</v>
       </c>
       <c r="M8">
-        <v>0.05</v>
+        <v>-0.22</v>
       </c>
       <c r="N8">
         <v>29</v>
@@ -1670,19 +1641,19 @@
         <v>46</v>
       </c>
       <c r="P8">
-        <v>135.57</v>
+        <v>135</v>
       </c>
       <c r="Q8">
-        <v>136.54</v>
+        <v>136.1</v>
       </c>
       <c r="R8">
-        <v>137.42</v>
+        <v>137.45</v>
       </c>
       <c r="S8">
-        <v>133.67</v>
+        <v>133.66</v>
       </c>
       <c r="T8">
-        <v>-0.52</v>
+        <v>0.59</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1694,37 +1665,37 @@
         <v>46</v>
       </c>
       <c r="X8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y8">
-        <v>38.23</v>
+        <v>43.23</v>
       </c>
       <c r="Z8">
-        <v>-1.03</v>
+        <v>-1.06</v>
       </c>
       <c r="AA8">
-        <v>-0.76</v>
+        <v>-0.82</v>
       </c>
       <c r="AB8">
-        <v>-0.26</v>
+        <v>-0.24</v>
       </c>
       <c r="AC8">
-        <v>33.62</v>
+        <v>25.84</v>
       </c>
       <c r="AD8">
-        <v>60.97</v>
+        <v>41.59</v>
       </c>
       <c r="AE8">
-        <v>3.64</v>
+        <v>3.53</v>
       </c>
       <c r="AF8">
-        <v>-71.15000000000001</v>
+        <v>-71.97</v>
       </c>
       <c r="AG8">
-        <v>141.64</v>
+        <v>140.2</v>
       </c>
       <c r="AH8">
-        <v>131.43</v>
+        <v>132</v>
       </c>
       <c r="AI8">
         <v>131.91</v>
@@ -1733,7 +1704,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>19.04</v>
+        <v>18.91</v>
       </c>
     </row>
   </sheetData>
@@ -1874,7 +1845,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1914,7 +1885,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>55</v>
@@ -1932,1042 +1903,988 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>69</v>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>1.02</v>
+      </c>
+      <c r="D7" s="6">
+        <v>2.57</v>
+      </c>
+      <c r="E7" s="7">
+        <v>1.55</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-4.04</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-2.83</v>
+      </c>
+      <c r="E8" s="7">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-3.99</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-13.42</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-9.43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-4.5</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-5.56</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-2.88</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-1.98</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-9.48</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-7.36</v>
+      </c>
+      <c r="E12" s="7">
+        <v>2.12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-6.47</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-6.18</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="7">
-        <v>4.57</v>
-      </c>
-      <c r="D8" s="7">
-        <v>1.02</v>
-      </c>
-      <c r="E8" s="8">
-        <v>-3.55</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="B14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="6">
+        <v>1.71</v>
+      </c>
+      <c r="D14" s="6">
+        <v>0.08</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-1.63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-10.96</v>
-      </c>
-      <c r="D9" s="7">
-        <v>-4.04</v>
-      </c>
-      <c r="E9" s="9">
-        <v>6.92</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6">
+        <v>12.95</v>
+      </c>
+      <c r="D15" s="6">
+        <v>8.4</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-4.55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>-7.46</v>
-      </c>
-      <c r="D10" s="7">
-        <v>-3.99</v>
-      </c>
-      <c r="E10" s="9">
-        <v>3.47</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-0.18</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-0.48</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>-5.46</v>
-      </c>
-      <c r="D11" s="7">
-        <v>-4.5</v>
-      </c>
-      <c r="E11" s="9">
-        <v>0.96</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-1.6</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-0.66</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>-3.27</v>
-      </c>
-      <c r="D12" s="7">
-        <v>-2.88</v>
-      </c>
-      <c r="E12" s="9">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-2.05</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-1.57</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>-8.1</v>
-      </c>
-      <c r="D13" s="7">
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-3.14</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-1.8</v>
+      </c>
+      <c r="E19" s="7">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-2.41</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-2.06</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>34.8</v>
+      </c>
+      <c r="D21" s="6">
+        <v>33.84</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-0.96</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="6">
+        <v>113.47</v>
+      </c>
+      <c r="D22" s="6">
+        <v>113.45</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-41.47</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-42.07</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="D24" s="6">
+        <v>0.72</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-1.78</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-10.55</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-11.12</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>17.95</v>
+      </c>
+      <c r="D26" s="6">
+        <v>19.14</v>
+      </c>
+      <c r="E26" s="7">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-0.64</v>
+      </c>
+      <c r="D27" s="6">
+        <v>0.49</v>
+      </c>
+      <c r="E27" s="7">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="6">
+        <v>15.26</v>
+      </c>
+      <c r="D28" s="6">
+        <v>16.5</v>
+      </c>
+      <c r="E28" s="7">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-7.81</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-10.05</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-2.24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="6">
+        <v>7.29</v>
+      </c>
+      <c r="D30" s="6">
+        <v>8.08</v>
+      </c>
+      <c r="E30" s="7">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="6">
+        <v>16.96</v>
+      </c>
+      <c r="D31" s="6">
+        <v>17.64</v>
+      </c>
+      <c r="E31" s="7">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="6">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="D32" s="6">
+        <v>13.11</v>
+      </c>
+      <c r="E32" s="7">
+        <v>3.64</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6">
+        <v>17.94</v>
+      </c>
+      <c r="D33" s="6">
+        <v>21.74</v>
+      </c>
+      <c r="E33" s="7">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-4.31</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-1.98</v>
+      </c>
+      <c r="E34" s="7">
+        <v>2.33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-3.57</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-3.58</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-24.07</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-22.78</v>
+      </c>
+      <c r="E36" s="7">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-44.75</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-45.25</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-8.48</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-9.49</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-1.01</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-17.88</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-17.9</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="6">
         <v>-9.48</v>
       </c>
-      <c r="E13" s="8">
-        <v>-1.38</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="D40" s="6">
+        <v>-8.48</v>
+      </c>
+      <c r="E40" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>-5.67</v>
-      </c>
-      <c r="D14" s="7">
-        <v>-6.47</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-0.8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B41" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-10.73</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-9.74</v>
+      </c>
+      <c r="E41" s="7">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="7">
-        <v>3.46</v>
-      </c>
-      <c r="D15" s="7">
-        <v>1.71</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-1.75</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B42" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="6">
+        <v>11920</v>
+      </c>
+      <c r="D42" s="6">
+        <v>11919</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="7">
-        <v>4.54</v>
-      </c>
-      <c r="D16" s="7">
-        <v>12.95</v>
-      </c>
-      <c r="E16" s="9">
-        <v>8.41</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B43" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="6">
+        <v>508.95</v>
+      </c>
+      <c r="D43" s="6">
+        <v>517.55</v>
+      </c>
+      <c r="E43" s="7">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-4.99</v>
-      </c>
-      <c r="D17" s="7">
-        <v>-0.18</v>
-      </c>
-      <c r="E17" s="9">
-        <v>4.81</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B44" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="6">
+        <v>334.2</v>
+      </c>
+      <c r="D44" s="6">
+        <v>331.15</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-3.05</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-1</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="E18" s="9">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B45" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="6">
+        <v>1992.1</v>
+      </c>
+      <c r="D45" s="6">
+        <v>1970</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-22.1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>-3.81</v>
-      </c>
-      <c r="D19" s="7">
-        <v>-2.05</v>
-      </c>
-      <c r="E19" s="9">
-        <v>1.76</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B46" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="6">
+        <v>11165</v>
+      </c>
+      <c r="D46" s="6">
+        <v>11162</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-2.68</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-3.14</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-0.46</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B47" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="6">
+        <v>1049</v>
+      </c>
+      <c r="D47" s="6">
+        <v>1060.5</v>
+      </c>
+      <c r="E47" s="7">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-2.08</v>
-      </c>
-      <c r="D21" s="7">
-        <v>-2.41</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-0.33</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B48" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="6">
+        <v>132.97</v>
+      </c>
+      <c r="D48" s="6">
+        <v>134.44</v>
+      </c>
+      <c r="E48" s="7">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="7">
-        <v>42.51</v>
-      </c>
-      <c r="D22" s="7">
-        <v>34.8</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-7.71</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B49" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="6">
+        <v>57.16</v>
+      </c>
+      <c r="D49" s="6">
+        <v>57.12</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="7">
-        <v>106.7</v>
-      </c>
-      <c r="D23" s="7">
-        <v>113.47</v>
-      </c>
-      <c r="E23" s="9">
-        <v>6.77</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B50" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="6">
+        <v>52.18</v>
+      </c>
+      <c r="D50" s="6">
+        <v>54.61</v>
+      </c>
+      <c r="E50" s="7">
+        <v>2.43</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="7">
-        <v>-43.13</v>
-      </c>
-      <c r="D24" s="7">
-        <v>-41.47</v>
-      </c>
-      <c r="E24" s="9">
-        <v>1.66</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B51" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="6">
+        <v>45.52</v>
+      </c>
+      <c r="D51" s="6">
+        <v>43.63</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-1.89</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="7">
-        <v>4</v>
-      </c>
-      <c r="D25" s="7">
-        <v>2.5</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-1.5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
+      <c r="B52" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="6">
+        <v>50.75</v>
+      </c>
+      <c r="D52" s="6">
+        <v>46.15</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-4.6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="7">
-        <v>-12.65</v>
-      </c>
-      <c r="D26" s="7">
-        <v>-10.55</v>
-      </c>
-      <c r="E26" s="9">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
+      <c r="B53" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="6">
+        <v>47.89</v>
+      </c>
+      <c r="D53" s="6">
+        <v>47.81</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-0.08</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="7">
-        <v>20.28</v>
-      </c>
-      <c r="D27" s="7">
-        <v>17.95</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-2.33</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
+      <c r="B54" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="6">
+        <v>41.3</v>
+      </c>
+      <c r="D54" s="6">
+        <v>45.89</v>
+      </c>
+      <c r="E54" s="7">
+        <v>4.59</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7">
-        <v>5.03</v>
-      </c>
-      <c r="D28" s="7">
-        <v>-0.64</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-5.67</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
+      <c r="B55" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="6">
+        <v>38.23</v>
+      </c>
+      <c r="D55" s="6">
+        <v>43.23</v>
+      </c>
+      <c r="E55" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="7">
-        <v>17.06</v>
-      </c>
-      <c r="D29" s="7">
-        <v>15.26</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-1.8</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
+      <c r="B56" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" s="6">
+        <v>23.8</v>
+      </c>
+      <c r="D56" s="6">
+        <v>-36.23</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-60.03</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="7">
-        <v>-13.29</v>
-      </c>
-      <c r="D30" s="7">
-        <v>-7.81</v>
-      </c>
-      <c r="E30" s="9">
-        <v>5.48</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
+      <c r="B57" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C57" s="6">
+        <v>102.38</v>
+      </c>
+      <c r="D57" s="6">
+        <v>53.36</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-49.02</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="7">
-        <v>6.53</v>
-      </c>
-      <c r="D31" s="7">
-        <v>7.29</v>
-      </c>
-      <c r="E31" s="9">
-        <v>0.76</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
+      <c r="B58" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="6">
+        <v>-83.34</v>
+      </c>
+      <c r="D58" s="6">
+        <v>-91.58</v>
+      </c>
+      <c r="E58" s="8">
+        <v>-8.24</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B32" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="7">
-        <v>16.39</v>
-      </c>
-      <c r="D32" s="7">
-        <v>16.96</v>
-      </c>
-      <c r="E32" s="9">
-        <v>0.57</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
+      <c r="B59" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="6">
+        <v>-52.33</v>
+      </c>
+      <c r="D59" s="6">
+        <v>-47.11</v>
+      </c>
+      <c r="E59" s="7">
+        <v>5.22</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="7">
-        <v>9.609999999999999</v>
-      </c>
-      <c r="D33" s="7">
-        <v>9.470000000000001</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-0.14</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
+      <c r="B60" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="6">
+        <v>172.12</v>
+      </c>
+      <c r="D60" s="6">
+        <v>-19</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-191.12</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="7">
-        <v>20.76</v>
-      </c>
-      <c r="D34" s="7">
-        <v>17.94</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-2.82</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
+      <c r="B61" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="6">
+        <v>25.12</v>
+      </c>
+      <c r="D61" s="6">
+        <v>10.9</v>
+      </c>
+      <c r="E61" s="8">
+        <v>-14.22</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B35" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="7">
-        <v>-3.93</v>
-      </c>
-      <c r="D35" s="7">
-        <v>-4.31</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-0.38</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="7">
-        <v>-1.87</v>
-      </c>
-      <c r="D36" s="7">
-        <v>-3.57</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-1.7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="7">
-        <v>-27.71</v>
-      </c>
-      <c r="D37" s="7">
-        <v>-24.07</v>
-      </c>
-      <c r="E37" s="9">
-        <v>3.64</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="7">
-        <v>-46.5</v>
-      </c>
-      <c r="D38" s="7">
-        <v>-44.75</v>
-      </c>
-      <c r="E38" s="9">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="7">
-        <v>-8.57</v>
-      </c>
-      <c r="D39" s="7">
-        <v>-8.48</v>
-      </c>
-      <c r="E39" s="9">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="7">
-        <v>-18.36</v>
-      </c>
-      <c r="D40" s="7">
-        <v>-17.88</v>
-      </c>
-      <c r="E40" s="9">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="7">
-        <v>-8.880000000000001</v>
-      </c>
-      <c r="D41" s="7">
-        <v>-9.48</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="7">
-        <v>-9.92</v>
-      </c>
-      <c r="D42" s="7">
-        <v>-10.73</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="7">
-        <v>12130</v>
-      </c>
-      <c r="D43" s="7">
-        <v>11920</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-210</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="7">
-        <v>484.55</v>
-      </c>
-      <c r="D44" s="7">
-        <v>508.95</v>
-      </c>
-      <c r="E44" s="9">
-        <v>24.4</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="7">
-        <v>323.6</v>
-      </c>
-      <c r="D45" s="7">
-        <v>334.2</v>
-      </c>
-      <c r="E45" s="9">
-        <v>10.6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="7">
-        <v>1990</v>
-      </c>
-      <c r="D46" s="7">
-        <v>1992.1</v>
-      </c>
-      <c r="E46" s="9">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="7">
-        <v>11100</v>
-      </c>
-      <c r="D47" s="7">
-        <v>11165</v>
-      </c>
-      <c r="E47" s="9">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="7">
-        <v>1055.9</v>
-      </c>
-      <c r="D48" s="7">
-        <v>1049</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-6.9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="7">
-        <v>134.18</v>
-      </c>
-      <c r="D49" s="7">
-        <v>132.97</v>
-      </c>
-      <c r="E49" s="8">
-        <v>-1.21</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C50" s="7">
-        <v>29</v>
-      </c>
-      <c r="D50" s="7">
-        <v>43</v>
-      </c>
-      <c r="E50" s="9">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C51" s="7">
-        <v>43</v>
-      </c>
-      <c r="D51" s="7">
-        <v>29</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="7">
-        <v>64.08</v>
-      </c>
-      <c r="D52" s="7">
-        <v>57.16</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-6.92</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="7">
-        <v>44.34</v>
-      </c>
-      <c r="D53" s="7">
-        <v>52.18</v>
-      </c>
-      <c r="E53" s="9">
-        <v>7.84</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="7">
-        <v>36.7</v>
-      </c>
-      <c r="D54" s="7">
-        <v>45.52</v>
-      </c>
-      <c r="E54" s="9">
-        <v>8.82</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="7">
-        <v>50.31</v>
-      </c>
-      <c r="D55" s="7">
-        <v>50.75</v>
-      </c>
-      <c r="E55" s="9">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="7">
-        <v>46.17</v>
-      </c>
-      <c r="D56" s="7">
-        <v>47.89</v>
-      </c>
-      <c r="E56" s="9">
-        <v>1.72</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="7">
-        <v>43.35</v>
-      </c>
-      <c r="D57" s="7">
-        <v>41.3</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-2.05</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="7">
-        <v>40.99</v>
-      </c>
-      <c r="D58" s="7">
-        <v>38.23</v>
-      </c>
-      <c r="E58" s="8">
-        <v>-2.76</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B59" s="6" t="s">
+      <c r="B62" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C59" s="7">
-        <v>36.56</v>
-      </c>
-      <c r="D59" s="7">
-        <v>23.8</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-12.76</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="7">
-        <v>242.05</v>
-      </c>
-      <c r="D60" s="7">
-        <v>102.38</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-139.67</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="7">
-        <v>-89.34</v>
-      </c>
-      <c r="D61" s="7">
-        <v>-83.34</v>
-      </c>
-      <c r="E61" s="9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="7">
-        <v>-25.53</v>
-      </c>
-      <c r="D62" s="7">
-        <v>-52.33</v>
+      <c r="C62" s="6">
+        <v>-71.15000000000001</v>
+      </c>
+      <c r="D62" s="6">
+        <v>-71.97</v>
       </c>
       <c r="E62" s="8">
-        <v>-26.8</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="7">
-        <v>-22.54</v>
-      </c>
-      <c r="D63" s="7">
-        <v>172.12</v>
-      </c>
-      <c r="E63" s="9">
-        <v>194.66</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="7">
-        <v>14.41</v>
-      </c>
-      <c r="D64" s="7">
-        <v>25.12</v>
-      </c>
-      <c r="E64" s="9">
-        <v>10.71</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="7">
-        <v>-70.48</v>
-      </c>
-      <c r="D65" s="7">
-        <v>-71.15000000000001</v>
-      </c>
-      <c r="E65" s="8">
-        <v>-0.67</v>
+        <v>-0.82</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2987,60 +2904,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E1" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>77</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="12">
-        <v>60.8</v>
-      </c>
-      <c r="C2" s="13">
+      <c r="B2" s="11">
+        <v>68.8</v>
+      </c>
+      <c r="C2" s="12">
         <v>7</v>
       </c>
-      <c r="D2" s="12">
-        <v>47.6</v>
-      </c>
-      <c r="E2" s="12">
-        <v>70</v>
-      </c>
-      <c r="F2" s="12">
-        <v>-4.3</v>
-      </c>
-      <c r="G2" s="12">
-        <v>7.8</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="D2" s="11">
+        <v>48.3</v>
+      </c>
+      <c r="E2" s="11">
+        <v>90</v>
+      </c>
+      <c r="F2" s="11">
+        <v>-5</v>
+      </c>
+      <c r="G2" s="11">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="H2" s="11">
         <v>57</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>60</v>
       </c>
     </row>
@@ -3142,49 +3059,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="15">
-        <v>0.2888</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.2249</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.1771</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.0728</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0.0359</v>
-      </c>
-      <c r="F2" s="15">
-        <v>0.0005</v>
-      </c>
-      <c r="G2" s="15">
-        <v>-0.2145</v>
+      <c r="A2" s="14">
+        <v>0.2876</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.231</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.1815</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.0757</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.0335</v>
+      </c>
+      <c r="F2" s="14">
+        <v>-0.0022</v>
+      </c>
+      <c r="G2" s="14">
+        <v>-0.2286</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="76">
   <si>
     <t>Symbol</t>
   </si>
@@ -190,16 +190,25 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>50.8 → 46.1</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>50.8</t>
-  </si>
-  <si>
-    <t>46.1</t>
+    <t>43.6 → 51.4</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>43.6</t>
+  </si>
+  <si>
+    <t>51.4</t>
+  </si>
+  <si>
+    <t>43.2 → 50.5</t>
+  </si>
+  <si>
+    <t>43.2</t>
+  </si>
+  <si>
+    <t>50.5</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -285,14 +294,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -325,13 +334,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -924,10 +933,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>11919</v>
+        <v>11800</v>
       </c>
       <c r="D2">
-        <v>-0.01</v>
+        <v>-1</v>
       </c>
       <c r="E2">
         <v>12361</v>
@@ -936,46 +945,46 @@
         <v>8506.780000000001</v>
       </c>
       <c r="G2">
-        <v>-3.58</v>
+        <v>-4.54</v>
       </c>
       <c r="H2">
-        <v>40.11</v>
+        <v>38.71</v>
       </c>
       <c r="I2">
-        <v>0.08</v>
+        <v>-2.72</v>
       </c>
       <c r="J2">
-        <v>2.57</v>
+        <v>1.18</v>
       </c>
       <c r="K2">
-        <v>16.5</v>
+        <v>15.87</v>
       </c>
       <c r="L2">
-        <v>33.84</v>
+        <v>31.26</v>
       </c>
       <c r="M2">
-        <v>28.76</v>
+        <v>28.53</v>
       </c>
       <c r="N2">
         <v>85</v>
       </c>
       <c r="O2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="P2">
-        <v>12092</v>
+        <v>12026</v>
       </c>
       <c r="Q2">
-        <v>11822.05</v>
+        <v>11828.2</v>
       </c>
       <c r="R2">
-        <v>11145.22</v>
+        <v>11188.62</v>
       </c>
       <c r="S2">
-        <v>9919.620000000001</v>
+        <v>9934.809999999999</v>
       </c>
       <c r="T2">
-        <v>20.16</v>
+        <v>18.77</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -990,34 +999,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>57.12</v>
+        <v>53.34</v>
       </c>
       <c r="Z2">
-        <v>225.57</v>
+        <v>199.03</v>
       </c>
       <c r="AA2">
-        <v>249.56</v>
+        <v>239.46</v>
       </c>
       <c r="AB2">
-        <v>-23.99</v>
+        <v>-40.42</v>
       </c>
       <c r="AC2">
-        <v>11.55</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>44.88</v>
+        <v>18.81</v>
       </c>
       <c r="AE2">
-        <v>230.89</v>
+        <v>228.11</v>
       </c>
       <c r="AF2">
-        <v>-36.23</v>
+        <v>-55.28</v>
       </c>
       <c r="AG2">
-        <v>12215.26</v>
+        <v>12215.67</v>
       </c>
       <c r="AH2">
-        <v>11428.84</v>
+        <v>11440.73</v>
       </c>
       <c r="AI2">
         <v>11623.52</v>
@@ -1026,7 +1035,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>45.68</v>
+        <v>40.52</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1037,10 +1046,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>517.55</v>
+        <v>526</v>
       </c>
       <c r="D3">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="E3">
         <v>670.25</v>
@@ -1049,46 +1058,46 @@
         <v>222.01</v>
       </c>
       <c r="G3">
-        <v>-22.78</v>
+        <v>-21.52</v>
       </c>
       <c r="H3">
-        <v>133.12</v>
+        <v>136.93</v>
       </c>
       <c r="I3">
-        <v>8.4</v>
+        <v>10.96</v>
       </c>
       <c r="J3">
-        <v>-2.83</v>
+        <v>-2.13</v>
       </c>
       <c r="K3">
-        <v>-10.05</v>
+        <v>-9.65</v>
       </c>
       <c r="L3">
-        <v>113.45</v>
+        <v>117.38</v>
       </c>
       <c r="M3">
-        <v>18.15</v>
+        <v>17.56</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P3">
-        <v>491.41</v>
+        <v>501.8</v>
       </c>
       <c r="Q3">
-        <v>492.64</v>
+        <v>491.59</v>
       </c>
       <c r="R3">
-        <v>539.9299999999999</v>
+        <v>538.51</v>
       </c>
       <c r="S3">
-        <v>430.36</v>
+        <v>431.61</v>
       </c>
       <c r="T3">
-        <v>20.26</v>
+        <v>21.87</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1103,43 +1112,43 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>54.61</v>
+        <v>56.92</v>
       </c>
       <c r="Z3">
-        <v>-12.47</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="AA3">
-        <v>-19.07</v>
+        <v>-16.98</v>
       </c>
       <c r="AB3">
-        <v>6.59</v>
+        <v>8.34</v>
       </c>
       <c r="AC3">
         <v>100</v>
       </c>
       <c r="AD3">
-        <v>92.23</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AE3">
         <v>21.96</v>
       </c>
       <c r="AF3">
-        <v>53.36</v>
+        <v>27.99</v>
       </c>
       <c r="AG3">
-        <v>550.71</v>
+        <v>546.16</v>
       </c>
       <c r="AH3">
-        <v>434.57</v>
+        <v>437.01</v>
       </c>
       <c r="AI3">
-        <v>521.85</v>
+        <v>451.64</v>
       </c>
       <c r="AJ3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AK3">
-        <v>31.13</v>
+        <v>33.04</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1150,10 +1159,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>331.15</v>
+        <v>342.1</v>
       </c>
       <c r="D4">
-        <v>-0.91</v>
+        <v>3.31</v>
       </c>
       <c r="E4">
         <v>604.85</v>
@@ -1162,46 +1171,46 @@
         <v>303.75</v>
       </c>
       <c r="G4">
-        <v>-45.25</v>
+        <v>-43.44</v>
       </c>
       <c r="H4">
-        <v>9.02</v>
+        <v>12.63</v>
       </c>
       <c r="I4">
-        <v>-0.48</v>
+        <v>5.33</v>
       </c>
       <c r="J4">
-        <v>-13.42</v>
+        <v>-7.83</v>
       </c>
       <c r="K4">
-        <v>8.08</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="L4">
-        <v>-42.07</v>
+        <v>-40.48</v>
       </c>
       <c r="M4">
-        <v>-22.86</v>
+        <v>-22.77</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
       <c r="O4">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="P4">
-        <v>327.92</v>
+        <v>331.38</v>
       </c>
       <c r="Q4">
-        <v>345.53</v>
+        <v>344.48</v>
       </c>
       <c r="R4">
-        <v>338.31</v>
+        <v>338.81</v>
       </c>
       <c r="S4">
-        <v>382.3</v>
+        <v>381.54</v>
       </c>
       <c r="T4">
-        <v>-13.38</v>
+        <v>-10.34</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1216,34 +1225,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>43.63</v>
+        <v>51.4</v>
       </c>
       <c r="Z4">
-        <v>-4.23</v>
+        <v>-3.4</v>
       </c>
       <c r="AA4">
-        <v>-1.49</v>
+        <v>-1.87</v>
       </c>
       <c r="AB4">
-        <v>-2.74</v>
+        <v>-1.52</v>
       </c>
       <c r="AC4">
-        <v>25.01</v>
+        <v>52.87</v>
       </c>
       <c r="AD4">
-        <v>13.37</v>
+        <v>30.56</v>
       </c>
       <c r="AE4">
-        <v>11.04</v>
+        <v>11.24</v>
       </c>
       <c r="AF4">
-        <v>-91.58</v>
+        <v>-19.9</v>
       </c>
       <c r="AG4">
-        <v>374.19</v>
+        <v>371.94</v>
       </c>
       <c r="AH4">
-        <v>316.87</v>
+        <v>317.02</v>
       </c>
       <c r="AI4">
         <v>357.31</v>
@@ -1252,7 +1261,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>32.56</v>
+        <v>30.36</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1263,10 +1272,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1970</v>
+        <v>1938.6</v>
       </c>
       <c r="D5">
-        <v>-1.11</v>
+        <v>-1.59</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1275,46 +1284,46 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-9.49</v>
+        <v>-10.93</v>
       </c>
       <c r="H5">
-        <v>20.73</v>
+        <v>18.8</v>
       </c>
       <c r="I5">
-        <v>-1.6</v>
+        <v>-4.08</v>
       </c>
       <c r="J5">
-        <v>-5.56</v>
+        <v>-3.5</v>
       </c>
       <c r="K5">
-        <v>17.64</v>
+        <v>14.5</v>
       </c>
       <c r="L5">
-        <v>0.72</v>
+        <v>-1.4</v>
       </c>
       <c r="M5">
-        <v>3.35</v>
+        <v>2.97</v>
       </c>
       <c r="N5">
         <v>57</v>
       </c>
       <c r="O5">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="P5">
-        <v>1989.02</v>
+        <v>1972.54</v>
       </c>
       <c r="Q5">
-        <v>2007.88</v>
+        <v>2003.74</v>
       </c>
       <c r="R5">
-        <v>1949.55</v>
+        <v>1953.14</v>
       </c>
       <c r="S5">
-        <v>1905.44</v>
+        <v>1904.88</v>
       </c>
       <c r="T5">
-        <v>3.39</v>
+        <v>1.77</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1329,43 +1338,43 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>46.15</v>
+        <v>40.54</v>
       </c>
       <c r="Z5">
-        <v>7.79</v>
+        <v>2.59</v>
       </c>
       <c r="AA5">
-        <v>18.02</v>
+        <v>14.93</v>
       </c>
       <c r="AB5">
-        <v>-10.23</v>
+        <v>-12.35</v>
       </c>
       <c r="AC5">
-        <v>18.24</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AD5">
-        <v>20.9</v>
+        <v>15.36</v>
       </c>
       <c r="AE5">
-        <v>37.32</v>
+        <v>37.11</v>
       </c>
       <c r="AF5">
-        <v>-47.11</v>
+        <v>-34.03</v>
       </c>
       <c r="AG5">
-        <v>2041.87</v>
+        <v>2049.09</v>
       </c>
       <c r="AH5">
-        <v>1973.89</v>
+        <v>1958.4</v>
       </c>
       <c r="AI5">
-        <v>1958.53</v>
+        <v>2067.13</v>
       </c>
       <c r="AJ5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AK5">
-        <v>29.61</v>
+        <v>33.54</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1376,10 +1385,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>11162</v>
+        <v>10956</v>
       </c>
       <c r="D6">
-        <v>-0.03</v>
+        <v>-1.85</v>
       </c>
       <c r="E6">
         <v>13595.75</v>
@@ -1388,46 +1397,46 @@
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-17.9</v>
+        <v>-19.42</v>
       </c>
       <c r="H6">
-        <v>27.62</v>
+        <v>25.27</v>
       </c>
       <c r="I6">
-        <v>-1.57</v>
+        <v>-5.91</v>
       </c>
       <c r="J6">
-        <v>-1.98</v>
+        <v>-2.73</v>
       </c>
       <c r="K6">
-        <v>13.11</v>
+        <v>6.86</v>
       </c>
       <c r="L6">
-        <v>-11.12</v>
+        <v>-15.46</v>
       </c>
       <c r="M6">
-        <v>23.1</v>
+        <v>22.47</v>
       </c>
       <c r="N6">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="O6">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="P6">
-        <v>11276.2</v>
+        <v>11138.6</v>
       </c>
       <c r="Q6">
-        <v>11372.1</v>
+        <v>11346.35</v>
       </c>
       <c r="R6">
-        <v>11032.68</v>
+        <v>11039.96</v>
       </c>
       <c r="S6">
-        <v>10702.66</v>
+        <v>10698.78</v>
       </c>
       <c r="T6">
-        <v>4.29</v>
+        <v>2.4</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1442,34 +1451,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>47.81</v>
+        <v>42.81</v>
       </c>
       <c r="Z6">
-        <v>44.85</v>
+        <v>14.82</v>
       </c>
       <c r="AA6">
-        <v>100.5</v>
+        <v>83.37</v>
       </c>
       <c r="AB6">
-        <v>-55.65</v>
+        <v>-68.54000000000001</v>
       </c>
       <c r="AC6">
         <v>7.08</v>
       </c>
       <c r="AD6">
-        <v>15.53</v>
+        <v>8.06</v>
       </c>
       <c r="AE6">
-        <v>253.55</v>
+        <v>252.87</v>
       </c>
       <c r="AF6">
-        <v>-19</v>
+        <v>-11.86</v>
       </c>
       <c r="AG6">
-        <v>11689.2</v>
+        <v>11709.87</v>
       </c>
       <c r="AH6">
-        <v>11055</v>
+        <v>10982.83</v>
       </c>
       <c r="AI6">
         <v>10787.84</v>
@@ -1478,7 +1487,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>20.65</v>
+        <v>21.15</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1489,10 +1498,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>1060.5</v>
+        <v>1060</v>
       </c>
       <c r="D7">
-        <v>1.1</v>
+        <v>-0.05</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1501,25 +1510,25 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-8.48</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="H7">
-        <v>32.31</v>
+        <v>32.24</v>
       </c>
       <c r="I7">
-        <v>-1.8</v>
+        <v>0.28</v>
       </c>
       <c r="J7">
-        <v>-7.36</v>
+        <v>-1.67</v>
       </c>
       <c r="K7">
-        <v>21.74</v>
+        <v>19.52</v>
       </c>
       <c r="L7">
-        <v>19.14</v>
+        <v>18.26</v>
       </c>
       <c r="M7">
-        <v>7.57</v>
+        <v>7.7</v>
       </c>
       <c r="N7">
         <v>71</v>
@@ -1528,19 +1537,19 @@
         <v>74</v>
       </c>
       <c r="P7">
-        <v>1055.26</v>
+        <v>1055.86</v>
       </c>
       <c r="Q7">
-        <v>1080.5</v>
+        <v>1078.39</v>
       </c>
       <c r="R7">
-        <v>1063.75</v>
+        <v>1065.31</v>
       </c>
       <c r="S7">
-        <v>976.83</v>
+        <v>977.1</v>
       </c>
       <c r="T7">
-        <v>8.57</v>
+        <v>8.48</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1555,34 +1564,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>45.89</v>
+        <v>45.72</v>
       </c>
       <c r="Z7">
-        <v>-3.05</v>
+        <v>-3.55</v>
       </c>
       <c r="AA7">
-        <v>3.54</v>
+        <v>2.12</v>
       </c>
       <c r="AB7">
-        <v>-6.6</v>
+        <v>-5.68</v>
       </c>
       <c r="AC7">
-        <v>12.84</v>
+        <v>21.55</v>
       </c>
       <c r="AD7">
-        <v>5.61</v>
+        <v>12.13</v>
       </c>
       <c r="AE7">
-        <v>21.88</v>
+        <v>21.44</v>
       </c>
       <c r="AF7">
-        <v>10.9</v>
+        <v>-32.87</v>
       </c>
       <c r="AG7">
-        <v>1112.95</v>
+        <v>1110.38</v>
       </c>
       <c r="AH7">
-        <v>1048.04</v>
+        <v>1046.39</v>
       </c>
       <c r="AI7">
         <v>1116.59</v>
@@ -1591,7 +1600,7 @@
         <v>48</v>
       </c>
       <c r="AK7">
-        <v>32.54</v>
+        <v>31.61</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1602,10 +1611,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>134.44</v>
+        <v>136.9</v>
       </c>
       <c r="D8">
-        <v>1.11</v>
+        <v>1.83</v>
       </c>
       <c r="E8">
         <v>148.95</v>
@@ -1614,46 +1623,46 @@
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>-9.74</v>
+        <v>-8.09</v>
       </c>
       <c r="H8">
-        <v>15.94</v>
+        <v>18.06</v>
       </c>
       <c r="I8">
-        <v>-2.06</v>
+        <v>-0.35</v>
       </c>
       <c r="J8">
-        <v>-6.18</v>
+        <v>-4.41</v>
       </c>
       <c r="K8">
-        <v>-1.98</v>
+        <v>-0.5</v>
       </c>
       <c r="L8">
-        <v>0.49</v>
+        <v>0.17</v>
       </c>
       <c r="M8">
-        <v>-0.22</v>
+        <v>0.31</v>
       </c>
       <c r="N8">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="O8">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="P8">
-        <v>135</v>
+        <v>134.9</v>
       </c>
       <c r="Q8">
-        <v>136.1</v>
+        <v>135.89</v>
       </c>
       <c r="R8">
-        <v>137.45</v>
+        <v>137.56</v>
       </c>
       <c r="S8">
-        <v>133.66</v>
+        <v>133.65</v>
       </c>
       <c r="T8">
-        <v>0.59</v>
+        <v>2.43</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1668,34 +1677,34 @@
         <v>2</v>
       </c>
       <c r="Y8">
-        <v>43.23</v>
+        <v>50.47</v>
       </c>
       <c r="Z8">
-        <v>-1.06</v>
+        <v>-0.88</v>
       </c>
       <c r="AA8">
-        <v>-0.82</v>
+        <v>-0.84</v>
       </c>
       <c r="AB8">
-        <v>-0.24</v>
+        <v>-0.05</v>
       </c>
       <c r="AC8">
-        <v>25.84</v>
+        <v>49.77</v>
       </c>
       <c r="AD8">
-        <v>41.59</v>
+        <v>36.41</v>
       </c>
       <c r="AE8">
-        <v>3.53</v>
+        <v>3.67</v>
       </c>
       <c r="AF8">
-        <v>-71.97</v>
+        <v>-39.97</v>
       </c>
       <c r="AG8">
-        <v>140.2</v>
+        <v>139.26</v>
       </c>
       <c r="AH8">
-        <v>132</v>
+        <v>132.51</v>
       </c>
       <c r="AI8">
         <v>131.91</v>
@@ -1704,7 +1713,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>18.91</v>
+        <v>20.2</v>
       </c>
     </row>
   </sheetData>
@@ -1845,7 +1854,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1885,7 +1894,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>55</v>
@@ -1903,988 +1912,1042 @@
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="B7" s="3" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>1.02</v>
-      </c>
-      <c r="D7" s="6">
-        <v>2.57</v>
-      </c>
-      <c r="E7" s="7">
-        <v>1.55</v>
+      <c r="C7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-4.04</v>
+        <v>2.57</v>
       </c>
       <c r="D8" s="6">
-        <v>-2.83</v>
+        <v>1.18</v>
       </c>
       <c r="E8" s="7">
-        <v>1.21</v>
+        <v>-1.39</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-3.99</v>
+        <v>-2.83</v>
       </c>
       <c r="D9" s="6">
-        <v>-13.42</v>
+        <v>-2.13</v>
       </c>
       <c r="E9" s="8">
-        <v>-9.43</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-4.5</v>
+        <v>-13.42</v>
       </c>
       <c r="D10" s="6">
-        <v>-5.56</v>
+        <v>-7.83</v>
       </c>
       <c r="E10" s="8">
-        <v>-1.06</v>
+        <v>5.59</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-2.88</v>
+        <v>-5.56</v>
       </c>
       <c r="D11" s="6">
-        <v>-1.98</v>
-      </c>
-      <c r="E11" s="7">
-        <v>0.9</v>
+        <v>-3.5</v>
+      </c>
+      <c r="E11" s="8">
+        <v>2.06</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-9.48</v>
+        <v>-1.98</v>
       </c>
       <c r="D12" s="6">
-        <v>-7.36</v>
+        <v>-2.73</v>
       </c>
       <c r="E12" s="7">
-        <v>2.12</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-6.47</v>
+        <v>-7.36</v>
       </c>
       <c r="D13" s="6">
-        <v>-6.18</v>
-      </c>
-      <c r="E13" s="7">
-        <v>0.29</v>
+        <v>-1.67</v>
+      </c>
+      <c r="E13" s="8">
+        <v>5.69</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>1.71</v>
+        <v>-6.18</v>
       </c>
       <c r="D14" s="6">
-        <v>0.08</v>
+        <v>-4.41</v>
       </c>
       <c r="E14" s="8">
-        <v>-1.63</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>12.95</v>
+        <v>0.08</v>
       </c>
       <c r="D15" s="6">
-        <v>8.4</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-4.55</v>
+        <v>-2.72</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-2.8</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-0.18</v>
+        <v>8.4</v>
       </c>
       <c r="D16" s="6">
-        <v>-0.48</v>
+        <v>10.96</v>
       </c>
       <c r="E16" s="8">
-        <v>-0.3</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-0.9399999999999999</v>
+        <v>-0.48</v>
       </c>
       <c r="D17" s="6">
-        <v>-1.6</v>
+        <v>5.33</v>
       </c>
       <c r="E17" s="8">
-        <v>-0.66</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-2.05</v>
+        <v>-1.6</v>
       </c>
       <c r="D18" s="6">
-        <v>-1.57</v>
+        <v>-4.08</v>
       </c>
       <c r="E18" s="7">
-        <v>0.48</v>
+        <v>-2.48</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-3.14</v>
+        <v>-1.57</v>
       </c>
       <c r="D19" s="6">
-        <v>-1.8</v>
+        <v>-5.91</v>
       </c>
       <c r="E19" s="7">
-        <v>1.34</v>
+        <v>-4.34</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>-2.41</v>
+        <v>-1.8</v>
       </c>
       <c r="D20" s="6">
-        <v>-2.06</v>
-      </c>
-      <c r="E20" s="7">
-        <v>0.35</v>
+        <v>0.28</v>
+      </c>
+      <c r="E20" s="8">
+        <v>2.08</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>34.8</v>
+        <v>-2.06</v>
       </c>
       <c r="D21" s="6">
-        <v>33.84</v>
+        <v>-0.35</v>
       </c>
       <c r="E21" s="8">
-        <v>-0.96</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C22" s="6">
-        <v>113.47</v>
+        <v>33.84</v>
       </c>
       <c r="D22" s="6">
-        <v>113.45</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-0.02</v>
+        <v>31.26</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-2.58</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C23" s="6">
-        <v>-41.47</v>
+        <v>113.45</v>
       </c>
       <c r="D23" s="6">
-        <v>-42.07</v>
+        <v>117.38</v>
       </c>
       <c r="E23" s="8">
-        <v>-0.6</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C24" s="6">
-        <v>2.5</v>
+        <v>-42.07</v>
       </c>
       <c r="D24" s="6">
-        <v>0.72</v>
+        <v>-40.48</v>
       </c>
       <c r="E24" s="8">
-        <v>-1.78</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>-10.55</v>
+        <v>0.72</v>
       </c>
       <c r="D25" s="6">
-        <v>-11.12</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-0.57</v>
+        <v>-1.4</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-2.12</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>17.95</v>
+        <v>-11.12</v>
       </c>
       <c r="D26" s="6">
-        <v>19.14</v>
+        <v>-15.46</v>
       </c>
       <c r="E26" s="7">
-        <v>1.19</v>
+        <v>-4.34</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>-0.64</v>
+        <v>19.14</v>
       </c>
       <c r="D27" s="6">
-        <v>0.49</v>
+        <v>18.26</v>
       </c>
       <c r="E27" s="7">
-        <v>1.13</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>15.26</v>
+        <v>0.49</v>
       </c>
       <c r="D28" s="6">
-        <v>16.5</v>
+        <v>0.17</v>
       </c>
       <c r="E28" s="7">
-        <v>1.24</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C29" s="6">
-        <v>-7.81</v>
+        <v>16.5</v>
       </c>
       <c r="D29" s="6">
-        <v>-10.05</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-2.24</v>
+        <v>15.87</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-0.63</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C30" s="6">
-        <v>7.29</v>
+        <v>-10.05</v>
       </c>
       <c r="D30" s="6">
-        <v>8.08</v>
-      </c>
-      <c r="E30" s="7">
-        <v>0.79</v>
+        <v>-9.65</v>
+      </c>
+      <c r="E30" s="8">
+        <v>0.4</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C31" s="6">
-        <v>16.96</v>
+        <v>8.08</v>
       </c>
       <c r="D31" s="6">
-        <v>17.64</v>
-      </c>
-      <c r="E31" s="7">
-        <v>0.68</v>
+        <v>9.539999999999999</v>
+      </c>
+      <c r="E31" s="8">
+        <v>1.46</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C32" s="6">
-        <v>9.470000000000001</v>
+        <v>17.64</v>
       </c>
       <c r="D32" s="6">
-        <v>13.11</v>
+        <v>14.5</v>
       </c>
       <c r="E32" s="7">
-        <v>3.64</v>
+        <v>-3.14</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C33" s="6">
-        <v>17.94</v>
+        <v>13.11</v>
       </c>
       <c r="D33" s="6">
-        <v>21.74</v>
+        <v>6.86</v>
       </c>
       <c r="E33" s="7">
-        <v>3.8</v>
+        <v>-6.25</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>-4.31</v>
+        <v>21.74</v>
       </c>
       <c r="D34" s="6">
-        <v>-1.98</v>
+        <v>19.52</v>
       </c>
       <c r="E34" s="7">
-        <v>2.33</v>
+        <v>-2.22</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>-3.57</v>
+        <v>-1.98</v>
       </c>
       <c r="D35" s="6">
-        <v>-3.58</v>
+        <v>-0.5</v>
       </c>
       <c r="E35" s="8">
-        <v>-0.01</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C36" s="6">
-        <v>-24.07</v>
+        <v>-3.58</v>
       </c>
       <c r="D36" s="6">
-        <v>-22.78</v>
+        <v>-4.54</v>
       </c>
       <c r="E36" s="7">
-        <v>1.29</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C37" s="6">
-        <v>-44.75</v>
+        <v>-22.78</v>
       </c>
       <c r="D37" s="6">
-        <v>-45.25</v>
+        <v>-21.52</v>
       </c>
       <c r="E37" s="8">
-        <v>-0.5</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C38" s="6">
-        <v>-8.48</v>
+        <v>-45.25</v>
       </c>
       <c r="D38" s="6">
-        <v>-9.49</v>
+        <v>-43.44</v>
       </c>
       <c r="E38" s="8">
-        <v>-1.01</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C39" s="6">
-        <v>-17.88</v>
+        <v>-9.49</v>
       </c>
       <c r="D39" s="6">
-        <v>-17.9</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-0.02</v>
+        <v>-10.93</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-1.44</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C40" s="6">
-        <v>-9.48</v>
+        <v>-17.9</v>
       </c>
       <c r="D40" s="6">
-        <v>-8.48</v>
+        <v>-19.42</v>
       </c>
       <c r="E40" s="7">
-        <v>1</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C41" s="6">
-        <v>-10.73</v>
+        <v>-8.48</v>
       </c>
       <c r="D41" s="6">
-        <v>-9.74</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="E41" s="7">
-        <v>0.99</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C42" s="6">
-        <v>11920</v>
+        <v>-9.74</v>
       </c>
       <c r="D42" s="6">
-        <v>11919</v>
+        <v>-8.09</v>
       </c>
       <c r="E42" s="8">
-        <v>-1</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C43" s="6">
-        <v>508.95</v>
+        <v>11919</v>
       </c>
       <c r="D43" s="6">
-        <v>517.55</v>
+        <v>11800</v>
       </c>
       <c r="E43" s="7">
-        <v>8.6</v>
+        <v>-119</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C44" s="6">
-        <v>334.2</v>
+        <v>517.55</v>
       </c>
       <c r="D44" s="6">
-        <v>331.15</v>
+        <v>526</v>
       </c>
       <c r="E44" s="8">
-        <v>-3.05</v>
+        <v>8.449999999999999</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C45" s="6">
-        <v>1992.1</v>
+        <v>331.15</v>
       </c>
       <c r="D45" s="6">
-        <v>1970</v>
+        <v>342.1</v>
       </c>
       <c r="E45" s="8">
-        <v>-22.1</v>
+        <v>10.95</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C46" s="6">
-        <v>11165</v>
+        <v>1970</v>
       </c>
       <c r="D46" s="6">
-        <v>11162</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-3</v>
+        <v>1938.6</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-31.4</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C47" s="6">
-        <v>1049</v>
+        <v>11162</v>
       </c>
       <c r="D47" s="6">
-        <v>1060.5</v>
+        <v>10956</v>
       </c>
       <c r="E47" s="7">
-        <v>11.5</v>
+        <v>-206</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C48" s="6">
-        <v>132.97</v>
+        <v>1060.5</v>
       </c>
       <c r="D48" s="6">
-        <v>134.44</v>
+        <v>1060</v>
       </c>
       <c r="E48" s="7">
-        <v>1.47</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C49" s="6">
-        <v>57.16</v>
+        <v>134.44</v>
       </c>
       <c r="D49" s="6">
-        <v>57.12</v>
+        <v>136.9</v>
       </c>
       <c r="E49" s="8">
-        <v>-0.04</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C50" s="6">
-        <v>52.18</v>
+        <v>43</v>
       </c>
       <c r="D50" s="6">
-        <v>54.61</v>
+        <v>29</v>
       </c>
       <c r="E50" s="7">
-        <v>2.43</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C51" s="6">
-        <v>45.52</v>
+        <v>29</v>
       </c>
       <c r="D51" s="6">
-        <v>43.63</v>
+        <v>43</v>
       </c>
       <c r="E51" s="8">
-        <v>-1.89</v>
+        <v>14</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C52" s="6">
-        <v>50.75</v>
+        <v>57.12</v>
       </c>
       <c r="D52" s="6">
-        <v>46.15</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-4.6</v>
+        <v>53.34</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-3.78</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C53" s="6">
-        <v>47.89</v>
+        <v>54.61</v>
       </c>
       <c r="D53" s="6">
-        <v>47.81</v>
+        <v>56.92</v>
       </c>
       <c r="E53" s="8">
-        <v>-0.08</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C54" s="6">
-        <v>41.3</v>
+        <v>43.63</v>
       </c>
       <c r="D54" s="6">
-        <v>45.89</v>
-      </c>
-      <c r="E54" s="7">
-        <v>4.59</v>
+        <v>51.4</v>
+      </c>
+      <c r="E54" s="8">
+        <v>7.77</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C55" s="6">
-        <v>38.23</v>
+        <v>46.15</v>
       </c>
       <c r="D55" s="6">
-        <v>43.23</v>
+        <v>40.54</v>
       </c>
       <c r="E55" s="7">
-        <v>5</v>
+        <v>-5.61</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C56" s="6">
-        <v>23.8</v>
+        <v>47.81</v>
       </c>
       <c r="D56" s="6">
-        <v>-36.23</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-60.03</v>
+        <v>42.81</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-5</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C57" s="6">
-        <v>102.38</v>
+        <v>45.89</v>
       </c>
       <c r="D57" s="6">
-        <v>53.36</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-49.02</v>
+        <v>45.72</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-0.17</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C58" s="6">
-        <v>-83.34</v>
+        <v>43.23</v>
       </c>
       <c r="D58" s="6">
-        <v>-91.58</v>
+        <v>50.47</v>
       </c>
       <c r="E58" s="8">
-        <v>-8.24</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C59" s="6">
-        <v>-52.33</v>
+        <v>-36.23</v>
       </c>
       <c r="D59" s="6">
-        <v>-47.11</v>
+        <v>-55.28</v>
       </c>
       <c r="E59" s="7">
-        <v>5.22</v>
+        <v>-19.05</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C60" s="6">
-        <v>172.12</v>
+        <v>53.36</v>
       </c>
       <c r="D60" s="6">
-        <v>-19</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-191.12</v>
+        <v>27.99</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-25.37</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C61" s="6">
-        <v>25.12</v>
+        <v>-91.58</v>
       </c>
       <c r="D61" s="6">
-        <v>10.9</v>
+        <v>-19.9</v>
       </c>
       <c r="E61" s="8">
-        <v>-14.22</v>
+        <v>71.68000000000001</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C62" s="6">
-        <v>-71.15000000000001</v>
+        <v>-47.11</v>
       </c>
       <c r="D62" s="6">
+        <v>-34.03</v>
+      </c>
+      <c r="E62" s="8">
+        <v>13.08</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="6">
+        <v>-19</v>
+      </c>
+      <c r="D63" s="6">
+        <v>-11.86</v>
+      </c>
+      <c r="E63" s="8">
+        <v>7.14</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="6">
+        <v>10.9</v>
+      </c>
+      <c r="D64" s="6">
+        <v>-32.87</v>
+      </c>
+      <c r="E64" s="7">
+        <v>-43.77</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="6">
         <v>-71.97</v>
       </c>
-      <c r="E62" s="8">
-        <v>-0.82</v>
+      <c r="D65" s="6">
+        <v>-39.97</v>
+      </c>
+      <c r="E65" s="8">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2908,28 +2971,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2943,16 +3006,16 @@
         <v>7</v>
       </c>
       <c r="D2" s="11">
-        <v>48.3</v>
+        <v>48.7</v>
       </c>
       <c r="E2" s="11">
         <v>90</v>
       </c>
       <c r="F2" s="11">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="G2" s="11">
-        <v>9.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="H2" s="11">
         <v>57</v>
@@ -3083,25 +3146,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="14">
-        <v>0.2876</v>
+        <v>0.2853</v>
       </c>
       <c r="B2" s="14">
-        <v>0.231</v>
+        <v>0.2247</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1815</v>
+        <v>0.1756</v>
       </c>
       <c r="D2" s="14">
-        <v>0.0757</v>
+        <v>0.077</v>
       </c>
       <c r="E2" s="14">
-        <v>0.0335</v>
+        <v>0.0297</v>
       </c>
       <c r="F2" s="14">
-        <v>-0.0022</v>
+        <v>0.0031</v>
       </c>
       <c r="G2" s="14">
-        <v>-0.2286</v>
+        <v>-0.2277</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="73">
   <si>
     <t>Symbol</t>
   </si>
@@ -190,25 +190,16 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>43.6 → 51.4</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>43.6</t>
+    <t>51.4 → 50.0</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>51.4</t>
   </si>
   <si>
-    <t>43.2 → 50.5</t>
-  </si>
-  <si>
-    <t>43.2</t>
-  </si>
-  <si>
-    <t>50.5</t>
+    <t>50.0</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -294,14 +285,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -334,13 +325,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -933,10 +924,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>11800</v>
+        <v>11880</v>
       </c>
       <c r="D2">
-        <v>-1</v>
+        <v>0.68</v>
       </c>
       <c r="E2">
         <v>12361</v>
@@ -945,46 +936,46 @@
         <v>8506.780000000001</v>
       </c>
       <c r="G2">
-        <v>-4.54</v>
+        <v>-3.89</v>
       </c>
       <c r="H2">
-        <v>38.71</v>
+        <v>39.65</v>
       </c>
       <c r="I2">
-        <v>-2.72</v>
+        <v>-3.89</v>
       </c>
       <c r="J2">
-        <v>1.18</v>
+        <v>1.74</v>
       </c>
       <c r="K2">
-        <v>15.87</v>
+        <v>17.11</v>
       </c>
       <c r="L2">
-        <v>31.26</v>
+        <v>32.81</v>
       </c>
       <c r="M2">
-        <v>28.53</v>
+        <v>29.02</v>
       </c>
       <c r="N2">
         <v>85</v>
       </c>
       <c r="O2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P2">
-        <v>12026</v>
+        <v>11929.8</v>
       </c>
       <c r="Q2">
-        <v>11828.2</v>
+        <v>11836.35</v>
       </c>
       <c r="R2">
-        <v>11188.62</v>
+        <v>11231.9</v>
       </c>
       <c r="S2">
-        <v>9934.809999999999</v>
+        <v>9949.940000000001</v>
       </c>
       <c r="T2">
-        <v>18.77</v>
+        <v>19.4</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -999,34 +990,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>53.34</v>
+        <v>55.47</v>
       </c>
       <c r="Z2">
-        <v>199.03</v>
+        <v>182.35</v>
       </c>
       <c r="AA2">
-        <v>239.46</v>
+        <v>228.03</v>
       </c>
       <c r="AB2">
-        <v>-40.42</v>
+        <v>-45.68</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD2">
-        <v>18.81</v>
+        <v>5.05</v>
       </c>
       <c r="AE2">
-        <v>228.11</v>
+        <v>223.75</v>
       </c>
       <c r="AF2">
-        <v>-55.28</v>
+        <v>-16.95</v>
       </c>
       <c r="AG2">
-        <v>12215.67</v>
+        <v>12220.81</v>
       </c>
       <c r="AH2">
-        <v>11440.73</v>
+        <v>11451.89</v>
       </c>
       <c r="AI2">
         <v>11623.52</v>
@@ -1035,7 +1026,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>40.52</v>
+        <v>36.45</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1046,10 +1037,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>526</v>
+        <v>514.1</v>
       </c>
       <c r="D3">
-        <v>1.63</v>
+        <v>-2.26</v>
       </c>
       <c r="E3">
         <v>670.25</v>
@@ -1058,25 +1049,25 @@
         <v>222.01</v>
       </c>
       <c r="G3">
-        <v>-21.52</v>
+        <v>-23.3</v>
       </c>
       <c r="H3">
-        <v>136.93</v>
+        <v>131.57</v>
       </c>
       <c r="I3">
-        <v>10.96</v>
+        <v>8.93</v>
       </c>
       <c r="J3">
-        <v>-2.13</v>
+        <v>-6.02</v>
       </c>
       <c r="K3">
-        <v>-9.65</v>
+        <v>-8.65</v>
       </c>
       <c r="L3">
-        <v>117.38</v>
+        <v>120.69</v>
       </c>
       <c r="M3">
-        <v>17.56</v>
+        <v>17.35</v>
       </c>
       <c r="N3">
         <v>99</v>
@@ -1085,19 +1076,19 @@
         <v>91</v>
       </c>
       <c r="P3">
-        <v>501.8</v>
+        <v>510.23</v>
       </c>
       <c r="Q3">
-        <v>491.59</v>
+        <v>490.25</v>
       </c>
       <c r="R3">
-        <v>538.51</v>
+        <v>536.8099999999999</v>
       </c>
       <c r="S3">
-        <v>431.61</v>
+        <v>432.79</v>
       </c>
       <c r="T3">
-        <v>21.87</v>
+        <v>18.79</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1112,43 +1103,43 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>56.92</v>
+        <v>52.84</v>
       </c>
       <c r="Z3">
-        <v>-8.640000000000001</v>
+        <v>-6.49</v>
       </c>
       <c r="AA3">
-        <v>-16.98</v>
+        <v>-14.88</v>
       </c>
       <c r="AB3">
-        <v>8.34</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="AC3">
-        <v>100</v>
+        <v>95.05</v>
       </c>
       <c r="AD3">
-        <v>97.90000000000001</v>
+        <v>98.34999999999999</v>
       </c>
       <c r="AE3">
-        <v>21.96</v>
+        <v>21.51</v>
       </c>
       <c r="AF3">
-        <v>27.99</v>
+        <v>-35.75</v>
       </c>
       <c r="AG3">
-        <v>546.16</v>
+        <v>540.89</v>
       </c>
       <c r="AH3">
-        <v>437.01</v>
+        <v>439.6</v>
       </c>
       <c r="AI3">
-        <v>451.64</v>
+        <v>455.28</v>
       </c>
       <c r="AJ3" t="s">
         <v>47</v>
       </c>
       <c r="AK3">
-        <v>33.04</v>
+        <v>34.7</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1159,10 +1150,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>342.1</v>
+        <v>339.95</v>
       </c>
       <c r="D4">
-        <v>3.31</v>
+        <v>-0.63</v>
       </c>
       <c r="E4">
         <v>604.85</v>
@@ -1171,25 +1162,25 @@
         <v>303.75</v>
       </c>
       <c r="G4">
-        <v>-43.44</v>
+        <v>-43.8</v>
       </c>
       <c r="H4">
-        <v>12.63</v>
+        <v>11.92</v>
       </c>
       <c r="I4">
-        <v>5.33</v>
+        <v>4.33</v>
       </c>
       <c r="J4">
-        <v>-7.83</v>
+        <v>-6.38</v>
       </c>
       <c r="K4">
-        <v>9.539999999999999</v>
+        <v>10.02</v>
       </c>
       <c r="L4">
-        <v>-40.48</v>
+        <v>-40.65</v>
       </c>
       <c r="M4">
-        <v>-22.77</v>
+        <v>-23</v>
       </c>
       <c r="N4">
         <v>15</v>
@@ -1198,19 +1189,19 @@
         <v>23</v>
       </c>
       <c r="P4">
-        <v>331.38</v>
+        <v>334.2</v>
       </c>
       <c r="Q4">
-        <v>344.48</v>
+        <v>343.46</v>
       </c>
       <c r="R4">
-        <v>338.81</v>
+        <v>339.22</v>
       </c>
       <c r="S4">
-        <v>381.54</v>
+        <v>380.76</v>
       </c>
       <c r="T4">
-        <v>-10.34</v>
+        <v>-10.72</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1225,34 +1216,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>51.4</v>
+        <v>49.95</v>
       </c>
       <c r="Z4">
-        <v>-3.4</v>
+        <v>-2.88</v>
       </c>
       <c r="AA4">
-        <v>-1.87</v>
+        <v>-2.07</v>
       </c>
       <c r="AB4">
-        <v>-1.52</v>
+        <v>-0.8</v>
       </c>
       <c r="AC4">
-        <v>52.87</v>
+        <v>65.45</v>
       </c>
       <c r="AD4">
-        <v>30.56</v>
+        <v>47.78</v>
       </c>
       <c r="AE4">
-        <v>11.24</v>
+        <v>10.94</v>
       </c>
       <c r="AF4">
-        <v>-19.9</v>
+        <v>-54.02</v>
       </c>
       <c r="AG4">
-        <v>371.94</v>
+        <v>369.94</v>
       </c>
       <c r="AH4">
-        <v>317.02</v>
+        <v>316.98</v>
       </c>
       <c r="AI4">
         <v>357.31</v>
@@ -1261,7 +1252,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>30.36</v>
+        <v>28.44</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1272,10 +1263,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1938.6</v>
+        <v>1938.1</v>
       </c>
       <c r="D5">
-        <v>-1.59</v>
+        <v>-0.03</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1284,46 +1275,46 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-10.93</v>
+        <v>-10.96</v>
       </c>
       <c r="H5">
-        <v>18.8</v>
+        <v>18.77</v>
       </c>
       <c r="I5">
-        <v>-4.08</v>
+        <v>-1.72</v>
       </c>
       <c r="J5">
-        <v>-3.5</v>
+        <v>-4.12</v>
       </c>
       <c r="K5">
-        <v>14.5</v>
+        <v>16.46</v>
       </c>
       <c r="L5">
-        <v>-1.4</v>
+        <v>-3.2</v>
       </c>
       <c r="M5">
-        <v>2.97</v>
+        <v>3.24</v>
       </c>
       <c r="N5">
         <v>57</v>
       </c>
       <c r="O5">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P5">
-        <v>1972.54</v>
+        <v>1965.76</v>
       </c>
       <c r="Q5">
-        <v>2003.74</v>
+        <v>1999.05</v>
       </c>
       <c r="R5">
-        <v>1953.14</v>
+        <v>1956.3</v>
       </c>
       <c r="S5">
-        <v>1904.88</v>
+        <v>1904.09</v>
       </c>
       <c r="T5">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1338,43 +1329,43 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>40.54</v>
+        <v>40.45</v>
       </c>
       <c r="Z5">
-        <v>2.59</v>
+        <v>-1.56</v>
       </c>
       <c r="AA5">
-        <v>14.93</v>
+        <v>11.64</v>
       </c>
       <c r="AB5">
-        <v>-12.35</v>
+        <v>-13.2</v>
       </c>
       <c r="AC5">
-        <v>9.619999999999999</v>
+        <v>0</v>
       </c>
       <c r="AD5">
-        <v>15.36</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="AE5">
-        <v>37.11</v>
+        <v>35.81</v>
       </c>
       <c r="AF5">
-        <v>-34.03</v>
+        <v>5.45</v>
       </c>
       <c r="AG5">
-        <v>2049.09</v>
+        <v>2051.03</v>
       </c>
       <c r="AH5">
-        <v>1958.4</v>
+        <v>1947.07</v>
       </c>
       <c r="AI5">
-        <v>2067.13</v>
+        <v>2049.88</v>
       </c>
       <c r="AJ5" t="s">
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>33.54</v>
+        <v>37.27</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1385,10 +1376,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>10956</v>
+        <v>11046</v>
       </c>
       <c r="D6">
-        <v>-1.85</v>
+        <v>0.82</v>
       </c>
       <c r="E6">
         <v>13595.75</v>
@@ -1397,46 +1388,46 @@
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-19.42</v>
+        <v>-18.75</v>
       </c>
       <c r="H6">
-        <v>25.27</v>
+        <v>26.3</v>
       </c>
       <c r="I6">
-        <v>-5.91</v>
+        <v>-2.33</v>
       </c>
       <c r="J6">
-        <v>-2.73</v>
+        <v>-3.7</v>
       </c>
       <c r="K6">
-        <v>6.86</v>
+        <v>10.07</v>
       </c>
       <c r="L6">
-        <v>-15.46</v>
+        <v>-14.49</v>
       </c>
       <c r="M6">
-        <v>22.47</v>
+        <v>22.4</v>
       </c>
       <c r="N6">
         <v>29</v>
       </c>
       <c r="O6">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="P6">
-        <v>11138.6</v>
+        <v>11085.8</v>
       </c>
       <c r="Q6">
-        <v>11346.35</v>
+        <v>11321.15</v>
       </c>
       <c r="R6">
-        <v>11039.96</v>
+        <v>11048.82</v>
       </c>
       <c r="S6">
-        <v>10698.78</v>
+        <v>10695.27</v>
       </c>
       <c r="T6">
-        <v>2.4</v>
+        <v>3.28</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1451,34 +1442,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>42.81</v>
+        <v>45.49</v>
       </c>
       <c r="Z6">
-        <v>14.82</v>
+        <v>-1.7</v>
       </c>
       <c r="AA6">
-        <v>83.37</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="AB6">
-        <v>-68.54000000000001</v>
+        <v>-68.05</v>
       </c>
       <c r="AC6">
-        <v>7.08</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="AD6">
-        <v>8.06</v>
+        <v>7.57</v>
       </c>
       <c r="AE6">
-        <v>252.87</v>
+        <v>246.81</v>
       </c>
       <c r="AF6">
-        <v>-11.86</v>
+        <v>-37.91</v>
       </c>
       <c r="AG6">
-        <v>11709.87</v>
+        <v>11694.96</v>
       </c>
       <c r="AH6">
-        <v>10982.83</v>
+        <v>10947.34</v>
       </c>
       <c r="AI6">
         <v>10787.84</v>
@@ -1487,7 +1478,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>21.15</v>
+        <v>21.58</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1498,10 +1489,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>1060</v>
+        <v>1054.1</v>
       </c>
       <c r="D7">
-        <v>-0.05</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1510,46 +1501,46 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-8.529999999999999</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="H7">
-        <v>32.24</v>
+        <v>31.51</v>
       </c>
       <c r="I7">
-        <v>0.28</v>
+        <v>0.02</v>
       </c>
       <c r="J7">
-        <v>-1.67</v>
+        <v>-4.36</v>
       </c>
       <c r="K7">
-        <v>19.52</v>
+        <v>19.23</v>
       </c>
       <c r="L7">
-        <v>18.26</v>
+        <v>12.77</v>
       </c>
       <c r="M7">
-        <v>7.7</v>
+        <v>7.56</v>
       </c>
       <c r="N7">
         <v>71</v>
       </c>
       <c r="O7">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="P7">
-        <v>1055.86</v>
+        <v>1055.9</v>
       </c>
       <c r="Q7">
-        <v>1078.39</v>
+        <v>1076.43</v>
       </c>
       <c r="R7">
-        <v>1065.31</v>
+        <v>1066.3</v>
       </c>
       <c r="S7">
-        <v>977.1</v>
+        <v>977.23</v>
       </c>
       <c r="T7">
-        <v>8.48</v>
+        <v>7.87</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1564,34 +1555,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>45.72</v>
+        <v>43.69</v>
       </c>
       <c r="Z7">
-        <v>-3.55</v>
+        <v>-4.38</v>
       </c>
       <c r="AA7">
-        <v>2.12</v>
+        <v>0.82</v>
       </c>
       <c r="AB7">
-        <v>-5.68</v>
+        <v>-5.2</v>
       </c>
       <c r="AC7">
-        <v>21.55</v>
+        <v>27.35</v>
       </c>
       <c r="AD7">
-        <v>12.13</v>
+        <v>20.58</v>
       </c>
       <c r="AE7">
-        <v>21.44</v>
+        <v>20.62</v>
       </c>
       <c r="AF7">
-        <v>-32.87</v>
+        <v>-24.36</v>
       </c>
       <c r="AG7">
-        <v>1110.38</v>
+        <v>1109.36</v>
       </c>
       <c r="AH7">
-        <v>1046.39</v>
+        <v>1043.49</v>
       </c>
       <c r="AI7">
         <v>1116.59</v>
@@ -1600,7 +1591,7 @@
         <v>48</v>
       </c>
       <c r="AK7">
-        <v>31.61</v>
+        <v>31.55</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1611,10 +1602,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>136.9</v>
+        <v>137.66</v>
       </c>
       <c r="D8">
-        <v>1.83</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E8">
         <v>148.95</v>
@@ -1623,46 +1614,46 @@
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>-8.09</v>
+        <v>-7.58</v>
       </c>
       <c r="H8">
-        <v>18.06</v>
+        <v>18.71</v>
       </c>
       <c r="I8">
-        <v>-0.35</v>
+        <v>1.2</v>
       </c>
       <c r="J8">
-        <v>-4.41</v>
+        <v>-2.47</v>
       </c>
       <c r="K8">
-        <v>-0.5</v>
+        <v>1.69</v>
       </c>
       <c r="L8">
-        <v>0.17</v>
+        <v>3.58</v>
       </c>
       <c r="M8">
-        <v>0.31</v>
+        <v>0.04</v>
       </c>
       <c r="N8">
         <v>43</v>
       </c>
       <c r="O8">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="P8">
-        <v>134.9</v>
+        <v>135.23</v>
       </c>
       <c r="Q8">
-        <v>135.89</v>
+        <v>135.74</v>
       </c>
       <c r="R8">
-        <v>137.56</v>
+        <v>137.67</v>
       </c>
       <c r="S8">
-        <v>133.65</v>
+        <v>133.66</v>
       </c>
       <c r="T8">
-        <v>2.43</v>
+        <v>2.99</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1677,34 +1668,34 @@
         <v>2</v>
       </c>
       <c r="Y8">
-        <v>50.47</v>
+        <v>52.48</v>
       </c>
       <c r="Z8">
-        <v>-0.88</v>
+        <v>-0.67</v>
       </c>
       <c r="AA8">
-        <v>-0.84</v>
+        <v>-0.8</v>
       </c>
       <c r="AB8">
-        <v>-0.05</v>
+        <v>0.13</v>
       </c>
       <c r="AC8">
-        <v>49.77</v>
+        <v>81.45</v>
       </c>
       <c r="AD8">
-        <v>36.41</v>
+        <v>52.35</v>
       </c>
       <c r="AE8">
-        <v>3.67</v>
+        <v>3.6</v>
       </c>
       <c r="AF8">
-        <v>-39.97</v>
+        <v>-51.26</v>
       </c>
       <c r="AG8">
-        <v>139.26</v>
+        <v>138.43</v>
       </c>
       <c r="AH8">
-        <v>132.51</v>
+        <v>133.05</v>
       </c>
       <c r="AI8">
         <v>131.91</v>
@@ -1713,7 +1704,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>20.2</v>
+        <v>21.33</v>
       </c>
     </row>
   </sheetData>
@@ -1854,7 +1845,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1912,1042 +1903,988 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C4" s="4" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+      <c r="E6" s="3" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>67</v>
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>1.18</v>
+      </c>
+      <c r="D7" s="6">
+        <v>1.74</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>2.57</v>
+        <v>-2.13</v>
       </c>
       <c r="D8" s="6">
-        <v>1.18</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-1.39</v>
+        <v>-6.02</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-3.89</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-2.83</v>
+        <v>-7.83</v>
       </c>
       <c r="D9" s="6">
-        <v>-2.13</v>
-      </c>
-      <c r="E9" s="8">
-        <v>0.7</v>
+        <v>-6.38</v>
+      </c>
+      <c r="E9" s="7">
+        <v>1.45</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-13.42</v>
+        <v>-3.5</v>
       </c>
       <c r="D10" s="6">
-        <v>-7.83</v>
+        <v>-4.12</v>
       </c>
       <c r="E10" s="8">
-        <v>5.59</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-5.56</v>
+        <v>-2.73</v>
       </c>
       <c r="D11" s="6">
-        <v>-3.5</v>
+        <v>-3.7</v>
       </c>
       <c r="E11" s="8">
-        <v>2.06</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-1.98</v>
+        <v>-1.67</v>
       </c>
       <c r="D12" s="6">
-        <v>-2.73</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-0.75</v>
+        <v>-4.36</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-2.69</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-7.36</v>
+        <v>-4.41</v>
       </c>
       <c r="D13" s="6">
-        <v>-1.67</v>
-      </c>
-      <c r="E13" s="8">
-        <v>5.69</v>
+        <v>-2.47</v>
+      </c>
+      <c r="E13" s="7">
+        <v>1.94</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C14" s="6">
-        <v>-6.18</v>
+        <v>-2.72</v>
       </c>
       <c r="D14" s="6">
-        <v>-4.41</v>
+        <v>-3.89</v>
       </c>
       <c r="E14" s="8">
-        <v>1.77</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>0.08</v>
+        <v>10.96</v>
       </c>
       <c r="D15" s="6">
-        <v>-2.72</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-2.8</v>
+        <v>8.93</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-2.03</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>8.4</v>
+        <v>5.33</v>
       </c>
       <c r="D16" s="6">
-        <v>10.96</v>
+        <v>4.33</v>
       </c>
       <c r="E16" s="8">
-        <v>2.56</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-0.48</v>
+        <v>-4.08</v>
       </c>
       <c r="D17" s="6">
-        <v>5.33</v>
-      </c>
-      <c r="E17" s="8">
-        <v>5.81</v>
+        <v>-1.72</v>
+      </c>
+      <c r="E17" s="7">
+        <v>2.36</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-1.6</v>
+        <v>-5.91</v>
       </c>
       <c r="D18" s="6">
-        <v>-4.08</v>
+        <v>-2.33</v>
       </c>
       <c r="E18" s="7">
-        <v>-2.48</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-1.57</v>
+        <v>0.28</v>
       </c>
       <c r="D19" s="6">
-        <v>-5.91</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-4.34</v>
+        <v>0.02</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-0.26</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>-1.8</v>
+        <v>-0.35</v>
       </c>
       <c r="D20" s="6">
-        <v>0.28</v>
-      </c>
-      <c r="E20" s="8">
-        <v>2.08</v>
+        <v>1.2</v>
+      </c>
+      <c r="E20" s="7">
+        <v>1.55</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C21" s="6">
-        <v>-2.06</v>
+        <v>31.26</v>
       </c>
       <c r="D21" s="6">
-        <v>-0.35</v>
-      </c>
-      <c r="E21" s="8">
-        <v>1.71</v>
+        <v>32.81</v>
+      </c>
+      <c r="E21" s="7">
+        <v>1.55</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C22" s="6">
-        <v>33.84</v>
+        <v>117.38</v>
       </c>
       <c r="D22" s="6">
-        <v>31.26</v>
+        <v>120.69</v>
       </c>
       <c r="E22" s="7">
-        <v>-2.58</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C23" s="6">
-        <v>113.45</v>
+        <v>-40.48</v>
       </c>
       <c r="D23" s="6">
-        <v>117.38</v>
+        <v>-40.65</v>
       </c>
       <c r="E23" s="8">
-        <v>3.93</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C24" s="6">
-        <v>-42.07</v>
+        <v>-1.4</v>
       </c>
       <c r="D24" s="6">
-        <v>-40.48</v>
+        <v>-3.2</v>
       </c>
       <c r="E24" s="8">
-        <v>1.59</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>0.72</v>
+        <v>-15.46</v>
       </c>
       <c r="D25" s="6">
-        <v>-1.4</v>
+        <v>-14.49</v>
       </c>
       <c r="E25" s="7">
-        <v>-2.12</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>-11.12</v>
+        <v>18.26</v>
       </c>
       <c r="D26" s="6">
-        <v>-15.46</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-4.34</v>
+        <v>12.77</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-5.49</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>19.14</v>
+        <v>0.17</v>
       </c>
       <c r="D27" s="6">
-        <v>18.26</v>
+        <v>3.58</v>
       </c>
       <c r="E27" s="7">
-        <v>-0.88</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C28" s="6">
-        <v>0.49</v>
+        <v>15.87</v>
       </c>
       <c r="D28" s="6">
-        <v>0.17</v>
+        <v>17.11</v>
       </c>
       <c r="E28" s="7">
-        <v>-0.32</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C29" s="6">
-        <v>16.5</v>
+        <v>-9.65</v>
       </c>
       <c r="D29" s="6">
-        <v>15.87</v>
+        <v>-8.65</v>
       </c>
       <c r="E29" s="7">
-        <v>-0.63</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C30" s="6">
-        <v>-10.05</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="D30" s="6">
-        <v>-9.65</v>
-      </c>
-      <c r="E30" s="8">
-        <v>0.4</v>
+        <v>10.02</v>
+      </c>
+      <c r="E30" s="7">
+        <v>0.48</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C31" s="6">
-        <v>8.08</v>
+        <v>14.5</v>
       </c>
       <c r="D31" s="6">
-        <v>9.539999999999999</v>
-      </c>
-      <c r="E31" s="8">
-        <v>1.46</v>
+        <v>16.46</v>
+      </c>
+      <c r="E31" s="7">
+        <v>1.96</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C32" s="6">
-        <v>17.64</v>
+        <v>6.86</v>
       </c>
       <c r="D32" s="6">
-        <v>14.5</v>
+        <v>10.07</v>
       </c>
       <c r="E32" s="7">
-        <v>-3.14</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C33" s="6">
-        <v>13.11</v>
+        <v>19.52</v>
       </c>
       <c r="D33" s="6">
-        <v>6.86</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-6.25</v>
+        <v>19.23</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-0.29</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>21.74</v>
+        <v>-0.5</v>
       </c>
       <c r="D34" s="6">
-        <v>19.52</v>
+        <v>1.69</v>
       </c>
       <c r="E34" s="7">
-        <v>-2.22</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C35" s="6">
-        <v>-1.98</v>
+        <v>-4.54</v>
       </c>
       <c r="D35" s="6">
-        <v>-0.5</v>
-      </c>
-      <c r="E35" s="8">
-        <v>1.48</v>
+        <v>-3.89</v>
+      </c>
+      <c r="E35" s="7">
+        <v>0.65</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C36" s="6">
-        <v>-3.58</v>
+        <v>-21.52</v>
       </c>
       <c r="D36" s="6">
-        <v>-4.54</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-0.96</v>
+        <v>-23.3</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-1.78</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C37" s="6">
-        <v>-22.78</v>
+        <v>-43.44</v>
       </c>
       <c r="D37" s="6">
-        <v>-21.52</v>
+        <v>-43.8</v>
       </c>
       <c r="E37" s="8">
-        <v>1.26</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C38" s="6">
-        <v>-45.25</v>
+        <v>-10.93</v>
       </c>
       <c r="D38" s="6">
-        <v>-43.44</v>
+        <v>-10.96</v>
       </c>
       <c r="E38" s="8">
-        <v>1.81</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C39" s="6">
-        <v>-9.49</v>
+        <v>-19.42</v>
       </c>
       <c r="D39" s="6">
-        <v>-10.93</v>
+        <v>-18.75</v>
       </c>
       <c r="E39" s="7">
-        <v>-1.44</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C40" s="6">
-        <v>-17.9</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="D40" s="6">
-        <v>-19.42</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-1.52</v>
+        <v>-9.039999999999999</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-0.51</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C41" s="6">
-        <v>-8.48</v>
+        <v>-8.09</v>
       </c>
       <c r="D41" s="6">
-        <v>-8.529999999999999</v>
+        <v>-7.58</v>
       </c>
       <c r="E41" s="7">
-        <v>-0.05</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C42" s="6">
-        <v>-9.74</v>
+        <v>11800</v>
       </c>
       <c r="D42" s="6">
-        <v>-8.09</v>
-      </c>
-      <c r="E42" s="8">
-        <v>1.65</v>
+        <v>11880</v>
+      </c>
+      <c r="E42" s="7">
+        <v>80</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C43" s="6">
-        <v>11919</v>
+        <v>526</v>
       </c>
       <c r="D43" s="6">
-        <v>11800</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-119</v>
+        <v>514.1</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-11.9</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C44" s="6">
-        <v>517.55</v>
+        <v>342.1</v>
       </c>
       <c r="D44" s="6">
-        <v>526</v>
+        <v>339.95</v>
       </c>
       <c r="E44" s="8">
-        <v>8.449999999999999</v>
+        <v>-2.15</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C45" s="6">
-        <v>331.15</v>
+        <v>1938.6</v>
       </c>
       <c r="D45" s="6">
-        <v>342.1</v>
+        <v>1938.1</v>
       </c>
       <c r="E45" s="8">
-        <v>10.95</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C46" s="6">
-        <v>1970</v>
+        <v>10956</v>
       </c>
       <c r="D46" s="6">
-        <v>1938.6</v>
+        <v>11046</v>
       </c>
       <c r="E46" s="7">
-        <v>-31.4</v>
+        <v>90</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C47" s="6">
-        <v>11162</v>
+        <v>1060</v>
       </c>
       <c r="D47" s="6">
-        <v>10956</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-206</v>
+        <v>1054.1</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-5.9</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C48" s="6">
-        <v>1060.5</v>
+        <v>136.9</v>
       </c>
       <c r="D48" s="6">
-        <v>1060</v>
+        <v>137.66</v>
       </c>
       <c r="E48" s="7">
-        <v>-0.5</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C49" s="6">
-        <v>134.44</v>
+        <v>53.34</v>
       </c>
       <c r="D49" s="6">
-        <v>136.9</v>
-      </c>
-      <c r="E49" s="8">
-        <v>2.46</v>
+        <v>55.47</v>
+      </c>
+      <c r="E49" s="7">
+        <v>2.13</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C50" s="6">
-        <v>43</v>
+        <v>56.92</v>
       </c>
       <c r="D50" s="6">
-        <v>29</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-14</v>
+        <v>52.84</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-4.08</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C51" s="6">
-        <v>29</v>
+        <v>51.4</v>
       </c>
       <c r="D51" s="6">
-        <v>43</v>
+        <v>49.95</v>
       </c>
       <c r="E51" s="8">
-        <v>14</v>
+        <v>-1.45</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C52" s="6">
-        <v>57.12</v>
+        <v>40.54</v>
       </c>
       <c r="D52" s="6">
-        <v>53.34</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-3.78</v>
+        <v>40.45</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C53" s="6">
-        <v>54.61</v>
+        <v>42.81</v>
       </c>
       <c r="D53" s="6">
-        <v>56.92</v>
-      </c>
-      <c r="E53" s="8">
-        <v>2.31</v>
+        <v>45.49</v>
+      </c>
+      <c r="E53" s="7">
+        <v>2.68</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C54" s="6">
-        <v>43.63</v>
+        <v>45.72</v>
       </c>
       <c r="D54" s="6">
-        <v>51.4</v>
+        <v>43.69</v>
       </c>
       <c r="E54" s="8">
-        <v>7.77</v>
+        <v>-2.03</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C55" s="6">
-        <v>46.15</v>
+        <v>50.47</v>
       </c>
       <c r="D55" s="6">
-        <v>40.54</v>
+        <v>52.48</v>
       </c>
       <c r="E55" s="7">
-        <v>-5.61</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C56" s="6">
-        <v>47.81</v>
+        <v>-55.28</v>
       </c>
       <c r="D56" s="6">
-        <v>42.81</v>
+        <v>-16.95</v>
       </c>
       <c r="E56" s="7">
-        <v>-5</v>
+        <v>38.33</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C57" s="6">
-        <v>45.89</v>
+        <v>27.99</v>
       </c>
       <c r="D57" s="6">
-        <v>45.72</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-0.17</v>
+        <v>-35.75</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-63.74</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C58" s="6">
-        <v>43.23</v>
+        <v>-19.9</v>
       </c>
       <c r="D58" s="6">
-        <v>50.47</v>
+        <v>-54.02</v>
       </c>
       <c r="E58" s="8">
-        <v>7.24</v>
+        <v>-34.12</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C59" s="6">
-        <v>-36.23</v>
+        <v>-34.03</v>
       </c>
       <c r="D59" s="6">
-        <v>-55.28</v>
+        <v>5.45</v>
       </c>
       <c r="E59" s="7">
-        <v>-19.05</v>
+        <v>39.48</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C60" s="6">
-        <v>53.36</v>
+        <v>-11.86</v>
       </c>
       <c r="D60" s="6">
-        <v>27.99</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-25.37</v>
+        <v>-37.91</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-26.05</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C61" s="6">
-        <v>-91.58</v>
+        <v>-32.87</v>
       </c>
       <c r="D61" s="6">
-        <v>-19.9</v>
-      </c>
-      <c r="E61" s="8">
-        <v>71.68000000000001</v>
+        <v>-24.36</v>
+      </c>
+      <c r="E61" s="7">
+        <v>8.51</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C62" s="6">
-        <v>-47.11</v>
+        <v>-39.97</v>
       </c>
       <c r="D62" s="6">
-        <v>-34.03</v>
+        <v>-51.26</v>
       </c>
       <c r="E62" s="8">
-        <v>13.08</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="6">
-        <v>-19</v>
-      </c>
-      <c r="D63" s="6">
-        <v>-11.86</v>
-      </c>
-      <c r="E63" s="8">
-        <v>7.14</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="6">
-        <v>10.9</v>
-      </c>
-      <c r="D64" s="6">
-        <v>-32.87</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-43.77</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="6">
-        <v>-71.97</v>
-      </c>
-      <c r="D65" s="6">
-        <v>-39.97</v>
-      </c>
-      <c r="E65" s="8">
-        <v>32</v>
+        <v>-11.29</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2971,28 +2908,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>72</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3006,16 +2943,16 @@
         <v>7</v>
       </c>
       <c r="D2" s="11">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="E2" s="11">
         <v>90</v>
       </c>
       <c r="F2" s="11">
-        <v>-3</v>
+        <v>-3.6</v>
       </c>
       <c r="G2" s="11">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="H2" s="11">
         <v>57</v>
@@ -3146,25 +3083,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="14">
-        <v>0.2853</v>
+        <v>0.2902</v>
       </c>
       <c r="B2" s="14">
-        <v>0.2247</v>
+        <v>0.224</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1756</v>
+        <v>0.1735</v>
       </c>
       <c r="D2" s="14">
-        <v>0.077</v>
+        <v>0.0756</v>
       </c>
       <c r="E2" s="14">
-        <v>0.0297</v>
+        <v>0.03240000000000001</v>
       </c>
       <c r="F2" s="14">
-        <v>0.0031</v>
+        <v>0.0004</v>
       </c>
       <c r="G2" s="14">
-        <v>-0.2277</v>
+        <v>-0.23</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="64">
   <si>
     <t>Symbol</t>
   </si>
@@ -172,34 +172,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>51.4 → 50.0</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>51.4</t>
-  </si>
-  <si>
-    <t>50.0</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -401,18 +374,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -924,10 +896,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>11880</v>
+        <v>11790</v>
       </c>
       <c r="D2">
-        <v>0.68</v>
+        <v>-0.76</v>
       </c>
       <c r="E2">
         <v>12361</v>
@@ -936,25 +908,25 @@
         <v>8506.780000000001</v>
       </c>
       <c r="G2">
-        <v>-3.89</v>
+        <v>-4.62</v>
       </c>
       <c r="H2">
-        <v>39.65</v>
+        <v>38.6</v>
       </c>
       <c r="I2">
-        <v>-3.89</v>
+        <v>-2.8</v>
       </c>
       <c r="J2">
-        <v>1.74</v>
+        <v>0.62</v>
       </c>
       <c r="K2">
-        <v>17.11</v>
+        <v>16.57</v>
       </c>
       <c r="L2">
-        <v>32.81</v>
+        <v>31.61</v>
       </c>
       <c r="M2">
-        <v>29.02</v>
+        <v>29</v>
       </c>
       <c r="N2">
         <v>85</v>
@@ -963,19 +935,19 @@
         <v>79</v>
       </c>
       <c r="P2">
-        <v>11929.8</v>
+        <v>11861.8</v>
       </c>
       <c r="Q2">
-        <v>11836.35</v>
+        <v>11840.85</v>
       </c>
       <c r="R2">
-        <v>11231.9</v>
+        <v>11270.86</v>
       </c>
       <c r="S2">
-        <v>9949.940000000001</v>
+        <v>9965.040000000001</v>
       </c>
       <c r="T2">
-        <v>19.4</v>
+        <v>18.31</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -990,34 +962,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>55.47</v>
+        <v>52.56</v>
       </c>
       <c r="Z2">
-        <v>182.35</v>
+        <v>160.03</v>
       </c>
       <c r="AA2">
-        <v>228.03</v>
+        <v>214.43</v>
       </c>
       <c r="AB2">
-        <v>-45.68</v>
+        <v>-54.41</v>
       </c>
       <c r="AC2">
         <v>3.6</v>
       </c>
       <c r="AD2">
-        <v>5.05</v>
+        <v>2.4</v>
       </c>
       <c r="AE2">
-        <v>223.75</v>
+        <v>218.91</v>
       </c>
       <c r="AF2">
-        <v>-16.95</v>
+        <v>-48.53</v>
       </c>
       <c r="AG2">
-        <v>12220.81</v>
+        <v>12220.67</v>
       </c>
       <c r="AH2">
-        <v>11451.89</v>
+        <v>11461.03</v>
       </c>
       <c r="AI2">
         <v>11623.52</v>
@@ -1026,7 +998,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>36.45</v>
+        <v>33.17</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1037,10 +1009,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>514.1</v>
+        <v>521.45</v>
       </c>
       <c r="D3">
-        <v>-2.26</v>
+        <v>1.43</v>
       </c>
       <c r="E3">
         <v>670.25</v>
@@ -1049,46 +1021,46 @@
         <v>222.01</v>
       </c>
       <c r="G3">
-        <v>-23.3</v>
+        <v>-22.2</v>
       </c>
       <c r="H3">
+        <v>134.88</v>
+      </c>
+      <c r="I3">
+        <v>7.62</v>
+      </c>
+      <c r="J3">
+        <v>-3.6</v>
+      </c>
+      <c r="K3">
+        <v>-7.91</v>
+      </c>
+      <c r="L3">
         <v>131.57</v>
       </c>
-      <c r="I3">
-        <v>8.93</v>
-      </c>
-      <c r="J3">
-        <v>-6.02</v>
-      </c>
-      <c r="K3">
-        <v>-8.65</v>
-      </c>
-      <c r="L3">
-        <v>120.69</v>
-      </c>
       <c r="M3">
-        <v>17.35</v>
+        <v>17.55</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="P3">
-        <v>510.23</v>
+        <v>517.61</v>
       </c>
       <c r="Q3">
-        <v>490.25</v>
+        <v>489.41</v>
       </c>
       <c r="R3">
-        <v>536.8099999999999</v>
+        <v>534.95</v>
       </c>
       <c r="S3">
-        <v>432.79</v>
+        <v>434.07</v>
       </c>
       <c r="T3">
-        <v>18.79</v>
+        <v>20.13</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1103,34 +1075,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>52.84</v>
+        <v>54.98</v>
       </c>
       <c r="Z3">
-        <v>-6.49</v>
+        <v>-4.14</v>
       </c>
       <c r="AA3">
-        <v>-14.88</v>
+        <v>-12.73</v>
       </c>
       <c r="AB3">
-        <v>8.390000000000001</v>
+        <v>8.59</v>
       </c>
       <c r="AC3">
-        <v>95.05</v>
+        <v>92.70999999999999</v>
       </c>
       <c r="AD3">
-        <v>98.34999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="AE3">
-        <v>21.51</v>
+        <v>21.04</v>
       </c>
       <c r="AF3">
-        <v>-35.75</v>
+        <v>-11.49</v>
       </c>
       <c r="AG3">
-        <v>540.89</v>
+        <v>537.17</v>
       </c>
       <c r="AH3">
-        <v>439.6</v>
+        <v>441.64</v>
       </c>
       <c r="AI3">
         <v>455.28</v>
@@ -1139,7 +1111,7 @@
         <v>47</v>
       </c>
       <c r="AK3">
-        <v>34.7</v>
+        <v>34.98</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1150,10 +1122,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>339.95</v>
+        <v>339.8</v>
       </c>
       <c r="D4">
-        <v>-0.63</v>
+        <v>-0.04</v>
       </c>
       <c r="E4">
         <v>604.85</v>
@@ -1162,46 +1134,46 @@
         <v>303.75</v>
       </c>
       <c r="G4">
-        <v>-43.8</v>
+        <v>-43.82</v>
       </c>
       <c r="H4">
-        <v>11.92</v>
+        <v>11.87</v>
       </c>
       <c r="I4">
-        <v>4.33</v>
+        <v>5.01</v>
       </c>
       <c r="J4">
-        <v>-6.38</v>
+        <v>-5.7</v>
       </c>
       <c r="K4">
-        <v>10.02</v>
+        <v>11.43</v>
       </c>
       <c r="L4">
-        <v>-40.65</v>
+        <v>-40.27</v>
       </c>
       <c r="M4">
-        <v>-23</v>
+        <v>-22.68</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
       <c r="O4">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="P4">
-        <v>334.2</v>
+        <v>337.44</v>
       </c>
       <c r="Q4">
-        <v>343.46</v>
+        <v>342.25</v>
       </c>
       <c r="R4">
-        <v>339.22</v>
+        <v>339.62</v>
       </c>
       <c r="S4">
-        <v>380.76</v>
+        <v>380.03</v>
       </c>
       <c r="T4">
-        <v>-10.72</v>
+        <v>-10.58</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1216,34 +1188,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>49.95</v>
+        <v>49.84</v>
       </c>
       <c r="Z4">
-        <v>-2.88</v>
+        <v>-2.45</v>
       </c>
       <c r="AA4">
-        <v>-2.07</v>
+        <v>-2.15</v>
       </c>
       <c r="AB4">
-        <v>-0.8</v>
+        <v>-0.3</v>
       </c>
       <c r="AC4">
-        <v>65.45</v>
+        <v>81.15000000000001</v>
       </c>
       <c r="AD4">
-        <v>47.78</v>
+        <v>66.48999999999999</v>
       </c>
       <c r="AE4">
-        <v>10.94</v>
+        <v>10.6</v>
       </c>
       <c r="AF4">
-        <v>-54.02</v>
+        <v>-53.33</v>
       </c>
       <c r="AG4">
-        <v>369.94</v>
+        <v>366.94</v>
       </c>
       <c r="AH4">
-        <v>316.98</v>
+        <v>317.57</v>
       </c>
       <c r="AI4">
         <v>357.31</v>
@@ -1252,7 +1224,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>28.44</v>
+        <v>26.81</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1263,10 +1235,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1938.1</v>
+        <v>1927</v>
       </c>
       <c r="D5">
-        <v>-0.03</v>
+        <v>-0.57</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1275,46 +1247,46 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-10.96</v>
+        <v>-11.47</v>
       </c>
       <c r="H5">
-        <v>18.77</v>
+        <v>18.09</v>
       </c>
       <c r="I5">
-        <v>-1.72</v>
+        <v>-3.17</v>
       </c>
       <c r="J5">
-        <v>-4.12</v>
+        <v>-5.17</v>
       </c>
       <c r="K5">
-        <v>16.46</v>
+        <v>17.14</v>
       </c>
       <c r="L5">
-        <v>-3.2</v>
+        <v>-4.34</v>
       </c>
       <c r="M5">
-        <v>3.24</v>
+        <v>2.88</v>
       </c>
       <c r="N5">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="O5">
         <v>59</v>
       </c>
       <c r="P5">
-        <v>1965.76</v>
+        <v>1953.16</v>
       </c>
       <c r="Q5">
-        <v>1999.05</v>
+        <v>1994.37</v>
       </c>
       <c r="R5">
-        <v>1956.3</v>
+        <v>1958.89</v>
       </c>
       <c r="S5">
-        <v>1904.09</v>
+        <v>1903.47</v>
       </c>
       <c r="T5">
-        <v>1.79</v>
+        <v>1.24</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1329,43 +1301,43 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>40.45</v>
+        <v>38.53</v>
       </c>
       <c r="Z5">
-        <v>-1.56</v>
+        <v>-5.68</v>
       </c>
       <c r="AA5">
-        <v>11.64</v>
+        <v>8.17</v>
       </c>
       <c r="AB5">
-        <v>-13.2</v>
+        <v>-13.85</v>
       </c>
       <c r="AC5">
         <v>0</v>
       </c>
       <c r="AD5">
-        <v>9.279999999999999</v>
+        <v>3.21</v>
       </c>
       <c r="AE5">
-        <v>35.81</v>
+        <v>35.42</v>
       </c>
       <c r="AF5">
-        <v>5.45</v>
+        <v>-6.38</v>
       </c>
       <c r="AG5">
-        <v>2051.03</v>
+        <v>2054.43</v>
       </c>
       <c r="AH5">
-        <v>1947.07</v>
+        <v>1934.32</v>
       </c>
       <c r="AI5">
-        <v>2049.88</v>
+        <v>2042.97</v>
       </c>
       <c r="AJ5" t="s">
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>37.27</v>
+        <v>41.14</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1376,10 +1348,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>11046</v>
+        <v>11078</v>
       </c>
       <c r="D6">
-        <v>0.82</v>
+        <v>0.29</v>
       </c>
       <c r="E6">
         <v>13595.75</v>
@@ -1388,46 +1360,46 @@
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-18.75</v>
+        <v>-18.52</v>
       </c>
       <c r="H6">
-        <v>26.3</v>
+        <v>26.66</v>
       </c>
       <c r="I6">
-        <v>-2.33</v>
+        <v>-0.2</v>
       </c>
       <c r="J6">
-        <v>-3.7</v>
+        <v>-4.09</v>
       </c>
       <c r="K6">
-        <v>10.07</v>
+        <v>12.32</v>
       </c>
       <c r="L6">
-        <v>-14.49</v>
+        <v>-13.87</v>
       </c>
       <c r="M6">
-        <v>22.4</v>
+        <v>22.69</v>
       </c>
       <c r="N6">
         <v>29</v>
       </c>
       <c r="O6">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="P6">
-        <v>11085.8</v>
+        <v>11081.4</v>
       </c>
       <c r="Q6">
-        <v>11321.15</v>
+        <v>11296.1</v>
       </c>
       <c r="R6">
-        <v>11048.82</v>
+        <v>11056</v>
       </c>
       <c r="S6">
-        <v>10695.27</v>
+        <v>10692.46</v>
       </c>
       <c r="T6">
-        <v>3.28</v>
+        <v>3.61</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1442,34 +1414,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>45.49</v>
+        <v>46.45</v>
       </c>
       <c r="Z6">
-        <v>-1.7</v>
+        <v>-12.07</v>
       </c>
       <c r="AA6">
-        <v>66.34999999999999</v>
+        <v>50.67</v>
       </c>
       <c r="AB6">
-        <v>-68.05</v>
+        <v>-62.74</v>
       </c>
       <c r="AC6">
-        <v>8.550000000000001</v>
+        <v>11.53</v>
       </c>
       <c r="AD6">
-        <v>7.57</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="AE6">
-        <v>246.81</v>
+        <v>238.61</v>
       </c>
       <c r="AF6">
-        <v>-37.91</v>
+        <v>-59.36</v>
       </c>
       <c r="AG6">
-        <v>11694.96</v>
+        <v>11664.26</v>
       </c>
       <c r="AH6">
-        <v>10947.34</v>
+        <v>10927.94</v>
       </c>
       <c r="AI6">
         <v>10787.84</v>
@@ -1478,7 +1450,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>21.58</v>
+        <v>21.71</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1489,10 +1461,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>1054.1</v>
+        <v>1039.3</v>
       </c>
       <c r="D7">
-        <v>-0.5600000000000001</v>
+        <v>-1.4</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1501,25 +1473,25 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-9.039999999999999</v>
+        <v>-10.31</v>
       </c>
       <c r="H7">
-        <v>31.51</v>
+        <v>29.66</v>
       </c>
       <c r="I7">
-        <v>0.02</v>
+        <v>-1.57</v>
       </c>
       <c r="J7">
-        <v>-4.36</v>
+        <v>-4.94</v>
       </c>
       <c r="K7">
-        <v>19.23</v>
+        <v>19.38</v>
       </c>
       <c r="L7">
-        <v>12.77</v>
+        <v>10.85</v>
       </c>
       <c r="M7">
-        <v>7.56</v>
+        <v>7.35</v>
       </c>
       <c r="N7">
         <v>71</v>
@@ -1528,19 +1500,19 @@
         <v>70</v>
       </c>
       <c r="P7">
-        <v>1055.9</v>
+        <v>1052.58</v>
       </c>
       <c r="Q7">
-        <v>1076.43</v>
+        <v>1073.68</v>
       </c>
       <c r="R7">
-        <v>1066.3</v>
+        <v>1066.79</v>
       </c>
       <c r="S7">
-        <v>977.23</v>
+        <v>977.4</v>
       </c>
       <c r="T7">
-        <v>7.87</v>
+        <v>6.33</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1555,43 +1527,43 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>43.69</v>
+        <v>39.02</v>
       </c>
       <c r="Z7">
-        <v>-4.38</v>
+        <v>-6.15</v>
       </c>
       <c r="AA7">
-        <v>0.82</v>
+        <v>-0.57</v>
       </c>
       <c r="AB7">
-        <v>-5.2</v>
+        <v>-5.58</v>
       </c>
       <c r="AC7">
-        <v>27.35</v>
+        <v>16.5</v>
       </c>
       <c r="AD7">
-        <v>20.58</v>
+        <v>21.8</v>
       </c>
       <c r="AE7">
-        <v>20.62</v>
+        <v>20.69</v>
       </c>
       <c r="AF7">
-        <v>-24.36</v>
+        <v>101.22</v>
       </c>
       <c r="AG7">
-        <v>1109.36</v>
+        <v>1109.41</v>
       </c>
       <c r="AH7">
-        <v>1043.49</v>
+        <v>1037.95</v>
       </c>
       <c r="AI7">
-        <v>1116.59</v>
+        <v>1111.38</v>
       </c>
       <c r="AJ7" t="s">
         <v>48</v>
       </c>
       <c r="AK7">
-        <v>31.55</v>
+        <v>33.2</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1602,10 +1574,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>137.66</v>
+        <v>139.69</v>
       </c>
       <c r="D8">
-        <v>0.5600000000000001</v>
+        <v>1.47</v>
       </c>
       <c r="E8">
         <v>148.95</v>
@@ -1614,46 +1586,46 @@
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>-7.58</v>
+        <v>-6.22</v>
       </c>
       <c r="H8">
-        <v>18.71</v>
+        <v>20.46</v>
       </c>
       <c r="I8">
-        <v>1.2</v>
+        <v>4.11</v>
       </c>
       <c r="J8">
-        <v>-2.47</v>
+        <v>-0.65</v>
       </c>
       <c r="K8">
-        <v>1.69</v>
+        <v>5.79</v>
       </c>
       <c r="L8">
-        <v>3.58</v>
+        <v>6.35</v>
       </c>
       <c r="M8">
-        <v>0.04</v>
+        <v>0.31</v>
       </c>
       <c r="N8">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="O8">
         <v>57</v>
       </c>
       <c r="P8">
-        <v>135.23</v>
+        <v>136.33</v>
       </c>
       <c r="Q8">
-        <v>135.74</v>
+        <v>135.95</v>
       </c>
       <c r="R8">
-        <v>137.67</v>
+        <v>137.81</v>
       </c>
       <c r="S8">
-        <v>133.66</v>
+        <v>133.7</v>
       </c>
       <c r="T8">
-        <v>2.99</v>
+        <v>4.48</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1668,34 +1640,34 @@
         <v>2</v>
       </c>
       <c r="Y8">
-        <v>52.48</v>
+        <v>57.46</v>
       </c>
       <c r="Z8">
-        <v>-0.67</v>
+        <v>-0.33</v>
       </c>
       <c r="AA8">
-        <v>-0.8</v>
+        <v>-0.71</v>
       </c>
       <c r="AB8">
-        <v>0.13</v>
+        <v>0.38</v>
       </c>
       <c r="AC8">
-        <v>81.45</v>
+        <v>100</v>
       </c>
       <c r="AD8">
-        <v>52.35</v>
+        <v>77.06999999999999</v>
       </c>
       <c r="AE8">
-        <v>3.6</v>
+        <v>3.76</v>
       </c>
       <c r="AF8">
-        <v>-51.26</v>
+        <v>17.18</v>
       </c>
       <c r="AG8">
-        <v>138.43</v>
+        <v>139.16</v>
       </c>
       <c r="AH8">
-        <v>133.05</v>
+        <v>132.73</v>
       </c>
       <c r="AI8">
         <v>131.91</v>
@@ -1704,7 +1676,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>21.33</v>
+        <v>24.87</v>
       </c>
     </row>
   </sheetData>
@@ -1845,7 +1817,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1865,47 +1837,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1913,972 +1850,1006 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>64</v>
+      <c r="B6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>1.18</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>1.74</v>
       </c>
-      <c r="E7" s="7">
-        <v>0.5600000000000001</v>
+      <c r="D7" s="5">
+        <v>0.62</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-1.12</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-2.13</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>-6.02</v>
       </c>
-      <c r="E8" s="8">
+      <c r="D8" s="5">
+        <v>-3.6</v>
+      </c>
+      <c r="E8" s="7">
+        <v>2.42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-6.38</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-5.7</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-4.12</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-5.17</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-1.05</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-3.7</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-4.09</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-4.36</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-4.94</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-2.47</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-0.65</v>
+      </c>
+      <c r="E13" s="7">
+        <v>1.82</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
         <v>-3.89</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="D14" s="5">
+        <v>-2.8</v>
+      </c>
+      <c r="E14" s="7">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>8.93</v>
+      </c>
+      <c r="D15" s="5">
+        <v>7.62</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-1.31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-7.83</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>4.33</v>
+      </c>
+      <c r="D16" s="5">
+        <v>5.01</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-1.72</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-3.17</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-1.45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-2.33</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.2</v>
+      </c>
+      <c r="E18" s="7">
+        <v>2.13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5">
+        <v>0.02</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-1.57</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-1.59</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="D20" s="5">
+        <v>4.11</v>
+      </c>
+      <c r="E20" s="7">
+        <v>2.91</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>32.81</v>
+      </c>
+      <c r="D21" s="5">
+        <v>31.61</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="5">
+        <v>120.69</v>
+      </c>
+      <c r="D22" s="5">
+        <v>131.57</v>
+      </c>
+      <c r="E22" s="7">
+        <v>10.88</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5">
+        <v>-40.65</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-40.27</v>
+      </c>
+      <c r="E23" s="7">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-3.2</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-4.34</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-1.14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-14.49</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-13.87</v>
+      </c>
+      <c r="E25" s="7">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>12.77</v>
+      </c>
+      <c r="D26" s="5">
+        <v>10.85</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-1.92</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>3.58</v>
+      </c>
+      <c r="D27" s="5">
+        <v>6.35</v>
+      </c>
+      <c r="E27" s="7">
+        <v>2.77</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="5">
+        <v>17.11</v>
+      </c>
+      <c r="D28" s="5">
+        <v>16.57</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-8.65</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-7.91</v>
+      </c>
+      <c r="E29" s="7">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="5">
+        <v>10.02</v>
+      </c>
+      <c r="D30" s="5">
+        <v>11.43</v>
+      </c>
+      <c r="E30" s="7">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="5">
+        <v>16.46</v>
+      </c>
+      <c r="D31" s="5">
+        <v>17.14</v>
+      </c>
+      <c r="E31" s="7">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="5">
+        <v>10.07</v>
+      </c>
+      <c r="D32" s="5">
+        <v>12.32</v>
+      </c>
+      <c r="E32" s="7">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="5">
+        <v>19.23</v>
+      </c>
+      <c r="D33" s="5">
+        <v>19.38</v>
+      </c>
+      <c r="E33" s="7">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>1.69</v>
+      </c>
+      <c r="D34" s="5">
+        <v>5.79</v>
+      </c>
+      <c r="E34" s="7">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-3.89</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-4.62</v>
+      </c>
+      <c r="E35" s="6">
+        <v>-0.73</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-23.3</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-22.2</v>
+      </c>
+      <c r="E36" s="7">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="5">
+        <v>-43.8</v>
+      </c>
+      <c r="D37" s="5">
+        <v>-43.82</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="5">
+        <v>-10.96</v>
+      </c>
+      <c r="D38" s="5">
+        <v>-11.47</v>
+      </c>
+      <c r="E38" s="6">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="5">
+        <v>-18.75</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-18.52</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="5">
+        <v>-9.039999999999999</v>
+      </c>
+      <c r="D40" s="5">
+        <v>-10.31</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-1.27</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="5">
+        <v>-7.58</v>
+      </c>
+      <c r="D41" s="5">
+        <v>-6.22</v>
+      </c>
+      <c r="E41" s="7">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="5">
+        <v>11880</v>
+      </c>
+      <c r="D42" s="5">
+        <v>11790</v>
+      </c>
+      <c r="E42" s="6">
+        <v>-90</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="5">
+        <v>514.1</v>
+      </c>
+      <c r="D43" s="5">
+        <v>521.45</v>
+      </c>
+      <c r="E43" s="7">
+        <v>7.35</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="5">
+        <v>339.95</v>
+      </c>
+      <c r="D44" s="5">
+        <v>339.8</v>
+      </c>
+      <c r="E44" s="6">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="5">
+        <v>1938.1</v>
+      </c>
+      <c r="D45" s="5">
+        <v>1927</v>
+      </c>
+      <c r="E45" s="6">
+        <v>-11.1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="5">
+        <v>11046</v>
+      </c>
+      <c r="D46" s="5">
+        <v>11078</v>
+      </c>
+      <c r="E46" s="7">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="5">
+        <v>1054.1</v>
+      </c>
+      <c r="D47" s="5">
+        <v>1039.3</v>
+      </c>
+      <c r="E47" s="6">
+        <v>-14.8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="5">
+        <v>137.66</v>
+      </c>
+      <c r="D48" s="5">
+        <v>139.69</v>
+      </c>
+      <c r="E48" s="7">
+        <v>2.03</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49" s="5">
+        <v>57</v>
+      </c>
+      <c r="D49" s="5">
+        <v>43</v>
+      </c>
+      <c r="E49" s="6">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" s="5">
+        <v>43</v>
+      </c>
+      <c r="D50" s="5">
+        <v>57</v>
+      </c>
+      <c r="E50" s="7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="5">
+        <v>55.47</v>
+      </c>
+      <c r="D51" s="5">
+        <v>52.56</v>
+      </c>
+      <c r="E51" s="6">
+        <v>-2.91</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="5">
+        <v>52.84</v>
+      </c>
+      <c r="D52" s="5">
+        <v>54.98</v>
+      </c>
+      <c r="E52" s="7">
+        <v>2.14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="5">
+        <v>49.95</v>
+      </c>
+      <c r="D53" s="5">
+        <v>49.84</v>
+      </c>
+      <c r="E53" s="6">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="5">
+        <v>40.45</v>
+      </c>
+      <c r="D54" s="5">
+        <v>38.53</v>
+      </c>
+      <c r="E54" s="6">
+        <v>-1.92</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="5">
+        <v>45.49</v>
+      </c>
+      <c r="D55" s="5">
+        <v>46.45</v>
+      </c>
+      <c r="E55" s="7">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="5">
+        <v>43.69</v>
+      </c>
+      <c r="D56" s="5">
+        <v>39.02</v>
+      </c>
+      <c r="E56" s="6">
+        <v>-4.67</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="5">
+        <v>52.48</v>
+      </c>
+      <c r="D57" s="5">
+        <v>57.46</v>
+      </c>
+      <c r="E57" s="7">
+        <v>4.98</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="5">
+        <v>-16.95</v>
+      </c>
+      <c r="D58" s="5">
+        <v>-48.53</v>
+      </c>
+      <c r="E58" s="6">
+        <v>-31.58</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="5">
+        <v>-35.75</v>
+      </c>
+      <c r="D59" s="5">
+        <v>-11.49</v>
+      </c>
+      <c r="E59" s="7">
+        <v>24.26</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="5">
+        <v>-54.02</v>
+      </c>
+      <c r="D60" s="5">
+        <v>-53.33</v>
+      </c>
+      <c r="E60" s="7">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="5">
+        <v>5.45</v>
+      </c>
+      <c r="D61" s="5">
         <v>-6.38</v>
       </c>
-      <c r="E9" s="7">
-        <v>1.45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-3.5</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-4.12</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-0.62</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="E61" s="6">
+        <v>-11.83</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-2.73</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-3.7</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-0.97</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B62" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="5">
+        <v>-37.91</v>
+      </c>
+      <c r="D62" s="5">
+        <v>-59.36</v>
+      </c>
+      <c r="E62" s="6">
+        <v>-21.45</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-1.67</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-4.36</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-2.69</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B63" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="5">
+        <v>-24.36</v>
+      </c>
+      <c r="D63" s="5">
+        <v>101.22</v>
+      </c>
+      <c r="E63" s="7">
+        <v>125.58</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-4.41</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-2.47</v>
-      </c>
-      <c r="E13" s="7">
-        <v>1.94</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-2.72</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-3.89</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-1.17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>10.96</v>
-      </c>
-      <c r="D15" s="6">
-        <v>8.93</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-2.03</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>5.33</v>
-      </c>
-      <c r="D16" s="6">
-        <v>4.33</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-4.08</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-1.72</v>
-      </c>
-      <c r="E17" s="7">
-        <v>2.36</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-5.91</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-2.33</v>
-      </c>
-      <c r="E18" s="7">
-        <v>3.58</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>0.28</v>
-      </c>
-      <c r="D19" s="6">
-        <v>0.02</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-0.26</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-0.35</v>
-      </c>
-      <c r="D20" s="6">
-        <v>1.2</v>
-      </c>
-      <c r="E20" s="7">
-        <v>1.55</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>31.26</v>
-      </c>
-      <c r="D21" s="6">
-        <v>32.81</v>
-      </c>
-      <c r="E21" s="7">
-        <v>1.55</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="6">
-        <v>117.38</v>
-      </c>
-      <c r="D22" s="6">
-        <v>120.69</v>
-      </c>
-      <c r="E22" s="7">
-        <v>3.31</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-40.48</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-40.65</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-1.4</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-3.2</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-1.8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-15.46</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-14.49</v>
-      </c>
-      <c r="E25" s="7">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>18.26</v>
-      </c>
-      <c r="D26" s="6">
-        <v>12.77</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-5.49</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>0.17</v>
-      </c>
-      <c r="D27" s="6">
-        <v>3.58</v>
-      </c>
-      <c r="E27" s="7">
-        <v>3.41</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="6">
-        <v>15.87</v>
-      </c>
-      <c r="D28" s="6">
-        <v>17.11</v>
-      </c>
-      <c r="E28" s="7">
-        <v>1.24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-9.65</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-8.65</v>
-      </c>
-      <c r="E29" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="6">
-        <v>9.539999999999999</v>
-      </c>
-      <c r="D30" s="6">
-        <v>10.02</v>
-      </c>
-      <c r="E30" s="7">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="6">
-        <v>14.5</v>
-      </c>
-      <c r="D31" s="6">
-        <v>16.46</v>
-      </c>
-      <c r="E31" s="7">
-        <v>1.96</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="6">
-        <v>6.86</v>
-      </c>
-      <c r="D32" s="6">
-        <v>10.07</v>
-      </c>
-      <c r="E32" s="7">
-        <v>3.21</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="6">
-        <v>19.52</v>
-      </c>
-      <c r="D33" s="6">
-        <v>19.23</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-0.29</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-0.5</v>
-      </c>
-      <c r="D34" s="6">
-        <v>1.69</v>
-      </c>
-      <c r="E34" s="7">
-        <v>2.19</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-4.54</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-3.89</v>
-      </c>
-      <c r="E35" s="7">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-21.52</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-23.3</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-1.78</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-43.44</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-43.8</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-0.36</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-10.93</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-10.96</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-0.03</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-19.42</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-18.75</v>
-      </c>
-      <c r="E39" s="7">
-        <v>0.67</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-8.529999999999999</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-9.039999999999999</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-0.51</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-8.09</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-7.58</v>
-      </c>
-      <c r="E41" s="7">
-        <v>0.51</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="6">
-        <v>11800</v>
-      </c>
-      <c r="D42" s="6">
-        <v>11880</v>
-      </c>
-      <c r="E42" s="7">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="6">
-        <v>526</v>
-      </c>
-      <c r="D43" s="6">
-        <v>514.1</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-11.9</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="6">
-        <v>342.1</v>
-      </c>
-      <c r="D44" s="6">
-        <v>339.95</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-2.15</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="6">
-        <v>1938.6</v>
-      </c>
-      <c r="D45" s="6">
-        <v>1938.1</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="6">
-        <v>10956</v>
-      </c>
-      <c r="D46" s="6">
-        <v>11046</v>
-      </c>
-      <c r="E46" s="7">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="6">
-        <v>1060</v>
-      </c>
-      <c r="D47" s="6">
-        <v>1054.1</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-5.9</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="6">
-        <v>136.9</v>
-      </c>
-      <c r="D48" s="6">
-        <v>137.66</v>
-      </c>
-      <c r="E48" s="7">
-        <v>0.76</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" s="6">
-        <v>53.34</v>
-      </c>
-      <c r="D49" s="6">
-        <v>55.47</v>
-      </c>
-      <c r="E49" s="7">
-        <v>2.13</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="6">
-        <v>56.92</v>
-      </c>
-      <c r="D50" s="6">
-        <v>52.84</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-4.08</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="6">
-        <v>51.4</v>
-      </c>
-      <c r="D51" s="6">
-        <v>49.95</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-1.45</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="6">
-        <v>40.54</v>
-      </c>
-      <c r="D52" s="6">
-        <v>40.45</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-0.09</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="6">
-        <v>42.81</v>
-      </c>
-      <c r="D53" s="6">
-        <v>45.49</v>
-      </c>
-      <c r="E53" s="7">
-        <v>2.68</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="6">
-        <v>45.72</v>
-      </c>
-      <c r="D54" s="6">
-        <v>43.69</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-2.03</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="6">
-        <v>50.47</v>
-      </c>
-      <c r="D55" s="6">
-        <v>52.48</v>
-      </c>
-      <c r="E55" s="7">
-        <v>2.01</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B56" s="5" t="s">
+      <c r="B64" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C56" s="6">
-        <v>-55.28</v>
-      </c>
-      <c r="D56" s="6">
-        <v>-16.95</v>
-      </c>
-      <c r="E56" s="7">
-        <v>38.33</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C57" s="6">
-        <v>27.99</v>
-      </c>
-      <c r="D57" s="6">
-        <v>-35.75</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-63.74</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C58" s="6">
-        <v>-19.9</v>
-      </c>
-      <c r="D58" s="6">
-        <v>-54.02</v>
-      </c>
-      <c r="E58" s="8">
-        <v>-34.12</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C59" s="6">
-        <v>-34.03</v>
-      </c>
-      <c r="D59" s="6">
-        <v>5.45</v>
-      </c>
-      <c r="E59" s="7">
-        <v>39.48</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="6">
-        <v>-11.86</v>
-      </c>
-      <c r="D60" s="6">
-        <v>-37.91</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-26.05</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="6">
-        <v>-32.87</v>
-      </c>
-      <c r="D61" s="6">
-        <v>-24.36</v>
-      </c>
-      <c r="E61" s="7">
-        <v>8.51</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="6">
-        <v>-39.97</v>
-      </c>
-      <c r="D62" s="6">
+      <c r="C64" s="5">
         <v>-51.26</v>
       </c>
-      <c r="E62" s="8">
-        <v>-11.29</v>
+      <c r="D64" s="5">
+        <v>17.18</v>
+      </c>
+      <c r="E64" s="7">
+        <v>68.44</v>
       </c>
     </row>
   </sheetData>
@@ -2904,60 +2875,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>72</v>
+      <c r="B1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>68.8</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>7</v>
       </c>
-      <c r="D2" s="11">
-        <v>48.6</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>48.4</v>
+      </c>
+      <c r="E2" s="10">
         <v>90</v>
       </c>
-      <c r="F2" s="11">
-        <v>-3.6</v>
-      </c>
-      <c r="G2" s="11">
-        <v>9.4</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-3.4</v>
+      </c>
+      <c r="G2" s="10">
+        <v>10.7</v>
+      </c>
+      <c r="H2" s="10">
         <v>57</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>60</v>
       </c>
     </row>
@@ -3059,49 +3030,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="14">
-        <v>0.2902</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.224</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.1735</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.0756</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.03240000000000001</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.0004</v>
-      </c>
-      <c r="G2" s="14">
-        <v>-0.23</v>
+      <c r="A2" s="13">
+        <v>0.29</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.2269</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.1755</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.0735</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.0288</v>
+      </c>
+      <c r="F2" s="13">
+        <v>0.0031</v>
+      </c>
+      <c r="G2" s="13">
+        <v>-0.2268</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="64">
   <si>
     <t>Symbol</t>
   </si>
@@ -755,8 +755,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -896,10 +896,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>11790</v>
+        <v>11768</v>
       </c>
       <c r="D2">
-        <v>-0.76</v>
+        <v>-0.19</v>
       </c>
       <c r="E2">
         <v>12361</v>
@@ -908,46 +908,46 @@
         <v>8506.780000000001</v>
       </c>
       <c r="G2">
-        <v>-4.62</v>
+        <v>-4.8</v>
       </c>
       <c r="H2">
-        <v>38.6</v>
+        <v>38.34</v>
       </c>
       <c r="I2">
-        <v>-2.8</v>
+        <v>-1.28</v>
       </c>
       <c r="J2">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="K2">
-        <v>16.57</v>
+        <v>16.94</v>
       </c>
       <c r="L2">
-        <v>31.61</v>
+        <v>26.5</v>
       </c>
       <c r="M2">
-        <v>29</v>
+        <v>29.01</v>
       </c>
       <c r="N2">
         <v>85</v>
       </c>
       <c r="O2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P2">
-        <v>11861.8</v>
+        <v>11831.4</v>
       </c>
       <c r="Q2">
-        <v>11840.85</v>
+        <v>11846.2</v>
       </c>
       <c r="R2">
-        <v>11270.86</v>
+        <v>11309.08</v>
       </c>
       <c r="S2">
-        <v>9965.040000000001</v>
+        <v>9979.469999999999</v>
       </c>
       <c r="T2">
-        <v>18.31</v>
+        <v>17.92</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -962,34 +962,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>52.56</v>
+        <v>51.84</v>
       </c>
       <c r="Z2">
-        <v>160.03</v>
+        <v>138.96</v>
       </c>
       <c r="AA2">
-        <v>214.43</v>
+        <v>199.34</v>
       </c>
       <c r="AB2">
-        <v>-54.41</v>
+        <v>-60.38</v>
       </c>
       <c r="AC2">
         <v>3.6</v>
       </c>
       <c r="AD2">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="AE2">
-        <v>218.91</v>
+        <v>213.77</v>
       </c>
       <c r="AF2">
-        <v>-48.53</v>
+        <v>-46.03</v>
       </c>
       <c r="AG2">
-        <v>12220.67</v>
+        <v>12218.29</v>
       </c>
       <c r="AH2">
-        <v>11461.03</v>
+        <v>11474.11</v>
       </c>
       <c r="AI2">
         <v>11623.52</v>
@@ -998,7 +998,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>33.17</v>
+        <v>28.82</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1009,10 +1009,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>521.45</v>
+        <v>524.45</v>
       </c>
       <c r="D3">
-        <v>1.43</v>
+        <v>0.58</v>
       </c>
       <c r="E3">
         <v>670.25</v>
@@ -1021,25 +1021,25 @@
         <v>222.01</v>
       </c>
       <c r="G3">
-        <v>-22.2</v>
+        <v>-21.75</v>
       </c>
       <c r="H3">
-        <v>134.88</v>
+        <v>136.23</v>
       </c>
       <c r="I3">
-        <v>7.62</v>
+        <v>3.05</v>
       </c>
       <c r="J3">
-        <v>-3.6</v>
+        <v>-2.56</v>
       </c>
       <c r="K3">
-        <v>-7.91</v>
+        <v>-11.36</v>
       </c>
       <c r="L3">
-        <v>131.57</v>
+        <v>133.93</v>
       </c>
       <c r="M3">
-        <v>17.55</v>
+        <v>17.14</v>
       </c>
       <c r="N3">
         <v>99</v>
@@ -1048,19 +1048,19 @@
         <v>93</v>
       </c>
       <c r="P3">
-        <v>517.61</v>
+        <v>520.71</v>
       </c>
       <c r="Q3">
-        <v>489.41</v>
+        <v>489.25</v>
       </c>
       <c r="R3">
-        <v>534.95</v>
+        <v>533.2</v>
       </c>
       <c r="S3">
-        <v>434.07</v>
+        <v>435.37</v>
       </c>
       <c r="T3">
-        <v>20.13</v>
+        <v>20.46</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1075,43 +1075,43 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>54.98</v>
+        <v>55.87</v>
       </c>
       <c r="Z3">
-        <v>-4.14</v>
+        <v>-2.02</v>
       </c>
       <c r="AA3">
-        <v>-12.73</v>
+        <v>-10.59</v>
       </c>
       <c r="AB3">
-        <v>8.59</v>
+        <v>8.57</v>
       </c>
       <c r="AC3">
-        <v>92.70999999999999</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="AD3">
-        <v>95.92</v>
+        <v>93.06</v>
       </c>
       <c r="AE3">
-        <v>21.04</v>
+        <v>20.88</v>
       </c>
       <c r="AF3">
-        <v>-11.49</v>
+        <v>23.29</v>
       </c>
       <c r="AG3">
-        <v>537.17</v>
+        <v>536.49</v>
       </c>
       <c r="AH3">
-        <v>441.64</v>
+        <v>442</v>
       </c>
       <c r="AI3">
-        <v>455.28</v>
+        <v>460.99</v>
       </c>
       <c r="AJ3" t="s">
         <v>47</v>
       </c>
       <c r="AK3">
-        <v>34.98</v>
+        <v>36.66</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1122,10 +1122,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>339.8</v>
+        <v>337.75</v>
       </c>
       <c r="D4">
-        <v>-0.04</v>
+        <v>-0.6</v>
       </c>
       <c r="E4">
         <v>604.85</v>
@@ -1134,25 +1134,25 @@
         <v>303.75</v>
       </c>
       <c r="G4">
-        <v>-43.82</v>
+        <v>-44.16</v>
       </c>
       <c r="H4">
-        <v>11.87</v>
+        <v>11.19</v>
       </c>
       <c r="I4">
-        <v>5.01</v>
+        <v>1.06</v>
       </c>
       <c r="J4">
-        <v>-5.7</v>
+        <v>-7.2</v>
       </c>
       <c r="K4">
-        <v>11.43</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="L4">
-        <v>-40.27</v>
+        <v>-40.22</v>
       </c>
       <c r="M4">
-        <v>-22.68</v>
+        <v>-22.8</v>
       </c>
       <c r="N4">
         <v>15</v>
@@ -1161,19 +1161,19 @@
         <v>25</v>
       </c>
       <c r="P4">
-        <v>337.44</v>
+        <v>338.15</v>
       </c>
       <c r="Q4">
-        <v>342.25</v>
+        <v>341.31</v>
       </c>
       <c r="R4">
-        <v>339.62</v>
+        <v>339.77</v>
       </c>
       <c r="S4">
-        <v>380.03</v>
+        <v>379.27</v>
       </c>
       <c r="T4">
-        <v>-10.58</v>
+        <v>-10.95</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1188,34 +1188,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>49.84</v>
+        <v>48.33</v>
       </c>
       <c r="Z4">
-        <v>-2.45</v>
+        <v>-2.25</v>
       </c>
       <c r="AA4">
-        <v>-2.15</v>
+        <v>-2.17</v>
       </c>
       <c r="AB4">
-        <v>-0.3</v>
+        <v>-0.08</v>
       </c>
       <c r="AC4">
-        <v>81.15000000000001</v>
+        <v>79.66</v>
       </c>
       <c r="AD4">
-        <v>66.48999999999999</v>
+        <v>75.42</v>
       </c>
       <c r="AE4">
-        <v>10.6</v>
+        <v>10.56</v>
       </c>
       <c r="AF4">
-        <v>-53.33</v>
+        <v>-22.99</v>
       </c>
       <c r="AG4">
-        <v>366.94</v>
+        <v>365.12</v>
       </c>
       <c r="AH4">
-        <v>317.57</v>
+        <v>317.51</v>
       </c>
       <c r="AI4">
         <v>357.31</v>
@@ -1224,7 +1224,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>26.81</v>
+        <v>27.15</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1235,10 +1235,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1927</v>
+        <v>1940.5</v>
       </c>
       <c r="D5">
-        <v>-0.57</v>
+        <v>0.7</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1247,46 +1247,46 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-11.47</v>
+        <v>-10.85</v>
       </c>
       <c r="H5">
-        <v>18.09</v>
+        <v>18.92</v>
       </c>
       <c r="I5">
-        <v>-3.17</v>
+        <v>-2.59</v>
       </c>
       <c r="J5">
-        <v>-5.17</v>
+        <v>-3.96</v>
       </c>
       <c r="K5">
-        <v>17.14</v>
+        <v>14.88</v>
       </c>
       <c r="L5">
-        <v>-4.34</v>
+        <v>-3.38</v>
       </c>
       <c r="M5">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="N5">
         <v>43</v>
       </c>
       <c r="O5">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P5">
-        <v>1953.16</v>
+        <v>1942.84</v>
       </c>
       <c r="Q5">
-        <v>1994.37</v>
+        <v>1990.15</v>
       </c>
       <c r="R5">
-        <v>1958.89</v>
+        <v>1960.58</v>
       </c>
       <c r="S5">
-        <v>1903.47</v>
+        <v>1903.01</v>
       </c>
       <c r="T5">
-        <v>1.24</v>
+        <v>1.97</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1301,43 +1301,43 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>38.53</v>
+        <v>42.13</v>
       </c>
       <c r="Z5">
-        <v>-5.68</v>
+        <v>-7.76</v>
       </c>
       <c r="AA5">
-        <v>8.17</v>
+        <v>4.99</v>
       </c>
       <c r="AB5">
-        <v>-13.85</v>
+        <v>-12.75</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>6.29</v>
       </c>
       <c r="AD5">
-        <v>3.21</v>
+        <v>2.1</v>
       </c>
       <c r="AE5">
-        <v>35.42</v>
+        <v>34.44</v>
       </c>
       <c r="AF5">
-        <v>-6.38</v>
+        <v>2.17</v>
       </c>
       <c r="AG5">
-        <v>2054.43</v>
+        <v>2052.96</v>
       </c>
       <c r="AH5">
-        <v>1934.32</v>
+        <v>1927.34</v>
       </c>
       <c r="AI5">
-        <v>2042.97</v>
+        <v>2035.21</v>
       </c>
       <c r="AJ5" t="s">
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>41.14</v>
+        <v>44.51</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1348,10 +1348,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>11078</v>
+        <v>10992</v>
       </c>
       <c r="D6">
-        <v>0.29</v>
+        <v>-0.78</v>
       </c>
       <c r="E6">
         <v>13595.75</v>
@@ -1360,25 +1360,25 @@
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-18.52</v>
+        <v>-19.15</v>
       </c>
       <c r="H6">
-        <v>26.66</v>
+        <v>25.68</v>
       </c>
       <c r="I6">
-        <v>-0.2</v>
+        <v>-1.55</v>
       </c>
       <c r="J6">
-        <v>-4.09</v>
+        <v>-5.07</v>
       </c>
       <c r="K6">
-        <v>12.32</v>
+        <v>8.18</v>
       </c>
       <c r="L6">
-        <v>-13.87</v>
+        <v>-13.5</v>
       </c>
       <c r="M6">
-        <v>22.69</v>
+        <v>22.55</v>
       </c>
       <c r="N6">
         <v>29</v>
@@ -1387,19 +1387,19 @@
         <v>49</v>
       </c>
       <c r="P6">
-        <v>11081.4</v>
+        <v>11046.8</v>
       </c>
       <c r="Q6">
-        <v>11296.1</v>
+        <v>11270.7</v>
       </c>
       <c r="R6">
-        <v>11056</v>
+        <v>11058.68</v>
       </c>
       <c r="S6">
-        <v>10692.46</v>
+        <v>10690.05</v>
       </c>
       <c r="T6">
-        <v>3.61</v>
+        <v>2.82</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1414,34 +1414,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>46.45</v>
+        <v>44.2</v>
       </c>
       <c r="Z6">
-        <v>-12.07</v>
+        <v>-26.91</v>
       </c>
       <c r="AA6">
-        <v>50.67</v>
+        <v>35.15</v>
       </c>
       <c r="AB6">
-        <v>-62.74</v>
+        <v>-62.07</v>
       </c>
       <c r="AC6">
-        <v>11.53</v>
+        <v>14.06</v>
       </c>
       <c r="AD6">
-        <v>9.050000000000001</v>
+        <v>11.38</v>
       </c>
       <c r="AE6">
-        <v>238.61</v>
+        <v>229.64</v>
       </c>
       <c r="AF6">
-        <v>-59.36</v>
+        <v>-59.65</v>
       </c>
       <c r="AG6">
-        <v>11664.26</v>
+        <v>11649.57</v>
       </c>
       <c r="AH6">
-        <v>10927.94</v>
+        <v>10891.83</v>
       </c>
       <c r="AI6">
         <v>10787.84</v>
@@ -1450,7 +1450,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>21.71</v>
+        <v>22.47</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1461,10 +1461,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>1039.3</v>
+        <v>1043.5</v>
       </c>
       <c r="D7">
-        <v>-1.4</v>
+        <v>0.4</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1473,46 +1473,46 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-10.31</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="H7">
-        <v>29.66</v>
+        <v>30.19</v>
       </c>
       <c r="I7">
-        <v>-1.57</v>
+        <v>-0.52</v>
       </c>
       <c r="J7">
-        <v>-4.94</v>
+        <v>-4.63</v>
       </c>
       <c r="K7">
-        <v>19.38</v>
+        <v>13.63</v>
       </c>
       <c r="L7">
-        <v>10.85</v>
+        <v>10.51</v>
       </c>
       <c r="M7">
-        <v>7.35</v>
+        <v>7.41</v>
       </c>
       <c r="N7">
         <v>71</v>
       </c>
       <c r="O7">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="P7">
-        <v>1052.58</v>
+        <v>1051.48</v>
       </c>
       <c r="Q7">
-        <v>1073.68</v>
+        <v>1071.32</v>
       </c>
       <c r="R7">
-        <v>1066.79</v>
+        <v>1067.29</v>
       </c>
       <c r="S7">
-        <v>977.4</v>
+        <v>977.65</v>
       </c>
       <c r="T7">
-        <v>6.33</v>
+        <v>6.74</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1527,43 +1527,43 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>39.02</v>
+        <v>40.95</v>
       </c>
       <c r="Z7">
-        <v>-6.15</v>
+        <v>-7.14</v>
       </c>
       <c r="AA7">
-        <v>-0.57</v>
+        <v>-1.89</v>
       </c>
       <c r="AB7">
-        <v>-5.58</v>
+        <v>-5.25</v>
       </c>
       <c r="AC7">
-        <v>16.5</v>
+        <v>10.52</v>
       </c>
       <c r="AD7">
-        <v>21.8</v>
+        <v>18.13</v>
       </c>
       <c r="AE7">
-        <v>20.69</v>
+        <v>20.09</v>
       </c>
       <c r="AF7">
-        <v>101.22</v>
+        <v>-17.38</v>
       </c>
       <c r="AG7">
-        <v>1109.41</v>
+        <v>1108.51</v>
       </c>
       <c r="AH7">
-        <v>1037.95</v>
+        <v>1034.12</v>
       </c>
       <c r="AI7">
-        <v>1111.38</v>
+        <v>1102.86</v>
       </c>
       <c r="AJ7" t="s">
         <v>48</v>
       </c>
       <c r="AK7">
-        <v>33.2</v>
+        <v>34.91</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1574,10 +1574,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>139.69</v>
+        <v>142.57</v>
       </c>
       <c r="D8">
-        <v>1.47</v>
+        <v>2.06</v>
       </c>
       <c r="E8">
         <v>148.95</v>
@@ -1586,46 +1586,46 @@
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>-6.22</v>
+        <v>-4.28</v>
       </c>
       <c r="H8">
-        <v>20.46</v>
+        <v>22.95</v>
       </c>
       <c r="I8">
-        <v>4.11</v>
+        <v>7.22</v>
       </c>
       <c r="J8">
-        <v>-0.65</v>
+        <v>5.17</v>
       </c>
       <c r="K8">
-        <v>5.79</v>
+        <v>6.22</v>
       </c>
       <c r="L8">
-        <v>6.35</v>
+        <v>4.64</v>
       </c>
       <c r="M8">
-        <v>0.31</v>
+        <v>0.8</v>
       </c>
       <c r="N8">
         <v>57</v>
       </c>
       <c r="O8">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="P8">
-        <v>136.33</v>
+        <v>138.25</v>
       </c>
       <c r="Q8">
-        <v>135.95</v>
+        <v>136.29</v>
       </c>
       <c r="R8">
-        <v>137.81</v>
+        <v>138</v>
       </c>
       <c r="S8">
-        <v>133.7</v>
+        <v>133.76</v>
       </c>
       <c r="T8">
-        <v>4.48</v>
+        <v>6.58</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1640,34 +1640,34 @@
         <v>2</v>
       </c>
       <c r="Y8">
-        <v>57.46</v>
+        <v>63.33</v>
       </c>
       <c r="Z8">
-        <v>-0.33</v>
+        <v>0.16</v>
       </c>
       <c r="AA8">
-        <v>-0.71</v>
+        <v>-0.53</v>
       </c>
       <c r="AB8">
-        <v>0.38</v>
+        <v>0.7</v>
       </c>
       <c r="AC8">
         <v>100</v>
       </c>
       <c r="AD8">
-        <v>77.06999999999999</v>
+        <v>93.81999999999999</v>
       </c>
       <c r="AE8">
-        <v>3.76</v>
+        <v>3.98</v>
       </c>
       <c r="AF8">
-        <v>17.18</v>
+        <v>115.85</v>
       </c>
       <c r="AG8">
-        <v>139.16</v>
+        <v>140.66</v>
       </c>
       <c r="AH8">
-        <v>132.73</v>
+        <v>131.93</v>
       </c>
       <c r="AI8">
         <v>131.91</v>
@@ -1676,7 +1676,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>24.87</v>
+        <v>30.58</v>
       </c>
     </row>
   </sheetData>
@@ -1817,7 +1817,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1874,13 +1874,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>1.74</v>
+        <v>0.62</v>
       </c>
       <c r="D7" s="5">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="E7" s="6">
-        <v>-1.12</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1891,13 +1891,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-6.02</v>
+        <v>-3.6</v>
       </c>
       <c r="D8" s="5">
-        <v>-3.6</v>
+        <v>-2.56</v>
       </c>
       <c r="E8" s="7">
-        <v>2.42</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1908,13 +1908,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-6.38</v>
+        <v>-5.7</v>
       </c>
       <c r="D9" s="5">
-        <v>-5.7</v>
-      </c>
-      <c r="E9" s="7">
-        <v>0.68</v>
+        <v>-7.2</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-1.5</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1925,13 +1925,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>-4.12</v>
+        <v>-5.17</v>
       </c>
       <c r="D10" s="5">
-        <v>-5.17</v>
-      </c>
-      <c r="E10" s="6">
-        <v>-1.05</v>
+        <v>-3.96</v>
+      </c>
+      <c r="E10" s="7">
+        <v>1.21</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1942,13 +1942,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>-3.7</v>
+        <v>-4.09</v>
       </c>
       <c r="D11" s="5">
-        <v>-4.09</v>
+        <v>-5.07</v>
       </c>
       <c r="E11" s="6">
-        <v>-0.39</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1959,13 +1959,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="5">
-        <v>-4.36</v>
+        <v>-4.94</v>
       </c>
       <c r="D12" s="5">
-        <v>-4.94</v>
-      </c>
-      <c r="E12" s="6">
-        <v>-0.58</v>
+        <v>-4.63</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.31</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1976,13 +1976,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="5">
-        <v>-2.47</v>
+        <v>-0.65</v>
       </c>
       <c r="D13" s="5">
-        <v>-0.65</v>
+        <v>5.17</v>
       </c>
       <c r="E13" s="7">
-        <v>1.82</v>
+        <v>5.82</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1993,13 +1993,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="5">
-        <v>-3.89</v>
+        <v>-2.8</v>
       </c>
       <c r="D14" s="5">
-        <v>-2.8</v>
+        <v>-1.28</v>
       </c>
       <c r="E14" s="7">
-        <v>1.09</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2010,13 +2010,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="5">
-        <v>8.93</v>
+        <v>7.62</v>
       </c>
       <c r="D15" s="5">
-        <v>7.62</v>
+        <v>3.05</v>
       </c>
       <c r="E15" s="6">
-        <v>-1.31</v>
+        <v>-4.57</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2027,13 +2027,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>4.33</v>
+        <v>5.01</v>
       </c>
       <c r="D16" s="5">
-        <v>5.01</v>
-      </c>
-      <c r="E16" s="7">
-        <v>0.68</v>
+        <v>1.06</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-3.95</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2044,13 +2044,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="5">
-        <v>-1.72</v>
+        <v>-3.17</v>
       </c>
       <c r="D17" s="5">
-        <v>-3.17</v>
-      </c>
-      <c r="E17" s="6">
-        <v>-1.45</v>
+        <v>-2.59</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.58</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2061,13 +2061,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="5">
-        <v>-2.33</v>
+        <v>-0.2</v>
       </c>
       <c r="D18" s="5">
-        <v>-0.2</v>
-      </c>
-      <c r="E18" s="7">
-        <v>2.13</v>
+        <v>-1.55</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-1.35</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2078,13 +2078,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="5">
-        <v>0.02</v>
+        <v>-1.57</v>
       </c>
       <c r="D19" s="5">
-        <v>-1.57</v>
-      </c>
-      <c r="E19" s="6">
-        <v>-1.59</v>
+        <v>-0.52</v>
+      </c>
+      <c r="E19" s="7">
+        <v>1.05</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2095,13 +2095,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="5">
-        <v>1.2</v>
+        <v>4.11</v>
       </c>
       <c r="D20" s="5">
-        <v>4.11</v>
+        <v>7.22</v>
       </c>
       <c r="E20" s="7">
-        <v>2.91</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2112,13 +2112,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="5">
-        <v>32.81</v>
+        <v>31.61</v>
       </c>
       <c r="D21" s="5">
-        <v>31.61</v>
+        <v>26.5</v>
       </c>
       <c r="E21" s="6">
-        <v>-1.2</v>
+        <v>-5.11</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2129,13 +2129,13 @@
         <v>11</v>
       </c>
       <c r="C22" s="5">
-        <v>120.69</v>
+        <v>131.57</v>
       </c>
       <c r="D22" s="5">
-        <v>131.57</v>
+        <v>133.93</v>
       </c>
       <c r="E22" s="7">
-        <v>10.88</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2146,13 +2146,13 @@
         <v>11</v>
       </c>
       <c r="C23" s="5">
-        <v>-40.65</v>
+        <v>-40.27</v>
       </c>
       <c r="D23" s="5">
-        <v>-40.27</v>
+        <v>-40.22</v>
       </c>
       <c r="E23" s="7">
-        <v>0.38</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2163,13 +2163,13 @@
         <v>11</v>
       </c>
       <c r="C24" s="5">
-        <v>-3.2</v>
+        <v>-4.34</v>
       </c>
       <c r="D24" s="5">
-        <v>-4.34</v>
-      </c>
-      <c r="E24" s="6">
-        <v>-1.14</v>
+        <v>-3.38</v>
+      </c>
+      <c r="E24" s="7">
+        <v>0.96</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2180,13 +2180,13 @@
         <v>11</v>
       </c>
       <c r="C25" s="5">
-        <v>-14.49</v>
+        <v>-13.87</v>
       </c>
       <c r="D25" s="5">
-        <v>-13.87</v>
+        <v>-13.5</v>
       </c>
       <c r="E25" s="7">
-        <v>0.62</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2197,13 +2197,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="5">
-        <v>12.77</v>
+        <v>10.85</v>
       </c>
       <c r="D26" s="5">
-        <v>10.85</v>
+        <v>10.51</v>
       </c>
       <c r="E26" s="6">
-        <v>-1.92</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2214,13 +2214,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="5">
-        <v>3.58</v>
+        <v>6.35</v>
       </c>
       <c r="D27" s="5">
-        <v>6.35</v>
-      </c>
-      <c r="E27" s="7">
-        <v>2.77</v>
+        <v>4.64</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-1.71</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2231,13 +2231,13 @@
         <v>10</v>
       </c>
       <c r="C28" s="5">
-        <v>17.11</v>
+        <v>16.57</v>
       </c>
       <c r="D28" s="5">
-        <v>16.57</v>
-      </c>
-      <c r="E28" s="6">
-        <v>-0.54</v>
+        <v>16.94</v>
+      </c>
+      <c r="E28" s="7">
+        <v>0.37</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2248,13 +2248,13 @@
         <v>10</v>
       </c>
       <c r="C29" s="5">
-        <v>-8.65</v>
+        <v>-7.91</v>
       </c>
       <c r="D29" s="5">
-        <v>-7.91</v>
-      </c>
-      <c r="E29" s="7">
-        <v>0.74</v>
+        <v>-11.36</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-3.45</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2265,13 +2265,13 @@
         <v>10</v>
       </c>
       <c r="C30" s="5">
-        <v>10.02</v>
+        <v>11.43</v>
       </c>
       <c r="D30" s="5">
-        <v>11.43</v>
-      </c>
-      <c r="E30" s="7">
-        <v>1.41</v>
+        <v>8.619999999999999</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-2.81</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2282,13 +2282,13 @@
         <v>10</v>
       </c>
       <c r="C31" s="5">
-        <v>16.46</v>
+        <v>17.14</v>
       </c>
       <c r="D31" s="5">
-        <v>17.14</v>
-      </c>
-      <c r="E31" s="7">
-        <v>0.68</v>
+        <v>14.88</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-2.26</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2299,13 +2299,13 @@
         <v>10</v>
       </c>
       <c r="C32" s="5">
-        <v>10.07</v>
+        <v>12.32</v>
       </c>
       <c r="D32" s="5">
-        <v>12.32</v>
-      </c>
-      <c r="E32" s="7">
-        <v>2.25</v>
+        <v>8.18</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-4.14</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2316,13 +2316,13 @@
         <v>10</v>
       </c>
       <c r="C33" s="5">
-        <v>19.23</v>
+        <v>19.38</v>
       </c>
       <c r="D33" s="5">
-        <v>19.38</v>
-      </c>
-      <c r="E33" s="7">
-        <v>0.15</v>
+        <v>13.63</v>
+      </c>
+      <c r="E33" s="6">
+        <v>-5.75</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2333,13 +2333,13 @@
         <v>10</v>
       </c>
       <c r="C34" s="5">
-        <v>1.69</v>
+        <v>5.79</v>
       </c>
       <c r="D34" s="5">
-        <v>5.79</v>
+        <v>6.22</v>
       </c>
       <c r="E34" s="7">
-        <v>4.1</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2350,13 +2350,13 @@
         <v>6</v>
       </c>
       <c r="C35" s="5">
-        <v>-3.89</v>
+        <v>-4.62</v>
       </c>
       <c r="D35" s="5">
-        <v>-4.62</v>
+        <v>-4.8</v>
       </c>
       <c r="E35" s="6">
-        <v>-0.73</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2367,13 +2367,13 @@
         <v>6</v>
       </c>
       <c r="C36" s="5">
-        <v>-23.3</v>
+        <v>-22.2</v>
       </c>
       <c r="D36" s="5">
-        <v>-22.2</v>
+        <v>-21.75</v>
       </c>
       <c r="E36" s="7">
-        <v>1.1</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2384,13 +2384,13 @@
         <v>6</v>
       </c>
       <c r="C37" s="5">
-        <v>-43.8</v>
+        <v>-43.82</v>
       </c>
       <c r="D37" s="5">
-        <v>-43.82</v>
+        <v>-44.16</v>
       </c>
       <c r="E37" s="6">
-        <v>-0.02</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2401,13 +2401,13 @@
         <v>6</v>
       </c>
       <c r="C38" s="5">
-        <v>-10.96</v>
+        <v>-11.47</v>
       </c>
       <c r="D38" s="5">
-        <v>-11.47</v>
-      </c>
-      <c r="E38" s="6">
-        <v>-0.51</v>
+        <v>-10.85</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0.62</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2418,13 +2418,13 @@
         <v>6</v>
       </c>
       <c r="C39" s="5">
-        <v>-18.75</v>
+        <v>-18.52</v>
       </c>
       <c r="D39" s="5">
-        <v>-18.52</v>
-      </c>
-      <c r="E39" s="7">
-        <v>0.23</v>
+        <v>-19.15</v>
+      </c>
+      <c r="E39" s="6">
+        <v>-0.63</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2435,13 +2435,13 @@
         <v>6</v>
       </c>
       <c r="C40" s="5">
-        <v>-9.039999999999999</v>
+        <v>-10.31</v>
       </c>
       <c r="D40" s="5">
-        <v>-10.31</v>
-      </c>
-      <c r="E40" s="6">
-        <v>-1.27</v>
+        <v>-9.949999999999999</v>
+      </c>
+      <c r="E40" s="7">
+        <v>0.36</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2452,13 +2452,13 @@
         <v>6</v>
       </c>
       <c r="C41" s="5">
-        <v>-7.58</v>
+        <v>-6.22</v>
       </c>
       <c r="D41" s="5">
-        <v>-6.22</v>
+        <v>-4.28</v>
       </c>
       <c r="E41" s="7">
-        <v>1.36</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2469,13 +2469,13 @@
         <v>2</v>
       </c>
       <c r="C42" s="5">
-        <v>11880</v>
+        <v>11790</v>
       </c>
       <c r="D42" s="5">
-        <v>11790</v>
+        <v>11768</v>
       </c>
       <c r="E42" s="6">
-        <v>-90</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2486,13 +2486,13 @@
         <v>2</v>
       </c>
       <c r="C43" s="5">
-        <v>514.1</v>
+        <v>521.45</v>
       </c>
       <c r="D43" s="5">
-        <v>521.45</v>
+        <v>524.45</v>
       </c>
       <c r="E43" s="7">
-        <v>7.35</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2503,13 +2503,13 @@
         <v>2</v>
       </c>
       <c r="C44" s="5">
-        <v>339.95</v>
+        <v>339.8</v>
       </c>
       <c r="D44" s="5">
-        <v>339.8</v>
+        <v>337.75</v>
       </c>
       <c r="E44" s="6">
-        <v>-0.15</v>
+        <v>-2.05</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2520,13 +2520,13 @@
         <v>2</v>
       </c>
       <c r="C45" s="5">
-        <v>1938.1</v>
+        <v>1927</v>
       </c>
       <c r="D45" s="5">
-        <v>1927</v>
-      </c>
-      <c r="E45" s="6">
-        <v>-11.1</v>
+        <v>1940.5</v>
+      </c>
+      <c r="E45" s="7">
+        <v>13.5</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2537,13 +2537,13 @@
         <v>2</v>
       </c>
       <c r="C46" s="5">
-        <v>11046</v>
+        <v>11078</v>
       </c>
       <c r="D46" s="5">
-        <v>11078</v>
-      </c>
-      <c r="E46" s="7">
-        <v>32</v>
+        <v>10992</v>
+      </c>
+      <c r="E46" s="6">
+        <v>-86</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2554,13 +2554,13 @@
         <v>2</v>
       </c>
       <c r="C47" s="5">
-        <v>1054.1</v>
+        <v>1039.3</v>
       </c>
       <c r="D47" s="5">
-        <v>1039.3</v>
-      </c>
-      <c r="E47" s="6">
-        <v>-14.8</v>
+        <v>1043.5</v>
+      </c>
+      <c r="E47" s="7">
+        <v>4.2</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2571,285 +2571,251 @@
         <v>2</v>
       </c>
       <c r="C48" s="5">
-        <v>137.66</v>
+        <v>139.69</v>
       </c>
       <c r="D48" s="5">
-        <v>139.69</v>
+        <v>142.57</v>
       </c>
       <c r="E48" s="7">
-        <v>2.03</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C49" s="5">
-        <v>57</v>
+        <v>52.56</v>
       </c>
       <c r="D49" s="5">
-        <v>43</v>
+        <v>51.84</v>
       </c>
       <c r="E49" s="6">
-        <v>-14</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C50" s="5">
-        <v>43</v>
+        <v>54.98</v>
       </c>
       <c r="D50" s="5">
-        <v>57</v>
+        <v>55.87</v>
       </c>
       <c r="E50" s="7">
-        <v>14</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C51" s="5">
-        <v>55.47</v>
+        <v>49.84</v>
       </c>
       <c r="D51" s="5">
-        <v>52.56</v>
+        <v>48.33</v>
       </c>
       <c r="E51" s="6">
-        <v>-2.91</v>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C52" s="5">
-        <v>52.84</v>
+        <v>38.53</v>
       </c>
       <c r="D52" s="5">
-        <v>54.98</v>
+        <v>42.13</v>
       </c>
       <c r="E52" s="7">
-        <v>2.14</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C53" s="5">
-        <v>49.95</v>
+        <v>46.45</v>
       </c>
       <c r="D53" s="5">
-        <v>49.84</v>
+        <v>44.2</v>
       </c>
       <c r="E53" s="6">
-        <v>-0.11</v>
+        <v>-2.25</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C54" s="5">
-        <v>40.45</v>
+        <v>39.02</v>
       </c>
       <c r="D54" s="5">
-        <v>38.53</v>
-      </c>
-      <c r="E54" s="6">
-        <v>-1.92</v>
+        <v>40.95</v>
+      </c>
+      <c r="E54" s="7">
+        <v>1.93</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C55" s="5">
-        <v>45.49</v>
+        <v>57.46</v>
       </c>
       <c r="D55" s="5">
-        <v>46.45</v>
+        <v>63.33</v>
       </c>
       <c r="E55" s="7">
-        <v>0.96</v>
+        <v>5.87</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C56" s="5">
-        <v>43.69</v>
+        <v>-48.53</v>
       </c>
       <c r="D56" s="5">
-        <v>39.02</v>
-      </c>
-      <c r="E56" s="6">
-        <v>-4.67</v>
+        <v>-46.03</v>
+      </c>
+      <c r="E56" s="7">
+        <v>2.5</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C57" s="5">
-        <v>52.48</v>
+        <v>-11.49</v>
       </c>
       <c r="D57" s="5">
-        <v>57.46</v>
+        <v>23.29</v>
       </c>
       <c r="E57" s="7">
-        <v>4.98</v>
+        <v>34.78</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C58" s="5">
-        <v>-16.95</v>
+        <v>-53.33</v>
       </c>
       <c r="D58" s="5">
-        <v>-48.53</v>
-      </c>
-      <c r="E58" s="6">
-        <v>-31.58</v>
+        <v>-22.99</v>
+      </c>
+      <c r="E58" s="7">
+        <v>30.34</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C59" s="5">
-        <v>-35.75</v>
+        <v>-6.38</v>
       </c>
       <c r="D59" s="5">
-        <v>-11.49</v>
+        <v>2.17</v>
       </c>
       <c r="E59" s="7">
-        <v>24.26</v>
+        <v>8.550000000000001</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C60" s="5">
-        <v>-54.02</v>
+        <v>-59.36</v>
       </c>
       <c r="D60" s="5">
-        <v>-53.33</v>
-      </c>
-      <c r="E60" s="7">
-        <v>0.6899999999999999</v>
+        <v>-59.65</v>
+      </c>
+      <c r="E60" s="6">
+        <v>-0.29</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C61" s="5">
-        <v>5.45</v>
+        <v>101.22</v>
       </c>
       <c r="D61" s="5">
-        <v>-6.38</v>
+        <v>-17.38</v>
       </c>
       <c r="E61" s="6">
-        <v>-11.83</v>
+        <v>-118.6</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C62" s="5">
-        <v>-37.91</v>
+        <v>17.18</v>
       </c>
       <c r="D62" s="5">
-        <v>-59.36</v>
-      </c>
-      <c r="E62" s="6">
-        <v>-21.45</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="5">
-        <v>-24.36</v>
-      </c>
-      <c r="D63" s="5">
-        <v>101.22</v>
-      </c>
-      <c r="E63" s="7">
-        <v>125.58</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="5">
-        <v>-51.26</v>
-      </c>
-      <c r="D64" s="5">
-        <v>17.18</v>
-      </c>
-      <c r="E64" s="7">
-        <v>68.44</v>
+        <v>115.85</v>
+      </c>
+      <c r="E62" s="7">
+        <v>98.67</v>
       </c>
     </row>
   </sheetData>
@@ -2914,16 +2880,16 @@
         <v>7</v>
       </c>
       <c r="D2" s="10">
-        <v>48.4</v>
+        <v>49.5</v>
       </c>
       <c r="E2" s="10">
         <v>90</v>
       </c>
       <c r="F2" s="10">
-        <v>-3.4</v>
+        <v>-2.5</v>
       </c>
       <c r="G2" s="10">
-        <v>10.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H2" s="10">
         <v>57</v>
@@ -3054,25 +3020,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="13">
-        <v>0.29</v>
+        <v>0.2901</v>
       </c>
       <c r="B2" s="13">
-        <v>0.2269</v>
+        <v>0.2255</v>
       </c>
       <c r="C2" s="13">
-        <v>0.1755</v>
+        <v>0.1714</v>
       </c>
       <c r="D2" s="13">
-        <v>0.0735</v>
+        <v>0.0741</v>
       </c>
       <c r="E2" s="13">
-        <v>0.0288</v>
+        <v>0.028</v>
       </c>
       <c r="F2" s="13">
-        <v>0.0031</v>
+        <v>0.008</v>
       </c>
       <c r="G2" s="13">
-        <v>-0.2268</v>
+        <v>-0.228</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="73">
   <si>
     <t>Symbol</t>
   </si>
@@ -172,7 +172,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>51.8 → 48.9</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>51.8</t>
+  </si>
+  <si>
+    <t>48.9</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -374,14 +401,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -755,8 +783,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -896,10 +924,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>11768</v>
+        <v>11678</v>
       </c>
       <c r="D2">
-        <v>-0.19</v>
+        <v>-0.76</v>
       </c>
       <c r="E2">
         <v>12361</v>
@@ -908,46 +936,46 @@
         <v>8506.780000000001</v>
       </c>
       <c r="G2">
-        <v>-4.8</v>
+        <v>-5.53</v>
       </c>
       <c r="H2">
-        <v>38.34</v>
+        <v>37.28</v>
       </c>
       <c r="I2">
-        <v>-1.28</v>
+        <v>-2.02</v>
       </c>
       <c r="J2">
-        <v>0.58</v>
+        <v>0.15</v>
       </c>
       <c r="K2">
-        <v>16.94</v>
+        <v>17.45</v>
       </c>
       <c r="L2">
-        <v>26.5</v>
+        <v>26.21</v>
       </c>
       <c r="M2">
-        <v>29.01</v>
+        <v>28.79</v>
       </c>
       <c r="N2">
         <v>85</v>
       </c>
       <c r="O2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P2">
-        <v>11831.4</v>
+        <v>11783.2</v>
       </c>
       <c r="Q2">
-        <v>11846.2</v>
+        <v>11845.1</v>
       </c>
       <c r="R2">
-        <v>11309.08</v>
+        <v>11346.93</v>
       </c>
       <c r="S2">
-        <v>9979.469999999999</v>
+        <v>9993.25</v>
       </c>
       <c r="T2">
-        <v>17.92</v>
+        <v>16.86</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -962,34 +990,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>51.84</v>
+        <v>48.9</v>
       </c>
       <c r="Z2">
-        <v>138.96</v>
+        <v>113.69</v>
       </c>
       <c r="AA2">
-        <v>199.34</v>
+        <v>182.21</v>
       </c>
       <c r="AB2">
-        <v>-60.38</v>
+        <v>-68.52</v>
       </c>
       <c r="AC2">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="AE2">
-        <v>213.77</v>
+        <v>215.57</v>
       </c>
       <c r="AF2">
-        <v>-46.03</v>
+        <v>-2.16</v>
       </c>
       <c r="AG2">
-        <v>12218.29</v>
+        <v>12219.14</v>
       </c>
       <c r="AH2">
-        <v>11474.11</v>
+        <v>11471.06</v>
       </c>
       <c r="AI2">
         <v>11623.52</v>
@@ -998,7 +1026,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>28.82</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1009,10 +1037,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>524.45</v>
+        <v>520.5</v>
       </c>
       <c r="D3">
-        <v>0.58</v>
+        <v>-0.75</v>
       </c>
       <c r="E3">
         <v>670.25</v>
@@ -1021,25 +1049,25 @@
         <v>222.01</v>
       </c>
       <c r="G3">
-        <v>-21.75</v>
+        <v>-22.34</v>
       </c>
       <c r="H3">
-        <v>136.23</v>
+        <v>134.45</v>
       </c>
       <c r="I3">
-        <v>3.05</v>
+        <v>0.57</v>
       </c>
       <c r="J3">
-        <v>-2.56</v>
+        <v>-1.36</v>
       </c>
       <c r="K3">
-        <v>-11.36</v>
+        <v>-12.14</v>
       </c>
       <c r="L3">
-        <v>133.93</v>
+        <v>134.44</v>
       </c>
       <c r="M3">
-        <v>17.14</v>
+        <v>16.95</v>
       </c>
       <c r="N3">
         <v>99</v>
@@ -1048,19 +1076,19 @@
         <v>93</v>
       </c>
       <c r="P3">
-        <v>520.71</v>
+        <v>521.3</v>
       </c>
       <c r="Q3">
-        <v>489.25</v>
+        <v>490.24</v>
       </c>
       <c r="R3">
-        <v>533.2</v>
+        <v>531.28</v>
       </c>
       <c r="S3">
-        <v>435.37</v>
+        <v>436.66</v>
       </c>
       <c r="T3">
-        <v>20.46</v>
+        <v>19.2</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1075,34 +1103,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>55.87</v>
+        <v>54.35</v>
       </c>
       <c r="Z3">
-        <v>-2.02</v>
+        <v>-0.65</v>
       </c>
       <c r="AA3">
-        <v>-10.59</v>
+        <v>-8.6</v>
       </c>
       <c r="AB3">
-        <v>8.57</v>
+        <v>7.95</v>
       </c>
       <c r="AC3">
-        <v>91.43000000000001</v>
+        <v>93.27</v>
       </c>
       <c r="AD3">
-        <v>93.06</v>
+        <v>92.47</v>
       </c>
       <c r="AE3">
-        <v>20.88</v>
+        <v>20.62</v>
       </c>
       <c r="AF3">
-        <v>23.29</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="AG3">
-        <v>536.49</v>
+        <v>539.3</v>
       </c>
       <c r="AH3">
-        <v>442</v>
+        <v>441.18</v>
       </c>
       <c r="AI3">
         <v>460.99</v>
@@ -1111,7 +1139,7 @@
         <v>47</v>
       </c>
       <c r="AK3">
-        <v>36.66</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1122,10 +1150,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>337.75</v>
+        <v>335.3</v>
       </c>
       <c r="D4">
-        <v>-0.6</v>
+        <v>-0.73</v>
       </c>
       <c r="E4">
         <v>604.85</v>
@@ -1134,46 +1162,46 @@
         <v>303.75</v>
       </c>
       <c r="G4">
-        <v>-44.16</v>
+        <v>-44.56</v>
       </c>
       <c r="H4">
-        <v>11.19</v>
+        <v>10.39</v>
       </c>
       <c r="I4">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="J4">
-        <v>-7.2</v>
+        <v>-5.97</v>
       </c>
       <c r="K4">
-        <v>8.619999999999999</v>
+        <v>4.63</v>
       </c>
       <c r="L4">
-        <v>-40.22</v>
+        <v>-40.99</v>
       </c>
       <c r="M4">
-        <v>-22.8</v>
+        <v>-22.9</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
       <c r="O4">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="P4">
-        <v>338.15</v>
+        <v>338.98</v>
       </c>
       <c r="Q4">
-        <v>341.31</v>
+        <v>339.96</v>
       </c>
       <c r="R4">
-        <v>339.77</v>
+        <v>339.9</v>
       </c>
       <c r="S4">
-        <v>379.27</v>
+        <v>378.51</v>
       </c>
       <c r="T4">
-        <v>-10.95</v>
+        <v>-11.41</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1188,34 +1216,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>48.33</v>
+        <v>46.52</v>
       </c>
       <c r="Z4">
-        <v>-2.25</v>
+        <v>-2.26</v>
       </c>
       <c r="AA4">
-        <v>-2.17</v>
+        <v>-2.19</v>
       </c>
       <c r="AB4">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AC4">
-        <v>79.66</v>
+        <v>76.81</v>
       </c>
       <c r="AD4">
-        <v>75.42</v>
+        <v>79.2</v>
       </c>
       <c r="AE4">
-        <v>10.56</v>
+        <v>10.57</v>
       </c>
       <c r="AF4">
-        <v>-22.99</v>
+        <v>-41.68</v>
       </c>
       <c r="AG4">
-        <v>365.12</v>
+        <v>361.7</v>
       </c>
       <c r="AH4">
-        <v>317.51</v>
+        <v>318.21</v>
       </c>
       <c r="AI4">
         <v>357.31</v>
@@ -1224,7 +1252,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>27.15</v>
+        <v>24.13</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1235,10 +1263,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1940.5</v>
+        <v>1913.5</v>
       </c>
       <c r="D5">
-        <v>0.7</v>
+        <v>-1.39</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1247,46 +1275,46 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-10.85</v>
+        <v>-12.09</v>
       </c>
       <c r="H5">
-        <v>18.92</v>
+        <v>17.26</v>
       </c>
       <c r="I5">
-        <v>-2.59</v>
+        <v>-2.87</v>
       </c>
       <c r="J5">
-        <v>-3.96</v>
+        <v>-5.51</v>
       </c>
       <c r="K5">
-        <v>14.88</v>
+        <v>9.33</v>
       </c>
       <c r="L5">
-        <v>-3.38</v>
+        <v>-5.52</v>
       </c>
       <c r="M5">
-        <v>2.8</v>
+        <v>2.51</v>
       </c>
       <c r="N5">
         <v>43</v>
       </c>
       <c r="O5">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="P5">
-        <v>1942.84</v>
+        <v>1931.54</v>
       </c>
       <c r="Q5">
-        <v>1990.15</v>
+        <v>1985.41</v>
       </c>
       <c r="R5">
-        <v>1960.58</v>
+        <v>1960.94</v>
       </c>
       <c r="S5">
-        <v>1903.01</v>
+        <v>1902.43</v>
       </c>
       <c r="T5">
-        <v>1.97</v>
+        <v>0.58</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1301,43 +1329,43 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>42.13</v>
+        <v>37.41</v>
       </c>
       <c r="Z5">
-        <v>-7.76</v>
+        <v>-11.46</v>
       </c>
       <c r="AA5">
-        <v>4.99</v>
+        <v>1.7</v>
       </c>
       <c r="AB5">
-        <v>-12.75</v>
+        <v>-13.16</v>
       </c>
       <c r="AC5">
         <v>6.29</v>
       </c>
       <c r="AD5">
-        <v>2.1</v>
+        <v>4.19</v>
       </c>
       <c r="AE5">
-        <v>34.44</v>
+        <v>35.23</v>
       </c>
       <c r="AF5">
-        <v>2.17</v>
+        <v>18.72</v>
       </c>
       <c r="AG5">
-        <v>2052.96</v>
+        <v>2056.25</v>
       </c>
       <c r="AH5">
-        <v>1927.34</v>
+        <v>1914.57</v>
       </c>
       <c r="AI5">
-        <v>2035.21</v>
+        <v>2016.18</v>
       </c>
       <c r="AJ5" t="s">
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>44.51</v>
+        <v>48.65</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1348,10 +1376,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>10992</v>
+        <v>11134</v>
       </c>
       <c r="D6">
-        <v>-0.78</v>
+        <v>1.29</v>
       </c>
       <c r="E6">
         <v>13595.75</v>
@@ -1360,46 +1388,46 @@
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-19.15</v>
+        <v>-18.11</v>
       </c>
       <c r="H6">
-        <v>25.68</v>
+        <v>27.3</v>
       </c>
       <c r="I6">
-        <v>-1.55</v>
+        <v>-0.25</v>
       </c>
       <c r="J6">
-        <v>-5.07</v>
+        <v>-3.18</v>
       </c>
       <c r="K6">
-        <v>8.18</v>
+        <v>8.24</v>
       </c>
       <c r="L6">
-        <v>-13.5</v>
+        <v>-14.35</v>
       </c>
       <c r="M6">
-        <v>22.55</v>
+        <v>22.86</v>
       </c>
       <c r="N6">
         <v>29</v>
       </c>
       <c r="O6">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="P6">
-        <v>11046.8</v>
+        <v>11041.2</v>
       </c>
       <c r="Q6">
-        <v>11270.7</v>
+        <v>11253.65</v>
       </c>
       <c r="R6">
-        <v>11058.68</v>
+        <v>11059.78</v>
       </c>
       <c r="S6">
-        <v>10690.05</v>
+        <v>10687.52</v>
       </c>
       <c r="T6">
-        <v>2.82</v>
+        <v>4.18</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1414,34 +1442,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>44.2</v>
+        <v>48.63</v>
       </c>
       <c r="Z6">
         <v>-26.91</v>
       </c>
       <c r="AA6">
-        <v>35.15</v>
+        <v>22.74</v>
       </c>
       <c r="AB6">
-        <v>-62.07</v>
+        <v>-49.65</v>
       </c>
       <c r="AC6">
-        <v>14.06</v>
+        <v>19.79</v>
       </c>
       <c r="AD6">
-        <v>11.38</v>
+        <v>15.12</v>
       </c>
       <c r="AE6">
-        <v>229.64</v>
+        <v>229.23</v>
       </c>
       <c r="AF6">
-        <v>-59.65</v>
+        <v>12.13</v>
       </c>
       <c r="AG6">
-        <v>11649.57</v>
+        <v>11624.41</v>
       </c>
       <c r="AH6">
-        <v>10891.83</v>
+        <v>10882.89</v>
       </c>
       <c r="AI6">
         <v>10787.84</v>
@@ -1450,7 +1478,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>22.47</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1461,10 +1489,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>1043.5</v>
+        <v>1034.5</v>
       </c>
       <c r="D7">
-        <v>0.4</v>
+        <v>-0.86</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1473,46 +1501,46 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-9.949999999999999</v>
+        <v>-10.73</v>
       </c>
       <c r="H7">
-        <v>30.19</v>
+        <v>29.06</v>
       </c>
       <c r="I7">
-        <v>-0.52</v>
+        <v>-2.45</v>
       </c>
       <c r="J7">
-        <v>-4.63</v>
+        <v>-5.16</v>
       </c>
       <c r="K7">
-        <v>13.63</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="L7">
-        <v>10.51</v>
+        <v>9.08</v>
       </c>
       <c r="M7">
-        <v>7.41</v>
+        <v>7.22</v>
       </c>
       <c r="N7">
         <v>71</v>
       </c>
       <c r="O7">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P7">
-        <v>1051.48</v>
+        <v>1046.28</v>
       </c>
       <c r="Q7">
-        <v>1071.32</v>
+        <v>1068.69</v>
       </c>
       <c r="R7">
-        <v>1067.29</v>
+        <v>1067.35</v>
       </c>
       <c r="S7">
-        <v>977.65</v>
+        <v>977.89</v>
       </c>
       <c r="T7">
-        <v>6.74</v>
+        <v>5.79</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1527,43 +1555,43 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>40.95</v>
+        <v>38.17</v>
       </c>
       <c r="Z7">
-        <v>-7.14</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="AA7">
-        <v>-1.89</v>
+        <v>-3.22</v>
       </c>
       <c r="AB7">
-        <v>-5.25</v>
+        <v>-5.33</v>
       </c>
       <c r="AC7">
-        <v>10.52</v>
+        <v>4.72</v>
       </c>
       <c r="AD7">
-        <v>18.13</v>
+        <v>10.58</v>
       </c>
       <c r="AE7">
-        <v>20.09</v>
+        <v>20.68</v>
       </c>
       <c r="AF7">
-        <v>-17.38</v>
+        <v>18.32</v>
       </c>
       <c r="AG7">
-        <v>1108.51</v>
+        <v>1108.54</v>
       </c>
       <c r="AH7">
-        <v>1034.12</v>
+        <v>1028.84</v>
       </c>
       <c r="AI7">
-        <v>1102.86</v>
+        <v>1087.09</v>
       </c>
       <c r="AJ7" t="s">
         <v>48</v>
       </c>
       <c r="AK7">
-        <v>34.91</v>
+        <v>38.61</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1574,10 +1602,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>142.57</v>
+        <v>139.48</v>
       </c>
       <c r="D8">
-        <v>2.06</v>
+        <v>-2.17</v>
       </c>
       <c r="E8">
         <v>148.95</v>
@@ -1586,46 +1614,46 @@
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>-4.28</v>
+        <v>-6.36</v>
       </c>
       <c r="H8">
-        <v>22.95</v>
+        <v>20.28</v>
       </c>
       <c r="I8">
-        <v>7.22</v>
+        <v>3.75</v>
       </c>
       <c r="J8">
-        <v>5.17</v>
+        <v>2.86</v>
       </c>
       <c r="K8">
-        <v>6.22</v>
+        <v>2.85</v>
       </c>
       <c r="L8">
-        <v>4.64</v>
+        <v>5.97</v>
       </c>
       <c r="M8">
-        <v>0.8</v>
+        <v>0.36</v>
       </c>
       <c r="N8">
         <v>57</v>
       </c>
       <c r="O8">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="P8">
-        <v>138.25</v>
+        <v>139.26</v>
       </c>
       <c r="Q8">
-        <v>136.29</v>
+        <v>136.56</v>
       </c>
       <c r="R8">
-        <v>138</v>
+        <v>138.13</v>
       </c>
       <c r="S8">
-        <v>133.76</v>
+        <v>133.8</v>
       </c>
       <c r="T8">
-        <v>6.58</v>
+        <v>4.24</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1640,34 +1668,34 @@
         <v>2</v>
       </c>
       <c r="Y8">
-        <v>63.33</v>
+        <v>54.62</v>
       </c>
       <c r="Z8">
-        <v>0.16</v>
+        <v>0.31</v>
       </c>
       <c r="AA8">
-        <v>-0.53</v>
+        <v>-0.37</v>
       </c>
       <c r="AB8">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="AC8">
-        <v>100</v>
+        <v>88.44</v>
       </c>
       <c r="AD8">
-        <v>93.81999999999999</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="AE8">
-        <v>3.98</v>
+        <v>4.03</v>
       </c>
       <c r="AF8">
-        <v>115.85</v>
+        <v>-10.14</v>
       </c>
       <c r="AG8">
-        <v>140.66</v>
+        <v>141.02</v>
       </c>
       <c r="AH8">
-        <v>131.93</v>
+        <v>132.1</v>
       </c>
       <c r="AI8">
         <v>131.91</v>
@@ -1676,7 +1704,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>30.58</v>
+        <v>32.61</v>
       </c>
     </row>
   </sheetData>
@@ -1837,12 +1865,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>50</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1850,972 +1913,972 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>55</v>
+      <c r="B6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>0.62</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>0.58</v>
       </c>
-      <c r="E7" s="6">
-        <v>-0.04</v>
+      <c r="D7" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-0.43</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-3.6</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>-2.56</v>
       </c>
-      <c r="E8" s="7">
+      <c r="D8" s="6">
+        <v>-1.36</v>
+      </c>
+      <c r="E8" s="8">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-7.2</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-5.97</v>
+      </c>
+      <c r="E9" s="8">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-3.96</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-5.51</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-1.55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-5.07</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-3.18</v>
+      </c>
+      <c r="E11" s="8">
+        <v>1.89</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-4.63</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-5.16</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>5.17</v>
+      </c>
+      <c r="D13" s="6">
+        <v>2.86</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-2.31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-1.28</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-2.02</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-0.74</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6">
+        <v>3.05</v>
+      </c>
+      <c r="D15" s="6">
+        <v>0.57</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-2.48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>1.06</v>
+      </c>
+      <c r="D16" s="6">
+        <v>1.25</v>
+      </c>
+      <c r="E16" s="8">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-2.59</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-2.87</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-0.28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-1.55</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-0.25</v>
+      </c>
+      <c r="E18" s="8">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-0.52</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-2.45</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-1.93</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>7.22</v>
+      </c>
+      <c r="D20" s="6">
+        <v>3.75</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-3.47</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>26.5</v>
+      </c>
+      <c r="D21" s="6">
+        <v>26.21</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="6">
+        <v>133.93</v>
+      </c>
+      <c r="D22" s="6">
+        <v>134.44</v>
+      </c>
+      <c r="E22" s="8">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-40.22</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-40.99</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-0.77</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-3.38</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-5.52</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-2.14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-13.5</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-14.35</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-0.85</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>10.51</v>
+      </c>
+      <c r="D26" s="6">
+        <v>9.08</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-1.43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>4.64</v>
+      </c>
+      <c r="D27" s="6">
+        <v>5.97</v>
+      </c>
+      <c r="E27" s="8">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="6">
+        <v>16.94</v>
+      </c>
+      <c r="D28" s="6">
+        <v>17.45</v>
+      </c>
+      <c r="E28" s="8">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-11.36</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-12.14</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-0.78</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="6">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="D30" s="6">
+        <v>4.63</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-3.99</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="6">
+        <v>14.88</v>
+      </c>
+      <c r="D31" s="6">
+        <v>9.33</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-5.55</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="6">
+        <v>8.18</v>
+      </c>
+      <c r="D32" s="6">
+        <v>8.24</v>
+      </c>
+      <c r="E32" s="8">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6">
+        <v>13.63</v>
+      </c>
+      <c r="D33" s="6">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-3.85</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>6.22</v>
+      </c>
+      <c r="D34" s="6">
+        <v>2.85</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-3.37</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-4.8</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-5.53</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-0.73</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-21.75</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-22.34</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-44.16</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-44.56</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-10.85</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-12.09</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-1.24</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-19.15</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-18.11</v>
+      </c>
+      <c r="E39" s="8">
         <v>1.04</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-9.949999999999999</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-10.73</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-0.78</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-4.28</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-6.36</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-2.08</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="6">
+        <v>11768</v>
+      </c>
+      <c r="D42" s="6">
+        <v>11678</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-90</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="6">
+        <v>524.45</v>
+      </c>
+      <c r="D43" s="6">
+        <v>520.5</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-3.95</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="5">
-        <v>-5.7</v>
-      </c>
-      <c r="D9" s="5">
-        <v>-7.2</v>
-      </c>
-      <c r="E9" s="6">
-        <v>-1.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="B44" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="6">
+        <v>337.75</v>
+      </c>
+      <c r="D44" s="6">
+        <v>335.3</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-2.45</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="5">
-        <v>-5.17</v>
-      </c>
-      <c r="D10" s="5">
-        <v>-3.96</v>
-      </c>
-      <c r="E10" s="7">
-        <v>1.21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="B45" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="6">
+        <v>1940.5</v>
+      </c>
+      <c r="D45" s="6">
+        <v>1913.5</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-27</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="5">
-        <v>-4.09</v>
-      </c>
-      <c r="D11" s="5">
-        <v>-5.07</v>
-      </c>
-      <c r="E11" s="6">
-        <v>-0.98</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="B46" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="6">
+        <v>10992</v>
+      </c>
+      <c r="D46" s="6">
+        <v>11134</v>
+      </c>
+      <c r="E46" s="8">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="5">
-        <v>-4.94</v>
-      </c>
-      <c r="D12" s="5">
-        <v>-4.63</v>
-      </c>
-      <c r="E12" s="7">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="B47" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="6">
+        <v>1043.5</v>
+      </c>
+      <c r="D47" s="6">
+        <v>1034.5</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="5">
-        <v>-0.65</v>
-      </c>
-      <c r="D13" s="5">
-        <v>5.17</v>
-      </c>
-      <c r="E13" s="7">
-        <v>5.82</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="B48" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="6">
+        <v>142.57</v>
+      </c>
+      <c r="D48" s="6">
+        <v>139.48</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-3.09</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="5">
-        <v>-2.8</v>
-      </c>
-      <c r="D14" s="5">
-        <v>-1.28</v>
-      </c>
-      <c r="E14" s="7">
-        <v>1.52</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B49" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="6">
+        <v>51.84</v>
+      </c>
+      <c r="D49" s="6">
+        <v>48.9</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-2.94</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="5">
-        <v>7.62</v>
-      </c>
-      <c r="D15" s="5">
-        <v>3.05</v>
-      </c>
-      <c r="E15" s="6">
-        <v>-4.57</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B50" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="6">
+        <v>55.87</v>
+      </c>
+      <c r="D50" s="6">
+        <v>54.35</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-1.52</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>5.01</v>
-      </c>
-      <c r="D16" s="5">
-        <v>1.06</v>
-      </c>
-      <c r="E16" s="6">
-        <v>-3.95</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B51" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="6">
+        <v>48.33</v>
+      </c>
+      <c r="D51" s="6">
+        <v>46.52</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-1.81</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-3.17</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-2.59</v>
-      </c>
-      <c r="E17" s="7">
-        <v>0.58</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B52" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="6">
+        <v>42.13</v>
+      </c>
+      <c r="D52" s="6">
+        <v>37.41</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-4.72</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>-0.2</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-1.55</v>
-      </c>
-      <c r="E18" s="6">
-        <v>-1.35</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B53" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="6">
+        <v>44.2</v>
+      </c>
+      <c r="D53" s="6">
+        <v>48.63</v>
+      </c>
+      <c r="E53" s="8">
+        <v>4.43</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-1.57</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.52</v>
-      </c>
-      <c r="E19" s="7">
-        <v>1.05</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B54" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="6">
+        <v>40.95</v>
+      </c>
+      <c r="D54" s="6">
+        <v>38.17</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-2.78</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="5">
-        <v>4.11</v>
-      </c>
-      <c r="D20" s="5">
-        <v>7.22</v>
-      </c>
-      <c r="E20" s="7">
-        <v>3.11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B55" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="6">
+        <v>63.33</v>
+      </c>
+      <c r="D55" s="6">
+        <v>54.62</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-8.710000000000001</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="5">
-        <v>31.61</v>
-      </c>
-      <c r="D21" s="5">
-        <v>26.5</v>
-      </c>
-      <c r="E21" s="6">
-        <v>-5.11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B56" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" s="6">
+        <v>-46.03</v>
+      </c>
+      <c r="D56" s="6">
+        <v>-2.16</v>
+      </c>
+      <c r="E56" s="8">
+        <v>43.87</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="5">
-        <v>131.57</v>
-      </c>
-      <c r="D22" s="5">
-        <v>133.93</v>
-      </c>
-      <c r="E22" s="7">
-        <v>2.36</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B57" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C57" s="6">
+        <v>23.29</v>
+      </c>
+      <c r="D57" s="6">
+        <v>-9.779999999999999</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-33.07</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="5">
-        <v>-40.27</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-40.22</v>
-      </c>
-      <c r="E23" s="7">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B58" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="6">
+        <v>-22.99</v>
+      </c>
+      <c r="D58" s="6">
+        <v>-41.68</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-18.69</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-4.34</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-3.38</v>
-      </c>
-      <c r="E24" s="7">
-        <v>0.96</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="B59" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="6">
+        <v>2.17</v>
+      </c>
+      <c r="D59" s="6">
+        <v>18.72</v>
+      </c>
+      <c r="E59" s="8">
+        <v>16.55</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>-13.87</v>
-      </c>
-      <c r="D25" s="5">
-        <v>-13.5</v>
-      </c>
-      <c r="E25" s="7">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="B60" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="6">
+        <v>-59.65</v>
+      </c>
+      <c r="D60" s="6">
+        <v>12.13</v>
+      </c>
+      <c r="E60" s="8">
+        <v>71.78</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>10.85</v>
-      </c>
-      <c r="D26" s="5">
-        <v>10.51</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-0.34</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="B61" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="6">
+        <v>-17.38</v>
+      </c>
+      <c r="D61" s="6">
+        <v>18.32</v>
+      </c>
+      <c r="E61" s="8">
+        <v>35.7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>6.35</v>
-      </c>
-      <c r="D27" s="5">
-        <v>4.64</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-1.71</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="5">
-        <v>16.57</v>
-      </c>
-      <c r="D28" s="5">
-        <v>16.94</v>
-      </c>
-      <c r="E28" s="7">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-7.91</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-11.36</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-3.45</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="5">
-        <v>11.43</v>
-      </c>
-      <c r="D30" s="5">
-        <v>8.619999999999999</v>
-      </c>
-      <c r="E30" s="6">
-        <v>-2.81</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="5">
-        <v>17.14</v>
-      </c>
-      <c r="D31" s="5">
-        <v>14.88</v>
-      </c>
-      <c r="E31" s="6">
-        <v>-2.26</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="5">
-        <v>12.32</v>
-      </c>
-      <c r="D32" s="5">
-        <v>8.18</v>
-      </c>
-      <c r="E32" s="6">
-        <v>-4.14</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="5">
-        <v>19.38</v>
-      </c>
-      <c r="D33" s="5">
-        <v>13.63</v>
-      </c>
-      <c r="E33" s="6">
-        <v>-5.75</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>5.79</v>
-      </c>
-      <c r="D34" s="5">
-        <v>6.22</v>
-      </c>
-      <c r="E34" s="7">
-        <v>0.43</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-4.62</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-4.8</v>
-      </c>
-      <c r="E35" s="6">
-        <v>-0.18</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-22.2</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-21.75</v>
-      </c>
-      <c r="E36" s="7">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="5">
-        <v>-43.82</v>
-      </c>
-      <c r="D37" s="5">
-        <v>-44.16</v>
-      </c>
-      <c r="E37" s="6">
-        <v>-0.34</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="5">
-        <v>-11.47</v>
-      </c>
-      <c r="D38" s="5">
-        <v>-10.85</v>
-      </c>
-      <c r="E38" s="7">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-18.52</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-19.15</v>
-      </c>
-      <c r="E39" s="6">
-        <v>-0.63</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="5">
-        <v>-10.31</v>
-      </c>
-      <c r="D40" s="5">
-        <v>-9.949999999999999</v>
-      </c>
-      <c r="E40" s="7">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="5">
-        <v>-6.22</v>
-      </c>
-      <c r="D41" s="5">
-        <v>-4.28</v>
-      </c>
-      <c r="E41" s="7">
-        <v>1.94</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="5">
-        <v>11790</v>
-      </c>
-      <c r="D42" s="5">
-        <v>11768</v>
-      </c>
-      <c r="E42" s="6">
-        <v>-22</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="5">
-        <v>521.45</v>
-      </c>
-      <c r="D43" s="5">
-        <v>524.45</v>
-      </c>
-      <c r="E43" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="5">
-        <v>339.8</v>
-      </c>
-      <c r="D44" s="5">
-        <v>337.75</v>
-      </c>
-      <c r="E44" s="6">
-        <v>-2.05</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="5">
-        <v>1927</v>
-      </c>
-      <c r="D45" s="5">
-        <v>1940.5</v>
-      </c>
-      <c r="E45" s="7">
-        <v>13.5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="5">
-        <v>11078</v>
-      </c>
-      <c r="D46" s="5">
-        <v>10992</v>
-      </c>
-      <c r="E46" s="6">
-        <v>-86</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="5">
-        <v>1039.3</v>
-      </c>
-      <c r="D47" s="5">
-        <v>1043.5</v>
-      </c>
-      <c r="E47" s="7">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="5">
-        <v>139.69</v>
-      </c>
-      <c r="D48" s="5">
-        <v>142.57</v>
-      </c>
-      <c r="E48" s="7">
-        <v>2.88</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" s="5">
-        <v>52.56</v>
-      </c>
-      <c r="D49" s="5">
-        <v>51.84</v>
-      </c>
-      <c r="E49" s="6">
-        <v>-0.72</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="5">
-        <v>54.98</v>
-      </c>
-      <c r="D50" s="5">
-        <v>55.87</v>
-      </c>
-      <c r="E50" s="7">
-        <v>0.89</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="5">
-        <v>49.84</v>
-      </c>
-      <c r="D51" s="5">
-        <v>48.33</v>
-      </c>
-      <c r="E51" s="6">
-        <v>-1.51</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="5">
-        <v>38.53</v>
-      </c>
-      <c r="D52" s="5">
-        <v>42.13</v>
-      </c>
-      <c r="E52" s="7">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="5">
-        <v>46.45</v>
-      </c>
-      <c r="D53" s="5">
-        <v>44.2</v>
-      </c>
-      <c r="E53" s="6">
-        <v>-2.25</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="5">
-        <v>39.02</v>
-      </c>
-      <c r="D54" s="5">
-        <v>40.95</v>
-      </c>
-      <c r="E54" s="7">
-        <v>1.93</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="5">
-        <v>57.46</v>
-      </c>
-      <c r="D55" s="5">
-        <v>63.33</v>
-      </c>
-      <c r="E55" s="7">
-        <v>5.87</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B56" s="3" t="s">
+      <c r="B62" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C56" s="5">
-        <v>-48.53</v>
-      </c>
-      <c r="D56" s="5">
-        <v>-46.03</v>
-      </c>
-      <c r="E56" s="7">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C57" s="5">
-        <v>-11.49</v>
-      </c>
-      <c r="D57" s="5">
-        <v>23.29</v>
-      </c>
-      <c r="E57" s="7">
-        <v>34.78</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C58" s="5">
-        <v>-53.33</v>
-      </c>
-      <c r="D58" s="5">
-        <v>-22.99</v>
-      </c>
-      <c r="E58" s="7">
-        <v>30.34</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C59" s="5">
-        <v>-6.38</v>
-      </c>
-      <c r="D59" s="5">
-        <v>2.17</v>
-      </c>
-      <c r="E59" s="7">
-        <v>8.550000000000001</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="5">
-        <v>-59.36</v>
-      </c>
-      <c r="D60" s="5">
-        <v>-59.65</v>
-      </c>
-      <c r="E60" s="6">
-        <v>-0.29</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="5">
-        <v>101.22</v>
-      </c>
-      <c r="D61" s="5">
-        <v>-17.38</v>
-      </c>
-      <c r="E61" s="6">
-        <v>-118.6</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="5">
-        <v>17.18</v>
-      </c>
-      <c r="D62" s="5">
+      <c r="C62" s="6">
         <v>115.85</v>
       </c>
+      <c r="D62" s="6">
+        <v>-10.14</v>
+      </c>
       <c r="E62" s="7">
-        <v>98.67</v>
+        <v>-125.99</v>
       </c>
     </row>
   </sheetData>
@@ -2841,60 +2904,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C1" s="8" t="s">
+      <c r="B1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="11">
+        <v>68.8</v>
+      </c>
+      <c r="C2" s="12">
+        <v>7</v>
+      </c>
+      <c r="D2" s="11">
+        <v>46.9</v>
+      </c>
+      <c r="E2" s="11">
+        <v>90</v>
+      </c>
+      <c r="F2" s="11">
+        <v>-2.6</v>
+      </c>
+      <c r="G2" s="11">
+        <v>5.7</v>
+      </c>
+      <c r="H2" s="11">
         <v>57</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="10">
-        <v>68.8</v>
-      </c>
-      <c r="C2" s="11">
-        <v>7</v>
-      </c>
-      <c r="D2" s="10">
-        <v>49.5</v>
-      </c>
-      <c r="E2" s="10">
-        <v>90</v>
-      </c>
-      <c r="F2" s="10">
-        <v>-2.5</v>
-      </c>
-      <c r="G2" s="10">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="H2" s="10">
-        <v>57</v>
-      </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>60</v>
       </c>
     </row>
@@ -2996,49 +3059,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="13">
-        <v>0.2901</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.2255</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.1714</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.0741</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.028</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0.008</v>
-      </c>
-      <c r="G2" s="13">
-        <v>-0.228</v>
+      <c r="A2" s="14">
+        <v>0.2879</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.2286</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.1695</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.0722</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.0251</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.0036</v>
+      </c>
+      <c r="G2" s="14">
+        <v>-0.229</v>
       </c>
     </row>
   </sheetData>
